--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091440</v>
+        <v>126091342</v>
       </c>
       <c r="B3" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556465</v>
+        <v>556306</v>
       </c>
       <c r="R3" t="n">
-        <v>7226995</v>
+        <v>7226876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091342</v>
+        <v>126091065</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556306</v>
+        <v>556817</v>
       </c>
       <c r="R4" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091128</v>
+        <v>126091370</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556830</v>
+        <v>556364</v>
       </c>
       <c r="R5" t="n">
-        <v>7227331</v>
+        <v>7226989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091123</v>
+        <v>126091395</v>
       </c>
       <c r="B6" t="n">
-        <v>91250</v>
+        <v>91528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557106</v>
+        <v>556308</v>
       </c>
       <c r="R6" t="n">
-        <v>7227606</v>
+        <v>7226876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091065</v>
+        <v>126091128</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556817</v>
+        <v>556830</v>
       </c>
       <c r="R7" t="n">
-        <v>7227591</v>
+        <v>7227331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091370</v>
+        <v>126091123</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556364</v>
+        <v>557106</v>
       </c>
       <c r="R8" t="n">
-        <v>7226989</v>
+        <v>7227606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091408</v>
+        <v>126091440</v>
       </c>
       <c r="B9" t="n">
-        <v>80111</v>
+        <v>80110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556467</v>
+        <v>556465</v>
       </c>
       <c r="R9" t="n">
-        <v>7226993</v>
+        <v>7226995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091395</v>
+        <v>126091408</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>80111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556308</v>
+        <v>556467</v>
       </c>
       <c r="R10" t="n">
-        <v>7226876</v>
+        <v>7226993</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091043</v>
+        <v>126091389</v>
       </c>
       <c r="B11" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556756</v>
+        <v>556589</v>
       </c>
       <c r="R11" t="n">
-        <v>7227253</v>
+        <v>7227109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091439</v>
+        <v>126091064</v>
       </c>
       <c r="B12" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556374</v>
+        <v>556833</v>
       </c>
       <c r="R12" t="n">
-        <v>7227007</v>
+        <v>7227720</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091420</v>
+        <v>126091374</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556284</v>
+        <v>556371</v>
       </c>
       <c r="R13" t="n">
-        <v>7227078</v>
+        <v>7226988</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,32 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091428</v>
+        <v>126091365</v>
       </c>
       <c r="B14" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556314</v>
+        <v>556359</v>
       </c>
       <c r="R14" t="n">
-        <v>7226891</v>
+        <v>7226943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,7 +1988,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091147</v>
+        <v>126091420</v>
       </c>
       <c r="B15" t="n">
         <v>78972</v>
@@ -2028,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556819</v>
+        <v>556284</v>
       </c>
       <c r="R15" t="n">
-        <v>7227694</v>
+        <v>7227078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,12 +2053,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2099,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091389</v>
+        <v>126091147</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556589</v>
+        <v>556819</v>
       </c>
       <c r="R16" t="n">
-        <v>7227109</v>
+        <v>7227694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,12 +2159,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091064</v>
+        <v>126091335</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556833</v>
+        <v>556339</v>
       </c>
       <c r="R17" t="n">
-        <v>7227720</v>
+        <v>7226946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091391</v>
+        <v>126091425</v>
       </c>
       <c r="B18" t="n">
-        <v>92046</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,37 +2312,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>253810</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skorpgrynna</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dichostereum boreale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556379</v>
+        <v>556591</v>
       </c>
       <c r="R18" t="n">
-        <v>7227009</v>
+        <v>7227022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2376,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ska se om det går få mikroskoperat. Förmodligen något annat, kanske någon brunaktig Phlebia t.ex. farinvaxskinn</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2388,7 +2385,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2411,10 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091335</v>
+        <v>126091043</v>
       </c>
       <c r="B19" t="n">
-        <v>91197</v>
+        <v>80104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,21 +2418,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2446,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556339</v>
+        <v>556756</v>
       </c>
       <c r="R19" t="n">
-        <v>7226946</v>
+        <v>7227253</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,12 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091374</v>
+        <v>126091439</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556371</v>
+        <v>556374</v>
       </c>
       <c r="R20" t="n">
-        <v>7226988</v>
+        <v>7227007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,27 +2609,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091425</v>
+        <v>126091428</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2648,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556591</v>
+        <v>556314</v>
       </c>
       <c r="R21" t="n">
-        <v>7227022</v>
+        <v>7226891</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,11 +2680,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2719,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091365</v>
+        <v>126091391</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,34 +2721,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>253810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skorpgrynna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dichostereum boreale</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556359</v>
+        <v>556379</v>
       </c>
       <c r="R22" t="n">
-        <v>7226943</v>
+        <v>7227009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,12 +2786,18 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ska se om det går få mikroskoperat. Förmodligen något annat, kanske någon brunaktig Phlebia t.ex. farinvaxskinn</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4042,32 +4042,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091042</v>
+        <v>126091448</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>91902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556817</v>
+        <v>556484</v>
       </c>
       <c r="R35" t="n">
-        <v>7227591</v>
+        <v>7226980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,12 +4107,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091414</v>
+        <v>126091369</v>
       </c>
       <c r="B36" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556303</v>
+        <v>556333</v>
       </c>
       <c r="R36" t="n">
-        <v>7226905</v>
+        <v>7227009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091369</v>
+        <v>126091013</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4255,21 +4255,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556333</v>
+        <v>556830</v>
       </c>
       <c r="R37" t="n">
-        <v>7227009</v>
+        <v>7227704</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4345,7 +4345,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091124</v>
+        <v>126091414</v>
       </c>
       <c r="B38" t="n">
         <v>91250</v>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556698</v>
+        <v>556303</v>
       </c>
       <c r="R38" t="n">
-        <v>7227248</v>
+        <v>7226905</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091349</v>
+        <v>126091124</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556613</v>
+        <v>556698</v>
       </c>
       <c r="R39" t="n">
-        <v>7227051</v>
+        <v>7227248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,17 +4511,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,32 +4547,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091013</v>
+        <v>126091042</v>
       </c>
       <c r="B40" t="n">
-        <v>91232</v>
+        <v>80104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4587,10 +4582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556830</v>
+        <v>556817</v>
       </c>
       <c r="R40" t="n">
-        <v>7227704</v>
+        <v>7227591</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4754,32 +4749,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091448</v>
+        <v>126091349</v>
       </c>
       <c r="B42" t="n">
-        <v>91902</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4789,10 +4784,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556484</v>
+        <v>556613</v>
       </c>
       <c r="R42" t="n">
-        <v>7226980</v>
+        <v>7227051</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4825,6 +4820,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4855,45 +4855,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091352</v>
+        <v>126091354</v>
       </c>
       <c r="B43" t="n">
-        <v>98360</v>
+        <v>91857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>5471</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Sorgvaxskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crustoderma triste</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Litsch. &amp; S.Lundell) Duhem</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556293</v>
+        <v>556340</v>
       </c>
       <c r="R43" t="n">
-        <v>7227068</v>
+        <v>7226957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4928,12 +4931,18 @@
           <t>2025-06-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Förmodligen något annat. Tog kollekt och ska se om det går få mikroskoperat. Lägger till nu så jag inte tappar bort koordinater</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4956,10 +4965,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091348</v>
+        <v>126091144</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,21 +4976,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4991,10 +5000,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556351</v>
+        <v>557048</v>
       </c>
       <c r="R44" t="n">
-        <v>7226920</v>
+        <v>7227797</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5021,17 +5030,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5062,10 +5066,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091075</v>
+        <v>126091422</v>
       </c>
       <c r="B45" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5097,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556792</v>
+        <v>556407</v>
       </c>
       <c r="R45" t="n">
-        <v>7227253</v>
+        <v>7226992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5127,12 +5131,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5163,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091403</v>
+        <v>126091145</v>
       </c>
       <c r="B46" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5174,21 +5183,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5198,10 +5207,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556357</v>
+        <v>556897</v>
       </c>
       <c r="R46" t="n">
-        <v>7227004</v>
+        <v>7227735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5228,12 +5237,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5264,32 +5278,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091044</v>
+        <v>126091129</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
+        <v>91250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5299,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556826</v>
+        <v>556685</v>
       </c>
       <c r="R47" t="n">
-        <v>7227309</v>
+        <v>7227107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5329,12 +5343,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5365,10 +5379,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091163</v>
+        <v>126091348</v>
       </c>
       <c r="B48" t="n">
-        <v>57572</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5376,16 +5390,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5400,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556711</v>
+        <v>556351</v>
       </c>
       <c r="R48" t="n">
-        <v>7227222</v>
+        <v>7226920</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5430,12 +5444,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5466,32 +5485,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091107</v>
+        <v>126091075</v>
       </c>
       <c r="B49" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5501,10 +5520,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556723</v>
+        <v>556792</v>
       </c>
       <c r="R49" t="n">
-        <v>7227276</v>
+        <v>7227253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5567,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091354</v>
+        <v>126091403</v>
       </c>
       <c r="B50" t="n">
-        <v>91857</v>
+        <v>80075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5578,37 +5597,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5471</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sorgvaxskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crustoderma triste</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S.Lundell) Duhem</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556340</v>
+        <v>556357</v>
       </c>
       <c r="R50" t="n">
-        <v>7226957</v>
+        <v>7227004</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5643,18 +5659,12 @@
           <t>2025-06-19</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Förmodligen något annat. Tog kollekt och ska se om det går få mikroskoperat. Lägger till nu så jag inte tappar bort koordinater</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5677,32 +5687,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091144</v>
+        <v>126091044</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5712,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557048</v>
+        <v>556826</v>
       </c>
       <c r="R51" t="n">
-        <v>7227797</v>
+        <v>7227309</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5778,10 +5788,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091422</v>
+        <v>126091163</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>57572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,21 +5799,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5813,10 +5823,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556407</v>
+        <v>556711</v>
       </c>
       <c r="R52" t="n">
-        <v>7226992</v>
+        <v>7227222</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5843,17 +5853,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5884,32 +5889,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091145</v>
+        <v>126091107</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5919,10 +5924,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556897</v>
+        <v>556723</v>
       </c>
       <c r="R53" t="n">
-        <v>7227735</v>
+        <v>7227276</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5955,11 +5960,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,32 +5990,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091129</v>
+        <v>126091352</v>
       </c>
       <c r="B54" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556685</v>
+        <v>556293</v>
       </c>
       <c r="R54" t="n">
-        <v>7227107</v>
+        <v>7227068</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6055,12 +6055,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6091,32 +6091,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091430</v>
+        <v>126091381</v>
       </c>
       <c r="B55" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556140</v>
+        <v>556280</v>
       </c>
       <c r="R55" t="n">
-        <v>7226895</v>
+        <v>7227059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,27 +6192,27 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091438</v>
+        <v>126091148</v>
       </c>
       <c r="B56" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556350</v>
+        <v>556787</v>
       </c>
       <c r="R56" t="n">
-        <v>7226997</v>
+        <v>7227605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6257,12 +6257,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6293,27 +6298,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091148</v>
+        <v>126091430</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6328,10 +6333,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556787</v>
+        <v>556140</v>
       </c>
       <c r="R57" t="n">
-        <v>7227605</v>
+        <v>7226895</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,17 +6363,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6399,32 +6399,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091381</v>
+        <v>126091438</v>
       </c>
       <c r="B58" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556280</v>
+        <v>556350</v>
       </c>
       <c r="R58" t="n">
-        <v>7227059</v>
+        <v>7226997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091400</v>
+        <v>126091151</v>
       </c>
       <c r="B60" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6612,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556261</v>
+        <v>556935</v>
       </c>
       <c r="R60" t="n">
-        <v>7227068</v>
+        <v>7227614</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6666,12 +6666,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6702,32 +6707,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091409</v>
+        <v>126091417</v>
       </c>
       <c r="B61" t="n">
-        <v>80111</v>
+        <v>91250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6737,10 +6742,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556480</v>
+        <v>556559</v>
       </c>
       <c r="R61" t="n">
-        <v>7226980</v>
+        <v>7226989</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,10 +6808,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091151</v>
+        <v>126091400</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6814,21 +6819,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6838,10 +6843,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556935</v>
+        <v>556261</v>
       </c>
       <c r="R62" t="n">
-        <v>7227614</v>
+        <v>7227068</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6868,17 +6873,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6909,32 +6909,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091095</v>
+        <v>126091409</v>
       </c>
       <c r="B63" t="n">
-        <v>91528</v>
+        <v>80111</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>557005</v>
+        <v>556480</v>
       </c>
       <c r="R63" t="n">
-        <v>7227490</v>
+        <v>7226980</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7010,32 +7010,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091343</v>
+        <v>126091442</v>
       </c>
       <c r="B64" t="n">
-        <v>91232</v>
+        <v>80110</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556373</v>
+        <v>556494</v>
       </c>
       <c r="R64" t="n">
-        <v>7227010</v>
+        <v>7226972</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091373</v>
+        <v>126091095</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>91528</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556350</v>
+        <v>557005</v>
       </c>
       <c r="R65" t="n">
-        <v>7226997</v>
+        <v>7227490</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7212,10 +7212,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091359</v>
+        <v>126091343</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7223,21 +7223,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556280</v>
+        <v>556373</v>
       </c>
       <c r="R66" t="n">
-        <v>7226845</v>
+        <v>7227010</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7313,7 +7313,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091361</v>
+        <v>126091373</v>
       </c>
       <c r="B67" t="n">
         <v>80076</v>
@@ -7348,10 +7348,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556321</v>
+        <v>556350</v>
       </c>
       <c r="R67" t="n">
-        <v>7226929</v>
+        <v>7226997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7414,32 +7414,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091442</v>
+        <v>126091359</v>
       </c>
       <c r="B68" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7449,10 +7449,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556494</v>
+        <v>556280</v>
       </c>
       <c r="R68" t="n">
-        <v>7226972</v>
+        <v>7226845</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091417</v>
+        <v>126091361</v>
       </c>
       <c r="B69" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,21 +7526,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556559</v>
+        <v>556321</v>
       </c>
       <c r="R69" t="n">
-        <v>7226989</v>
+        <v>7226929</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7823,32 +7823,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091337</v>
+        <v>126091384</v>
       </c>
       <c r="B72" t="n">
-        <v>91197</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556374</v>
+        <v>556376</v>
       </c>
       <c r="R72" t="n">
-        <v>7226996</v>
+        <v>7227009</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7924,32 +7924,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B73" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R73" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8338,32 +8338,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091393</v>
+        <v>126091015</v>
       </c>
       <c r="B77" t="n">
-        <v>79979</v>
+        <v>91232</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556291</v>
+        <v>556931</v>
       </c>
       <c r="R77" t="n">
-        <v>7226913</v>
+        <v>7227622</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8403,12 +8403,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8439,32 +8439,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091012</v>
+        <v>126091051</v>
       </c>
       <c r="B78" t="n">
-        <v>91197</v>
+        <v>79941</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>388</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556977</v>
+        <v>556679</v>
       </c>
       <c r="R78" t="n">
-        <v>7227576</v>
+        <v>7227232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8540,10 +8540,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091015</v>
+        <v>126091360</v>
       </c>
       <c r="B79" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8551,21 +8551,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8575,10 +8575,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556931</v>
+        <v>556326</v>
       </c>
       <c r="R79" t="n">
-        <v>7227622</v>
+        <v>7226893</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091143</v>
+        <v>126091375</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8652,21 +8652,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>557106</v>
+        <v>556423</v>
       </c>
       <c r="R80" t="n">
-        <v>7227606</v>
+        <v>7226984</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8742,10 +8742,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091051</v>
+        <v>126091067</v>
       </c>
       <c r="B81" t="n">
-        <v>79941</v>
+        <v>80076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,21 +8753,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8777,10 +8777,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556679</v>
+        <v>556690</v>
       </c>
       <c r="R81" t="n">
-        <v>7227232</v>
+        <v>7227262</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8843,32 +8843,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091174</v>
+        <v>126091355</v>
       </c>
       <c r="B82" t="n">
-        <v>91642</v>
+        <v>80076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8878,10 +8878,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556888</v>
+        <v>556346</v>
       </c>
       <c r="R82" t="n">
-        <v>7227746</v>
+        <v>7227118</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8908,12 +8908,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8944,32 +8944,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091360</v>
+        <v>126091012</v>
       </c>
       <c r="B83" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556326</v>
+        <v>556977</v>
       </c>
       <c r="R83" t="n">
-        <v>7226893</v>
+        <v>7227576</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9009,12 +9009,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9045,10 +9045,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091375</v>
+        <v>126091143</v>
       </c>
       <c r="B84" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9056,21 +9056,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9080,10 +9080,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556423</v>
+        <v>557106</v>
       </c>
       <c r="R84" t="n">
-        <v>7226984</v>
+        <v>7227606</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9146,32 +9146,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091402</v>
+        <v>126091174</v>
       </c>
       <c r="B85" t="n">
-        <v>80075</v>
+        <v>91642</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556280</v>
+        <v>556888</v>
       </c>
       <c r="R85" t="n">
-        <v>7227059</v>
+        <v>7227746</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9211,12 +9211,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9247,32 +9247,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091067</v>
+        <v>126091393</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>79979</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9282,10 +9282,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556690</v>
+        <v>556291</v>
       </c>
       <c r="R86" t="n">
-        <v>7227262</v>
+        <v>7226913</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9312,12 +9312,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9348,10 +9348,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091355</v>
+        <v>126091402</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9359,21 +9359,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556346</v>
+        <v>556280</v>
       </c>
       <c r="R87" t="n">
-        <v>7227118</v>
+        <v>7227059</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9449,32 +9449,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091166</v>
+        <v>126091027</v>
       </c>
       <c r="B88" t="n">
-        <v>80110</v>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556690</v>
+        <v>557059</v>
       </c>
       <c r="R88" t="n">
-        <v>7227262</v>
+        <v>7227538</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9520,6 +9520,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9752,10 +9757,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091153</v>
+        <v>126091344</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9763,21 +9768,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9787,10 +9792,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556996</v>
+        <v>556452</v>
       </c>
       <c r="R91" t="n">
-        <v>7227559</v>
+        <v>7226989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9817,12 +9822,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9853,10 +9858,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091344</v>
+        <v>126091372</v>
       </c>
       <c r="B92" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,21 +9869,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9888,10 +9893,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556452</v>
+        <v>556359</v>
       </c>
       <c r="R92" t="n">
-        <v>7226989</v>
+        <v>7226988</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9954,27 +9959,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091165</v>
+        <v>126091153</v>
       </c>
       <c r="B93" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9989,10 +9994,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556874</v>
+        <v>556996</v>
       </c>
       <c r="R93" t="n">
-        <v>7227697</v>
+        <v>7227559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10055,10 +10060,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126091027</v>
+        <v>126091141</v>
       </c>
       <c r="B94" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10066,21 +10071,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10090,10 +10095,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557059</v>
+        <v>556931</v>
       </c>
       <c r="R94" t="n">
-        <v>7227538</v>
+        <v>7227622</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10130,7 +10135,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10161,27 +10166,27 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091141</v>
+        <v>126091166</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10196,10 +10201,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556931</v>
+        <v>556690</v>
       </c>
       <c r="R95" t="n">
-        <v>7227622</v>
+        <v>7227262</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10232,11 +10237,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10267,32 +10267,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091372</v>
+        <v>126091165</v>
       </c>
       <c r="B96" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556359</v>
+        <v>556874</v>
       </c>
       <c r="R96" t="n">
-        <v>7226988</v>
+        <v>7227697</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10332,12 +10332,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10469,32 +10469,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091441</v>
+        <v>126091357</v>
       </c>
       <c r="B98" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10504,10 +10504,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556480</v>
+        <v>556061</v>
       </c>
       <c r="R98" t="n">
-        <v>7226980</v>
+        <v>7226781</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10570,32 +10570,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091167</v>
+        <v>126091339</v>
       </c>
       <c r="B99" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556728</v>
+        <v>556393</v>
       </c>
       <c r="R99" t="n">
-        <v>7227275</v>
+        <v>7226994</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10635,12 +10635,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10772,10 +10772,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091357</v>
+        <v>126091125</v>
       </c>
       <c r="B101" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10783,21 +10783,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556061</v>
+        <v>556893</v>
       </c>
       <c r="R101" t="n">
-        <v>7226781</v>
+        <v>7227703</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10837,12 +10837,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10873,32 +10873,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091339</v>
+        <v>126091441</v>
       </c>
       <c r="B102" t="n">
-        <v>91232</v>
+        <v>80110</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>556393</v>
+        <v>556480</v>
       </c>
       <c r="R102" t="n">
-        <v>7226994</v>
+        <v>7226980</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10974,32 +10974,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091125</v>
+        <v>126091167</v>
       </c>
       <c r="B103" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>556893</v>
+        <v>556728</v>
       </c>
       <c r="R103" t="n">
-        <v>7227703</v>
+        <v>7227275</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091392</v>
+        <v>126091019</v>
       </c>
       <c r="B105" t="n">
-        <v>56227</v>
+        <v>91232</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11187,21 +11187,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>556271</v>
+        <v>557005</v>
       </c>
       <c r="R105" t="n">
-        <v>7226832</v>
+        <v>7227490</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11241,12 +11241,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11277,10 +11277,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091019</v>
+        <v>126091358</v>
       </c>
       <c r="B106" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>557005</v>
+        <v>556070</v>
       </c>
       <c r="R106" t="n">
-        <v>7227490</v>
+        <v>7226750</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11342,12 +11342,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11484,10 +11484,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091358</v>
+        <v>126091392</v>
       </c>
       <c r="B108" t="n">
-        <v>80076</v>
+        <v>56227</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11495,21 +11495,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>206004</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11519,10 +11519,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556070</v>
+        <v>556271</v>
       </c>
       <c r="R108" t="n">
-        <v>7226750</v>
+        <v>7226832</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11585,10 +11585,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091072</v>
+        <v>126091010</v>
       </c>
       <c r="B109" t="n">
-        <v>80076</v>
+        <v>79004</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11596,21 +11596,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556913</v>
+        <v>556904</v>
       </c>
       <c r="R109" t="n">
-        <v>7227621</v>
+        <v>7227703</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091380</v>
+        <v>126091072</v>
       </c>
       <c r="B110" t="n">
         <v>80076</v>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556261</v>
+        <v>556913</v>
       </c>
       <c r="R110" t="n">
-        <v>7227068</v>
+        <v>7227621</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11751,12 +11751,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11787,32 +11787,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091407</v>
+        <v>126091380</v>
       </c>
       <c r="B111" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11822,10 +11822,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556365</v>
+        <v>556261</v>
       </c>
       <c r="R111" t="n">
-        <v>7227004</v>
+        <v>7227068</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12090,32 +12090,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091010</v>
+        <v>126091407</v>
       </c>
       <c r="B114" t="n">
-        <v>79004</v>
+        <v>80111</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12125,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556904</v>
+        <v>556365</v>
       </c>
       <c r="R114" t="n">
-        <v>7227703</v>
+        <v>7227004</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12155,12 +12155,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12191,32 +12191,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091416</v>
+        <v>126091115</v>
       </c>
       <c r="B115" t="n">
-        <v>91250</v>
+        <v>57755</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556600</v>
+        <v>556797</v>
       </c>
       <c r="R115" t="n">
-        <v>7227123</v>
+        <v>7227252</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12256,12 +12256,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12292,10 +12292,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091421</v>
+        <v>126091416</v>
       </c>
       <c r="B116" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12303,21 +12303,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12327,10 +12327,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556111</v>
+        <v>556600</v>
       </c>
       <c r="R116" t="n">
-        <v>7226873</v>
+        <v>7227123</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12363,11 +12363,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12398,32 +12393,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091115</v>
+        <v>126091421</v>
       </c>
       <c r="B117" t="n">
-        <v>57755</v>
+        <v>78972</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12433,10 +12428,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556797</v>
+        <v>556111</v>
       </c>
       <c r="R117" t="n">
-        <v>7227252</v>
+        <v>7226873</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12463,12 +12458,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13004,32 +13004,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091052</v>
+        <v>126091387</v>
       </c>
       <c r="B123" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13039,10 +13039,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>557007</v>
+        <v>556497</v>
       </c>
       <c r="R123" t="n">
-        <v>7227805</v>
+        <v>7226978</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13105,32 +13105,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091445</v>
+        <v>126091379</v>
       </c>
       <c r="B124" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556584</v>
+        <v>556305</v>
       </c>
       <c r="R124" t="n">
-        <v>7227109</v>
+        <v>7227093</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13206,32 +13206,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091444</v>
+        <v>126091394</v>
       </c>
       <c r="B125" t="n">
-        <v>80110</v>
+        <v>91528</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R125" t="n">
-        <v>7227068</v>
+        <v>7226757</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13307,32 +13307,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091410</v>
+        <v>126091424</v>
       </c>
       <c r="B126" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13342,10 +13342,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556584</v>
+        <v>556549</v>
       </c>
       <c r="R126" t="n">
-        <v>7227068</v>
+        <v>7226986</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13378,6 +13378,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13408,27 +13413,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091424</v>
+        <v>126091445</v>
       </c>
       <c r="B127" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13443,10 +13448,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R127" t="n">
-        <v>7226986</v>
+        <v>7227109</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13479,11 +13484,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13514,32 +13514,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091387</v>
+        <v>126091444</v>
       </c>
       <c r="B128" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R128" t="n">
-        <v>7226978</v>
+        <v>7227068</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13615,32 +13615,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091379</v>
+        <v>126091410</v>
       </c>
       <c r="B129" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13650,10 +13650,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R129" t="n">
-        <v>7227093</v>
+        <v>7227068</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13716,32 +13716,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126091394</v>
+        <v>126091052</v>
       </c>
       <c r="B130" t="n">
-        <v>91528</v>
+        <v>98360</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>556098</v>
+        <v>557007</v>
       </c>
       <c r="R130" t="n">
-        <v>7226757</v>
+        <v>7227805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13781,12 +13781,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14428,32 +14428,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091433</v>
+        <v>126091385</v>
       </c>
       <c r="B137" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556280</v>
+        <v>556410</v>
       </c>
       <c r="R137" t="n">
-        <v>7226845</v>
+        <v>7226996</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14529,32 +14529,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091385</v>
+        <v>126091433</v>
       </c>
       <c r="B138" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14564,10 +14564,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556410</v>
+        <v>556280</v>
       </c>
       <c r="R138" t="n">
-        <v>7226996</v>
+        <v>7226845</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14630,32 +14630,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091431</v>
+        <v>126091415</v>
       </c>
       <c r="B139" t="n">
-        <v>80110</v>
+        <v>91250</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14665,10 +14665,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556179</v>
+        <v>556315</v>
       </c>
       <c r="R139" t="n">
-        <v>7226822</v>
+        <v>7226927</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14731,7 +14731,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091415</v>
+        <v>126091127</v>
       </c>
       <c r="B140" t="n">
         <v>91250</v>
@@ -14766,10 +14766,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556315</v>
+        <v>556728</v>
       </c>
       <c r="R140" t="n">
-        <v>7226927</v>
+        <v>7227249</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14796,12 +14796,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14832,27 +14832,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091429</v>
+        <v>126091140</v>
       </c>
       <c r="B141" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556272</v>
+        <v>557026</v>
       </c>
       <c r="R141" t="n">
-        <v>7227058</v>
+        <v>7227519</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14897,12 +14897,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14933,32 +14938,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091029</v>
+        <v>126091431</v>
       </c>
       <c r="B142" t="n">
-        <v>57651</v>
+        <v>80110</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14968,10 +14973,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556819</v>
+        <v>556179</v>
       </c>
       <c r="R142" t="n">
-        <v>7227694</v>
+        <v>7226822</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14998,17 +15003,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15039,32 +15039,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091413</v>
+        <v>126091429</v>
       </c>
       <c r="B143" t="n">
-        <v>56834</v>
+        <v>80110</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15074,10 +15074,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556662</v>
+        <v>556272</v>
       </c>
       <c r="R143" t="n">
-        <v>7227178</v>
+        <v>7227058</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15110,11 +15110,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15145,32 +15140,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091127</v>
+        <v>126091443</v>
       </c>
       <c r="B144" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15180,10 +15175,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556728</v>
+        <v>556529</v>
       </c>
       <c r="R144" t="n">
-        <v>7227249</v>
+        <v>7226958</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15210,12 +15205,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15246,7 +15241,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091443</v>
+        <v>126091437</v>
       </c>
       <c r="B145" t="n">
         <v>80110</v>
@@ -15281,10 +15276,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556529</v>
+        <v>556361</v>
       </c>
       <c r="R145" t="n">
-        <v>7226958</v>
+        <v>7227004</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15347,7 +15342,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091437</v>
+        <v>126091432</v>
       </c>
       <c r="B146" t="n">
         <v>80110</v>
@@ -15382,10 +15377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556361</v>
+        <v>556230</v>
       </c>
       <c r="R146" t="n">
-        <v>7227004</v>
+        <v>7226809</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15448,10 +15443,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091432</v>
+        <v>126091105</v>
       </c>
       <c r="B147" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15459,21 +15454,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15483,10 +15478,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556230</v>
+        <v>556807</v>
       </c>
       <c r="R147" t="n">
-        <v>7226809</v>
+        <v>7227608</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15513,12 +15508,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15549,32 +15544,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091105</v>
+        <v>126091413</v>
       </c>
       <c r="B148" t="n">
-        <v>80111</v>
+        <v>56834</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15584,10 +15579,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556807</v>
+        <v>556662</v>
       </c>
       <c r="R148" t="n">
-        <v>7227608</v>
+        <v>7227178</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15614,12 +15609,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15650,10 +15650,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091140</v>
+        <v>126091029</v>
       </c>
       <c r="B149" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15661,21 +15661,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15685,10 +15685,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>557026</v>
+        <v>556819</v>
       </c>
       <c r="R149" t="n">
-        <v>7227519</v>
+        <v>7227694</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15958,10 +15958,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091152</v>
+        <v>126091388</v>
       </c>
       <c r="B152" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15969,21 +15969,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15993,10 +15993,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556975</v>
+        <v>556529</v>
       </c>
       <c r="R152" t="n">
-        <v>7227579</v>
+        <v>7226958</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16023,17 +16023,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16064,32 +16059,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091397</v>
+        <v>126091378</v>
       </c>
       <c r="B153" t="n">
-        <v>80103</v>
+        <v>80076</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16099,10 +16094,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556378</v>
+        <v>556353</v>
       </c>
       <c r="R153" t="n">
-        <v>7226996</v>
+        <v>7227115</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16165,10 +16160,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091388</v>
+        <v>126091152</v>
       </c>
       <c r="B154" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16176,21 +16171,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16200,10 +16195,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556529</v>
+        <v>556975</v>
       </c>
       <c r="R154" t="n">
-        <v>7226958</v>
+        <v>7227579</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16230,12 +16225,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16266,10 +16266,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091378</v>
+        <v>126091149</v>
       </c>
       <c r="B155" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16277,21 +16277,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16301,10 +16301,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556353</v>
+        <v>556807</v>
       </c>
       <c r="R155" t="n">
-        <v>7227115</v>
+        <v>7227608</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16331,12 +16331,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16367,32 +16372,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091350</v>
       </c>
       <c r="B156" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16402,10 +16407,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556589</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7227059</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16438,6 +16443,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16468,7 +16478,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091350</v>
+        <v>126091040</v>
       </c>
       <c r="B157" t="n">
         <v>57651</v>
@@ -16503,10 +16513,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556589</v>
+        <v>556781</v>
       </c>
       <c r="R157" t="n">
-        <v>7227059</v>
+        <v>7227272</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16533,17 +16543,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16574,32 +16584,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091040</v>
+        <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16609,10 +16619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556781</v>
+        <v>556996</v>
       </c>
       <c r="R158" t="n">
-        <v>7227272</v>
+        <v>7227559</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16645,11 +16655,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16680,10 +16685,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126091169</v>
+        <v>126091397</v>
       </c>
       <c r="B159" t="n">
-        <v>80110</v>
+        <v>80103</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16691,21 +16696,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16715,10 +16720,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>556756</v>
+        <v>556378</v>
       </c>
       <c r="R159" t="n">
-        <v>7227253</v>
+        <v>7226996</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16745,12 +16750,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16781,32 +16786,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126091149</v>
+        <v>126091404</v>
       </c>
       <c r="B160" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16816,10 +16821,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>556807</v>
+        <v>556272</v>
       </c>
       <c r="R160" t="n">
-        <v>7227608</v>
+        <v>7227058</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16846,17 +16851,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16887,10 +16887,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126091053</v>
+        <v>126091169</v>
       </c>
       <c r="B161" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16898,21 +16898,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16922,10 +16922,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>556996</v>
+        <v>556756</v>
       </c>
       <c r="R161" t="n">
-        <v>7227559</v>
+        <v>7227253</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY161"/>
+  <dimension ref="A1:AY158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091391</v>
+        <v>126091041</v>
       </c>
       <c r="B22" t="n">
-        <v>92046</v>
+        <v>57811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,37 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>253810</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skorpgrynna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dichostereum boreale</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pouzar) Ginns &amp; M.N.L.Lefebvre</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556379</v>
+        <v>557020</v>
       </c>
       <c r="R22" t="n">
-        <v>7227009</v>
+        <v>7227532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,17 +2775,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ska se om det går få mikroskoperat. Förmodligen något annat, kanske någon brunaktig Phlebia t.ex. farinvaxskinn</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2797,7 +2789,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B23" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2855,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R23" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,10 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091146</v>
+        <v>126091368</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556904</v>
+        <v>556346</v>
       </c>
       <c r="R24" t="n">
-        <v>7227703</v>
+        <v>7226961</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2986,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3022,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091435</v>
+        <v>126091164</v>
       </c>
       <c r="B25" t="n">
-        <v>80110</v>
+        <v>88641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3057,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556359</v>
+        <v>556775</v>
       </c>
       <c r="R25" t="n">
-        <v>7226941</v>
+        <v>7227253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3087,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3123,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091106</v>
+        <v>126091340</v>
       </c>
       <c r="B26" t="n">
-        <v>80111</v>
+        <v>91232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556709</v>
+        <v>556312</v>
       </c>
       <c r="R26" t="n">
-        <v>7227248</v>
+        <v>7227107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,12 +3179,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3224,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091368</v>
+        <v>126091073</v>
       </c>
       <c r="B27" t="n">
         <v>80076</v>
@@ -3259,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556346</v>
+        <v>556756</v>
       </c>
       <c r="R27" t="n">
-        <v>7226961</v>
+        <v>7227253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3325,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091164</v>
+        <v>126091435</v>
       </c>
       <c r="B28" t="n">
-        <v>88641</v>
+        <v>80110</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556775</v>
+        <v>556359</v>
       </c>
       <c r="R28" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3390,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091340</v>
+        <v>126091106</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>80111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3461,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556312</v>
+        <v>556709</v>
       </c>
       <c r="R29" t="n">
-        <v>7227107</v>
+        <v>7227248</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3527,7 +3518,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091073</v>
+        <v>126091382</v>
       </c>
       <c r="B30" t="n">
         <v>80076</v>
@@ -3562,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556756</v>
+        <v>556140</v>
       </c>
       <c r="R30" t="n">
-        <v>7227253</v>
+        <v>7226895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3592,12 +3583,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3840,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091382</v>
+        <v>126091349</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3851,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3875,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556140</v>
+        <v>556613</v>
       </c>
       <c r="R33" t="n">
-        <v>7226895</v>
+        <v>7227051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,6 +3902,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4749,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091349</v>
+        <v>126091075</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4760,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4784,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556613</v>
+        <v>556792</v>
       </c>
       <c r="R42" t="n">
-        <v>7227051</v>
+        <v>7227253</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4814,17 +4810,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4855,10 +4846,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091354</v>
+        <v>126091144</v>
       </c>
       <c r="B43" t="n">
-        <v>91857</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4866,37 +4857,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5471</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sorgvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crustoderma triste</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Litsch. &amp; S.Lundell) Duhem</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tallbacksmyrorna, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556340</v>
+        <v>557048</v>
       </c>
       <c r="R43" t="n">
-        <v>7226957</v>
+        <v>7227797</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4923,17 +4911,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Förmodligen något annat. Tog kollekt och ska se om det går få mikroskoperat. Lägger till nu så jag inte tappar bort koordinater</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4942,7 +4925,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4965,7 +4947,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -5000,10 +4982,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R44" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,12 +5012,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5066,7 +5053,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091422</v>
+        <v>126091145</v>
       </c>
       <c r="B45" t="n">
         <v>78972</v>
@@ -5101,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556407</v>
+        <v>556897</v>
       </c>
       <c r="R45" t="n">
-        <v>7226992</v>
+        <v>7227735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5131,12 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5172,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091145</v>
+        <v>126091129</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5183,21 +5170,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5207,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556897</v>
+        <v>556685</v>
       </c>
       <c r="R46" t="n">
-        <v>7227735</v>
+        <v>7227107</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5237,17 +5224,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091129</v>
+        <v>126091403</v>
       </c>
       <c r="B47" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,21 +5271,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5313,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556685</v>
+        <v>556357</v>
       </c>
       <c r="R47" t="n">
-        <v>7227107</v>
+        <v>7227004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,12 +5325,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5379,32 +5361,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091348</v>
+        <v>126091044</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5414,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556351</v>
+        <v>556826</v>
       </c>
       <c r="R48" t="n">
-        <v>7226920</v>
+        <v>7227309</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5444,17 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,32 +5462,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091075</v>
+        <v>126091107</v>
       </c>
       <c r="B49" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5520,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556792</v>
+        <v>556723</v>
       </c>
       <c r="R49" t="n">
-        <v>7227253</v>
+        <v>7227276</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,10 +5563,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091403</v>
+        <v>126091348</v>
       </c>
       <c r="B50" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5597,21 +5574,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5621,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556357</v>
+        <v>556351</v>
       </c>
       <c r="R50" t="n">
-        <v>7227004</v>
+        <v>7226920</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5657,6 +5634,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5687,10 +5669,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091044</v>
+        <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>80104</v>
+        <v>98360</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5698,21 +5680,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5722,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556826</v>
+        <v>556293</v>
       </c>
       <c r="R51" t="n">
-        <v>7227309</v>
+        <v>7227068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5752,12 +5734,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5788,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091163</v>
+        <v>126091381</v>
       </c>
       <c r="B52" t="n">
-        <v>57572</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5799,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100001</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5823,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556711</v>
+        <v>556280</v>
       </c>
       <c r="R52" t="n">
-        <v>7227222</v>
+        <v>7227059</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5853,12 +5835,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5889,32 +5871,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091107</v>
+        <v>126091148</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5924,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556723</v>
+        <v>556787</v>
       </c>
       <c r="R53" t="n">
-        <v>7227276</v>
+        <v>7227605</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5960,6 +5942,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5990,10 +5977,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091352</v>
+        <v>126091430</v>
       </c>
       <c r="B54" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6001,21 +5988,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6025,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556293</v>
+        <v>556140</v>
       </c>
       <c r="R54" t="n">
-        <v>7227068</v>
+        <v>7226895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6091,32 +6078,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091381</v>
+        <v>126091438</v>
       </c>
       <c r="B55" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6126,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556280</v>
+        <v>556350</v>
       </c>
       <c r="R55" t="n">
-        <v>7227059</v>
+        <v>7226997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6192,10 +6179,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091148</v>
+        <v>126091401</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6203,21 +6190,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6227,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556787</v>
+        <v>556271</v>
       </c>
       <c r="R56" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6257,17 +6244,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6298,32 +6280,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091430</v>
+        <v>126091095</v>
       </c>
       <c r="B57" t="n">
-        <v>80110</v>
+        <v>91528</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6333,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556140</v>
+        <v>557005</v>
       </c>
       <c r="R57" t="n">
-        <v>7226895</v>
+        <v>7227490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6363,12 +6345,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6399,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091438</v>
+        <v>126091343</v>
       </c>
       <c r="B58" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6434,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556350</v>
+        <v>556373</v>
       </c>
       <c r="R58" t="n">
-        <v>7226997</v>
+        <v>7227010</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6500,10 +6482,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091401</v>
+        <v>126091373</v>
       </c>
       <c r="B59" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6511,21 +6493,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6535,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556271</v>
+        <v>556350</v>
       </c>
       <c r="R59" t="n">
-        <v>7227059</v>
+        <v>7226997</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6601,10 +6583,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091151</v>
+        <v>126091359</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6612,21 +6594,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6636,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556935</v>
+        <v>556280</v>
       </c>
       <c r="R60" t="n">
-        <v>7227614</v>
+        <v>7226845</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6666,17 +6648,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6707,10 +6684,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091417</v>
+        <v>126091361</v>
       </c>
       <c r="B61" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6718,21 +6695,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6742,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556559</v>
+        <v>556321</v>
       </c>
       <c r="R61" t="n">
-        <v>7226989</v>
+        <v>7226929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6808,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091400</v>
+        <v>126091386</v>
       </c>
       <c r="B62" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6819,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6843,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556261</v>
+        <v>556480</v>
       </c>
       <c r="R62" t="n">
-        <v>7227068</v>
+        <v>7226980</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6909,32 +6886,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091409</v>
+        <v>126091066</v>
       </c>
       <c r="B63" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556480</v>
+        <v>556946</v>
       </c>
       <c r="R63" t="n">
-        <v>7226980</v>
+        <v>7227602</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6974,12 +6951,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7010,27 +6992,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091442</v>
+        <v>126091151</v>
       </c>
       <c r="B64" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7045,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556494</v>
+        <v>556935</v>
       </c>
       <c r="R64" t="n">
-        <v>7226972</v>
+        <v>7227614</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7075,12 +7057,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7111,10 +7098,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091095</v>
+        <v>126091417</v>
       </c>
       <c r="B65" t="n">
-        <v>91528</v>
+        <v>91250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,21 +7109,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7133,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>557005</v>
+        <v>556559</v>
       </c>
       <c r="R65" t="n">
-        <v>7227490</v>
+        <v>7226989</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7176,12 +7163,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7212,10 +7199,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091343</v>
+        <v>126091400</v>
       </c>
       <c r="B66" t="n">
-        <v>91232</v>
+        <v>80075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7223,21 +7210,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7247,10 +7234,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556373</v>
+        <v>556261</v>
       </c>
       <c r="R66" t="n">
-        <v>7227010</v>
+        <v>7227068</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7313,32 +7300,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091373</v>
+        <v>126091409</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7348,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556350</v>
+        <v>556480</v>
       </c>
       <c r="R67" t="n">
-        <v>7226997</v>
+        <v>7226980</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7414,32 +7401,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091359</v>
+        <v>126091442</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7449,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556280</v>
+        <v>556494</v>
       </c>
       <c r="R68" t="n">
-        <v>7226845</v>
+        <v>7226972</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,7 +7502,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091361</v>
+        <v>126091384</v>
       </c>
       <c r="B69" t="n">
         <v>80076</v>
@@ -7550,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556321</v>
+        <v>556376</v>
       </c>
       <c r="R69" t="n">
-        <v>7226929</v>
+        <v>7227009</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7616,32 +7603,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091386</v>
+        <v>126091337</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7651,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556480</v>
+        <v>556374</v>
       </c>
       <c r="R70" t="n">
-        <v>7226980</v>
+        <v>7226996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7717,32 +7704,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091066</v>
+        <v>126091090</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>79979</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556946</v>
+        <v>556690</v>
       </c>
       <c r="R71" t="n">
-        <v>7227602</v>
+        <v>7227262</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7788,11 +7775,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7823,10 +7805,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091384</v>
+        <v>126091345</v>
       </c>
       <c r="B72" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7834,21 +7816,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7858,10 +7840,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556376</v>
+        <v>556499</v>
       </c>
       <c r="R72" t="n">
-        <v>7227009</v>
+        <v>7227184</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7894,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7924,32 +7911,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091337</v>
+        <v>126091346</v>
       </c>
       <c r="B73" t="n">
-        <v>91197</v>
+        <v>57651</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7959,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556374</v>
+        <v>556194</v>
       </c>
       <c r="R73" t="n">
-        <v>7226996</v>
+        <v>7226815</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,6 +7982,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8025,32 +8017,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091090</v>
+        <v>126091015</v>
       </c>
       <c r="B74" t="n">
-        <v>79979</v>
+        <v>91232</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8060,10 +8052,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556690</v>
+        <v>556931</v>
       </c>
       <c r="R74" t="n">
-        <v>7227262</v>
+        <v>7227622</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8126,10 +8118,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091345</v>
+        <v>126091051</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>79941</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8137,21 +8129,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +8153,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556499</v>
+        <v>556679</v>
       </c>
       <c r="R75" t="n">
-        <v>7227184</v>
+        <v>7227232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8191,17 +8183,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8232,10 +8219,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091346</v>
+        <v>126091360</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8243,21 +8230,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8267,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556194</v>
+        <v>556326</v>
       </c>
       <c r="R76" t="n">
-        <v>7226815</v>
+        <v>7226893</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8303,11 +8290,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8338,10 +8320,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091015</v>
+        <v>126091375</v>
       </c>
       <c r="B77" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8349,21 +8331,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8373,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556931</v>
+        <v>556423</v>
       </c>
       <c r="R77" t="n">
-        <v>7227622</v>
+        <v>7226984</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8403,12 +8385,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8439,10 +8421,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091051</v>
+        <v>126091067</v>
       </c>
       <c r="B78" t="n">
-        <v>79941</v>
+        <v>80076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8450,21 +8432,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8474,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556679</v>
+        <v>556690</v>
       </c>
       <c r="R78" t="n">
-        <v>7227232</v>
+        <v>7227262</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8540,7 +8522,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091360</v>
+        <v>126091355</v>
       </c>
       <c r="B79" t="n">
         <v>80076</v>
@@ -8575,10 +8557,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556326</v>
+        <v>556346</v>
       </c>
       <c r="R79" t="n">
-        <v>7226893</v>
+        <v>7227118</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8641,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091375</v>
+        <v>126091012</v>
       </c>
       <c r="B80" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8676,10 +8658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556423</v>
+        <v>556977</v>
       </c>
       <c r="R80" t="n">
-        <v>7226984</v>
+        <v>7227576</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8706,12 +8688,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8742,10 +8724,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091067</v>
+        <v>126091143</v>
       </c>
       <c r="B81" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8753,21 +8735,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8777,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556690</v>
+        <v>557106</v>
       </c>
       <c r="R81" t="n">
-        <v>7227262</v>
+        <v>7227606</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8843,32 +8825,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091355</v>
+        <v>126091174</v>
       </c>
       <c r="B82" t="n">
-        <v>80076</v>
+        <v>91642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8878,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556346</v>
+        <v>556888</v>
       </c>
       <c r="R82" t="n">
-        <v>7227118</v>
+        <v>7227746</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8908,12 +8890,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8944,10 +8926,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091012</v>
+        <v>126091393</v>
       </c>
       <c r="B83" t="n">
-        <v>91197</v>
+        <v>79979</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8955,21 +8937,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8979,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556977</v>
+        <v>556291</v>
       </c>
       <c r="R83" t="n">
-        <v>7227576</v>
+        <v>7226913</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9009,12 +8991,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9045,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091143</v>
+        <v>126091402</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9056,21 +9038,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9080,10 +9062,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>557106</v>
+        <v>556280</v>
       </c>
       <c r="R84" t="n">
-        <v>7227606</v>
+        <v>7227059</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9110,12 +9092,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9146,32 +9128,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091174</v>
+        <v>126091027</v>
       </c>
       <c r="B85" t="n">
-        <v>91642</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9181,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556888</v>
+        <v>557059</v>
       </c>
       <c r="R85" t="n">
-        <v>7227746</v>
+        <v>7227538</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9217,6 +9199,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9247,32 +9234,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091393</v>
+        <v>126091383</v>
       </c>
       <c r="B86" t="n">
-        <v>79979</v>
+        <v>80076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9282,10 +9269,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556291</v>
+        <v>556230</v>
       </c>
       <c r="R86" t="n">
-        <v>7226913</v>
+        <v>7226809</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9348,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091402</v>
+        <v>126091377</v>
       </c>
       <c r="B87" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9359,21 +9346,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9383,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556280</v>
+        <v>556584</v>
       </c>
       <c r="R87" t="n">
-        <v>7227059</v>
+        <v>7227068</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9449,10 +9436,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091027</v>
+        <v>126091344</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9460,21 +9447,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9484,10 +9471,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>557059</v>
+        <v>556452</v>
       </c>
       <c r="R88" t="n">
-        <v>7227538</v>
+        <v>7226989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9514,17 +9501,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9555,7 +9537,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091383</v>
+        <v>126091372</v>
       </c>
       <c r="B89" t="n">
         <v>80076</v>
@@ -9590,10 +9572,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556230</v>
+        <v>556359</v>
       </c>
       <c r="R89" t="n">
-        <v>7226809</v>
+        <v>7226988</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9656,10 +9638,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091377</v>
+        <v>126091153</v>
       </c>
       <c r="B90" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9667,21 +9649,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9691,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556584</v>
+        <v>556996</v>
       </c>
       <c r="R90" t="n">
-        <v>7227068</v>
+        <v>7227559</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9721,12 +9703,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9757,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091344</v>
+        <v>126091141</v>
       </c>
       <c r="B91" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9768,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9792,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556452</v>
+        <v>556931</v>
       </c>
       <c r="R91" t="n">
-        <v>7226989</v>
+        <v>7227622</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9822,12 +9804,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9858,32 +9845,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091372</v>
+        <v>126091166</v>
       </c>
       <c r="B92" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9893,10 +9880,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556359</v>
+        <v>556690</v>
       </c>
       <c r="R92" t="n">
-        <v>7226988</v>
+        <v>7227262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9923,12 +9910,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9959,27 +9946,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091153</v>
+        <v>126091165</v>
       </c>
       <c r="B93" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9994,10 +9981,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556996</v>
+        <v>556874</v>
       </c>
       <c r="R93" t="n">
-        <v>7227559</v>
+        <v>7227697</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10060,32 +10047,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126091141</v>
+        <v>126091351</v>
       </c>
       <c r="B94" t="n">
-        <v>78972</v>
+        <v>80104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10095,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556931</v>
+        <v>556346</v>
       </c>
       <c r="R94" t="n">
-        <v>7227622</v>
+        <v>7227118</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10125,17 +10112,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10166,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091166</v>
+        <v>126091357</v>
       </c>
       <c r="B95" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10201,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556690</v>
+        <v>556061</v>
       </c>
       <c r="R95" t="n">
-        <v>7227262</v>
+        <v>7226781</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10231,12 +10213,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10267,32 +10249,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091165</v>
+        <v>126091339</v>
       </c>
       <c r="B96" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10302,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556874</v>
+        <v>556393</v>
       </c>
       <c r="R96" t="n">
-        <v>7227697</v>
+        <v>7226994</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10332,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10368,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091351</v>
+        <v>126091418</v>
       </c>
       <c r="B97" t="n">
-        <v>80104</v>
+        <v>91250</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10403,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556346</v>
+        <v>556550</v>
       </c>
       <c r="R97" t="n">
-        <v>7227118</v>
+        <v>7227005</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10469,10 +10451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091357</v>
+        <v>126091125</v>
       </c>
       <c r="B98" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10480,21 +10462,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10504,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556061</v>
+        <v>556893</v>
       </c>
       <c r="R98" t="n">
-        <v>7226781</v>
+        <v>7227703</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10534,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10570,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091339</v>
+        <v>126091441</v>
       </c>
       <c r="B99" t="n">
-        <v>91232</v>
+        <v>80110</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10605,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556393</v>
+        <v>556480</v>
       </c>
       <c r="R99" t="n">
-        <v>7226994</v>
+        <v>7226980</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10671,32 +10653,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091418</v>
+        <v>126091167</v>
       </c>
       <c r="B100" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10706,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556550</v>
+        <v>556728</v>
       </c>
       <c r="R100" t="n">
-        <v>7227005</v>
+        <v>7227275</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10736,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10772,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091125</v>
+        <v>126091405</v>
       </c>
       <c r="B101" t="n">
-        <v>91250</v>
+        <v>80111</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10807,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556893</v>
+        <v>556230</v>
       </c>
       <c r="R101" t="n">
-        <v>7227703</v>
+        <v>7226809</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10837,12 +10819,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10873,32 +10855,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091441</v>
+        <v>126091019</v>
       </c>
       <c r="B102" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10908,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>556480</v>
+        <v>557005</v>
       </c>
       <c r="R102" t="n">
-        <v>7226980</v>
+        <v>7227490</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10938,12 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10974,32 +10956,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091167</v>
+        <v>126091358</v>
       </c>
       <c r="B103" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11009,10 +10991,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>556728</v>
+        <v>556070</v>
       </c>
       <c r="R103" t="n">
-        <v>7227275</v>
+        <v>7226750</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11039,12 +11021,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11075,32 +11057,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091405</v>
+        <v>126091028</v>
       </c>
       <c r="B104" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11110,10 +11092,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>556230</v>
+        <v>557117</v>
       </c>
       <c r="R104" t="n">
-        <v>7226809</v>
+        <v>7227635</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11140,12 +11122,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11176,10 +11163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091019</v>
+        <v>126091392</v>
       </c>
       <c r="B105" t="n">
-        <v>91232</v>
+        <v>56227</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11187,21 +11174,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11211,10 +11198,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557005</v>
+        <v>556271</v>
       </c>
       <c r="R105" t="n">
-        <v>7227490</v>
+        <v>7226832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11241,12 +11228,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11277,10 +11264,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091358</v>
+        <v>126091010</v>
       </c>
       <c r="B106" t="n">
-        <v>80076</v>
+        <v>79004</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11288,21 +11275,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11312,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556070</v>
+        <v>556904</v>
       </c>
       <c r="R106" t="n">
-        <v>7226750</v>
+        <v>7227703</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11342,12 +11329,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11378,10 +11365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091028</v>
+        <v>126091416</v>
       </c>
       <c r="B107" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11389,21 +11376,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11413,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>557117</v>
+        <v>556600</v>
       </c>
       <c r="R107" t="n">
-        <v>7227635</v>
+        <v>7227123</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11443,17 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11484,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091392</v>
+        <v>126091421</v>
       </c>
       <c r="B108" t="n">
-        <v>56227</v>
+        <v>78972</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11495,21 +11477,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11519,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556271</v>
+        <v>556111</v>
       </c>
       <c r="R108" t="n">
-        <v>7226832</v>
+        <v>7226873</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11555,6 +11537,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11585,32 +11572,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091010</v>
+        <v>126091407</v>
       </c>
       <c r="B109" t="n">
-        <v>79004</v>
+        <v>80111</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11620,10 +11607,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556904</v>
+        <v>556365</v>
       </c>
       <c r="R109" t="n">
-        <v>7227703</v>
+        <v>7227004</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11650,12 +11637,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12090,10 +12077,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091407</v>
+        <v>126091115</v>
       </c>
       <c r="B114" t="n">
-        <v>80111</v>
+        <v>57755</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12101,21 +12088,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556365</v>
+        <v>556797</v>
       </c>
       <c r="R114" t="n">
-        <v>7227004</v>
+        <v>7227252</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12155,12 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12191,32 +12178,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091115</v>
+        <v>126091084</v>
       </c>
       <c r="B115" t="n">
-        <v>57755</v>
+        <v>80076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12226,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556797</v>
+        <v>556737</v>
       </c>
       <c r="R115" t="n">
-        <v>7227252</v>
+        <v>7227192</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12256,12 +12243,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12292,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091416</v>
+        <v>126091068</v>
       </c>
       <c r="B116" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12303,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12327,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556600</v>
+        <v>556707</v>
       </c>
       <c r="R116" t="n">
-        <v>7227123</v>
+        <v>7227243</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12357,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12393,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091421</v>
+        <v>126091017</v>
       </c>
       <c r="B117" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12404,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12428,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556111</v>
+        <v>556929</v>
       </c>
       <c r="R117" t="n">
-        <v>7226873</v>
+        <v>7227610</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12458,17 +12445,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12499,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091102</v>
+        <v>126091121</v>
       </c>
       <c r="B118" t="n">
-        <v>80075</v>
+        <v>91228</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12510,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12534,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556740</v>
+        <v>556907</v>
       </c>
       <c r="R118" t="n">
-        <v>7227186</v>
+        <v>7227720</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12564,12 +12546,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12600,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B119" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12611,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12635,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R119" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12701,7 +12683,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091068</v>
+        <v>126091387</v>
       </c>
       <c r="B120" t="n">
         <v>80076</v>
@@ -12736,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556707</v>
+        <v>556497</v>
       </c>
       <c r="R120" t="n">
-        <v>7227243</v>
+        <v>7226978</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12766,12 +12748,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12802,10 +12784,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091017</v>
+        <v>126091379</v>
       </c>
       <c r="B121" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12813,21 +12795,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12837,10 +12819,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556929</v>
+        <v>556305</v>
       </c>
       <c r="R121" t="n">
-        <v>7227610</v>
+        <v>7227093</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12867,12 +12849,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12903,10 +12885,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091121</v>
+        <v>126091394</v>
       </c>
       <c r="B122" t="n">
-        <v>91228</v>
+        <v>91528</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12914,21 +12896,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12938,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556907</v>
+        <v>556098</v>
       </c>
       <c r="R122" t="n">
-        <v>7227720</v>
+        <v>7226757</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12968,12 +12950,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13004,10 +12986,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091387</v>
+        <v>126091424</v>
       </c>
       <c r="B123" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13015,21 +12997,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13039,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556497</v>
+        <v>556549</v>
       </c>
       <c r="R123" t="n">
-        <v>7226978</v>
+        <v>7226986</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13075,6 +13057,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13105,32 +13092,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091379</v>
+        <v>126091445</v>
       </c>
       <c r="B124" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13140,10 +13127,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R124" t="n">
-        <v>7227093</v>
+        <v>7227109</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13206,32 +13193,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091394</v>
+        <v>126091444</v>
       </c>
       <c r="B125" t="n">
-        <v>91528</v>
+        <v>80110</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13241,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556098</v>
+        <v>556584</v>
       </c>
       <c r="R125" t="n">
-        <v>7226757</v>
+        <v>7227068</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13307,32 +13294,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091424</v>
+        <v>126091410</v>
       </c>
       <c r="B126" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13342,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R126" t="n">
-        <v>7226986</v>
+        <v>7227068</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13378,11 +13365,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13413,10 +13395,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091445</v>
+        <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13424,21 +13406,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13448,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556584</v>
+        <v>557007</v>
       </c>
       <c r="R127" t="n">
-        <v>7227109</v>
+        <v>7227805</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13478,12 +13460,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13514,32 +13496,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091444</v>
+        <v>126091366</v>
       </c>
       <c r="B128" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13549,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556584</v>
+        <v>556348</v>
       </c>
       <c r="R128" t="n">
-        <v>7227068</v>
+        <v>7226965</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13615,32 +13597,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091410</v>
+        <v>126091363</v>
       </c>
       <c r="B129" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13650,10 +13632,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556584</v>
+        <v>556361</v>
       </c>
       <c r="R129" t="n">
-        <v>7227068</v>
+        <v>7226943</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13686,6 +13668,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13716,32 +13703,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126091052</v>
+        <v>126091085</v>
       </c>
       <c r="B130" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13751,10 +13738,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>557007</v>
+        <v>556709</v>
       </c>
       <c r="R130" t="n">
-        <v>7227805</v>
+        <v>7227134</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13781,12 +13768,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13817,10 +13804,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126091366</v>
+        <v>126091338</v>
       </c>
       <c r="B131" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13828,21 +13815,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13852,10 +13839,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>556348</v>
+        <v>556326</v>
       </c>
       <c r="R131" t="n">
-        <v>7226965</v>
+        <v>7227114</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13918,7 +13905,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091363</v>
+        <v>126091071</v>
       </c>
       <c r="B132" t="n">
         <v>80076</v>
@@ -13953,10 +13940,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556361</v>
+        <v>556807</v>
       </c>
       <c r="R132" t="n">
-        <v>7226943</v>
+        <v>7227608</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13983,17 +13970,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14024,7 +14006,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091085</v>
+        <v>126091367</v>
       </c>
       <c r="B133" t="n">
         <v>80076</v>
@@ -14059,10 +14041,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556709</v>
+        <v>556347</v>
       </c>
       <c r="R133" t="n">
-        <v>7227134</v>
+        <v>7226967</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14089,12 +14071,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14125,10 +14107,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091338</v>
+        <v>126091385</v>
       </c>
       <c r="B134" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14136,21 +14118,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14160,10 +14142,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556326</v>
+        <v>556410</v>
       </c>
       <c r="R134" t="n">
-        <v>7227114</v>
+        <v>7226996</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14226,32 +14208,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091071</v>
+        <v>126091433</v>
       </c>
       <c r="B135" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14261,10 +14243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556807</v>
+        <v>556280</v>
       </c>
       <c r="R135" t="n">
-        <v>7227608</v>
+        <v>7226845</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14291,12 +14273,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14327,10 +14309,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091367</v>
+        <v>126091415</v>
       </c>
       <c r="B136" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14338,21 +14320,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14362,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556347</v>
+        <v>556315</v>
       </c>
       <c r="R136" t="n">
-        <v>7226967</v>
+        <v>7226927</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14428,10 +14410,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091385</v>
+        <v>126091127</v>
       </c>
       <c r="B137" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14439,21 +14421,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14463,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556410</v>
+        <v>556728</v>
       </c>
       <c r="R137" t="n">
-        <v>7226996</v>
+        <v>7227249</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14493,12 +14475,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14529,27 +14511,27 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091433</v>
+        <v>126091140</v>
       </c>
       <c r="B138" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14564,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556280</v>
+        <v>557026</v>
       </c>
       <c r="R138" t="n">
-        <v>7226845</v>
+        <v>7227519</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14594,12 +14576,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14630,32 +14617,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091415</v>
+        <v>126091431</v>
       </c>
       <c r="B139" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14665,10 +14652,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556315</v>
+        <v>556179</v>
       </c>
       <c r="R139" t="n">
-        <v>7226927</v>
+        <v>7226822</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14731,32 +14718,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091127</v>
+        <v>126091429</v>
       </c>
       <c r="B140" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14766,10 +14753,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556728</v>
+        <v>556272</v>
       </c>
       <c r="R140" t="n">
-        <v>7227249</v>
+        <v>7227058</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14796,12 +14783,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14832,27 +14819,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091140</v>
+        <v>126091443</v>
       </c>
       <c r="B141" t="n">
-        <v>78972</v>
+        <v>80110</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14867,10 +14854,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557026</v>
+        <v>556529</v>
       </c>
       <c r="R141" t="n">
-        <v>7227519</v>
+        <v>7226958</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14897,17 +14884,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14938,7 +14920,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091431</v>
+        <v>126091437</v>
       </c>
       <c r="B142" t="n">
         <v>80110</v>
@@ -14973,10 +14955,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556179</v>
+        <v>556361</v>
       </c>
       <c r="R142" t="n">
-        <v>7226822</v>
+        <v>7227004</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15039,7 +15021,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091429</v>
+        <v>126091432</v>
       </c>
       <c r="B143" t="n">
         <v>80110</v>
@@ -15074,10 +15056,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556272</v>
+        <v>556230</v>
       </c>
       <c r="R143" t="n">
-        <v>7227058</v>
+        <v>7226809</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15140,10 +15122,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091443</v>
+        <v>126091105</v>
       </c>
       <c r="B144" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15151,21 +15133,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15175,10 +15157,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556529</v>
+        <v>556807</v>
       </c>
       <c r="R144" t="n">
-        <v>7226958</v>
+        <v>7227608</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15205,12 +15187,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15241,32 +15223,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091437</v>
+        <v>126091413</v>
       </c>
       <c r="B145" t="n">
-        <v>80110</v>
+        <v>56834</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15276,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556361</v>
+        <v>556662</v>
       </c>
       <c r="R145" t="n">
-        <v>7227004</v>
+        <v>7227178</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15312,6 +15294,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15342,32 +15329,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091432</v>
+        <v>126091029</v>
       </c>
       <c r="B146" t="n">
-        <v>80110</v>
+        <v>57651</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15377,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556230</v>
+        <v>556819</v>
       </c>
       <c r="R146" t="n">
-        <v>7226809</v>
+        <v>7227694</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15407,12 +15394,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15443,32 +15435,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091105</v>
+        <v>126091371</v>
       </c>
       <c r="B147" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15478,10 +15470,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556807</v>
+        <v>556365</v>
       </c>
       <c r="R147" t="n">
-        <v>7227608</v>
+        <v>7227004</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15508,12 +15500,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15544,10 +15536,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091413</v>
+        <v>126091063</v>
       </c>
       <c r="B148" t="n">
-        <v>56834</v>
+        <v>80076</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15555,21 +15547,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15579,10 +15571,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556662</v>
+        <v>556836</v>
       </c>
       <c r="R148" t="n">
-        <v>7227178</v>
+        <v>7227732</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15609,17 +15601,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15650,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091029</v>
+        <v>126091388</v>
       </c>
       <c r="B149" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15661,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15685,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556819</v>
+        <v>556529</v>
       </c>
       <c r="R149" t="n">
-        <v>7227694</v>
+        <v>7226958</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15715,17 +15702,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15756,7 +15738,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091371</v>
+        <v>126091378</v>
       </c>
       <c r="B150" t="n">
         <v>80076</v>
@@ -15791,10 +15773,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556365</v>
+        <v>556353</v>
       </c>
       <c r="R150" t="n">
-        <v>7227004</v>
+        <v>7227115</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15857,10 +15839,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091063</v>
+        <v>126091152</v>
       </c>
       <c r="B151" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15868,21 +15850,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15892,10 +15874,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556836</v>
+        <v>556975</v>
       </c>
       <c r="R151" t="n">
-        <v>7227732</v>
+        <v>7227579</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15928,6 +15910,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15958,10 +15945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091388</v>
+        <v>126091149</v>
       </c>
       <c r="B152" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15969,21 +15956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15993,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556529</v>
+        <v>556807</v>
       </c>
       <c r="R152" t="n">
-        <v>7226958</v>
+        <v>7227608</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16023,12 +16010,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16059,10 +16051,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091378</v>
+        <v>126091350</v>
       </c>
       <c r="B153" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16070,21 +16062,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16094,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556353</v>
+        <v>556589</v>
       </c>
       <c r="R153" t="n">
-        <v>7227115</v>
+        <v>7227059</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16130,6 +16122,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16160,10 +16157,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091152</v>
+        <v>126091040</v>
       </c>
       <c r="B154" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16171,21 +16168,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16195,10 +16192,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556975</v>
+        <v>556781</v>
       </c>
       <c r="R154" t="n">
-        <v>7227579</v>
+        <v>7227272</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16235,7 +16232,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16266,32 +16263,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091149</v>
+        <v>126091053</v>
       </c>
       <c r="B155" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16301,10 +16298,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556807</v>
+        <v>556996</v>
       </c>
       <c r="R155" t="n">
-        <v>7227608</v>
+        <v>7227559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16337,11 +16334,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16372,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091350</v>
+        <v>126091397</v>
       </c>
       <c r="B156" t="n">
-        <v>57651</v>
+        <v>80103</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16407,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556589</v>
+        <v>556378</v>
       </c>
       <c r="R156" t="n">
-        <v>7227059</v>
+        <v>7226996</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16443,11 +16435,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16478,32 +16465,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091040</v>
+        <v>126091404</v>
       </c>
       <c r="B157" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16513,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556781</v>
+        <v>556272</v>
       </c>
       <c r="R157" t="n">
-        <v>7227272</v>
+        <v>7227058</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16543,17 +16530,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16584,10 +16566,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091053</v>
+        <v>126091169</v>
       </c>
       <c r="B158" t="n">
-        <v>98360</v>
+        <v>80110</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16595,21 +16577,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16619,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556996</v>
+        <v>556756</v>
       </c>
       <c r="R158" t="n">
-        <v>7227559</v>
+        <v>7227253</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16678,309 +16660,6 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>126091397</v>
-      </c>
-      <c r="B159" t="n">
-        <v>80103</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q159" t="n">
-        <v>556378</v>
-      </c>
-      <c r="R159" t="n">
-        <v>7226996</v>
-      </c>
-      <c r="S159" t="n">
-        <v>10</v>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT159" t="inlineStr"/>
-      <c r="AW159" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX159" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>126091404</v>
-      </c>
-      <c r="B160" t="n">
-        <v>80111</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q160" t="n">
-        <v>556272</v>
-      </c>
-      <c r="R160" t="n">
-        <v>7227058</v>
-      </c>
-      <c r="S160" t="n">
-        <v>10</v>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT160" t="inlineStr"/>
-      <c r="AW160" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX160" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>126091169</v>
-      </c>
-      <c r="B161" t="n">
-        <v>80110</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Tallbacksmyrorna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q161" t="n">
-        <v>556756</v>
-      </c>
-      <c r="R161" t="n">
-        <v>7227253</v>
-      </c>
-      <c r="S161" t="n">
-        <v>10</v>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AD161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT161" t="inlineStr"/>
-      <c r="AW161" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX161" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B22" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R22" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R23" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091368</v>
+        <v>126091435</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556346</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>7226961</v>
+        <v>7226941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091164</v>
+        <v>126091106</v>
       </c>
       <c r="B25" t="n">
-        <v>88641</v>
+        <v>80111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556775</v>
+        <v>556709</v>
       </c>
       <c r="R25" t="n">
-        <v>7227253</v>
+        <v>7227248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091340</v>
+        <v>126091368</v>
       </c>
       <c r="B26" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556312</v>
+        <v>556346</v>
       </c>
       <c r="R26" t="n">
-        <v>7227107</v>
+        <v>7226961</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091073</v>
+        <v>126091164</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>88641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556756</v>
+        <v>556775</v>
       </c>
       <c r="R27" t="n">
         <v>7227253</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091435</v>
+        <v>126091340</v>
       </c>
       <c r="B28" t="n">
-        <v>80110</v>
+        <v>91232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556359</v>
+        <v>556312</v>
       </c>
       <c r="R28" t="n">
-        <v>7226941</v>
+        <v>7227107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B29" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R29" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091075</v>
+        <v>126091144</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556792</v>
+        <v>557048</v>
       </c>
       <c r="R42" t="n">
-        <v>7227253</v>
+        <v>7227797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B43" t="n">
         <v>78972</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R43" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,12 +4911,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,7 +4952,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091422</v>
+        <v>126091145</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556407</v>
+        <v>556897</v>
       </c>
       <c r="R44" t="n">
-        <v>7226992</v>
+        <v>7227735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,12 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5053,10 +5058,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091145</v>
+        <v>126091129</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,21 +5069,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5093,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556897</v>
+        <v>556685</v>
       </c>
       <c r="R45" t="n">
-        <v>7227735</v>
+        <v>7227107</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,17 +5123,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5159,10 +5159,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091129</v>
+        <v>126091348</v>
       </c>
       <c r="B46" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,21 +5170,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556685</v>
+        <v>556351</v>
       </c>
       <c r="R46" t="n">
-        <v>7227107</v>
+        <v>7226920</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5224,12 +5224,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5260,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091403</v>
+        <v>126091075</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,21 +5276,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5295,10 +5300,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556357</v>
+        <v>556792</v>
       </c>
       <c r="R47" t="n">
-        <v>7227004</v>
+        <v>7227253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5325,12 +5330,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5361,32 +5366,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091044</v>
+        <v>126091403</v>
       </c>
       <c r="B48" t="n">
-        <v>80104</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556826</v>
+        <v>556357</v>
       </c>
       <c r="R48" t="n">
-        <v>7227309</v>
+        <v>7227004</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,12 +5431,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5467,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091107</v>
+        <v>126091044</v>
       </c>
       <c r="B49" t="n">
-        <v>80111</v>
+        <v>80104</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5478,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5502,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556723</v>
+        <v>556826</v>
       </c>
       <c r="R49" t="n">
-        <v>7227276</v>
+        <v>7227309</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5563,32 +5568,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091348</v>
+        <v>126091107</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556351</v>
+        <v>556723</v>
       </c>
       <c r="R50" t="n">
-        <v>7226920</v>
+        <v>7227276</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5628,17 +5633,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6280,10 +6280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091095</v>
+        <v>126091151</v>
       </c>
       <c r="B57" t="n">
-        <v>91528</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557005</v>
+        <v>556935</v>
       </c>
       <c r="R57" t="n">
-        <v>7227490</v>
+        <v>7227614</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6351,6 +6351,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091343</v>
+        <v>126091417</v>
       </c>
       <c r="B58" t="n">
-        <v>91232</v>
+        <v>91250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6397,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556373</v>
+        <v>556559</v>
       </c>
       <c r="R58" t="n">
-        <v>7227010</v>
+        <v>7226989</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6482,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091373</v>
+        <v>126091400</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6493,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556350</v>
+        <v>556261</v>
       </c>
       <c r="R59" t="n">
-        <v>7226997</v>
+        <v>7227068</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091359</v>
+        <v>126091409</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556280</v>
+        <v>556480</v>
       </c>
       <c r="R60" t="n">
-        <v>7226845</v>
+        <v>7226980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6684,32 +6689,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091361</v>
+        <v>126091442</v>
       </c>
       <c r="B61" t="n">
-        <v>80076</v>
+        <v>80110</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6719,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556321</v>
+        <v>556494</v>
       </c>
       <c r="R61" t="n">
-        <v>7226929</v>
+        <v>7226972</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6785,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091386</v>
+        <v>126091095</v>
       </c>
       <c r="B62" t="n">
-        <v>80076</v>
+        <v>91528</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556480</v>
+        <v>557005</v>
       </c>
       <c r="R62" t="n">
-        <v>7226980</v>
+        <v>7227490</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6850,12 +6855,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6886,10 +6891,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091066</v>
+        <v>126091343</v>
       </c>
       <c r="B63" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,21 +6902,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6921,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556946</v>
+        <v>556373</v>
       </c>
       <c r="R63" t="n">
-        <v>7227602</v>
+        <v>7227010</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,17 +6956,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6992,10 +6992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091151</v>
+        <v>126091373</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556935</v>
+        <v>556350</v>
       </c>
       <c r="R64" t="n">
-        <v>7227614</v>
+        <v>7226997</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,17 +7057,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7098,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091417</v>
+        <v>126091359</v>
       </c>
       <c r="B65" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7109,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556559</v>
+        <v>556280</v>
       </c>
       <c r="R65" t="n">
-        <v>7226989</v>
+        <v>7226845</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7199,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091400</v>
+        <v>126091361</v>
       </c>
       <c r="B66" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7210,21 +7205,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7234,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556261</v>
+        <v>556321</v>
       </c>
       <c r="R66" t="n">
-        <v>7227068</v>
+        <v>7226929</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7300,32 +7295,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091409</v>
+        <v>126091386</v>
       </c>
       <c r="B67" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7401,32 +7396,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091442</v>
+        <v>126091066</v>
       </c>
       <c r="B68" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556494</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7226972</v>
+        <v>7227602</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7466,12 +7461,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B69" t="n">
-        <v>80076</v>
+        <v>91197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R69" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091337</v>
+        <v>126091090</v>
       </c>
       <c r="B70" t="n">
-        <v>91197</v>
+        <v>79979</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,21 +7614,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556374</v>
+        <v>556690</v>
       </c>
       <c r="R70" t="n">
-        <v>7226996</v>
+        <v>7227262</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7704,32 +7704,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091090</v>
+        <v>126091384</v>
       </c>
       <c r="B71" t="n">
-        <v>79979</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556690</v>
+        <v>556376</v>
       </c>
       <c r="R71" t="n">
-        <v>7227262</v>
+        <v>7227009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,12 +7769,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10148,10 +10148,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091357</v>
+        <v>126091418</v>
       </c>
       <c r="B95" t="n">
-        <v>80076</v>
+        <v>91250</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10159,21 +10159,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556061</v>
+        <v>556550</v>
       </c>
       <c r="R95" t="n">
-        <v>7226781</v>
+        <v>7227005</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091339</v>
+        <v>126091125</v>
       </c>
       <c r="B96" t="n">
-        <v>91232</v>
+        <v>91250</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556393</v>
+        <v>556893</v>
       </c>
       <c r="R96" t="n">
-        <v>7226994</v>
+        <v>7227703</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091418</v>
+        <v>126091441</v>
       </c>
       <c r="B97" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556550</v>
+        <v>556480</v>
       </c>
       <c r="R97" t="n">
-        <v>7227005</v>
+        <v>7226980</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10451,32 +10451,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091125</v>
+        <v>126091167</v>
       </c>
       <c r="B98" t="n">
-        <v>91250</v>
+        <v>80110</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556893</v>
+        <v>556728</v>
       </c>
       <c r="R98" t="n">
-        <v>7227703</v>
+        <v>7227275</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091441</v>
+        <v>126091405</v>
       </c>
       <c r="B99" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10563,21 +10563,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556480</v>
+        <v>556230</v>
       </c>
       <c r="R99" t="n">
-        <v>7226980</v>
+        <v>7226809</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10653,32 +10653,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091167</v>
+        <v>126091357</v>
       </c>
       <c r="B100" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556728</v>
+        <v>556061</v>
       </c>
       <c r="R100" t="n">
-        <v>7227275</v>
+        <v>7226781</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10754,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091405</v>
+        <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>80111</v>
+        <v>91232</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556230</v>
+        <v>556393</v>
       </c>
       <c r="R101" t="n">
-        <v>7226809</v>
+        <v>7226994</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11264,10 +11264,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091010</v>
+        <v>126091416</v>
       </c>
       <c r="B106" t="n">
-        <v>79004</v>
+        <v>91250</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11275,21 +11275,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556904</v>
+        <v>556600</v>
       </c>
       <c r="R106" t="n">
-        <v>7227703</v>
+        <v>7227123</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11365,10 +11365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091416</v>
+        <v>126091421</v>
       </c>
       <c r="B107" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11376,21 +11376,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556600</v>
+        <v>556111</v>
       </c>
       <c r="R107" t="n">
-        <v>7227123</v>
+        <v>7226873</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11436,6 +11436,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,10 +11471,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091421</v>
+        <v>126091010</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11477,21 +11482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11506,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556111</v>
+        <v>556904</v>
       </c>
       <c r="R108" t="n">
-        <v>7226873</v>
+        <v>7227703</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,17 +11536,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11572,32 +11572,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091407</v>
+        <v>126091072</v>
       </c>
       <c r="B109" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556365</v>
+        <v>556913</v>
       </c>
       <c r="R109" t="n">
-        <v>7227004</v>
+        <v>7227621</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11673,7 +11673,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091072</v>
+        <v>126091380</v>
       </c>
       <c r="B110" t="n">
         <v>80076</v>
@@ -11708,10 +11708,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556913</v>
+        <v>556261</v>
       </c>
       <c r="R110" t="n">
-        <v>7227621</v>
+        <v>7227068</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11738,12 +11738,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11774,7 +11774,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091380</v>
+        <v>126091070</v>
       </c>
       <c r="B111" t="n">
         <v>80076</v>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556261</v>
+        <v>556723</v>
       </c>
       <c r="R111" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11839,12 +11839,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11875,10 +11875,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091070</v>
+        <v>126091341</v>
       </c>
       <c r="B112" t="n">
-        <v>80076</v>
+        <v>91232</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556723</v>
+        <v>556187</v>
       </c>
       <c r="R112" t="n">
-        <v>7227276</v>
+        <v>7226946</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091341</v>
+        <v>126091407</v>
       </c>
       <c r="B113" t="n">
-        <v>91232</v>
+        <v>80111</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556187</v>
+        <v>556365</v>
       </c>
       <c r="R113" t="n">
-        <v>7226946</v>
+        <v>7227004</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B115" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R115" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091068</v>
+        <v>126091084</v>
       </c>
       <c r="B116" t="n">
         <v>80076</v>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556707</v>
+        <v>556737</v>
       </c>
       <c r="R116" t="n">
-        <v>7227243</v>
+        <v>7227192</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12344,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091017</v>
+        <v>126091068</v>
       </c>
       <c r="B117" t="n">
-        <v>91232</v>
+        <v>80076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556929</v>
+        <v>556707</v>
       </c>
       <c r="R117" t="n">
-        <v>7227610</v>
+        <v>7227243</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091121</v>
+        <v>126091017</v>
       </c>
       <c r="B118" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556907</v>
+        <v>556929</v>
       </c>
       <c r="R118" t="n">
-        <v>7227720</v>
+        <v>7227610</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091102</v>
+        <v>126091121</v>
       </c>
       <c r="B119" t="n">
-        <v>80075</v>
+        <v>91228</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556740</v>
+        <v>556907</v>
       </c>
       <c r="R119" t="n">
-        <v>7227186</v>
+        <v>7227720</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091388</v>
+        <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556529</v>
+        <v>556975</v>
       </c>
       <c r="R149" t="n">
-        <v>7226958</v>
+        <v>7227579</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,12 +15702,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15738,10 +15743,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091378</v>
+        <v>126091149</v>
       </c>
       <c r="B150" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15749,21 +15754,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15773,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556353</v>
+        <v>556807</v>
       </c>
       <c r="R150" t="n">
-        <v>7227115</v>
+        <v>7227608</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15803,12 +15808,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15839,10 +15849,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091152</v>
+        <v>126091350</v>
       </c>
       <c r="B151" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15850,21 +15860,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15874,10 +15884,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556975</v>
+        <v>556589</v>
       </c>
       <c r="R151" t="n">
-        <v>7227579</v>
+        <v>7227059</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15904,17 +15914,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15945,10 +15955,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091149</v>
+        <v>126091040</v>
       </c>
       <c r="B152" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15956,21 +15966,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15980,10 +15990,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556807</v>
+        <v>556781</v>
       </c>
       <c r="R152" t="n">
-        <v>7227608</v>
+        <v>7227272</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16020,7 +16030,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Lång bål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,10 +16061,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091350</v>
+        <v>126091388</v>
       </c>
       <c r="B153" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16062,21 +16072,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16096,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556589</v>
+        <v>556529</v>
       </c>
       <c r="R153" t="n">
-        <v>7227059</v>
+        <v>7226958</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16122,11 +16132,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16157,10 +16162,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091040</v>
+        <v>126091378</v>
       </c>
       <c r="B154" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16168,21 +16173,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16192,10 +16197,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556781</v>
+        <v>556353</v>
       </c>
       <c r="R154" t="n">
-        <v>7227272</v>
+        <v>7227115</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16222,17 +16227,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16263,10 +16263,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091053</v>
+        <v>126091397</v>
       </c>
       <c r="B155" t="n">
-        <v>98360</v>
+        <v>80103</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16274,21 +16274,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556996</v>
+        <v>556378</v>
       </c>
       <c r="R155" t="n">
-        <v>7227559</v>
+        <v>7226996</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16328,12 +16328,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16364,10 +16364,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091397</v>
+        <v>126091404</v>
       </c>
       <c r="B156" t="n">
-        <v>80103</v>
+        <v>80111</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16375,21 +16375,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556378</v>
+        <v>556272</v>
       </c>
       <c r="R156" t="n">
-        <v>7226996</v>
+        <v>7227058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16465,10 +16465,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091404</v>
+        <v>126091169</v>
       </c>
       <c r="B157" t="n">
-        <v>80111</v>
+        <v>80110</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16476,21 +16476,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556272</v>
+        <v>556756</v>
       </c>
       <c r="R157" t="n">
-        <v>7227058</v>
+        <v>7227253</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16566,10 +16566,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091169</v>
+        <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>80110</v>
+        <v>98360</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16577,21 +16577,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16601,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556756</v>
+        <v>556996</v>
       </c>
       <c r="R158" t="n">
-        <v>7227253</v>
+        <v>7227559</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091362</v>
+        <v>126091440</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556369</v>
+        <v>556465</v>
       </c>
       <c r="R2" t="n">
-        <v>7226946</v>
+        <v>7226995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091342</v>
+        <v>126091408</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556306</v>
+        <v>556467</v>
       </c>
       <c r="R3" t="n">
-        <v>7226876</v>
+        <v>7226993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091065</v>
+        <v>126091362</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556817</v>
+        <v>556369</v>
       </c>
       <c r="R4" t="n">
-        <v>7227591</v>
+        <v>7226946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091370</v>
+        <v>126091342</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556364</v>
+        <v>556306</v>
       </c>
       <c r="R5" t="n">
-        <v>7226989</v>
+        <v>7226876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091395</v>
+        <v>126091065</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>80077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556308</v>
+        <v>556817</v>
       </c>
       <c r="R6" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091128</v>
+        <v>126091370</v>
       </c>
       <c r="B7" t="n">
-        <v>91250</v>
+        <v>80077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556830</v>
+        <v>556364</v>
       </c>
       <c r="R7" t="n">
-        <v>7227331</v>
+        <v>7226989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091123</v>
+        <v>126091395</v>
       </c>
       <c r="B8" t="n">
-        <v>91250</v>
+        <v>91530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557106</v>
+        <v>556308</v>
       </c>
       <c r="R8" t="n">
-        <v>7227606</v>
+        <v>7226876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091440</v>
+        <v>126091128</v>
       </c>
       <c r="B9" t="n">
-        <v>80110</v>
+        <v>91252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556465</v>
+        <v>556830</v>
       </c>
       <c r="R9" t="n">
-        <v>7226995</v>
+        <v>7227331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091408</v>
+        <v>126091123</v>
       </c>
       <c r="B10" t="n">
-        <v>80111</v>
+        <v>91252</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556467</v>
+        <v>557106</v>
       </c>
       <c r="R10" t="n">
-        <v>7226993</v>
+        <v>7227606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,7 +1587,7 @@
         <v>126091389</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126091064</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126091374</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126091365</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126091420</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>126091147</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126091335</v>
       </c>
       <c r="B17" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>126091425</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>126091043</v>
       </c>
       <c r="B19" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>126091439</v>
       </c>
       <c r="B20" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>126091428</v>
       </c>
       <c r="B21" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>126091146</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>126091041</v>
       </c>
       <c r="B23" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>126091435</v>
       </c>
       <c r="B24" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>126091106</v>
       </c>
       <c r="B25" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>126091368</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091164</v>
+        <v>126091073</v>
       </c>
       <c r="B27" t="n">
-        <v>88641</v>
+        <v>80077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556775</v>
+        <v>556756</v>
       </c>
       <c r="R27" t="n">
         <v>7227253</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091340</v>
+        <v>126091164</v>
       </c>
       <c r="B28" t="n">
-        <v>91232</v>
+        <v>88643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556312</v>
+        <v>556775</v>
       </c>
       <c r="R28" t="n">
-        <v>7227107</v>
+        <v>7227253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091073</v>
+        <v>126091340</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556756</v>
+        <v>556312</v>
       </c>
       <c r="R29" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3521,7 +3521,7 @@
         <v>126091382</v>
       </c>
       <c r="B30" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>126091347</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>126091034</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091349</v>
+        <v>126091356</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>80077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556613</v>
+        <v>556271</v>
       </c>
       <c r="R33" t="n">
-        <v>7227051</v>
+        <v>7227059</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,11 +3902,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,32 +3932,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091356</v>
+        <v>126091448</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>91904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>898</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3972,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556271</v>
+        <v>556484</v>
       </c>
       <c r="R34" t="n">
-        <v>7227059</v>
+        <v>7226980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,32 +4033,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091448</v>
+        <v>126091369</v>
       </c>
       <c r="B35" t="n">
-        <v>91902</v>
+        <v>80077</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>898</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556484</v>
+        <v>556333</v>
       </c>
       <c r="R35" t="n">
-        <v>7226980</v>
+        <v>7227009</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4139,10 +4134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091369</v>
+        <v>126091013</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,21 +4145,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556333</v>
+        <v>556830</v>
       </c>
       <c r="R36" t="n">
-        <v>7227009</v>
+        <v>7227704</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4240,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091013</v>
+        <v>126091349</v>
       </c>
       <c r="B37" t="n">
-        <v>91232</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4251,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556830</v>
+        <v>556613</v>
       </c>
       <c r="R37" t="n">
-        <v>7227704</v>
+        <v>7227051</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4305,12 +4300,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4344,7 +4344,7 @@
         <v>126091414</v>
       </c>
       <c r="B38" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>126091124</v>
       </c>
       <c r="B39" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>126091042</v>
       </c>
       <c r="B40" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>126091406</v>
       </c>
       <c r="B41" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091144</v>
+        <v>126091348</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557048</v>
+        <v>556351</v>
       </c>
       <c r="R42" t="n">
-        <v>7227797</v>
+        <v>7226920</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,32 +4851,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091422</v>
+        <v>126091352</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556407</v>
+        <v>556293</v>
       </c>
       <c r="R43" t="n">
-        <v>7226992</v>
+        <v>7227068</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,11 +4922,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091145</v>
+        <v>126091403</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,21 +4963,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556897</v>
+        <v>556357</v>
       </c>
       <c r="R44" t="n">
-        <v>7227735</v>
+        <v>7227004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5017,17 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5058,10 +5053,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091129</v>
+        <v>126091144</v>
       </c>
       <c r="B45" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5069,21 +5064,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556685</v>
+        <v>557048</v>
       </c>
       <c r="R45" t="n">
-        <v>7227107</v>
+        <v>7227797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5123,12 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5159,10 +5154,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091348</v>
+        <v>126091422</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5170,21 +5165,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5194,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556351</v>
+        <v>556407</v>
       </c>
       <c r="R46" t="n">
-        <v>7226920</v>
+        <v>7226992</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5234,7 +5229,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5265,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091075</v>
+        <v>126091145</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5276,21 +5271,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5300,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556792</v>
+        <v>556897</v>
       </c>
       <c r="R47" t="n">
-        <v>7227253</v>
+        <v>7227735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5336,6 +5331,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091403</v>
+        <v>126091129</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,21 +5377,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556357</v>
+        <v>556685</v>
       </c>
       <c r="R48" t="n">
-        <v>7227004</v>
+        <v>7227107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5467,32 +5467,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091044</v>
+        <v>126091075</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556826</v>
+        <v>556792</v>
       </c>
       <c r="R49" t="n">
-        <v>7227309</v>
+        <v>7227253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091107</v>
+        <v>126091044</v>
       </c>
       <c r="B50" t="n">
-        <v>80111</v>
+        <v>80105</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,21 +5579,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556723</v>
+        <v>556826</v>
       </c>
       <c r="R50" t="n">
-        <v>7227276</v>
+        <v>7227309</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091352</v>
+        <v>126091107</v>
       </c>
       <c r="B51" t="n">
-        <v>98360</v>
+        <v>80112</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5680,21 +5680,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556293</v>
+        <v>556723</v>
       </c>
       <c r="R51" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091381</v>
+        <v>126091148</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556280</v>
+        <v>556787</v>
       </c>
       <c r="R52" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5835,12 +5835,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5871,10 +5876,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091148</v>
+        <v>126091401</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,21 +5887,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5906,10 +5911,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556787</v>
+        <v>556271</v>
       </c>
       <c r="R53" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5936,17 +5941,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5980,7 +5980,7 @@
         <v>126091430</v>
       </c>
       <c r="B54" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>126091438</v>
       </c>
       <c r="B55" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6179,10 +6179,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091401</v>
+        <v>126091381</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6190,21 +6190,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556271</v>
+        <v>556280</v>
       </c>
       <c r="R56" t="n">
         <v>7227059</v>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091151</v>
+        <v>126091095</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>91530</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556935</v>
+        <v>557005</v>
       </c>
       <c r="R57" t="n">
-        <v>7227614</v>
+        <v>7227490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6351,11 +6351,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091417</v>
+        <v>126091343</v>
       </c>
       <c r="B58" t="n">
-        <v>91250</v>
+        <v>91234</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6421,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556559</v>
+        <v>556373</v>
       </c>
       <c r="R58" t="n">
-        <v>7226989</v>
+        <v>7227010</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6487,10 +6482,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091400</v>
+        <v>126091373</v>
       </c>
       <c r="B59" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6498,21 +6493,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556261</v>
+        <v>556350</v>
       </c>
       <c r="R59" t="n">
-        <v>7227068</v>
+        <v>7226997</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,32 +6583,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091409</v>
+        <v>126091359</v>
       </c>
       <c r="B60" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556480</v>
+        <v>556280</v>
       </c>
       <c r="R60" t="n">
-        <v>7226980</v>
+        <v>7226845</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6689,32 +6684,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091442</v>
+        <v>126091361</v>
       </c>
       <c r="B61" t="n">
-        <v>80110</v>
+        <v>80077</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556494</v>
+        <v>556321</v>
       </c>
       <c r="R61" t="n">
-        <v>7226972</v>
+        <v>7226929</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6790,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091095</v>
+        <v>126091386</v>
       </c>
       <c r="B62" t="n">
-        <v>91528</v>
+        <v>80077</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6801,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557005</v>
+        <v>556480</v>
       </c>
       <c r="R62" t="n">
-        <v>7227490</v>
+        <v>7226980</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6855,12 +6850,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6891,10 +6886,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091343</v>
+        <v>126091066</v>
       </c>
       <c r="B63" t="n">
-        <v>91232</v>
+        <v>80077</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6902,21 +6897,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6926,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556373</v>
+        <v>556946</v>
       </c>
       <c r="R63" t="n">
-        <v>7227010</v>
+        <v>7227602</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6956,12 +6951,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6992,7 +6992,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091373</v>
+        <v>126091400</v>
       </c>
       <c r="B64" t="n">
         <v>80076</v>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556350</v>
+        <v>556261</v>
       </c>
       <c r="R64" t="n">
-        <v>7226997</v>
+        <v>7227068</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091359</v>
+        <v>126091151</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556280</v>
+        <v>556935</v>
       </c>
       <c r="R65" t="n">
-        <v>7226845</v>
+        <v>7227614</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7158,12 +7158,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7194,10 +7199,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091361</v>
+        <v>126091417</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7205,21 +7210,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7229,10 +7234,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556321</v>
+        <v>556559</v>
       </c>
       <c r="R66" t="n">
-        <v>7226929</v>
+        <v>7226989</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,32 +7300,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091386</v>
+        <v>126091409</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7396,32 +7401,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091066</v>
+        <v>126091442</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>556494</v>
       </c>
       <c r="R68" t="n">
-        <v>7227602</v>
+        <v>7226972</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7461,17 +7466,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091337</v>
+        <v>126091345</v>
       </c>
       <c r="B69" t="n">
-        <v>91197</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556374</v>
+        <v>556499</v>
       </c>
       <c r="R69" t="n">
-        <v>7226996</v>
+        <v>7227184</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,6 +7573,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7603,10 +7608,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091090</v>
+        <v>126091337</v>
       </c>
       <c r="B70" t="n">
-        <v>79979</v>
+        <v>91199</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,21 +7619,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7638,10 +7643,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556690</v>
+        <v>556374</v>
       </c>
       <c r="R70" t="n">
-        <v>7227262</v>
+        <v>7226996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,12 +7673,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7704,32 +7709,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091384</v>
+        <v>126091090</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>79980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7739,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556376</v>
+        <v>556690</v>
       </c>
       <c r="R71" t="n">
-        <v>7227009</v>
+        <v>7227262</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,12 +7774,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7805,10 +7810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091345</v>
+        <v>126091384</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>80077</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7816,21 +7821,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7840,10 +7845,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556499</v>
+        <v>556376</v>
       </c>
       <c r="R72" t="n">
-        <v>7227184</v>
+        <v>7227009</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7876,11 +7881,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7911,10 +7911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091346</v>
+        <v>126091015</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>91234</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,21 +7922,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556194</v>
+        <v>556931</v>
       </c>
       <c r="R73" t="n">
-        <v>7226815</v>
+        <v>7227622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,17 +7976,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8017,10 +8012,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091015</v>
+        <v>126091051</v>
       </c>
       <c r="B74" t="n">
-        <v>91232</v>
+        <v>79942</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8028,21 +8023,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8052,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556931</v>
+        <v>556679</v>
       </c>
       <c r="R74" t="n">
-        <v>7227622</v>
+        <v>7227232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8118,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091051</v>
+        <v>126091360</v>
       </c>
       <c r="B75" t="n">
-        <v>79941</v>
+        <v>80077</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8129,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8153,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556679</v>
+        <v>556326</v>
       </c>
       <c r="R75" t="n">
-        <v>7227232</v>
+        <v>7226893</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8183,12 +8178,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8219,10 +8214,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091360</v>
+        <v>126091375</v>
       </c>
       <c r="B76" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556326</v>
+        <v>556423</v>
       </c>
       <c r="R76" t="n">
-        <v>7226893</v>
+        <v>7226984</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8320,10 +8315,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091375</v>
+        <v>126091067</v>
       </c>
       <c r="B77" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8355,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556423</v>
+        <v>556690</v>
       </c>
       <c r="R77" t="n">
-        <v>7226984</v>
+        <v>7227262</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,12 +8380,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8421,10 +8416,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091067</v>
+        <v>126091355</v>
       </c>
       <c r="B78" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556690</v>
+        <v>556346</v>
       </c>
       <c r="R78" t="n">
-        <v>7227262</v>
+        <v>7227118</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8486,12 +8481,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,10 +8517,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091355</v>
+        <v>126091346</v>
       </c>
       <c r="B79" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8533,21 +8528,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8557,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556346</v>
+        <v>556194</v>
       </c>
       <c r="R79" t="n">
-        <v>7227118</v>
+        <v>7226815</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8593,6 +8588,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8623,10 +8623,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091012</v>
+        <v>126091393</v>
       </c>
       <c r="B80" t="n">
-        <v>91197</v>
+        <v>79980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8634,21 +8634,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,10 +8658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556977</v>
+        <v>556291</v>
       </c>
       <c r="R80" t="n">
-        <v>7227576</v>
+        <v>7226913</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8724,32 +8724,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091143</v>
+        <v>126091012</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>91199</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8759,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>557106</v>
+        <v>556977</v>
       </c>
       <c r="R81" t="n">
-        <v>7227606</v>
+        <v>7227576</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,32 +8825,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091174</v>
+        <v>126091143</v>
       </c>
       <c r="B82" t="n">
-        <v>91642</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556888</v>
+        <v>557106</v>
       </c>
       <c r="R82" t="n">
-        <v>7227746</v>
+        <v>7227606</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8926,10 +8926,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091393</v>
+        <v>126091174</v>
       </c>
       <c r="B83" t="n">
-        <v>79979</v>
+        <v>91644</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8937,21 +8937,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6456</v>
+        <v>4217</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556291</v>
+        <v>556888</v>
       </c>
       <c r="R83" t="n">
-        <v>7226913</v>
+        <v>7227746</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8991,12 +8991,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9030,7 +9030,7 @@
         <v>126091402</v>
       </c>
       <c r="B84" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9128,10 +9128,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091027</v>
+        <v>126091153</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9139,21 +9139,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>557059</v>
+        <v>556996</v>
       </c>
       <c r="R85" t="n">
-        <v>7227538</v>
+        <v>7227559</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9199,11 +9199,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9234,10 +9229,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091383</v>
+        <v>126091141</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9245,21 +9240,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9269,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556230</v>
+        <v>556931</v>
       </c>
       <c r="R86" t="n">
-        <v>7226809</v>
+        <v>7227622</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9299,12 +9294,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9335,32 +9335,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091377</v>
+        <v>126091166</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556584</v>
+        <v>556690</v>
       </c>
       <c r="R87" t="n">
-        <v>7227068</v>
+        <v>7227262</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9436,32 +9436,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091344</v>
+        <v>126091165</v>
       </c>
       <c r="B88" t="n">
-        <v>91232</v>
+        <v>80111</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556452</v>
+        <v>556874</v>
       </c>
       <c r="R88" t="n">
-        <v>7226989</v>
+        <v>7227697</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9537,32 +9537,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091372</v>
+        <v>126091351</v>
       </c>
       <c r="B89" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9572,10 +9572,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556359</v>
+        <v>556346</v>
       </c>
       <c r="R89" t="n">
-        <v>7226988</v>
+        <v>7227118</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091153</v>
+        <v>126091383</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>80077</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556996</v>
+        <v>556230</v>
       </c>
       <c r="R90" t="n">
-        <v>7227559</v>
+        <v>7226809</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9739,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091141</v>
+        <v>126091377</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>80077</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556931</v>
+        <v>556584</v>
       </c>
       <c r="R91" t="n">
-        <v>7227622</v>
+        <v>7227068</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9804,17 +9804,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9845,32 +9840,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091166</v>
+        <v>126091344</v>
       </c>
       <c r="B92" t="n">
-        <v>80110</v>
+        <v>91234</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9880,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556690</v>
+        <v>556452</v>
       </c>
       <c r="R92" t="n">
-        <v>7227262</v>
+        <v>7226989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9910,12 +9905,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9946,32 +9941,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091165</v>
+        <v>126091372</v>
       </c>
       <c r="B93" t="n">
-        <v>80110</v>
+        <v>80077</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9981,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556874</v>
+        <v>556359</v>
       </c>
       <c r="R93" t="n">
-        <v>7227697</v>
+        <v>7226988</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10011,12 +10006,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10047,32 +10042,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126091351</v>
+        <v>126091027</v>
       </c>
       <c r="B94" t="n">
-        <v>80104</v>
+        <v>57652</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556346</v>
+        <v>557059</v>
       </c>
       <c r="R94" t="n">
-        <v>7227118</v>
+        <v>7227538</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10112,12 +10107,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10151,7 +10151,7 @@
         <v>126091418</v>
       </c>
       <c r="B95" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>126091125</v>
       </c>
       <c r="B96" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>126091441</v>
       </c>
       <c r="B97" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>126091167</v>
       </c>
       <c r="B98" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>126091405</v>
       </c>
       <c r="B99" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>126091357</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>126091019</v>
       </c>
       <c r="B102" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>126091358</v>
       </c>
       <c r="B103" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>126091028</v>
       </c>
       <c r="B104" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>126091392</v>
       </c>
       <c r="B105" t="n">
-        <v>56227</v>
+        <v>56228</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>126091416</v>
       </c>
       <c r="B106" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>126091421</v>
       </c>
       <c r="B107" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11471,32 +11471,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091010</v>
+        <v>126091407</v>
       </c>
       <c r="B108" t="n">
-        <v>79004</v>
+        <v>80112</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556904</v>
+        <v>556365</v>
       </c>
       <c r="R108" t="n">
-        <v>7227703</v>
+        <v>7227004</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11575,7 +11575,7 @@
         <v>126091072</v>
       </c>
       <c r="B109" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>126091380</v>
       </c>
       <c r="B110" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>126091070</v>
       </c>
       <c r="B111" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>126091341</v>
       </c>
       <c r="B112" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11976,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091407</v>
+        <v>126091010</v>
       </c>
       <c r="B113" t="n">
-        <v>80111</v>
+        <v>79005</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556365</v>
+        <v>556904</v>
       </c>
       <c r="R113" t="n">
-        <v>7227004</v>
+        <v>7227703</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12080,7 +12080,7 @@
         <v>126091115</v>
       </c>
       <c r="B114" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>126091102</v>
       </c>
       <c r="B115" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>126091084</v>
       </c>
       <c r="B116" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>126091068</v>
       </c>
       <c r="B117" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>126091017</v>
       </c>
       <c r="B118" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>126091121</v>
       </c>
       <c r="B119" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12683,10 +12683,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091387</v>
+        <v>126091424</v>
       </c>
       <c r="B120" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556497</v>
+        <v>556549</v>
       </c>
       <c r="R120" t="n">
-        <v>7226978</v>
+        <v>7226986</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12754,6 +12754,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12784,32 +12789,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091379</v>
+        <v>126091445</v>
       </c>
       <c r="B121" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12819,10 +12824,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R121" t="n">
-        <v>7227093</v>
+        <v>7227109</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,32 +12890,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091394</v>
+        <v>126091444</v>
       </c>
       <c r="B122" t="n">
-        <v>91528</v>
+        <v>80111</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12920,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556098</v>
+        <v>556584</v>
       </c>
       <c r="R122" t="n">
-        <v>7226757</v>
+        <v>7227068</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,32 +12991,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091424</v>
+        <v>126091410</v>
       </c>
       <c r="B123" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13026,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R123" t="n">
-        <v>7226986</v>
+        <v>7227068</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,11 +13062,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13092,10 +13092,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091445</v>
+        <v>126091052</v>
       </c>
       <c r="B124" t="n">
-        <v>80110</v>
+        <v>98362</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556584</v>
+        <v>557007</v>
       </c>
       <c r="R124" t="n">
-        <v>7227109</v>
+        <v>7227805</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13157,12 +13157,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091444</v>
+        <v>126091387</v>
       </c>
       <c r="B125" t="n">
-        <v>80110</v>
+        <v>80077</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556584</v>
+        <v>556497</v>
       </c>
       <c r="R125" t="n">
-        <v>7227068</v>
+        <v>7226978</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13294,32 +13294,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091410</v>
+        <v>126091379</v>
       </c>
       <c r="B126" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556584</v>
+        <v>556305</v>
       </c>
       <c r="R126" t="n">
-        <v>7227068</v>
+        <v>7227093</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13395,32 +13395,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091052</v>
+        <v>126091394</v>
       </c>
       <c r="B127" t="n">
-        <v>98360</v>
+        <v>91530</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13430,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>557007</v>
+        <v>556098</v>
       </c>
       <c r="R127" t="n">
-        <v>7227805</v>
+        <v>7226757</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,12 +13460,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13496,32 +13496,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091366</v>
+        <v>126091433</v>
       </c>
       <c r="B128" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556348</v>
+        <v>556280</v>
       </c>
       <c r="R128" t="n">
-        <v>7226965</v>
+        <v>7226845</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13597,10 +13597,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091363</v>
+        <v>126091366</v>
       </c>
       <c r="B129" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13632,10 +13632,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556361</v>
+        <v>556348</v>
       </c>
       <c r="R129" t="n">
-        <v>7226943</v>
+        <v>7226965</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13668,11 +13668,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13703,10 +13698,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126091085</v>
+        <v>126091363</v>
       </c>
       <c r="B130" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13738,10 +13733,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>556709</v>
+        <v>556361</v>
       </c>
       <c r="R130" t="n">
-        <v>7227134</v>
+        <v>7226943</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13768,12 +13763,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13804,10 +13804,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126091338</v>
+        <v>126091085</v>
       </c>
       <c r="B131" t="n">
-        <v>91232</v>
+        <v>80077</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13815,21 +13815,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>556326</v>
+        <v>556709</v>
       </c>
       <c r="R131" t="n">
-        <v>7227114</v>
+        <v>7227134</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13905,10 +13905,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091071</v>
+        <v>126091338</v>
       </c>
       <c r="B132" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13916,21 +13916,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556807</v>
+        <v>556326</v>
       </c>
       <c r="R132" t="n">
-        <v>7227608</v>
+        <v>7227114</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14006,10 +14006,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091367</v>
+        <v>126091071</v>
       </c>
       <c r="B133" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556347</v>
+        <v>556807</v>
       </c>
       <c r="R133" t="n">
-        <v>7226967</v>
+        <v>7227608</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14071,12 +14071,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14107,10 +14107,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091385</v>
+        <v>126091367</v>
       </c>
       <c r="B134" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556410</v>
+        <v>556347</v>
       </c>
       <c r="R134" t="n">
-        <v>7226996</v>
+        <v>7226967</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14208,32 +14208,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091433</v>
+        <v>126091385</v>
       </c>
       <c r="B135" t="n">
-        <v>80110</v>
+        <v>80077</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14243,10 +14243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556280</v>
+        <v>556410</v>
       </c>
       <c r="R135" t="n">
-        <v>7226845</v>
+        <v>7226996</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091415</v>
+        <v>126091431</v>
       </c>
       <c r="B136" t="n">
-        <v>91250</v>
+        <v>80111</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556315</v>
+        <v>556179</v>
       </c>
       <c r="R136" t="n">
-        <v>7226927</v>
+        <v>7226822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14410,32 +14410,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091127</v>
+        <v>126091429</v>
       </c>
       <c r="B137" t="n">
-        <v>91250</v>
+        <v>80111</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556728</v>
+        <v>556272</v>
       </c>
       <c r="R137" t="n">
-        <v>7227249</v>
+        <v>7227058</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14475,12 +14475,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14511,27 +14511,27 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091140</v>
+        <v>126091443</v>
       </c>
       <c r="B138" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14546,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>557026</v>
+        <v>556529</v>
       </c>
       <c r="R138" t="n">
-        <v>7227519</v>
+        <v>7226958</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14576,17 +14576,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14617,10 +14612,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091431</v>
+        <v>126091437</v>
       </c>
       <c r="B139" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14652,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556179</v>
+        <v>556361</v>
       </c>
       <c r="R139" t="n">
-        <v>7226822</v>
+        <v>7227004</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14718,10 +14713,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091429</v>
+        <v>126091432</v>
       </c>
       <c r="B140" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14753,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556272</v>
+        <v>556230</v>
       </c>
       <c r="R140" t="n">
-        <v>7227058</v>
+        <v>7226809</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14819,10 +14814,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091443</v>
+        <v>126091105</v>
       </c>
       <c r="B141" t="n">
-        <v>80110</v>
+        <v>80112</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14830,21 +14825,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14854,10 +14849,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556529</v>
+        <v>556807</v>
       </c>
       <c r="R141" t="n">
-        <v>7226958</v>
+        <v>7227608</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14884,12 +14879,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14920,32 +14915,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091437</v>
+        <v>126091029</v>
       </c>
       <c r="B142" t="n">
-        <v>80110</v>
+        <v>57652</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14955,10 +14950,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556361</v>
+        <v>556819</v>
       </c>
       <c r="R142" t="n">
-        <v>7227004</v>
+        <v>7227694</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14985,12 +14980,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15021,32 +15021,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091432</v>
+        <v>126091413</v>
       </c>
       <c r="B143" t="n">
-        <v>80110</v>
+        <v>56835</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15056,10 +15056,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556230</v>
+        <v>556662</v>
       </c>
       <c r="R143" t="n">
-        <v>7226809</v>
+        <v>7227178</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15092,6 +15092,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15122,32 +15127,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091105</v>
+        <v>126091415</v>
       </c>
       <c r="B144" t="n">
-        <v>80111</v>
+        <v>91252</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15157,10 +15162,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556807</v>
+        <v>556315</v>
       </c>
       <c r="R144" t="n">
-        <v>7227608</v>
+        <v>7226927</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15187,12 +15192,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15223,10 +15228,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091413</v>
+        <v>126091127</v>
       </c>
       <c r="B145" t="n">
-        <v>56834</v>
+        <v>91252</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15234,21 +15239,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15258,10 +15263,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556662</v>
+        <v>556728</v>
       </c>
       <c r="R145" t="n">
-        <v>7227178</v>
+        <v>7227249</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15288,17 +15293,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15329,10 +15329,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091029</v>
+        <v>126091140</v>
       </c>
       <c r="B146" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,21 +15340,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556819</v>
+        <v>557026</v>
       </c>
       <c r="R146" t="n">
-        <v>7227694</v>
+        <v>7227519</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15438,7 +15438,7 @@
         <v>126091371</v>
       </c>
       <c r="B147" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>126091063</v>
       </c>
       <c r="B148" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>126091149</v>
       </c>
       <c r="B150" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15849,32 +15849,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091350</v>
+        <v>126091397</v>
       </c>
       <c r="B151" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15884,10 +15884,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556589</v>
+        <v>556378</v>
       </c>
       <c r="R151" t="n">
-        <v>7227059</v>
+        <v>7226996</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15920,11 +15920,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15955,32 +15950,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091040</v>
+        <v>126091404</v>
       </c>
       <c r="B152" t="n">
-        <v>57651</v>
+        <v>80112</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15990,10 +15985,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556781</v>
+        <v>556272</v>
       </c>
       <c r="R152" t="n">
-        <v>7227272</v>
+        <v>7227058</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16020,17 +16015,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16061,32 +16051,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091388</v>
+        <v>126091169</v>
       </c>
       <c r="B153" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16096,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556529</v>
+        <v>556756</v>
       </c>
       <c r="R153" t="n">
-        <v>7226958</v>
+        <v>7227253</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16126,12 +16116,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16162,10 +16152,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091378</v>
+        <v>126091350</v>
       </c>
       <c r="B154" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16173,21 +16163,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16197,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556353</v>
+        <v>556589</v>
       </c>
       <c r="R154" t="n">
-        <v>7227115</v>
+        <v>7227059</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16233,6 +16223,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16263,32 +16258,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091397</v>
+        <v>126091040</v>
       </c>
       <c r="B155" t="n">
-        <v>80103</v>
+        <v>57652</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16298,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556378</v>
+        <v>556781</v>
       </c>
       <c r="R155" t="n">
-        <v>7226996</v>
+        <v>7227272</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16328,12 +16323,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16364,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091388</v>
       </c>
       <c r="B156" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556529</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7226958</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16465,32 +16465,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091169</v>
+        <v>126091378</v>
       </c>
       <c r="B157" t="n">
-        <v>80110</v>
+        <v>80077</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556756</v>
+        <v>556353</v>
       </c>
       <c r="R157" t="n">
-        <v>7227253</v>
+        <v>7227115</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16569,7 +16569,7 @@
         <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091389</v>
+        <v>126091043</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556589</v>
+        <v>556756</v>
       </c>
       <c r="R11" t="n">
-        <v>7227109</v>
+        <v>7227253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091064</v>
+        <v>126091439</v>
       </c>
       <c r="B12" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556833</v>
+        <v>556374</v>
       </c>
       <c r="R12" t="n">
-        <v>7227720</v>
+        <v>7227007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091374</v>
+        <v>126091428</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556371</v>
+        <v>556314</v>
       </c>
       <c r="R13" t="n">
-        <v>7226988</v>
+        <v>7226891</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091365</v>
+        <v>126091389</v>
       </c>
       <c r="B14" t="n">
         <v>80077</v>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556359</v>
+        <v>556589</v>
       </c>
       <c r="R14" t="n">
-        <v>7226943</v>
+        <v>7227109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091420</v>
+        <v>126091064</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1999,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556284</v>
+        <v>556833</v>
       </c>
       <c r="R15" t="n">
-        <v>7227078</v>
+        <v>7227720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,17 +2053,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091147</v>
+        <v>126091374</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556819</v>
+        <v>556371</v>
       </c>
       <c r="R16" t="n">
-        <v>7227694</v>
+        <v>7226988</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,17 +2154,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,32 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091335</v>
+        <v>126091365</v>
       </c>
       <c r="B17" t="n">
-        <v>91199</v>
+        <v>80077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556339</v>
+        <v>556359</v>
       </c>
       <c r="R17" t="n">
-        <v>7226946</v>
+        <v>7226943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2291,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091425</v>
+        <v>126091420</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2336,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556591</v>
+        <v>556284</v>
       </c>
       <c r="R18" t="n">
-        <v>7227022</v>
+        <v>7227078</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,32 +2397,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091043</v>
+        <v>126091147</v>
       </c>
       <c r="B19" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556756</v>
+        <v>556819</v>
       </c>
       <c r="R19" t="n">
-        <v>7227253</v>
+        <v>7227694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,6 +2468,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091439</v>
+        <v>126091335</v>
       </c>
       <c r="B20" t="n">
-        <v>80111</v>
+        <v>91199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2519,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556374</v>
+        <v>556339</v>
       </c>
       <c r="R20" t="n">
-        <v>7227007</v>
+        <v>7226946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,27 +2604,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091428</v>
+        <v>126091425</v>
       </c>
       <c r="B21" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556314</v>
+        <v>556591</v>
       </c>
       <c r="R21" t="n">
-        <v>7226891</v>
+        <v>7227022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4235,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091349</v>
+        <v>126091414</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>91252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556613</v>
+        <v>556303</v>
       </c>
       <c r="R37" t="n">
-        <v>7227051</v>
+        <v>7226905</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4306,11 +4306,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,7 +4336,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091414</v>
+        <v>126091124</v>
       </c>
       <c r="B38" t="n">
         <v>91252</v>
@@ -4376,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556303</v>
+        <v>556698</v>
       </c>
       <c r="R38" t="n">
-        <v>7226905</v>
+        <v>7227248</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,12 +4401,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4442,32 +4437,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091124</v>
+        <v>126091042</v>
       </c>
       <c r="B39" t="n">
-        <v>91252</v>
+        <v>80105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556698</v>
+        <v>556817</v>
       </c>
       <c r="R39" t="n">
-        <v>7227248</v>
+        <v>7227591</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4543,10 +4538,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091042</v>
+        <v>126091406</v>
       </c>
       <c r="B40" t="n">
-        <v>80105</v>
+        <v>80112</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4554,21 +4549,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556817</v>
+        <v>556314</v>
       </c>
       <c r="R40" t="n">
-        <v>7227591</v>
+        <v>7226891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,12 +4603,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4644,32 +4639,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091406</v>
+        <v>126091349</v>
       </c>
       <c r="B41" t="n">
-        <v>80112</v>
+        <v>57652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556314</v>
+        <v>556613</v>
       </c>
       <c r="R41" t="n">
-        <v>7226891</v>
+        <v>7227051</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,6 +4710,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4745,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091348</v>
+        <v>126091044</v>
       </c>
       <c r="B42" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556351</v>
+        <v>556826</v>
       </c>
       <c r="R42" t="n">
-        <v>7226920</v>
+        <v>7227309</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,17 +4810,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4851,10 +4846,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091352</v>
+        <v>126091107</v>
       </c>
       <c r="B43" t="n">
-        <v>98362</v>
+        <v>80112</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4862,21 +4857,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556293</v>
+        <v>556723</v>
       </c>
       <c r="R43" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4916,12 +4911,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4952,10 +4947,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091403</v>
+        <v>126091348</v>
       </c>
       <c r="B44" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,21 +4958,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4987,10 +4982,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556357</v>
+        <v>556351</v>
       </c>
       <c r="R44" t="n">
-        <v>7227004</v>
+        <v>7226920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5023,6 +5018,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5053,32 +5053,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091144</v>
+        <v>126091352</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557048</v>
+        <v>556293</v>
       </c>
       <c r="R45" t="n">
-        <v>7227797</v>
+        <v>7227068</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091422</v>
+        <v>126091403</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556407</v>
+        <v>556357</v>
       </c>
       <c r="R46" t="n">
-        <v>7226992</v>
+        <v>7227004</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5225,11 +5225,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5260,7 +5255,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091145</v>
+        <v>126091144</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5295,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556897</v>
+        <v>557048</v>
       </c>
       <c r="R47" t="n">
-        <v>7227735</v>
+        <v>7227797</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,11 +5326,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5366,10 +5356,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091129</v>
+        <v>126091422</v>
       </c>
       <c r="B48" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,21 +5367,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5401,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556685</v>
+        <v>556407</v>
       </c>
       <c r="R48" t="n">
-        <v>7227107</v>
+        <v>7226992</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5431,12 +5421,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5467,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091075</v>
+        <v>126091145</v>
       </c>
       <c r="B49" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5478,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5502,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556792</v>
+        <v>556897</v>
       </c>
       <c r="R49" t="n">
-        <v>7227253</v>
+        <v>7227735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5538,6 +5533,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5568,32 +5568,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091044</v>
+        <v>126091129</v>
       </c>
       <c r="B50" t="n">
-        <v>80105</v>
+        <v>91252</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556826</v>
+        <v>556685</v>
       </c>
       <c r="R50" t="n">
-        <v>7227309</v>
+        <v>7227107</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5669,32 +5669,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091107</v>
+        <v>126091075</v>
       </c>
       <c r="B51" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556723</v>
+        <v>556792</v>
       </c>
       <c r="R51" t="n">
-        <v>7227276</v>
+        <v>7227253</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7911,32 +7911,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091015</v>
+        <v>126091393</v>
       </c>
       <c r="B73" t="n">
-        <v>91234</v>
+        <v>79980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556931</v>
+        <v>556291</v>
       </c>
       <c r="R73" t="n">
-        <v>7227622</v>
+        <v>7226913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,12 +7976,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091051</v>
+        <v>126091012</v>
       </c>
       <c r="B74" t="n">
-        <v>79942</v>
+        <v>91199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556679</v>
+        <v>556977</v>
       </c>
       <c r="R74" t="n">
-        <v>7227232</v>
+        <v>7227576</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091360</v>
+        <v>126091143</v>
       </c>
       <c r="B75" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556326</v>
+        <v>557106</v>
       </c>
       <c r="R75" t="n">
-        <v>7226893</v>
+        <v>7227606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8214,32 +8214,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091375</v>
+        <v>126091174</v>
       </c>
       <c r="B76" t="n">
-        <v>80077</v>
+        <v>91644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556423</v>
+        <v>556888</v>
       </c>
       <c r="R76" t="n">
-        <v>7226984</v>
+        <v>7227746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8315,10 +8315,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091067</v>
+        <v>126091402</v>
       </c>
       <c r="B77" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8326,21 +8326,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556690</v>
+        <v>556280</v>
       </c>
       <c r="R77" t="n">
-        <v>7227262</v>
+        <v>7227059</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,10 +8416,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091355</v>
+        <v>126091015</v>
       </c>
       <c r="B78" t="n">
-        <v>80077</v>
+        <v>91234</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556346</v>
+        <v>556931</v>
       </c>
       <c r="R78" t="n">
-        <v>7227118</v>
+        <v>7227622</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8481,12 +8481,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8517,10 +8517,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091346</v>
+        <v>126091051</v>
       </c>
       <c r="B79" t="n">
-        <v>57652</v>
+        <v>79942</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8528,21 +8528,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556194</v>
+        <v>556679</v>
       </c>
       <c r="R79" t="n">
-        <v>7226815</v>
+        <v>7227232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8582,17 +8582,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8623,32 +8618,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091393</v>
+        <v>126091360</v>
       </c>
       <c r="B80" t="n">
-        <v>79980</v>
+        <v>80077</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,10 +8653,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556291</v>
+        <v>556326</v>
       </c>
       <c r="R80" t="n">
-        <v>7226913</v>
+        <v>7226893</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8724,32 +8719,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091012</v>
+        <v>126091375</v>
       </c>
       <c r="B81" t="n">
-        <v>91199</v>
+        <v>80077</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556977</v>
+        <v>556423</v>
       </c>
       <c r="R81" t="n">
-        <v>7227576</v>
+        <v>7226984</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8789,12 +8784,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8825,10 +8820,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091143</v>
+        <v>126091067</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8831,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557106</v>
+        <v>556690</v>
       </c>
       <c r="R82" t="n">
-        <v>7227606</v>
+        <v>7227262</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8926,32 +8921,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091174</v>
+        <v>126091355</v>
       </c>
       <c r="B83" t="n">
-        <v>91644</v>
+        <v>80077</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8961,10 +8956,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556888</v>
+        <v>556346</v>
       </c>
       <c r="R83" t="n">
-        <v>7227746</v>
+        <v>7227118</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8991,12 +8986,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9027,10 +9022,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091402</v>
+        <v>126091346</v>
       </c>
       <c r="B84" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,21 +9033,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556280</v>
+        <v>556194</v>
       </c>
       <c r="R84" t="n">
-        <v>7227059</v>
+        <v>7226815</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9098,6 +9093,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11471,32 +11471,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091407</v>
+        <v>126091072</v>
       </c>
       <c r="B108" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556365</v>
+        <v>556913</v>
       </c>
       <c r="R108" t="n">
-        <v>7227004</v>
+        <v>7227621</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11572,7 +11572,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091072</v>
+        <v>126091380</v>
       </c>
       <c r="B109" t="n">
         <v>80077</v>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556913</v>
+        <v>556261</v>
       </c>
       <c r="R109" t="n">
-        <v>7227621</v>
+        <v>7227068</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11673,7 +11673,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091380</v>
+        <v>126091070</v>
       </c>
       <c r="B110" t="n">
         <v>80077</v>
@@ -11708,10 +11708,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556261</v>
+        <v>556723</v>
       </c>
       <c r="R110" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11738,12 +11738,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091070</v>
+        <v>126091341</v>
       </c>
       <c r="B111" t="n">
-        <v>80077</v>
+        <v>91234</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11785,21 +11785,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556723</v>
+        <v>556187</v>
       </c>
       <c r="R111" t="n">
-        <v>7227276</v>
+        <v>7226946</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11839,12 +11839,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11875,10 +11875,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091341</v>
+        <v>126091010</v>
       </c>
       <c r="B112" t="n">
-        <v>91234</v>
+        <v>79005</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556187</v>
+        <v>556904</v>
       </c>
       <c r="R112" t="n">
-        <v>7226946</v>
+        <v>7227703</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091010</v>
+        <v>126091115</v>
       </c>
       <c r="B113" t="n">
-        <v>79005</v>
+        <v>57756</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556904</v>
+        <v>556797</v>
       </c>
       <c r="R113" t="n">
-        <v>7227703</v>
+        <v>7227252</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12077,10 +12077,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091115</v>
+        <v>126091407</v>
       </c>
       <c r="B114" t="n">
-        <v>57756</v>
+        <v>80112</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556797</v>
+        <v>556365</v>
       </c>
       <c r="R114" t="n">
-        <v>7227252</v>
+        <v>7227004</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12142,12 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091440</v>
+        <v>126091408</v>
       </c>
       <c r="B2" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556465</v>
+        <v>556467</v>
       </c>
       <c r="R2" t="n">
-        <v>7226995</v>
+        <v>7226993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091408</v>
+        <v>126091440</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556467</v>
+        <v>556465</v>
       </c>
       <c r="R3" t="n">
-        <v>7226993</v>
+        <v>7226995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
         <v>126091342</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091395</v>
+        <v>126091128</v>
       </c>
       <c r="B8" t="n">
-        <v>91530</v>
+        <v>91254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556308</v>
+        <v>556830</v>
       </c>
       <c r="R8" t="n">
-        <v>7226876</v>
+        <v>7227331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091128</v>
+        <v>126091123</v>
       </c>
       <c r="B9" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556830</v>
+        <v>557106</v>
       </c>
       <c r="R9" t="n">
-        <v>7227331</v>
+        <v>7227606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091123</v>
+        <v>126091395</v>
       </c>
       <c r="B10" t="n">
-        <v>91252</v>
+        <v>91532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557106</v>
+        <v>556308</v>
       </c>
       <c r="R10" t="n">
-        <v>7227606</v>
+        <v>7226876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091043</v>
+        <v>126091335</v>
       </c>
       <c r="B11" t="n">
-        <v>80105</v>
+        <v>91201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556756</v>
+        <v>556339</v>
       </c>
       <c r="R11" t="n">
-        <v>7227253</v>
+        <v>7226946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,27 +1685,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091439</v>
+        <v>126091425</v>
       </c>
       <c r="B12" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556374</v>
+        <v>556591</v>
       </c>
       <c r="R12" t="n">
-        <v>7227007</v>
+        <v>7227022</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091389</v>
+        <v>126091420</v>
       </c>
       <c r="B14" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1922,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556589</v>
+        <v>556284</v>
       </c>
       <c r="R14" t="n">
-        <v>7227109</v>
+        <v>7227078</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,6 +1963,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1988,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091064</v>
+        <v>126091043</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2023,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556833</v>
+        <v>556756</v>
       </c>
       <c r="R15" t="n">
-        <v>7227720</v>
+        <v>7227253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091374</v>
+        <v>126091439</v>
       </c>
       <c r="B16" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556371</v>
+        <v>556374</v>
       </c>
       <c r="R16" t="n">
-        <v>7226988</v>
+        <v>7227007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091365</v>
+        <v>126091147</v>
       </c>
       <c r="B17" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556359</v>
+        <v>556819</v>
       </c>
       <c r="R17" t="n">
-        <v>7226943</v>
+        <v>7227694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,12 +2265,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2291,10 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091420</v>
+        <v>126091389</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2317,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2326,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556284</v>
+        <v>556589</v>
       </c>
       <c r="R18" t="n">
-        <v>7227078</v>
+        <v>7227109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,11 +2377,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,10 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091147</v>
+        <v>126091064</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2418,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556819</v>
+        <v>556833</v>
       </c>
       <c r="R19" t="n">
-        <v>7227694</v>
+        <v>7227720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,11 +2478,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091335</v>
+        <v>126091374</v>
       </c>
       <c r="B20" t="n">
-        <v>91199</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556339</v>
+        <v>556371</v>
       </c>
       <c r="R20" t="n">
-        <v>7226946</v>
+        <v>7226988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091425</v>
+        <v>126091365</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556591</v>
+        <v>556359</v>
       </c>
       <c r="R21" t="n">
-        <v>7227022</v>
+        <v>7226943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,11 +2680,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R22" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B23" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R23" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091073</v>
+        <v>126091340</v>
       </c>
       <c r="B27" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556756</v>
+        <v>556312</v>
       </c>
       <c r="R27" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091164</v>
+        <v>126091073</v>
       </c>
       <c r="B28" t="n">
-        <v>88643</v>
+        <v>80077</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556775</v>
+        <v>556756</v>
       </c>
       <c r="R28" t="n">
         <v>7227253</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091340</v>
+        <v>126091164</v>
       </c>
       <c r="B29" t="n">
-        <v>91234</v>
+        <v>88645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556312</v>
+        <v>556775</v>
       </c>
       <c r="R29" t="n">
-        <v>7227107</v>
+        <v>7227253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091356</v>
+        <v>126091042</v>
       </c>
       <c r="B33" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556271</v>
+        <v>556817</v>
       </c>
       <c r="R33" t="n">
-        <v>7227059</v>
+        <v>7227591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,32 +3932,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091448</v>
+        <v>126091406</v>
       </c>
       <c r="B34" t="n">
-        <v>91904</v>
+        <v>80112</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>898</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556484</v>
+        <v>556314</v>
       </c>
       <c r="R34" t="n">
-        <v>7226980</v>
+        <v>7226891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091369</v>
+        <v>126091356</v>
       </c>
       <c r="B35" t="n">
         <v>80077</v>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556333</v>
+        <v>556271</v>
       </c>
       <c r="R35" t="n">
-        <v>7227009</v>
+        <v>7227059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4134,32 +4134,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091013</v>
+        <v>126091448</v>
       </c>
       <c r="B36" t="n">
-        <v>91234</v>
+        <v>91906</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556830</v>
+        <v>556484</v>
       </c>
       <c r="R36" t="n">
-        <v>7227704</v>
+        <v>7226980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4238,7 +4238,7 @@
         <v>126091414</v>
       </c>
       <c r="B37" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091124</v>
+        <v>126091369</v>
       </c>
       <c r="B38" t="n">
-        <v>91252</v>
+        <v>80077</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,21 +4347,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556698</v>
+        <v>556333</v>
       </c>
       <c r="R38" t="n">
-        <v>7227248</v>
+        <v>7227009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4437,32 +4437,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091042</v>
+        <v>126091124</v>
       </c>
       <c r="B39" t="n">
-        <v>80105</v>
+        <v>91254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556817</v>
+        <v>556698</v>
       </c>
       <c r="R39" t="n">
-        <v>7227591</v>
+        <v>7227248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4538,32 +4538,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091406</v>
+        <v>126091013</v>
       </c>
       <c r="B40" t="n">
-        <v>80112</v>
+        <v>91236</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556314</v>
+        <v>556830</v>
       </c>
       <c r="R40" t="n">
-        <v>7226891</v>
+        <v>7227704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4745,32 +4745,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091044</v>
+        <v>126091403</v>
       </c>
       <c r="B42" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556826</v>
+        <v>556357</v>
       </c>
       <c r="R42" t="n">
-        <v>7227309</v>
+        <v>7227004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,32 +4846,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091107</v>
+        <v>126091145</v>
       </c>
       <c r="B43" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556723</v>
+        <v>556897</v>
       </c>
       <c r="R43" t="n">
-        <v>7227276</v>
+        <v>7227735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,6 +4917,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,32 +4952,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091348</v>
+        <v>126091107</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556351</v>
+        <v>556723</v>
       </c>
       <c r="R44" t="n">
-        <v>7226920</v>
+        <v>7227276</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,17 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091352</v>
+        <v>126091044</v>
       </c>
       <c r="B45" t="n">
-        <v>98362</v>
+        <v>80105</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556293</v>
+        <v>556826</v>
       </c>
       <c r="R45" t="n">
-        <v>7227068</v>
+        <v>7227309</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091403</v>
+        <v>126091144</v>
       </c>
       <c r="B46" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556357</v>
+        <v>557048</v>
       </c>
       <c r="R46" t="n">
-        <v>7227004</v>
+        <v>7227797</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,7 +5255,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R47" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,12 +5320,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5356,10 +5361,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091422</v>
+        <v>126091075</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5367,21 +5372,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556407</v>
+        <v>556792</v>
       </c>
       <c r="R48" t="n">
-        <v>7226992</v>
+        <v>7227253</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5421,17 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091145</v>
+        <v>126091129</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556897</v>
+        <v>556685</v>
       </c>
       <c r="R49" t="n">
-        <v>7227735</v>
+        <v>7227107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,17 +5527,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5568,10 +5563,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091129</v>
+        <v>126091348</v>
       </c>
       <c r="B50" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,21 +5574,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5603,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556685</v>
+        <v>556351</v>
       </c>
       <c r="R50" t="n">
-        <v>7227107</v>
+        <v>7226920</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,12 +5628,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5669,32 +5669,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091075</v>
+        <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>80077</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556792</v>
+        <v>556293</v>
       </c>
       <c r="R51" t="n">
-        <v>7227253</v>
+        <v>7227068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,27 +5770,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091148</v>
+        <v>126091438</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556787</v>
+        <v>556350</v>
       </c>
       <c r="R52" t="n">
-        <v>7227605</v>
+        <v>7226997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5835,17 +5835,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5876,32 +5871,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091401</v>
+        <v>126091430</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5911,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556271</v>
+        <v>556140</v>
       </c>
       <c r="R53" t="n">
-        <v>7227059</v>
+        <v>7226895</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5977,32 +5972,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091430</v>
+        <v>126091401</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556140</v>
+        <v>556271</v>
       </c>
       <c r="R54" t="n">
-        <v>7226895</v>
+        <v>7227059</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,27 +6073,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091438</v>
+        <v>126091148</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6113,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556350</v>
+        <v>556787</v>
       </c>
       <c r="R55" t="n">
-        <v>7226997</v>
+        <v>7227605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6143,12 +6138,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6283,7 +6283,7 @@
         <v>126091095</v>
       </c>
       <c r="B57" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>126091343</v>
       </c>
       <c r="B58" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091386</v>
+        <v>126091417</v>
       </c>
       <c r="B62" t="n">
-        <v>80077</v>
+        <v>91254</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6796,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556480</v>
+        <v>556559</v>
       </c>
       <c r="R62" t="n">
-        <v>7226980</v>
+        <v>7226989</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6886,7 +6886,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091066</v>
+        <v>126091386</v>
       </c>
       <c r="B63" t="n">
         <v>80077</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556946</v>
+        <v>556480</v>
       </c>
       <c r="R63" t="n">
-        <v>7227602</v>
+        <v>7226980</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,17 +6951,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6992,10 +6987,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091400</v>
+        <v>126091066</v>
       </c>
       <c r="B64" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,21 +6998,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7027,10 +7022,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556261</v>
+        <v>556946</v>
       </c>
       <c r="R64" t="n">
-        <v>7227068</v>
+        <v>7227602</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,12 +7052,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7093,27 +7093,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091151</v>
+        <v>126091442</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556935</v>
+        <v>556494</v>
       </c>
       <c r="R65" t="n">
-        <v>7227614</v>
+        <v>7226972</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7158,17 +7158,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7199,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091417</v>
+        <v>126091400</v>
       </c>
       <c r="B66" t="n">
-        <v>91252</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7210,21 +7205,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7234,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556559</v>
+        <v>556261</v>
       </c>
       <c r="R66" t="n">
-        <v>7226989</v>
+        <v>7227068</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7401,27 +7396,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091442</v>
+        <v>126091151</v>
       </c>
       <c r="B68" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556494</v>
+        <v>556935</v>
       </c>
       <c r="R68" t="n">
-        <v>7226972</v>
+        <v>7227614</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7466,12 +7461,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,10 +7502,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091345</v>
+        <v>126091384</v>
       </c>
       <c r="B69" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7513,21 +7513,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556499</v>
+        <v>556376</v>
       </c>
       <c r="R69" t="n">
-        <v>7227184</v>
+        <v>7227009</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,11 +7573,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7608,10 +7603,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091337</v>
+        <v>126091090</v>
       </c>
       <c r="B70" t="n">
-        <v>91199</v>
+        <v>79980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7619,21 +7614,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7643,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556374</v>
+        <v>556690</v>
       </c>
       <c r="R70" t="n">
-        <v>7226996</v>
+        <v>7227262</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7673,12 +7668,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7709,10 +7704,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091090</v>
+        <v>126091337</v>
       </c>
       <c r="B71" t="n">
-        <v>79980</v>
+        <v>91201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7720,21 +7715,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7744,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556690</v>
+        <v>556374</v>
       </c>
       <c r="R71" t="n">
-        <v>7227262</v>
+        <v>7226996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7774,12 +7769,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7810,10 +7805,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091384</v>
+        <v>126091345</v>
       </c>
       <c r="B72" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7821,21 +7816,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7845,10 +7840,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556376</v>
+        <v>556499</v>
       </c>
       <c r="R72" t="n">
-        <v>7227009</v>
+        <v>7227184</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7881,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091012</v>
+        <v>126091402</v>
       </c>
       <c r="B74" t="n">
-        <v>91199</v>
+        <v>80076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556977</v>
+        <v>556280</v>
       </c>
       <c r="R74" t="n">
-        <v>7227576</v>
+        <v>7227059</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091143</v>
+        <v>126091346</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557106</v>
+        <v>556194</v>
       </c>
       <c r="R75" t="n">
-        <v>7227606</v>
+        <v>7226815</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,12 +8178,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8214,10 +8219,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091174</v>
+        <v>126091012</v>
       </c>
       <c r="B76" t="n">
-        <v>91644</v>
+        <v>91201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8225,21 +8230,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556888</v>
+        <v>556977</v>
       </c>
       <c r="R76" t="n">
-        <v>7227746</v>
+        <v>7227576</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8315,10 +8320,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091402</v>
+        <v>126091143</v>
       </c>
       <c r="B77" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8326,21 +8331,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556280</v>
+        <v>557106</v>
       </c>
       <c r="R77" t="n">
-        <v>7227059</v>
+        <v>7227606</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,12 +8385,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,10 +8421,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091015</v>
+        <v>126091051</v>
       </c>
       <c r="B78" t="n">
-        <v>91234</v>
+        <v>79942</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,21 +8432,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556931</v>
+        <v>556679</v>
       </c>
       <c r="R78" t="n">
-        <v>7227622</v>
+        <v>7227232</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8517,10 +8522,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091051</v>
+        <v>126091015</v>
       </c>
       <c r="B79" t="n">
-        <v>79942</v>
+        <v>91236</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8528,21 +8533,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8552,10 +8557,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556679</v>
+        <v>556931</v>
       </c>
       <c r="R79" t="n">
-        <v>7227232</v>
+        <v>7227622</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8618,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091360</v>
+        <v>126091174</v>
       </c>
       <c r="B80" t="n">
-        <v>80077</v>
+        <v>91646</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8653,10 +8658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556326</v>
+        <v>556888</v>
       </c>
       <c r="R80" t="n">
-        <v>7226893</v>
+        <v>7227746</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8683,12 +8688,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8719,7 +8724,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091375</v>
+        <v>126091360</v>
       </c>
       <c r="B81" t="n">
         <v>80077</v>
@@ -8754,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556423</v>
+        <v>556326</v>
       </c>
       <c r="R81" t="n">
-        <v>7226984</v>
+        <v>7226893</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8820,7 +8825,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091067</v>
+        <v>126091375</v>
       </c>
       <c r="B82" t="n">
         <v>80077</v>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556690</v>
+        <v>556423</v>
       </c>
       <c r="R82" t="n">
-        <v>7227262</v>
+        <v>7226984</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8885,12 +8890,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8921,7 +8926,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091355</v>
+        <v>126091067</v>
       </c>
       <c r="B83" t="n">
         <v>80077</v>
@@ -8956,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556346</v>
+        <v>556690</v>
       </c>
       <c r="R83" t="n">
-        <v>7227118</v>
+        <v>7227262</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8986,12 +8991,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091346</v>
+        <v>126091355</v>
       </c>
       <c r="B84" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9033,21 +9038,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9057,10 +9062,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556194</v>
+        <v>556346</v>
       </c>
       <c r="R84" t="n">
-        <v>7226815</v>
+        <v>7227118</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9093,11 +9098,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,27 +9128,27 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091153</v>
+        <v>126091165</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556996</v>
+        <v>556874</v>
       </c>
       <c r="R85" t="n">
-        <v>7227559</v>
+        <v>7227697</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091166</v>
+        <v>126091351</v>
       </c>
       <c r="B87" t="n">
-        <v>80111</v>
+        <v>80105</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9346,21 +9346,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556690</v>
+        <v>556346</v>
       </c>
       <c r="R87" t="n">
-        <v>7227262</v>
+        <v>7227118</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9436,7 +9436,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091165</v>
+        <v>126091166</v>
       </c>
       <c r="B88" t="n">
         <v>80111</v>
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556874</v>
+        <v>556690</v>
       </c>
       <c r="R88" t="n">
-        <v>7227697</v>
+        <v>7227262</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9537,32 +9537,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091351</v>
+        <v>126091383</v>
       </c>
       <c r="B89" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9572,10 +9572,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556346</v>
+        <v>556230</v>
       </c>
       <c r="R89" t="n">
-        <v>7227118</v>
+        <v>7226809</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9638,7 +9638,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091383</v>
+        <v>126091377</v>
       </c>
       <c r="B90" t="n">
         <v>80077</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556230</v>
+        <v>556584</v>
       </c>
       <c r="R90" t="n">
-        <v>7226809</v>
+        <v>7227068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9739,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091377</v>
+        <v>126091344</v>
       </c>
       <c r="B91" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556584</v>
+        <v>556452</v>
       </c>
       <c r="R91" t="n">
-        <v>7227068</v>
+        <v>7226989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091344</v>
+        <v>126091372</v>
       </c>
       <c r="B92" t="n">
-        <v>91234</v>
+        <v>80077</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9851,21 +9851,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556452</v>
+        <v>556359</v>
       </c>
       <c r="R92" t="n">
-        <v>7226989</v>
+        <v>7226988</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091372</v>
+        <v>126091153</v>
       </c>
       <c r="B93" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9952,21 +9952,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556359</v>
+        <v>556996</v>
       </c>
       <c r="R93" t="n">
-        <v>7226988</v>
+        <v>7227559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,12 +10006,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10148,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091418</v>
+        <v>126091167</v>
       </c>
       <c r="B95" t="n">
-        <v>91252</v>
+        <v>80111</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556550</v>
+        <v>556728</v>
       </c>
       <c r="R95" t="n">
-        <v>7227005</v>
+        <v>7227275</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10213,12 +10213,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10249,32 +10249,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091125</v>
+        <v>126091405</v>
       </c>
       <c r="B96" t="n">
-        <v>91252</v>
+        <v>80112</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556893</v>
+        <v>556230</v>
       </c>
       <c r="R96" t="n">
-        <v>7227703</v>
+        <v>7226809</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10451,32 +10451,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091167</v>
+        <v>126091418</v>
       </c>
       <c r="B98" t="n">
-        <v>80111</v>
+        <v>91254</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556728</v>
+        <v>556550</v>
       </c>
       <c r="R98" t="n">
-        <v>7227275</v>
+        <v>7227005</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10552,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091405</v>
+        <v>126091357</v>
       </c>
       <c r="B99" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556230</v>
+        <v>556061</v>
       </c>
       <c r="R99" t="n">
-        <v>7226809</v>
+        <v>7226781</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091357</v>
+        <v>126091339</v>
       </c>
       <c r="B100" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556061</v>
+        <v>556393</v>
       </c>
       <c r="R100" t="n">
-        <v>7226781</v>
+        <v>7226994</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091339</v>
+        <v>126091125</v>
       </c>
       <c r="B101" t="n">
-        <v>91234</v>
+        <v>91254</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,21 +10765,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556393</v>
+        <v>556893</v>
       </c>
       <c r="R101" t="n">
-        <v>7226994</v>
+        <v>7227703</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091019</v>
+        <v>126091028</v>
       </c>
       <c r="B102" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557005</v>
+        <v>557117</v>
       </c>
       <c r="R102" t="n">
-        <v>7227490</v>
+        <v>7227635</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10926,6 +10926,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10956,10 +10961,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091358</v>
+        <v>126091019</v>
       </c>
       <c r="B103" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10967,21 +10972,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10991,10 +10996,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>556070</v>
+        <v>557005</v>
       </c>
       <c r="R103" t="n">
-        <v>7226750</v>
+        <v>7227490</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11021,12 +11026,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11057,10 +11062,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091028</v>
+        <v>126091358</v>
       </c>
       <c r="B104" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11068,21 +11073,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11092,10 +11097,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>557117</v>
+        <v>556070</v>
       </c>
       <c r="R104" t="n">
-        <v>7227635</v>
+        <v>7226750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11122,17 +11127,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11264,10 +11264,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091416</v>
+        <v>126091421</v>
       </c>
       <c r="B106" t="n">
-        <v>91252</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11275,21 +11275,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556600</v>
+        <v>556111</v>
       </c>
       <c r="R106" t="n">
-        <v>7227123</v>
+        <v>7226873</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11335,6 +11335,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11365,10 +11370,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091421</v>
+        <v>126091010</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11376,21 +11381,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11405,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556111</v>
+        <v>556904</v>
       </c>
       <c r="R107" t="n">
-        <v>7226873</v>
+        <v>7227703</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,17 +11435,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11777,7 +11777,7 @@
         <v>126091341</v>
       </c>
       <c r="B111" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11875,10 +11875,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091010</v>
+        <v>126091416</v>
       </c>
       <c r="B112" t="n">
-        <v>79005</v>
+        <v>91254</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556904</v>
+        <v>556600</v>
       </c>
       <c r="R112" t="n">
-        <v>7227703</v>
+        <v>7227123</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B115" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R115" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091084</v>
+        <v>126091068</v>
       </c>
       <c r="B116" t="n">
         <v>80077</v>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556737</v>
+        <v>556707</v>
       </c>
       <c r="R116" t="n">
-        <v>7227192</v>
+        <v>7227243</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12344,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091068</v>
+        <v>126091017</v>
       </c>
       <c r="B117" t="n">
-        <v>80077</v>
+        <v>91236</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556707</v>
+        <v>556929</v>
       </c>
       <c r="R117" t="n">
-        <v>7227243</v>
+        <v>7227610</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091017</v>
+        <v>126091121</v>
       </c>
       <c r="B118" t="n">
-        <v>91234</v>
+        <v>91232</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556929</v>
+        <v>556907</v>
       </c>
       <c r="R118" t="n">
-        <v>7227610</v>
+        <v>7227720</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091121</v>
+        <v>126091102</v>
       </c>
       <c r="B119" t="n">
-        <v>91230</v>
+        <v>80076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556907</v>
+        <v>556740</v>
       </c>
       <c r="R119" t="n">
-        <v>7227720</v>
+        <v>7227186</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12789,32 +12789,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091445</v>
+        <v>126091387</v>
       </c>
       <c r="B121" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12824,10 +12824,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556584</v>
+        <v>556497</v>
       </c>
       <c r="R121" t="n">
-        <v>7227109</v>
+        <v>7226978</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,32 +12890,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091444</v>
+        <v>126091379</v>
       </c>
       <c r="B122" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556584</v>
+        <v>556305</v>
       </c>
       <c r="R122" t="n">
-        <v>7227068</v>
+        <v>7227093</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12991,32 +12991,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091410</v>
+        <v>126091394</v>
       </c>
       <c r="B123" t="n">
-        <v>80112</v>
+        <v>91532</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13026,10 +13026,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R123" t="n">
-        <v>7227068</v>
+        <v>7226757</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091052</v>
+        <v>126091410</v>
       </c>
       <c r="B124" t="n">
-        <v>98362</v>
+        <v>80112</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>557007</v>
+        <v>556584</v>
       </c>
       <c r="R124" t="n">
-        <v>7227805</v>
+        <v>7227068</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13157,12 +13157,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091387</v>
+        <v>126091444</v>
       </c>
       <c r="B125" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R125" t="n">
-        <v>7226978</v>
+        <v>7227068</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13294,32 +13294,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091379</v>
+        <v>126091445</v>
       </c>
       <c r="B126" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R126" t="n">
-        <v>7227093</v>
+        <v>7227109</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13395,32 +13395,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091394</v>
+        <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>91530</v>
+        <v>98364</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13430,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556098</v>
+        <v>557007</v>
       </c>
       <c r="R127" t="n">
-        <v>7226757</v>
+        <v>7227805</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,12 +13460,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13908,7 +13908,7 @@
         <v>126091338</v>
       </c>
       <c r="B132" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091431</v>
+        <v>126091029</v>
       </c>
       <c r="B136" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556179</v>
+        <v>556819</v>
       </c>
       <c r="R136" t="n">
-        <v>7226822</v>
+        <v>7227694</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,12 +14374,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091429</v>
+        <v>126091105</v>
       </c>
       <c r="B137" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556272</v>
+        <v>556807</v>
       </c>
       <c r="R137" t="n">
-        <v>7227058</v>
+        <v>7227608</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14475,12 +14480,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14511,7 +14516,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091443</v>
+        <v>126091429</v>
       </c>
       <c r="B138" t="n">
         <v>80111</v>
@@ -14546,10 +14551,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556529</v>
+        <v>556272</v>
       </c>
       <c r="R138" t="n">
-        <v>7226958</v>
+        <v>7227058</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,7 +14617,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091437</v>
+        <v>126091443</v>
       </c>
       <c r="B139" t="n">
         <v>80111</v>
@@ -14647,10 +14652,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556361</v>
+        <v>556529</v>
       </c>
       <c r="R139" t="n">
-        <v>7227004</v>
+        <v>7226958</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14713,7 +14718,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091432</v>
+        <v>126091431</v>
       </c>
       <c r="B140" t="n">
         <v>80111</v>
@@ -14748,10 +14753,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556230</v>
+        <v>556179</v>
       </c>
       <c r="R140" t="n">
-        <v>7226809</v>
+        <v>7226822</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14814,32 +14819,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091105</v>
+        <v>126091140</v>
       </c>
       <c r="B141" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14849,10 +14854,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556807</v>
+        <v>557026</v>
       </c>
       <c r="R141" t="n">
-        <v>7227608</v>
+        <v>7227519</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14885,6 +14890,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14915,32 +14925,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091029</v>
+        <v>126091432</v>
       </c>
       <c r="B142" t="n">
-        <v>57652</v>
+        <v>80111</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14950,10 +14960,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556819</v>
+        <v>556230</v>
       </c>
       <c r="R142" t="n">
-        <v>7227694</v>
+        <v>7226809</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14980,17 +14990,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15021,32 +15026,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091413</v>
+        <v>126091437</v>
       </c>
       <c r="B143" t="n">
-        <v>56835</v>
+        <v>80111</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15056,10 +15061,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556662</v>
+        <v>556361</v>
       </c>
       <c r="R143" t="n">
-        <v>7227178</v>
+        <v>7227004</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15092,11 +15097,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15130,7 +15130,7 @@
         <v>126091415</v>
       </c>
       <c r="B144" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>126091127</v>
       </c>
       <c r="B145" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15329,10 +15329,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091140</v>
+        <v>126091371</v>
       </c>
       <c r="B146" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,21 +15340,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>557026</v>
+        <v>556365</v>
       </c>
       <c r="R146" t="n">
-        <v>7227519</v>
+        <v>7227004</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15394,17 +15394,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15435,7 +15430,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091371</v>
+        <v>126091063</v>
       </c>
       <c r="B147" t="n">
         <v>80077</v>
@@ -15470,10 +15465,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556365</v>
+        <v>556836</v>
       </c>
       <c r="R147" t="n">
-        <v>7227004</v>
+        <v>7227732</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15500,12 +15495,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15536,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091063</v>
+        <v>126091413</v>
       </c>
       <c r="B148" t="n">
-        <v>80077</v>
+        <v>56835</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15547,21 +15542,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15571,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556836</v>
+        <v>556662</v>
       </c>
       <c r="R148" t="n">
-        <v>7227732</v>
+        <v>7227178</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15601,12 +15596,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15849,32 +15849,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091397</v>
+        <v>126091388</v>
       </c>
       <c r="B151" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15884,10 +15884,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556378</v>
+        <v>556529</v>
       </c>
       <c r="R151" t="n">
-        <v>7226996</v>
+        <v>7226958</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15950,32 +15950,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091404</v>
+        <v>126091378</v>
       </c>
       <c r="B152" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15985,10 +15985,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556272</v>
+        <v>556353</v>
       </c>
       <c r="R152" t="n">
-        <v>7227058</v>
+        <v>7227115</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16051,32 +16051,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091169</v>
+        <v>126091350</v>
       </c>
       <c r="B153" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556756</v>
+        <v>556589</v>
       </c>
       <c r="R153" t="n">
-        <v>7227253</v>
+        <v>7227059</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16116,12 +16116,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,7 +16157,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091350</v>
+        <v>126091040</v>
       </c>
       <c r="B154" t="n">
         <v>57652</v>
@@ -16187,10 +16192,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556589</v>
+        <v>556781</v>
       </c>
       <c r="R154" t="n">
-        <v>7227059</v>
+        <v>7227272</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16217,17 +16222,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16258,32 +16263,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091040</v>
+        <v>126091169</v>
       </c>
       <c r="B155" t="n">
-        <v>57652</v>
+        <v>80111</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16293,10 +16298,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556781</v>
+        <v>556756</v>
       </c>
       <c r="R155" t="n">
-        <v>7227272</v>
+        <v>7227253</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16329,11 +16334,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16364,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091388</v>
+        <v>126091404</v>
       </c>
       <c r="B156" t="n">
-        <v>80077</v>
+        <v>80112</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556529</v>
+        <v>556272</v>
       </c>
       <c r="R156" t="n">
-        <v>7226958</v>
+        <v>7227058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16465,32 +16465,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091378</v>
+        <v>126091397</v>
       </c>
       <c r="B157" t="n">
-        <v>80077</v>
+        <v>80104</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556353</v>
+        <v>556378</v>
       </c>
       <c r="R157" t="n">
-        <v>7227115</v>
+        <v>7226996</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16569,7 +16569,7 @@
         <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091335</v>
+        <v>126091147</v>
       </c>
       <c r="B11" t="n">
-        <v>91201</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556339</v>
+        <v>556819</v>
       </c>
       <c r="R11" t="n">
-        <v>7226946</v>
+        <v>7227694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091425</v>
+        <v>126091335</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>91201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556591</v>
+        <v>556339</v>
       </c>
       <c r="R12" t="n">
-        <v>7227022</v>
+        <v>7226946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1761,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,27 +1791,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091428</v>
+        <v>126091425</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556314</v>
+        <v>556591</v>
       </c>
       <c r="R13" t="n">
-        <v>7226891</v>
+        <v>7227022</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091420</v>
+        <v>126091389</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556284</v>
+        <v>556589</v>
       </c>
       <c r="R14" t="n">
-        <v>7227078</v>
+        <v>7227109</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,32 +1998,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091043</v>
+        <v>126091064</v>
       </c>
       <c r="B15" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556756</v>
+        <v>556833</v>
       </c>
       <c r="R15" t="n">
-        <v>7227253</v>
+        <v>7227720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091439</v>
+        <v>126091374</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556374</v>
+        <v>556371</v>
       </c>
       <c r="R16" t="n">
-        <v>7227007</v>
+        <v>7226988</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091147</v>
+        <v>126091365</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556819</v>
+        <v>556359</v>
       </c>
       <c r="R17" t="n">
-        <v>7227694</v>
+        <v>7226943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,17 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091389</v>
+        <v>126091428</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2341,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556589</v>
+        <v>556314</v>
       </c>
       <c r="R18" t="n">
-        <v>7227109</v>
+        <v>7226891</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091064</v>
+        <v>126091420</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556833</v>
+        <v>556284</v>
       </c>
       <c r="R19" t="n">
-        <v>7227720</v>
+        <v>7227078</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,12 +2467,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091374</v>
+        <v>126091043</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556371</v>
+        <v>556756</v>
       </c>
       <c r="R20" t="n">
-        <v>7226988</v>
+        <v>7227253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091365</v>
+        <v>126091439</v>
       </c>
       <c r="B21" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556359</v>
+        <v>556374</v>
       </c>
       <c r="R21" t="n">
-        <v>7226943</v>
+        <v>7227007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B22" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R22" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R23" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091148</v>
+        <v>126091381</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,21 +6084,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556787</v>
+        <v>556280</v>
       </c>
       <c r="R55" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,17 +6138,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6179,10 +6174,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091381</v>
+        <v>126091148</v>
       </c>
       <c r="B56" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6190,21 +6185,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6214,10 +6209,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556280</v>
+        <v>556787</v>
       </c>
       <c r="R56" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,12 +6239,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091421</v>
+        <v>126091407</v>
       </c>
       <c r="B106" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556111</v>
+        <v>556365</v>
       </c>
       <c r="R106" t="n">
-        <v>7226873</v>
+        <v>7227004</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11335,11 +11335,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11370,10 +11365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091010</v>
+        <v>126091421</v>
       </c>
       <c r="B107" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11381,21 +11376,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11405,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556904</v>
+        <v>556111</v>
       </c>
       <c r="R107" t="n">
-        <v>7227703</v>
+        <v>7226873</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11435,12 +11430,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11471,10 +11471,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091072</v>
+        <v>126091010</v>
       </c>
       <c r="B108" t="n">
-        <v>80077</v>
+        <v>79005</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11482,21 +11482,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11506,10 +11506,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556913</v>
+        <v>556904</v>
       </c>
       <c r="R108" t="n">
-        <v>7227621</v>
+        <v>7227703</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11572,32 +11572,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091380</v>
+        <v>126091115</v>
       </c>
       <c r="B109" t="n">
-        <v>80077</v>
+        <v>57756</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556261</v>
+        <v>556797</v>
       </c>
       <c r="R109" t="n">
-        <v>7227068</v>
+        <v>7227252</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11673,7 +11673,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091070</v>
+        <v>126091072</v>
       </c>
       <c r="B110" t="n">
         <v>80077</v>
@@ -11708,10 +11708,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556723</v>
+        <v>556913</v>
       </c>
       <c r="R110" t="n">
-        <v>7227276</v>
+        <v>7227621</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11774,10 +11774,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091341</v>
+        <v>126091380</v>
       </c>
       <c r="B111" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11785,21 +11785,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556187</v>
+        <v>556261</v>
       </c>
       <c r="R111" t="n">
-        <v>7226946</v>
+        <v>7227068</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11875,10 +11875,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091416</v>
+        <v>126091070</v>
       </c>
       <c r="B112" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11886,21 +11886,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556600</v>
+        <v>556723</v>
       </c>
       <c r="R112" t="n">
-        <v>7227123</v>
+        <v>7227276</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091115</v>
+        <v>126091341</v>
       </c>
       <c r="B113" t="n">
-        <v>57756</v>
+        <v>91236</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556797</v>
+        <v>556187</v>
       </c>
       <c r="R113" t="n">
-        <v>7227252</v>
+        <v>7226946</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,32 +12077,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091407</v>
+        <v>126091416</v>
       </c>
       <c r="B114" t="n">
-        <v>80112</v>
+        <v>91254</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556365</v>
+        <v>556600</v>
       </c>
       <c r="R114" t="n">
-        <v>7227004</v>
+        <v>7227123</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091424</v>
+        <v>126091410</v>
       </c>
       <c r="B120" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R120" t="n">
-        <v>7226986</v>
+        <v>7227068</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12754,11 +12754,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12789,32 +12784,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091387</v>
+        <v>126091444</v>
       </c>
       <c r="B121" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12824,10 +12819,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R121" t="n">
-        <v>7226978</v>
+        <v>7227068</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,32 +12885,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091379</v>
+        <v>126091445</v>
       </c>
       <c r="B122" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R122" t="n">
-        <v>7227093</v>
+        <v>7227109</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12991,10 +12986,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091394</v>
+        <v>126091424</v>
       </c>
       <c r="B123" t="n">
-        <v>91532</v>
+        <v>78973</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13002,21 +12997,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13026,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556098</v>
+        <v>556549</v>
       </c>
       <c r="R123" t="n">
-        <v>7226757</v>
+        <v>7226986</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13062,6 +13057,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13092,32 +13092,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091410</v>
+        <v>126091387</v>
       </c>
       <c r="B124" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556584</v>
+        <v>556497</v>
       </c>
       <c r="R124" t="n">
-        <v>7227068</v>
+        <v>7226978</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13193,32 +13193,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091444</v>
+        <v>126091379</v>
       </c>
       <c r="B125" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556584</v>
+        <v>556305</v>
       </c>
       <c r="R125" t="n">
-        <v>7227068</v>
+        <v>7227093</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13294,32 +13294,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091445</v>
+        <v>126091394</v>
       </c>
       <c r="B126" t="n">
-        <v>80111</v>
+        <v>91532</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R126" t="n">
-        <v>7227109</v>
+        <v>7226757</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091029</v>
+        <v>126091413</v>
       </c>
       <c r="B136" t="n">
-        <v>57652</v>
+        <v>56835</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14320,16 +14320,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556819</v>
+        <v>556662</v>
       </c>
       <c r="R136" t="n">
-        <v>7227694</v>
+        <v>7227178</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,17 +14374,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091413</v>
+        <v>126091029</v>
       </c>
       <c r="B148" t="n">
-        <v>56835</v>
+        <v>57652</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556662</v>
+        <v>556819</v>
       </c>
       <c r="R148" t="n">
-        <v>7227178</v>
+        <v>7227694</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15596,17 +15596,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Tupp</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16263,10 +16263,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091169</v>
+        <v>126091053</v>
       </c>
       <c r="B155" t="n">
-        <v>80111</v>
+        <v>98364</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16274,21 +16274,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556756</v>
+        <v>556996</v>
       </c>
       <c r="R155" t="n">
-        <v>7227253</v>
+        <v>7227559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16364,10 +16364,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091169</v>
       </c>
       <c r="B156" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16375,21 +16375,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556756</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7227253</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16429,12 +16429,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16465,10 +16465,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091397</v>
+        <v>126091404</v>
       </c>
       <c r="B157" t="n">
-        <v>80104</v>
+        <v>80112</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16476,21 +16476,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556378</v>
+        <v>556272</v>
       </c>
       <c r="R157" t="n">
-        <v>7226996</v>
+        <v>7227058</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16566,10 +16566,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091053</v>
+        <v>126091397</v>
       </c>
       <c r="B158" t="n">
-        <v>98364</v>
+        <v>80104</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16577,21 +16577,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16601,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556996</v>
+        <v>556378</v>
       </c>
       <c r="R158" t="n">
-        <v>7227559</v>
+        <v>7226996</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16631,12 +16631,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091408</v>
+        <v>126091440</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556467</v>
+        <v>556465</v>
       </c>
       <c r="R2" t="n">
-        <v>7226993</v>
+        <v>7226995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091440</v>
+        <v>126091408</v>
       </c>
       <c r="B3" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556465</v>
+        <v>556467</v>
       </c>
       <c r="R3" t="n">
-        <v>7226995</v>
+        <v>7226993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091362</v>
+        <v>126091128</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556369</v>
+        <v>556830</v>
       </c>
       <c r="R4" t="n">
-        <v>7226946</v>
+        <v>7227331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091342</v>
+        <v>126091123</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556306</v>
+        <v>557106</v>
       </c>
       <c r="R5" t="n">
-        <v>7226876</v>
+        <v>7227606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091065</v>
+        <v>126091362</v>
       </c>
       <c r="B6" t="n">
         <v>80077</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556817</v>
+        <v>556369</v>
       </c>
       <c r="R6" t="n">
-        <v>7227591</v>
+        <v>7226946</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091370</v>
+        <v>126091342</v>
       </c>
       <c r="B7" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556364</v>
+        <v>556306</v>
       </c>
       <c r="R7" t="n">
-        <v>7226989</v>
+        <v>7226876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091128</v>
+        <v>126091065</v>
       </c>
       <c r="B8" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556830</v>
+        <v>556817</v>
       </c>
       <c r="R8" t="n">
-        <v>7227331</v>
+        <v>7227591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091123</v>
+        <v>126091370</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557106</v>
+        <v>556364</v>
       </c>
       <c r="R9" t="n">
-        <v>7227606</v>
+        <v>7226989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,7 +1486,7 @@
         <v>126091395</v>
       </c>
       <c r="B10" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091147</v>
+        <v>126091043</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556819</v>
+        <v>556756</v>
       </c>
       <c r="R11" t="n">
-        <v>7227694</v>
+        <v>7227253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,11 +1655,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091335</v>
+        <v>126091439</v>
       </c>
       <c r="B12" t="n">
-        <v>91201</v>
+        <v>80111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556339</v>
+        <v>556374</v>
       </c>
       <c r="R12" t="n">
-        <v>7226946</v>
+        <v>7227007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,7 +1786,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091425</v>
+        <v>126091420</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556591</v>
+        <v>556284</v>
       </c>
       <c r="R13" t="n">
-        <v>7227022</v>
+        <v>7227078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,32 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091389</v>
+        <v>126091428</v>
       </c>
       <c r="B14" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556589</v>
+        <v>556314</v>
       </c>
       <c r="R14" t="n">
-        <v>7227109</v>
+        <v>7226891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,10 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091064</v>
+        <v>126091147</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2004,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2033,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556833</v>
+        <v>556819</v>
       </c>
       <c r="R15" t="n">
-        <v>7227720</v>
+        <v>7227694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,6 +2064,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091374</v>
+        <v>126091335</v>
       </c>
       <c r="B16" t="n">
-        <v>80077</v>
+        <v>91203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556371</v>
+        <v>556339</v>
       </c>
       <c r="R16" t="n">
-        <v>7226988</v>
+        <v>7226946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091365</v>
+        <v>126091425</v>
       </c>
       <c r="B17" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556359</v>
+        <v>556591</v>
       </c>
       <c r="R17" t="n">
-        <v>7226943</v>
+        <v>7227022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,6 +2271,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2301,32 +2306,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091428</v>
+        <v>126091389</v>
       </c>
       <c r="B18" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556314</v>
+        <v>556589</v>
       </c>
       <c r="R18" t="n">
-        <v>7226891</v>
+        <v>7227109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,10 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091420</v>
+        <v>126091064</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,21 +2418,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556284</v>
+        <v>556833</v>
       </c>
       <c r="R19" t="n">
-        <v>7227078</v>
+        <v>7227720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,17 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091043</v>
+        <v>126091374</v>
       </c>
       <c r="B20" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556756</v>
+        <v>556371</v>
       </c>
       <c r="R20" t="n">
-        <v>7227253</v>
+        <v>7226988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,32 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091439</v>
+        <v>126091365</v>
       </c>
       <c r="B21" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556374</v>
+        <v>556359</v>
       </c>
       <c r="R21" t="n">
-        <v>7227007</v>
+        <v>7226943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091435</v>
+        <v>126091368</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556346</v>
       </c>
       <c r="R24" t="n">
-        <v>7226941</v>
+        <v>7226961</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091106</v>
+        <v>126091164</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>88647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556709</v>
+        <v>556775</v>
       </c>
       <c r="R25" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091368</v>
+        <v>126091340</v>
       </c>
       <c r="B26" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556346</v>
+        <v>556312</v>
       </c>
       <c r="R26" t="n">
-        <v>7226961</v>
+        <v>7227107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091340</v>
+        <v>126091073</v>
       </c>
       <c r="B27" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556312</v>
+        <v>556756</v>
       </c>
       <c r="R27" t="n">
-        <v>7227107</v>
+        <v>7227253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091073</v>
+        <v>126091435</v>
       </c>
       <c r="B28" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556756</v>
+        <v>556359</v>
       </c>
       <c r="R28" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091164</v>
+        <v>126091106</v>
       </c>
       <c r="B29" t="n">
-        <v>88645</v>
+        <v>80112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556775</v>
+        <v>556709</v>
       </c>
       <c r="R29" t="n">
-        <v>7227253</v>
+        <v>7227248</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091042</v>
+        <v>126091349</v>
       </c>
       <c r="B33" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556817</v>
+        <v>556613</v>
       </c>
       <c r="R33" t="n">
-        <v>7227591</v>
+        <v>7227051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,12 +3896,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091406</v>
+        <v>126091042</v>
       </c>
       <c r="B34" t="n">
-        <v>80112</v>
+        <v>80105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,21 +3948,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3972,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556314</v>
+        <v>556817</v>
       </c>
       <c r="R34" t="n">
-        <v>7226891</v>
+        <v>7227591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3997,12 +4002,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4033,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091356</v>
+        <v>126091414</v>
       </c>
       <c r="B35" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556271</v>
+        <v>556303</v>
       </c>
       <c r="R35" t="n">
-        <v>7227059</v>
+        <v>7226905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4134,32 +4139,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091448</v>
+        <v>126091124</v>
       </c>
       <c r="B36" t="n">
-        <v>91906</v>
+        <v>91256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556484</v>
+        <v>556698</v>
       </c>
       <c r="R36" t="n">
-        <v>7226980</v>
+        <v>7227248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,12 +4204,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,32 +4240,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091414</v>
+        <v>126091406</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>80112</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556303</v>
+        <v>556314</v>
       </c>
       <c r="R37" t="n">
-        <v>7226905</v>
+        <v>7226891</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,7 +4341,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091369</v>
+        <v>126091356</v>
       </c>
       <c r="B38" t="n">
         <v>80077</v>
@@ -4371,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556333</v>
+        <v>556271</v>
       </c>
       <c r="R38" t="n">
-        <v>7227009</v>
+        <v>7227059</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091124</v>
+        <v>126091448</v>
       </c>
       <c r="B39" t="n">
-        <v>91254</v>
+        <v>91908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4472,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556698</v>
+        <v>556484</v>
       </c>
       <c r="R39" t="n">
-        <v>7227248</v>
+        <v>7226980</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4507,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4538,10 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091013</v>
+        <v>126091369</v>
       </c>
       <c r="B40" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,21 +4554,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556830</v>
+        <v>556333</v>
       </c>
       <c r="R40" t="n">
-        <v>7227704</v>
+        <v>7227009</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,12 +4608,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4639,10 +4644,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091349</v>
+        <v>126091013</v>
       </c>
       <c r="B41" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,21 +4655,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4674,10 +4679,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556613</v>
+        <v>556830</v>
       </c>
       <c r="R41" t="n">
-        <v>7227051</v>
+        <v>7227704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4704,17 +4709,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,32 +4846,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091145</v>
+        <v>126091044</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556897</v>
+        <v>556826</v>
       </c>
       <c r="R43" t="n">
-        <v>7227735</v>
+        <v>7227309</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,11 +4917,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5053,32 +5048,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091044</v>
+        <v>126091144</v>
       </c>
       <c r="B45" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556826</v>
+        <v>557048</v>
       </c>
       <c r="R45" t="n">
-        <v>7227309</v>
+        <v>7227797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,7 +5149,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -5189,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R46" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5219,12 +5214,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,7 +5255,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091422</v>
+        <v>126091145</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556407</v>
+        <v>556897</v>
       </c>
       <c r="R47" t="n">
-        <v>7226992</v>
+        <v>7227735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5361,10 +5361,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091075</v>
+        <v>126091129</v>
       </c>
       <c r="B48" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,21 +5372,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556792</v>
+        <v>556685</v>
       </c>
       <c r="R48" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091129</v>
+        <v>126091075</v>
       </c>
       <c r="B49" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556685</v>
+        <v>556792</v>
       </c>
       <c r="R49" t="n">
-        <v>7227107</v>
+        <v>7227253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5672,7 +5672,7 @@
         <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5770,32 +5770,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091438</v>
+        <v>126091381</v>
       </c>
       <c r="B52" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556350</v>
+        <v>556280</v>
       </c>
       <c r="R52" t="n">
-        <v>7226997</v>
+        <v>7227059</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,32 +5972,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091401</v>
+        <v>126091438</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556271</v>
+        <v>556350</v>
       </c>
       <c r="R54" t="n">
-        <v>7227059</v>
+        <v>7226997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091381</v>
+        <v>126091148</v>
       </c>
       <c r="B55" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,21 +6084,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556280</v>
+        <v>556787</v>
       </c>
       <c r="R55" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,12 +6138,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6174,10 +6179,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091148</v>
+        <v>126091401</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6185,21 +6190,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6209,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556787</v>
+        <v>556271</v>
       </c>
       <c r="R56" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6239,17 +6244,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6280,10 +6280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091095</v>
+        <v>126091400</v>
       </c>
       <c r="B57" t="n">
-        <v>91532</v>
+        <v>80076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557005</v>
+        <v>556261</v>
       </c>
       <c r="R57" t="n">
-        <v>7227490</v>
+        <v>7227068</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091343</v>
+        <v>126091409</v>
       </c>
       <c r="B58" t="n">
-        <v>91236</v>
+        <v>80112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556373</v>
+        <v>556480</v>
       </c>
       <c r="R58" t="n">
-        <v>7227010</v>
+        <v>7226980</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091373</v>
+        <v>126091151</v>
       </c>
       <c r="B59" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6493,21 +6493,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556350</v>
+        <v>556935</v>
       </c>
       <c r="R59" t="n">
-        <v>7226997</v>
+        <v>7227614</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,12 +6547,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6583,32 +6588,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091359</v>
+        <v>126091442</v>
       </c>
       <c r="B60" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556280</v>
+        <v>556494</v>
       </c>
       <c r="R60" t="n">
-        <v>7226845</v>
+        <v>7226972</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6684,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091361</v>
+        <v>126091417</v>
       </c>
       <c r="B61" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6695,21 +6700,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6719,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556321</v>
+        <v>556559</v>
       </c>
       <c r="R61" t="n">
-        <v>7226929</v>
+        <v>7226989</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6785,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091417</v>
+        <v>126091095</v>
       </c>
       <c r="B62" t="n">
-        <v>91254</v>
+        <v>91534</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6796,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556559</v>
+        <v>557005</v>
       </c>
       <c r="R62" t="n">
-        <v>7226989</v>
+        <v>7227490</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6850,12 +6855,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6886,10 +6891,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091386</v>
+        <v>126091343</v>
       </c>
       <c r="B63" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,21 +6902,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6921,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556480</v>
+        <v>556373</v>
       </c>
       <c r="R63" t="n">
-        <v>7226980</v>
+        <v>7227010</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6987,7 +6992,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091066</v>
+        <v>126091373</v>
       </c>
       <c r="B64" t="n">
         <v>80077</v>
@@ -7022,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556946</v>
+        <v>556350</v>
       </c>
       <c r="R64" t="n">
-        <v>7227602</v>
+        <v>7226997</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7052,17 +7057,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7093,32 +7093,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091442</v>
+        <v>126091359</v>
       </c>
       <c r="B65" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556494</v>
+        <v>556280</v>
       </c>
       <c r="R65" t="n">
-        <v>7226972</v>
+        <v>7226845</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091400</v>
+        <v>126091361</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556261</v>
+        <v>556321</v>
       </c>
       <c r="R66" t="n">
-        <v>7227068</v>
+        <v>7226929</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,32 +7295,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091409</v>
+        <v>126091386</v>
       </c>
       <c r="B67" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091151</v>
+        <v>126091066</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556935</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7227614</v>
+        <v>7227602</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Lång bål</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B69" t="n">
-        <v>80077</v>
+        <v>91203</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R69" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7704,32 +7704,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091337</v>
+        <v>126091384</v>
       </c>
       <c r="B71" t="n">
-        <v>91201</v>
+        <v>80077</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556374</v>
+        <v>556376</v>
       </c>
       <c r="R71" t="n">
-        <v>7226996</v>
+        <v>7227009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091402</v>
+        <v>126091012</v>
       </c>
       <c r="B74" t="n">
-        <v>80076</v>
+        <v>91203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556280</v>
+        <v>556977</v>
       </c>
       <c r="R74" t="n">
-        <v>7227059</v>
+        <v>7227576</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091346</v>
+        <v>126091143</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556194</v>
+        <v>557106</v>
       </c>
       <c r="R75" t="n">
-        <v>7226815</v>
+        <v>7227606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,17 +8178,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8219,10 +8214,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091012</v>
+        <v>126091174</v>
       </c>
       <c r="B76" t="n">
-        <v>91201</v>
+        <v>91648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8230,21 +8225,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556977</v>
+        <v>556888</v>
       </c>
       <c r="R76" t="n">
-        <v>7227576</v>
+        <v>7227746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8320,10 +8315,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091143</v>
+        <v>126091402</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8331,21 +8326,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8355,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>557106</v>
+        <v>556280</v>
       </c>
       <c r="R77" t="n">
-        <v>7227606</v>
+        <v>7227059</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,12 +8380,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8421,10 +8416,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091051</v>
+        <v>126091015</v>
       </c>
       <c r="B78" t="n">
-        <v>79942</v>
+        <v>91238</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8432,21 +8427,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556679</v>
+        <v>556931</v>
       </c>
       <c r="R78" t="n">
-        <v>7227232</v>
+        <v>7227622</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8522,10 +8517,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091015</v>
+        <v>126091051</v>
       </c>
       <c r="B79" t="n">
-        <v>91236</v>
+        <v>79942</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8533,21 +8528,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8557,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556931</v>
+        <v>556679</v>
       </c>
       <c r="R79" t="n">
-        <v>7227622</v>
+        <v>7227232</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8623,32 +8618,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091174</v>
+        <v>126091360</v>
       </c>
       <c r="B80" t="n">
-        <v>91646</v>
+        <v>80077</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,10 +8653,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556888</v>
+        <v>556326</v>
       </c>
       <c r="R80" t="n">
-        <v>7227746</v>
+        <v>7226893</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8688,12 +8683,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8724,7 +8719,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091360</v>
+        <v>126091375</v>
       </c>
       <c r="B81" t="n">
         <v>80077</v>
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556326</v>
+        <v>556423</v>
       </c>
       <c r="R81" t="n">
-        <v>7226893</v>
+        <v>7226984</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,7 +8820,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091375</v>
+        <v>126091067</v>
       </c>
       <c r="B82" t="n">
         <v>80077</v>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556423</v>
+        <v>556690</v>
       </c>
       <c r="R82" t="n">
-        <v>7226984</v>
+        <v>7227262</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8890,12 +8885,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,7 +8921,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091067</v>
+        <v>126091355</v>
       </c>
       <c r="B83" t="n">
         <v>80077</v>
@@ -8961,10 +8956,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556690</v>
+        <v>556346</v>
       </c>
       <c r="R83" t="n">
-        <v>7227262</v>
+        <v>7227118</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8991,12 +8986,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9027,10 +9022,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091355</v>
+        <v>126091346</v>
       </c>
       <c r="B84" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,21 +9033,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556346</v>
+        <v>556194</v>
       </c>
       <c r="R84" t="n">
-        <v>7227118</v>
+        <v>7226815</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9098,6 +9093,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,7 +9128,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091165</v>
+        <v>126091166</v>
       </c>
       <c r="B85" t="n">
         <v>80111</v>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556874</v>
+        <v>556690</v>
       </c>
       <c r="R85" t="n">
-        <v>7227697</v>
+        <v>7227262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9229,7 +9229,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091141</v>
+        <v>126091153</v>
       </c>
       <c r="B86" t="n">
         <v>78973</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556931</v>
+        <v>556996</v>
       </c>
       <c r="R86" t="n">
-        <v>7227622</v>
+        <v>7227559</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9300,11 +9300,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9335,10 +9330,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091351</v>
+        <v>126091165</v>
       </c>
       <c r="B87" t="n">
-        <v>80105</v>
+        <v>80111</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9346,21 +9341,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9370,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556346</v>
+        <v>556874</v>
       </c>
       <c r="R87" t="n">
-        <v>7227118</v>
+        <v>7227697</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9400,12 +9395,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9436,27 +9431,27 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091166</v>
+        <v>126091141</v>
       </c>
       <c r="B88" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9471,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556690</v>
+        <v>556931</v>
       </c>
       <c r="R88" t="n">
-        <v>7227262</v>
+        <v>7227622</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9507,6 +9502,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9537,32 +9537,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091383</v>
+        <v>126091351</v>
       </c>
       <c r="B89" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9572,10 +9572,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556230</v>
+        <v>556346</v>
       </c>
       <c r="R89" t="n">
-        <v>7226809</v>
+        <v>7227118</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9638,7 +9638,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091377</v>
+        <v>126091383</v>
       </c>
       <c r="B90" t="n">
         <v>80077</v>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556584</v>
+        <v>556230</v>
       </c>
       <c r="R90" t="n">
-        <v>7227068</v>
+        <v>7226809</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9739,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091344</v>
+        <v>126091377</v>
       </c>
       <c r="B91" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556452</v>
+        <v>556584</v>
       </c>
       <c r="R91" t="n">
-        <v>7226989</v>
+        <v>7227068</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091372</v>
+        <v>126091344</v>
       </c>
       <c r="B92" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9851,21 +9851,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556359</v>
+        <v>556452</v>
       </c>
       <c r="R92" t="n">
-        <v>7226988</v>
+        <v>7226989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9941,10 +9941,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091153</v>
+        <v>126091372</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9952,21 +9952,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556996</v>
+        <v>556359</v>
       </c>
       <c r="R93" t="n">
-        <v>7227559</v>
+        <v>7226988</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,12 +10006,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10148,7 +10148,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091167</v>
+        <v>126091441</v>
       </c>
       <c r="B95" t="n">
         <v>80111</v>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556728</v>
+        <v>556480</v>
       </c>
       <c r="R95" t="n">
-        <v>7227275</v>
+        <v>7226980</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10213,12 +10213,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10249,10 +10249,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091405</v>
+        <v>126091167</v>
       </c>
       <c r="B96" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10260,21 +10260,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556230</v>
+        <v>556728</v>
       </c>
       <c r="R96" t="n">
-        <v>7226809</v>
+        <v>7227275</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091441</v>
+        <v>126091418</v>
       </c>
       <c r="B97" t="n">
-        <v>80111</v>
+        <v>91256</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556480</v>
+        <v>556550</v>
       </c>
       <c r="R97" t="n">
-        <v>7226980</v>
+        <v>7227005</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10451,10 +10451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091418</v>
+        <v>126091125</v>
       </c>
       <c r="B98" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556550</v>
+        <v>556893</v>
       </c>
       <c r="R98" t="n">
-        <v>7227005</v>
+        <v>7227703</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10552,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091357</v>
+        <v>126091405</v>
       </c>
       <c r="B99" t="n">
-        <v>80077</v>
+        <v>80112</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556061</v>
+        <v>556230</v>
       </c>
       <c r="R99" t="n">
-        <v>7226781</v>
+        <v>7226809</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091339</v>
+        <v>126091357</v>
       </c>
       <c r="B100" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556393</v>
+        <v>556061</v>
       </c>
       <c r="R100" t="n">
-        <v>7226994</v>
+        <v>7226781</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,10 +10754,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091125</v>
+        <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>91254</v>
+        <v>91238</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,21 +10765,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556893</v>
+        <v>556393</v>
       </c>
       <c r="R101" t="n">
-        <v>7227703</v>
+        <v>7226994</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10964,7 +10964,7 @@
         <v>126091019</v>
       </c>
       <c r="B103" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11264,10 +11264,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091407</v>
+        <v>126091115</v>
       </c>
       <c r="B106" t="n">
-        <v>80112</v>
+        <v>57756</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11275,21 +11275,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556365</v>
+        <v>556797</v>
       </c>
       <c r="R106" t="n">
-        <v>7227004</v>
+        <v>7227252</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11365,32 +11365,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091421</v>
+        <v>126091407</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556111</v>
+        <v>556365</v>
       </c>
       <c r="R107" t="n">
-        <v>7226873</v>
+        <v>7227004</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11436,11 +11436,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11471,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091010</v>
+        <v>126091416</v>
       </c>
       <c r="B108" t="n">
-        <v>79005</v>
+        <v>91256</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11482,21 +11477,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11506,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556904</v>
+        <v>556600</v>
       </c>
       <c r="R108" t="n">
-        <v>7227703</v>
+        <v>7227123</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11536,12 +11531,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11572,32 +11567,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091115</v>
+        <v>126091421</v>
       </c>
       <c r="B109" t="n">
-        <v>57756</v>
+        <v>78973</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11607,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556797</v>
+        <v>556111</v>
       </c>
       <c r="R109" t="n">
-        <v>7227252</v>
+        <v>7226873</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11637,12 +11632,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11979,7 +11979,7 @@
         <v>126091341</v>
       </c>
       <c r="B113" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12077,10 +12077,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091416</v>
+        <v>126091010</v>
       </c>
       <c r="B114" t="n">
-        <v>91254</v>
+        <v>79005</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556600</v>
+        <v>556904</v>
       </c>
       <c r="R114" t="n">
-        <v>7227123</v>
+        <v>7227703</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12142,12 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B115" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R115" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12279,7 +12279,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091068</v>
+        <v>126091084</v>
       </c>
       <c r="B116" t="n">
         <v>80077</v>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556707</v>
+        <v>556737</v>
       </c>
       <c r="R116" t="n">
-        <v>7227243</v>
+        <v>7227192</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12344,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091017</v>
+        <v>126091068</v>
       </c>
       <c r="B117" t="n">
-        <v>91236</v>
+        <v>80077</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556929</v>
+        <v>556707</v>
       </c>
       <c r="R117" t="n">
-        <v>7227610</v>
+        <v>7227243</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091121</v>
+        <v>126091017</v>
       </c>
       <c r="B118" t="n">
-        <v>91232</v>
+        <v>91238</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556907</v>
+        <v>556929</v>
       </c>
       <c r="R118" t="n">
-        <v>7227720</v>
+        <v>7227610</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091102</v>
+        <v>126091121</v>
       </c>
       <c r="B119" t="n">
-        <v>80076</v>
+        <v>91234</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556740</v>
+        <v>556907</v>
       </c>
       <c r="R119" t="n">
-        <v>7227186</v>
+        <v>7227720</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091410</v>
+        <v>126091445</v>
       </c>
       <c r="B120" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
         <v>556584</v>
       </c>
       <c r="R120" t="n">
-        <v>7227068</v>
+        <v>7227109</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12885,10 +12885,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091445</v>
+        <v>126091410</v>
       </c>
       <c r="B122" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12896,21 +12896,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12923,7 +12923,7 @@
         <v>556584</v>
       </c>
       <c r="R122" t="n">
-        <v>7227109</v>
+        <v>7227068</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13297,7 +13297,7 @@
         <v>126091394</v>
       </c>
       <c r="B126" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>126091338</v>
       </c>
       <c r="B132" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091413</v>
+        <v>126091431</v>
       </c>
       <c r="B136" t="n">
-        <v>56835</v>
+        <v>80111</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556662</v>
+        <v>556179</v>
       </c>
       <c r="R136" t="n">
-        <v>7227178</v>
+        <v>7226822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14380,11 +14380,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14415,32 +14410,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091105</v>
+        <v>126091415</v>
       </c>
       <c r="B137" t="n">
-        <v>80112</v>
+        <v>91256</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556807</v>
+        <v>556315</v>
       </c>
       <c r="R137" t="n">
-        <v>7227608</v>
+        <v>7226927</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14480,12 +14475,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14617,32 +14612,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091443</v>
+        <v>126091127</v>
       </c>
       <c r="B139" t="n">
-        <v>80111</v>
+        <v>91256</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14652,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556529</v>
+        <v>556728</v>
       </c>
       <c r="R139" t="n">
-        <v>7226958</v>
+        <v>7227249</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14682,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14718,7 +14713,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091431</v>
+        <v>126091443</v>
       </c>
       <c r="B140" t="n">
         <v>80111</v>
@@ -14753,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556179</v>
+        <v>556529</v>
       </c>
       <c r="R140" t="n">
-        <v>7226822</v>
+        <v>7226958</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14819,27 +14814,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091140</v>
+        <v>126091437</v>
       </c>
       <c r="B141" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -14854,10 +14849,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>557026</v>
+        <v>556361</v>
       </c>
       <c r="R141" t="n">
-        <v>7227519</v>
+        <v>7227004</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14884,17 +14879,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15026,10 +15016,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091437</v>
+        <v>126091105</v>
       </c>
       <c r="B143" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15037,21 +15027,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15061,10 +15051,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556361</v>
+        <v>556807</v>
       </c>
       <c r="R143" t="n">
-        <v>7227004</v>
+        <v>7227608</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15091,12 +15081,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,10 +15117,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091415</v>
+        <v>126091140</v>
       </c>
       <c r="B144" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15138,21 +15128,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15162,10 +15152,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556315</v>
+        <v>557026</v>
       </c>
       <c r="R144" t="n">
-        <v>7226927</v>
+        <v>7227519</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15192,12 +15182,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15228,10 +15223,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091127</v>
+        <v>126091413</v>
       </c>
       <c r="B145" t="n">
-        <v>91254</v>
+        <v>56835</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15239,21 +15234,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15263,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556728</v>
+        <v>556662</v>
       </c>
       <c r="R145" t="n">
-        <v>7227249</v>
+        <v>7227178</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15293,12 +15288,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091152</v>
+        <v>126091388</v>
       </c>
       <c r="B149" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556975</v>
+        <v>556529</v>
       </c>
       <c r="R149" t="n">
-        <v>7227579</v>
+        <v>7226958</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,17 +15702,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15743,10 +15738,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091149</v>
+        <v>126091378</v>
       </c>
       <c r="B150" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15754,21 +15749,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15778,10 +15773,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556807</v>
+        <v>556353</v>
       </c>
       <c r="R150" t="n">
-        <v>7227608</v>
+        <v>7227115</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15808,17 +15803,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15849,10 +15839,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091388</v>
+        <v>126091350</v>
       </c>
       <c r="B151" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15860,21 +15850,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15884,10 +15874,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556529</v>
+        <v>556589</v>
       </c>
       <c r="R151" t="n">
-        <v>7226958</v>
+        <v>7227059</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15920,6 +15910,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15950,10 +15945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091378</v>
+        <v>126091040</v>
       </c>
       <c r="B152" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15961,21 +15956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15985,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556353</v>
+        <v>556781</v>
       </c>
       <c r="R152" t="n">
-        <v>7227115</v>
+        <v>7227272</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16015,12 +16010,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,32 +16051,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091350</v>
+        <v>126091053</v>
       </c>
       <c r="B153" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556589</v>
+        <v>556996</v>
       </c>
       <c r="R153" t="n">
-        <v>7227059</v>
+        <v>7227559</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16116,17 +16116,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16157,10 +16152,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091040</v>
+        <v>126091152</v>
       </c>
       <c r="B154" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16168,21 +16163,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16192,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556781</v>
+        <v>556975</v>
       </c>
       <c r="R154" t="n">
-        <v>7227272</v>
+        <v>7227579</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16232,7 +16227,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16263,10 +16258,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091053</v>
+        <v>126091397</v>
       </c>
       <c r="B155" t="n">
-        <v>98364</v>
+        <v>80104</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16274,21 +16269,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16298,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556996</v>
+        <v>556378</v>
       </c>
       <c r="R155" t="n">
-        <v>7227559</v>
+        <v>7226996</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16328,12 +16323,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16364,10 +16359,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091169</v>
+        <v>126091404</v>
       </c>
       <c r="B156" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16375,21 +16370,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16394,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556756</v>
+        <v>556272</v>
       </c>
       <c r="R156" t="n">
-        <v>7227253</v>
+        <v>7227058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16429,12 +16424,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16465,10 +16460,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091404</v>
+        <v>126091169</v>
       </c>
       <c r="B157" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16476,21 +16471,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16495,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556272</v>
+        <v>556756</v>
       </c>
       <c r="R157" t="n">
-        <v>7227058</v>
+        <v>7227253</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16530,12 +16525,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16566,32 +16561,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091397</v>
+        <v>126091149</v>
       </c>
       <c r="B158" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16601,10 +16596,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556378</v>
+        <v>556807</v>
       </c>
       <c r="R158" t="n">
-        <v>7226996</v>
+        <v>7227608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16631,12 +16626,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091043</v>
+        <v>126091389</v>
       </c>
       <c r="B11" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556756</v>
+        <v>556589</v>
       </c>
       <c r="R11" t="n">
-        <v>7227253</v>
+        <v>7227109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091439</v>
+        <v>126091064</v>
       </c>
       <c r="B12" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556374</v>
+        <v>556833</v>
       </c>
       <c r="R12" t="n">
-        <v>7227007</v>
+        <v>7227720</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091420</v>
+        <v>126091374</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556284</v>
+        <v>556371</v>
       </c>
       <c r="R13" t="n">
-        <v>7227078</v>
+        <v>7226988</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,32 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091428</v>
+        <v>126091365</v>
       </c>
       <c r="B14" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556314</v>
+        <v>556359</v>
       </c>
       <c r="R14" t="n">
-        <v>7226891</v>
+        <v>7226943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,32 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091147</v>
+        <v>126091043</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556819</v>
+        <v>556756</v>
       </c>
       <c r="R15" t="n">
-        <v>7227694</v>
+        <v>7227253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,11 +2059,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091335</v>
+        <v>126091439</v>
       </c>
       <c r="B16" t="n">
-        <v>91203</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2110,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556339</v>
+        <v>556374</v>
       </c>
       <c r="R16" t="n">
-        <v>7226946</v>
+        <v>7227007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091425</v>
+        <v>126091420</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2235,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556591</v>
+        <v>556284</v>
       </c>
       <c r="R17" t="n">
-        <v>7227022</v>
+        <v>7227078</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091389</v>
+        <v>126091428</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2341,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556589</v>
+        <v>556314</v>
       </c>
       <c r="R18" t="n">
-        <v>7227109</v>
+        <v>7226891</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091064</v>
+        <v>126091147</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556833</v>
+        <v>556819</v>
       </c>
       <c r="R19" t="n">
-        <v>7227720</v>
+        <v>7227694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2478,6 +2468,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,32 +2503,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091374</v>
+        <v>126091335</v>
       </c>
       <c r="B20" t="n">
-        <v>80077</v>
+        <v>91203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556371</v>
+        <v>556339</v>
       </c>
       <c r="R20" t="n">
-        <v>7226988</v>
+        <v>7226946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,10 +2604,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091365</v>
+        <v>126091425</v>
       </c>
       <c r="B21" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,21 +2615,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556359</v>
+        <v>556591</v>
       </c>
       <c r="R21" t="n">
-        <v>7226943</v>
+        <v>7227022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,6 +2675,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091028</v>
+        <v>126091392</v>
       </c>
       <c r="B102" t="n">
-        <v>57652</v>
+        <v>56228</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557117</v>
+        <v>556271</v>
       </c>
       <c r="R102" t="n">
-        <v>7227635</v>
+        <v>7226832</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,17 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11163,10 +11158,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091392</v>
+        <v>126091028</v>
       </c>
       <c r="B105" t="n">
-        <v>56228</v>
+        <v>57652</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11174,21 +11169,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11198,10 +11193,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>556271</v>
+        <v>557117</v>
       </c>
       <c r="R105" t="n">
-        <v>7226832</v>
+        <v>7227635</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11228,12 +11223,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11365,32 +11365,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091407</v>
+        <v>126091072</v>
       </c>
       <c r="B107" t="n">
-        <v>80112</v>
+        <v>80077</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556365</v>
+        <v>556913</v>
       </c>
       <c r="R107" t="n">
-        <v>7227004</v>
+        <v>7227621</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091416</v>
+        <v>126091380</v>
       </c>
       <c r="B108" t="n">
-        <v>91256</v>
+        <v>80077</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11477,21 +11477,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556600</v>
+        <v>556261</v>
       </c>
       <c r="R108" t="n">
-        <v>7227123</v>
+        <v>7227068</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091421</v>
+        <v>126091070</v>
       </c>
       <c r="B109" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556111</v>
+        <v>556723</v>
       </c>
       <c r="R109" t="n">
-        <v>7226873</v>
+        <v>7227276</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,17 +11632,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11673,10 +11668,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091072</v>
+        <v>126091341</v>
       </c>
       <c r="B110" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11684,21 +11679,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11708,10 +11703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556913</v>
+        <v>556187</v>
       </c>
       <c r="R110" t="n">
-        <v>7227621</v>
+        <v>7226946</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11738,12 +11733,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11774,10 +11769,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091380</v>
+        <v>126091010</v>
       </c>
       <c r="B111" t="n">
-        <v>80077</v>
+        <v>79005</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11785,21 +11780,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11809,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556261</v>
+        <v>556904</v>
       </c>
       <c r="R111" t="n">
-        <v>7227068</v>
+        <v>7227703</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11839,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11875,32 +11870,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091070</v>
+        <v>126091407</v>
       </c>
       <c r="B112" t="n">
-        <v>80077</v>
+        <v>80112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11910,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556723</v>
+        <v>556365</v>
       </c>
       <c r="R112" t="n">
-        <v>7227276</v>
+        <v>7227004</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11935,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,10 +11971,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091341</v>
+        <v>126091416</v>
       </c>
       <c r="B113" t="n">
-        <v>91238</v>
+        <v>91256</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11987,21 +11982,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556187</v>
+        <v>556600</v>
       </c>
       <c r="R113" t="n">
-        <v>7226946</v>
+        <v>7227123</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12077,10 +12072,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091010</v>
+        <v>126091421</v>
       </c>
       <c r="B114" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12083,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556904</v>
+        <v>556111</v>
       </c>
       <c r="R114" t="n">
-        <v>7227703</v>
+        <v>7226873</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12142,12 +12137,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091068</v>
+        <v>126091121</v>
       </c>
       <c r="B117" t="n">
-        <v>80077</v>
+        <v>91234</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556707</v>
+        <v>556907</v>
       </c>
       <c r="R117" t="n">
-        <v>7227243</v>
+        <v>7227720</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091017</v>
+        <v>126091068</v>
       </c>
       <c r="B118" t="n">
-        <v>91238</v>
+        <v>80077</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556929</v>
+        <v>556707</v>
       </c>
       <c r="R118" t="n">
-        <v>7227610</v>
+        <v>7227243</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091121</v>
+        <v>126091017</v>
       </c>
       <c r="B119" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556907</v>
+        <v>556929</v>
       </c>
       <c r="R119" t="n">
-        <v>7227720</v>
+        <v>7227610</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091431</v>
+        <v>126091029</v>
       </c>
       <c r="B136" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556179</v>
+        <v>556819</v>
       </c>
       <c r="R136" t="n">
-        <v>7226822</v>
+        <v>7227694</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,12 +14374,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14410,10 +14415,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091415</v>
+        <v>126091413</v>
       </c>
       <c r="B137" t="n">
-        <v>91256</v>
+        <v>56835</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14421,21 +14426,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556315</v>
+        <v>556662</v>
       </c>
       <c r="R137" t="n">
-        <v>7226927</v>
+        <v>7227178</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14481,6 +14486,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14511,7 +14521,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091429</v>
+        <v>126091431</v>
       </c>
       <c r="B138" t="n">
         <v>80111</v>
@@ -14546,10 +14556,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556272</v>
+        <v>556179</v>
       </c>
       <c r="R138" t="n">
-        <v>7227058</v>
+        <v>7226822</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,7 +14622,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091127</v>
+        <v>126091415</v>
       </c>
       <c r="B139" t="n">
         <v>91256</v>
@@ -14647,10 +14657,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556728</v>
+        <v>556315</v>
       </c>
       <c r="R139" t="n">
-        <v>7227249</v>
+        <v>7226927</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14677,12 +14687,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14713,7 +14723,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091443</v>
+        <v>126091429</v>
       </c>
       <c r="B140" t="n">
         <v>80111</v>
@@ -14748,10 +14758,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556529</v>
+        <v>556272</v>
       </c>
       <c r="R140" t="n">
-        <v>7226958</v>
+        <v>7227058</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14814,32 +14824,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091437</v>
+        <v>126091127</v>
       </c>
       <c r="B141" t="n">
-        <v>80111</v>
+        <v>91256</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14849,10 +14859,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556361</v>
+        <v>556728</v>
       </c>
       <c r="R141" t="n">
-        <v>7227004</v>
+        <v>7227249</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14879,12 +14889,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14915,7 +14925,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091432</v>
+        <v>126091443</v>
       </c>
       <c r="B142" t="n">
         <v>80111</v>
@@ -14950,10 +14960,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556230</v>
+        <v>556529</v>
       </c>
       <c r="R142" t="n">
-        <v>7226809</v>
+        <v>7226958</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15016,10 +15026,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091105</v>
+        <v>126091437</v>
       </c>
       <c r="B143" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15027,21 +15037,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15051,10 +15061,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556807</v>
+        <v>556361</v>
       </c>
       <c r="R143" t="n">
-        <v>7227608</v>
+        <v>7227004</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15081,12 +15091,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15117,27 +15127,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091140</v>
+        <v>126091432</v>
       </c>
       <c r="B144" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15152,10 +15162,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557026</v>
+        <v>556230</v>
       </c>
       <c r="R144" t="n">
-        <v>7227519</v>
+        <v>7226809</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15182,17 +15192,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15223,32 +15228,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091413</v>
+        <v>126091105</v>
       </c>
       <c r="B145" t="n">
-        <v>56835</v>
+        <v>80112</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15258,10 +15263,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556662</v>
+        <v>556807</v>
       </c>
       <c r="R145" t="n">
-        <v>7227178</v>
+        <v>7227608</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15288,17 +15293,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Tupp</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15329,10 +15329,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091371</v>
+        <v>126091140</v>
       </c>
       <c r="B146" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,21 +15340,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556365</v>
+        <v>557026</v>
       </c>
       <c r="R146" t="n">
-        <v>7227004</v>
+        <v>7227519</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15394,12 +15394,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15430,7 +15435,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091063</v>
+        <v>126091371</v>
       </c>
       <c r="B147" t="n">
         <v>80077</v>
@@ -15465,10 +15470,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556836</v>
+        <v>556365</v>
       </c>
       <c r="R147" t="n">
-        <v>7227732</v>
+        <v>7227004</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15495,12 +15500,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15531,10 +15536,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091029</v>
+        <v>126091063</v>
       </c>
       <c r="B148" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15542,21 +15547,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15566,10 +15571,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556819</v>
+        <v>556836</v>
       </c>
       <c r="R148" t="n">
-        <v>7227694</v>
+        <v>7227732</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15602,11 +15607,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091388</v>
+        <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556529</v>
+        <v>556975</v>
       </c>
       <c r="R149" t="n">
-        <v>7226958</v>
+        <v>7227579</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,12 +15702,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15738,32 +15743,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091378</v>
+        <v>126091397</v>
       </c>
       <c r="B150" t="n">
-        <v>80077</v>
+        <v>80104</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15773,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556353</v>
+        <v>556378</v>
       </c>
       <c r="R150" t="n">
-        <v>7227115</v>
+        <v>7226996</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15839,32 +15844,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091350</v>
+        <v>126091404</v>
       </c>
       <c r="B151" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15874,10 +15879,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556589</v>
+        <v>556272</v>
       </c>
       <c r="R151" t="n">
-        <v>7227059</v>
+        <v>7227058</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15910,11 +15915,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15945,32 +15945,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091040</v>
+        <v>126091169</v>
       </c>
       <c r="B152" t="n">
-        <v>57652</v>
+        <v>80111</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556781</v>
+        <v>556756</v>
       </c>
       <c r="R152" t="n">
-        <v>7227272</v>
+        <v>7227253</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16016,11 +16016,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,32 +16046,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091053</v>
+        <v>126091149</v>
       </c>
       <c r="B153" t="n">
-        <v>98366</v>
+        <v>78973</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16081,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556996</v>
+        <v>556807</v>
       </c>
       <c r="R153" t="n">
-        <v>7227559</v>
+        <v>7227608</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16122,6 +16117,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,10 +16152,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091152</v>
+        <v>126091388</v>
       </c>
       <c r="B154" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16163,21 +16163,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16187,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556975</v>
+        <v>556529</v>
       </c>
       <c r="R154" t="n">
-        <v>7227579</v>
+        <v>7226958</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16217,17 +16217,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16258,32 +16253,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091397</v>
+        <v>126091378</v>
       </c>
       <c r="B155" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16293,10 +16288,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556378</v>
+        <v>556353</v>
       </c>
       <c r="R155" t="n">
-        <v>7226996</v>
+        <v>7227115</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16359,32 +16354,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091350</v>
       </c>
       <c r="B156" t="n">
-        <v>80112</v>
+        <v>57652</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16394,10 +16389,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556589</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7227059</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16430,6 +16425,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16460,32 +16460,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091169</v>
+        <v>126091040</v>
       </c>
       <c r="B157" t="n">
-        <v>80111</v>
+        <v>57652</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16495,10 +16495,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556756</v>
+        <v>556781</v>
       </c>
       <c r="R157" t="n">
-        <v>7227253</v>
+        <v>7227272</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16531,6 +16531,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16561,32 +16566,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091149</v>
+        <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16596,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556807</v>
+        <v>556996</v>
       </c>
       <c r="R158" t="n">
-        <v>7227608</v>
+        <v>7227559</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16632,11 +16637,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091440</v>
+        <v>126091395</v>
       </c>
       <c r="B2" t="n">
-        <v>80111</v>
+        <v>91538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556465</v>
+        <v>556308</v>
       </c>
       <c r="R2" t="n">
-        <v>7226995</v>
+        <v>7226876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091408</v>
+        <v>126091342</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>91242</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556467</v>
+        <v>556306</v>
       </c>
       <c r="R3" t="n">
-        <v>7226993</v>
+        <v>7226876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091128</v>
+        <v>126091440</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556830</v>
+        <v>556465</v>
       </c>
       <c r="R4" t="n">
-        <v>7227331</v>
+        <v>7226995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091123</v>
+        <v>126091408</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>80116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557106</v>
+        <v>556467</v>
       </c>
       <c r="R5" t="n">
-        <v>7227606</v>
+        <v>7226993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,7 +1082,7 @@
         <v>126091362</v>
       </c>
       <c r="B6" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091342</v>
+        <v>126091065</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556306</v>
+        <v>556817</v>
       </c>
       <c r="R7" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091065</v>
+        <v>126091370</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556817</v>
+        <v>556364</v>
       </c>
       <c r="R8" t="n">
-        <v>7227591</v>
+        <v>7226989</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091370</v>
+        <v>126091128</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556364</v>
+        <v>556830</v>
       </c>
       <c r="R9" t="n">
-        <v>7226989</v>
+        <v>7227331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091395</v>
+        <v>126091123</v>
       </c>
       <c r="B10" t="n">
-        <v>91534</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556308</v>
+        <v>557106</v>
       </c>
       <c r="R10" t="n">
-        <v>7226876</v>
+        <v>7227606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091389</v>
+        <v>126091147</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556589</v>
+        <v>556819</v>
       </c>
       <c r="R11" t="n">
-        <v>7227109</v>
+        <v>7227694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091064</v>
+        <v>126091389</v>
       </c>
       <c r="B12" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1720,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556833</v>
+        <v>556589</v>
       </c>
       <c r="R12" t="n">
-        <v>7227720</v>
+        <v>7227109</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091374</v>
+        <v>126091064</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556371</v>
+        <v>556833</v>
       </c>
       <c r="R13" t="n">
-        <v>7226988</v>
+        <v>7227720</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,12 +1856,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,32 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091365</v>
+        <v>126091335</v>
       </c>
       <c r="B14" t="n">
-        <v>80077</v>
+        <v>91207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1922,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556359</v>
+        <v>556339</v>
       </c>
       <c r="R14" t="n">
-        <v>7226943</v>
+        <v>7226946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,32 +1993,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091043</v>
+        <v>126091374</v>
       </c>
       <c r="B15" t="n">
-        <v>80105</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2023,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556756</v>
+        <v>556371</v>
       </c>
       <c r="R15" t="n">
-        <v>7227253</v>
+        <v>7226988</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,12 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2089,32 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091439</v>
+        <v>126091365</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556374</v>
+        <v>556359</v>
       </c>
       <c r="R16" t="n">
-        <v>7227007</v>
+        <v>7226943</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,32 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091420</v>
+        <v>126091043</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2225,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556284</v>
+        <v>556756</v>
       </c>
       <c r="R17" t="n">
-        <v>7227078</v>
+        <v>7227253</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,17 +2260,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2296,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091428</v>
+        <v>126091439</v>
       </c>
       <c r="B18" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556314</v>
+        <v>556374</v>
       </c>
       <c r="R18" t="n">
-        <v>7226891</v>
+        <v>7227007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091147</v>
+        <v>126091420</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556819</v>
+        <v>556284</v>
       </c>
       <c r="R19" t="n">
-        <v>7227694</v>
+        <v>7227078</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091335</v>
+        <v>126091428</v>
       </c>
       <c r="B20" t="n">
-        <v>91203</v>
+        <v>80115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556339</v>
+        <v>556314</v>
       </c>
       <c r="R20" t="n">
-        <v>7226946</v>
+        <v>7226891</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,7 +2607,7 @@
         <v>126091425</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>57816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R22" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B23" t="n">
-        <v>57812</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R23" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091368</v>
+        <v>126091164</v>
       </c>
       <c r="B24" t="n">
-        <v>80077</v>
+        <v>88651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556346</v>
+        <v>556775</v>
       </c>
       <c r="R24" t="n">
-        <v>7226961</v>
+        <v>7227253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091164</v>
+        <v>126091340</v>
       </c>
       <c r="B25" t="n">
-        <v>88647</v>
+        <v>91242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556775</v>
+        <v>556312</v>
       </c>
       <c r="R25" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091340</v>
+        <v>126091435</v>
       </c>
       <c r="B26" t="n">
-        <v>91238</v>
+        <v>80115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556312</v>
+        <v>556359</v>
       </c>
       <c r="R26" t="n">
-        <v>7227107</v>
+        <v>7226941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091073</v>
+        <v>126091106</v>
       </c>
       <c r="B27" t="n">
-        <v>80077</v>
+        <v>80116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556756</v>
+        <v>556709</v>
       </c>
       <c r="R27" t="n">
-        <v>7227253</v>
+        <v>7227248</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,32 +3316,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091435</v>
+        <v>126091368</v>
       </c>
       <c r="B28" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556359</v>
+        <v>556346</v>
       </c>
       <c r="R28" t="n">
-        <v>7226941</v>
+        <v>7226961</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,32 +3417,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B29" t="n">
-        <v>80112</v>
+        <v>80081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R29" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091382</v>
+        <v>126091347</v>
       </c>
       <c r="B30" t="n">
-        <v>80077</v>
+        <v>57656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556140</v>
+        <v>556316</v>
       </c>
       <c r="R30" t="n">
-        <v>7226895</v>
+        <v>7226927</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,6 +3589,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3619,10 +3624,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091347</v>
+        <v>126091034</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3654,10 +3659,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556316</v>
+        <v>556720</v>
       </c>
       <c r="R31" t="n">
-        <v>7226927</v>
+        <v>7227243</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3684,12 +3689,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3725,10 +3730,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091034</v>
+        <v>126091382</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>80081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3736,21 +3741,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3760,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556720</v>
+        <v>556140</v>
       </c>
       <c r="R32" t="n">
-        <v>7227243</v>
+        <v>7226895</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,17 +3795,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091349</v>
+        <v>126091042</v>
       </c>
       <c r="B33" t="n">
-        <v>57652</v>
+        <v>80109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556613</v>
+        <v>556817</v>
       </c>
       <c r="R33" t="n">
-        <v>7227051</v>
+        <v>7227591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,17 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091042</v>
+        <v>126091406</v>
       </c>
       <c r="B34" t="n">
-        <v>80105</v>
+        <v>80116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,21 +3943,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3972,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556817</v>
+        <v>556314</v>
       </c>
       <c r="R34" t="n">
-        <v>7227591</v>
+        <v>7226891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4038,10 +4033,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091414</v>
+        <v>126091349</v>
       </c>
       <c r="B35" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,21 +4044,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556303</v>
+        <v>556613</v>
       </c>
       <c r="R35" t="n">
-        <v>7226905</v>
+        <v>7227051</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,6 +4104,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4139,10 +4139,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091124</v>
+        <v>126091356</v>
       </c>
       <c r="B36" t="n">
-        <v>91256</v>
+        <v>80081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556698</v>
+        <v>556271</v>
       </c>
       <c r="R36" t="n">
-        <v>7227248</v>
+        <v>7227059</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4240,32 +4240,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091406</v>
+        <v>126091414</v>
       </c>
       <c r="B37" t="n">
-        <v>80112</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556314</v>
+        <v>556303</v>
       </c>
       <c r="R37" t="n">
-        <v>7226891</v>
+        <v>7226905</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,10 +4341,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091356</v>
+        <v>126091369</v>
       </c>
       <c r="B38" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556271</v>
+        <v>556333</v>
       </c>
       <c r="R38" t="n">
-        <v>7227059</v>
+        <v>7227009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4442,32 +4442,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091448</v>
+        <v>126091124</v>
       </c>
       <c r="B39" t="n">
-        <v>91908</v>
+        <v>91260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556484</v>
+        <v>556698</v>
       </c>
       <c r="R39" t="n">
-        <v>7226980</v>
+        <v>7227248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4543,10 +4543,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091369</v>
+        <v>126091013</v>
       </c>
       <c r="B40" t="n">
-        <v>80077</v>
+        <v>91242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4554,21 +4554,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556333</v>
+        <v>556830</v>
       </c>
       <c r="R40" t="n">
-        <v>7227009</v>
+        <v>7227704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4644,32 +4644,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091013</v>
+        <v>126091448</v>
       </c>
       <c r="B41" t="n">
-        <v>91238</v>
+        <v>91912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556830</v>
+        <v>556484</v>
       </c>
       <c r="R41" t="n">
-        <v>7227704</v>
+        <v>7226980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091403</v>
+        <v>126091075</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556357</v>
+        <v>556792</v>
       </c>
       <c r="R42" t="n">
-        <v>7227004</v>
+        <v>7227253</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,32 +4846,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091044</v>
+        <v>126091145</v>
       </c>
       <c r="B43" t="n">
-        <v>80105</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556826</v>
+        <v>556897</v>
       </c>
       <c r="R43" t="n">
-        <v>7227309</v>
+        <v>7227735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,6 +4917,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,32 +4952,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091107</v>
+        <v>126091129</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>91260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556723</v>
+        <v>556685</v>
       </c>
       <c r="R44" t="n">
-        <v>7227276</v>
+        <v>7227107</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,12 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091144</v>
+        <v>126091403</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557048</v>
+        <v>556357</v>
       </c>
       <c r="R45" t="n">
-        <v>7227797</v>
+        <v>7227004</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,12 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5149,32 +5154,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091422</v>
+        <v>126091044</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>80109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556407</v>
+        <v>556826</v>
       </c>
       <c r="R46" t="n">
-        <v>7226992</v>
+        <v>7227309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,17 +5219,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,32 +5255,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091145</v>
+        <v>126091107</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>80116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556897</v>
+        <v>556723</v>
       </c>
       <c r="R47" t="n">
-        <v>7227735</v>
+        <v>7227276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5326,11 +5326,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5361,10 +5356,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091129</v>
+        <v>126091144</v>
       </c>
       <c r="B48" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,21 +5367,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556685</v>
+        <v>557048</v>
       </c>
       <c r="R48" t="n">
-        <v>7227107</v>
+        <v>7227797</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,12 +5421,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5457,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091075</v>
+        <v>126091422</v>
       </c>
       <c r="B49" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5468,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5492,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556792</v>
+        <v>556407</v>
       </c>
       <c r="R49" t="n">
-        <v>7227253</v>
+        <v>7226992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,12 +5522,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5566,7 +5566,7 @@
         <v>126091348</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091381</v>
+        <v>126091148</v>
       </c>
       <c r="B52" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556280</v>
+        <v>556787</v>
       </c>
       <c r="R52" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5835,12 +5835,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5871,32 +5876,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091430</v>
+        <v>126091381</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5906,10 +5911,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556140</v>
+        <v>556280</v>
       </c>
       <c r="R53" t="n">
-        <v>7226895</v>
+        <v>7227059</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5972,10 +5977,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091438</v>
+        <v>126091430</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6007,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556350</v>
+        <v>556140</v>
       </c>
       <c r="R54" t="n">
-        <v>7226997</v>
+        <v>7226895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6073,27 +6078,27 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091148</v>
+        <v>126091438</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>80115</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6108,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556787</v>
+        <v>556350</v>
       </c>
       <c r="R55" t="n">
-        <v>7227605</v>
+        <v>7226997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,17 +6143,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6182,7 +6182,7 @@
         <v>126091401</v>
       </c>
       <c r="B56" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091400</v>
+        <v>126091343</v>
       </c>
       <c r="B57" t="n">
-        <v>80076</v>
+        <v>91242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556261</v>
+        <v>556373</v>
       </c>
       <c r="R57" t="n">
-        <v>7227068</v>
+        <v>7227010</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6381,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091409</v>
+        <v>126091400</v>
       </c>
       <c r="B58" t="n">
-        <v>80112</v>
+        <v>80080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556480</v>
+        <v>556261</v>
       </c>
       <c r="R58" t="n">
-        <v>7226980</v>
+        <v>7227068</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6482,32 +6482,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091151</v>
+        <v>126091409</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>80116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556935</v>
+        <v>556480</v>
       </c>
       <c r="R59" t="n">
-        <v>7227614</v>
+        <v>7226980</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,17 +6547,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6591,7 +6586,7 @@
         <v>126091442</v>
       </c>
       <c r="B60" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6689,10 +6684,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091417</v>
+        <v>126091151</v>
       </c>
       <c r="B61" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6700,21 +6695,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556559</v>
+        <v>556935</v>
       </c>
       <c r="R61" t="n">
-        <v>7226989</v>
+        <v>7227614</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6754,12 +6749,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091095</v>
+        <v>126091373</v>
       </c>
       <c r="B62" t="n">
-        <v>91534</v>
+        <v>80081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557005</v>
+        <v>556350</v>
       </c>
       <c r="R62" t="n">
-        <v>7227490</v>
+        <v>7226997</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6891,10 +6891,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091343</v>
+        <v>126091359</v>
       </c>
       <c r="B63" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6902,21 +6902,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556373</v>
+        <v>556280</v>
       </c>
       <c r="R63" t="n">
-        <v>7227010</v>
+        <v>7226845</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091373</v>
+        <v>126091361</v>
       </c>
       <c r="B64" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556350</v>
+        <v>556321</v>
       </c>
       <c r="R64" t="n">
-        <v>7226997</v>
+        <v>7226929</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091359</v>
+        <v>126091417</v>
       </c>
       <c r="B65" t="n">
-        <v>80077</v>
+        <v>91260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556280</v>
+        <v>556559</v>
       </c>
       <c r="R65" t="n">
-        <v>7226845</v>
+        <v>7226989</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091361</v>
+        <v>126091386</v>
       </c>
       <c r="B66" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556321</v>
+        <v>556480</v>
       </c>
       <c r="R66" t="n">
-        <v>7226929</v>
+        <v>7226980</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091386</v>
+        <v>126091066</v>
       </c>
       <c r="B67" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556480</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7226980</v>
+        <v>7227602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,12 +7360,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7396,10 +7401,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091066</v>
+        <v>126091095</v>
       </c>
       <c r="B68" t="n">
-        <v>80077</v>
+        <v>91538</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7407,21 +7412,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>557005</v>
       </c>
       <c r="R68" t="n">
-        <v>7227602</v>
+        <v>7227490</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7467,11 +7472,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,10 +7502,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091337</v>
+        <v>126091090</v>
       </c>
       <c r="B69" t="n">
-        <v>91203</v>
+        <v>79984</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7513,21 +7513,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556374</v>
+        <v>556690</v>
       </c>
       <c r="R69" t="n">
-        <v>7226996</v>
+        <v>7227262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7603,32 +7603,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091090</v>
+        <v>126091345</v>
       </c>
       <c r="B70" t="n">
-        <v>79980</v>
+        <v>57656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556690</v>
+        <v>556499</v>
       </c>
       <c r="R70" t="n">
-        <v>7227262</v>
+        <v>7227184</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,12 +7668,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7704,32 +7709,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B71" t="n">
-        <v>80077</v>
+        <v>91207</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7739,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R71" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7805,10 +7810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091345</v>
+        <v>126091384</v>
       </c>
       <c r="B72" t="n">
-        <v>57652</v>
+        <v>80081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7816,21 +7821,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7840,10 +7845,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556499</v>
+        <v>556376</v>
       </c>
       <c r="R72" t="n">
-        <v>7227184</v>
+        <v>7227009</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7876,11 +7881,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7914,7 +7914,7 @@
         <v>126091393</v>
       </c>
       <c r="B73" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091012</v>
+        <v>126091402</v>
       </c>
       <c r="B74" t="n">
-        <v>91203</v>
+        <v>80080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556977</v>
+        <v>556280</v>
       </c>
       <c r="R74" t="n">
-        <v>7227576</v>
+        <v>7227059</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091143</v>
+        <v>126091346</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>557106</v>
+        <v>556194</v>
       </c>
       <c r="R75" t="n">
-        <v>7227606</v>
+        <v>7226815</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,12 +8178,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8214,32 +8219,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091174</v>
+        <v>126091015</v>
       </c>
       <c r="B76" t="n">
-        <v>91648</v>
+        <v>91242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556888</v>
+        <v>556931</v>
       </c>
       <c r="R76" t="n">
-        <v>7227746</v>
+        <v>7227622</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8315,10 +8320,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091402</v>
+        <v>126091051</v>
       </c>
       <c r="B77" t="n">
-        <v>80076</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8326,21 +8331,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556280</v>
+        <v>556679</v>
       </c>
       <c r="R77" t="n">
-        <v>7227059</v>
+        <v>7227232</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,12 +8385,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,10 +8421,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091015</v>
+        <v>126091143</v>
       </c>
       <c r="B78" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,21 +8432,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556931</v>
+        <v>557106</v>
       </c>
       <c r="R78" t="n">
-        <v>7227622</v>
+        <v>7227606</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8517,32 +8522,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091051</v>
+        <v>126091012</v>
       </c>
       <c r="B79" t="n">
-        <v>79942</v>
+        <v>91207</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8552,10 +8557,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556679</v>
+        <v>556977</v>
       </c>
       <c r="R79" t="n">
-        <v>7227232</v>
+        <v>7227576</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8618,32 +8623,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091360</v>
+        <v>126091174</v>
       </c>
       <c r="B80" t="n">
-        <v>80077</v>
+        <v>91652</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8653,10 +8658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556326</v>
+        <v>556888</v>
       </c>
       <c r="R80" t="n">
-        <v>7226893</v>
+        <v>7227746</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8683,12 +8688,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8719,10 +8724,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091375</v>
+        <v>126091360</v>
       </c>
       <c r="B81" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8754,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556423</v>
+        <v>556326</v>
       </c>
       <c r="R81" t="n">
-        <v>7226984</v>
+        <v>7226893</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8820,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091067</v>
+        <v>126091375</v>
       </c>
       <c r="B82" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556690</v>
+        <v>556423</v>
       </c>
       <c r="R82" t="n">
-        <v>7227262</v>
+        <v>7226984</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8885,12 +8890,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8921,10 +8926,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091355</v>
+        <v>126091067</v>
       </c>
       <c r="B83" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8956,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556346</v>
+        <v>556690</v>
       </c>
       <c r="R83" t="n">
-        <v>7227118</v>
+        <v>7227262</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8986,12 +8991,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9022,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091346</v>
+        <v>126091355</v>
       </c>
       <c r="B84" t="n">
-        <v>57652</v>
+        <v>80081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9033,21 +9038,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9057,10 +9062,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556194</v>
+        <v>556346</v>
       </c>
       <c r="R84" t="n">
-        <v>7226815</v>
+        <v>7227118</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9093,11 +9098,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,10 +9128,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091166</v>
+        <v>126091351</v>
       </c>
       <c r="B85" t="n">
-        <v>80111</v>
+        <v>80109</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9139,21 +9139,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556690</v>
+        <v>556346</v>
       </c>
       <c r="R85" t="n">
-        <v>7227262</v>
+        <v>7227118</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9229,10 +9229,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091153</v>
+        <v>126091383</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9240,21 +9240,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556996</v>
+        <v>556230</v>
       </c>
       <c r="R86" t="n">
-        <v>7227559</v>
+        <v>7226809</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9330,32 +9330,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091165</v>
+        <v>126091377</v>
       </c>
       <c r="B87" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556874</v>
+        <v>556584</v>
       </c>
       <c r="R87" t="n">
-        <v>7227697</v>
+        <v>7227068</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9431,10 +9431,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091141</v>
+        <v>126091153</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556931</v>
+        <v>556996</v>
       </c>
       <c r="R88" t="n">
-        <v>7227622</v>
+        <v>7227559</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9502,11 +9502,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9537,32 +9532,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091351</v>
+        <v>126091141</v>
       </c>
       <c r="B89" t="n">
-        <v>80105</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9572,10 +9567,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556346</v>
+        <v>556931</v>
       </c>
       <c r="R89" t="n">
-        <v>7227118</v>
+        <v>7227622</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9602,12 +9597,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9638,10 +9638,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091383</v>
+        <v>126091372</v>
       </c>
       <c r="B90" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556230</v>
+        <v>556359</v>
       </c>
       <c r="R90" t="n">
-        <v>7226809</v>
+        <v>7226988</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9739,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091377</v>
+        <v>126091344</v>
       </c>
       <c r="B91" t="n">
-        <v>80077</v>
+        <v>91242</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556584</v>
+        <v>556452</v>
       </c>
       <c r="R91" t="n">
-        <v>7227068</v>
+        <v>7226989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9840,32 +9840,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091344</v>
+        <v>126091166</v>
       </c>
       <c r="B92" t="n">
-        <v>91238</v>
+        <v>80115</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556452</v>
+        <v>556690</v>
       </c>
       <c r="R92" t="n">
-        <v>7226989</v>
+        <v>7227262</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9941,32 +9941,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091372</v>
+        <v>126091165</v>
       </c>
       <c r="B93" t="n">
-        <v>80077</v>
+        <v>80115</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556359</v>
+        <v>556874</v>
       </c>
       <c r="R93" t="n">
-        <v>7226988</v>
+        <v>7227697</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,12 +10006,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10045,7 +10045,7 @@
         <v>126091027</v>
       </c>
       <c r="B94" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>126091441</v>
       </c>
       <c r="B95" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>126091167</v>
       </c>
       <c r="B96" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091418</v>
+        <v>126091405</v>
       </c>
       <c r="B97" t="n">
-        <v>91256</v>
+        <v>80116</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556550</v>
+        <v>556230</v>
       </c>
       <c r="R97" t="n">
-        <v>7227005</v>
+        <v>7226809</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10451,10 +10451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091125</v>
+        <v>126091418</v>
       </c>
       <c r="B98" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556893</v>
+        <v>556550</v>
       </c>
       <c r="R98" t="n">
-        <v>7227703</v>
+        <v>7227005</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10552,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091405</v>
+        <v>126091357</v>
       </c>
       <c r="B99" t="n">
-        <v>80112</v>
+        <v>80081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556230</v>
+        <v>556061</v>
       </c>
       <c r="R99" t="n">
-        <v>7226809</v>
+        <v>7226781</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091357</v>
+        <v>126091125</v>
       </c>
       <c r="B100" t="n">
-        <v>80077</v>
+        <v>91260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556061</v>
+        <v>556893</v>
       </c>
       <c r="R100" t="n">
-        <v>7226781</v>
+        <v>7227703</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10757,7 +10757,7 @@
         <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091392</v>
+        <v>126091019</v>
       </c>
       <c r="B102" t="n">
-        <v>56228</v>
+        <v>91242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>556271</v>
+        <v>557005</v>
       </c>
       <c r="R102" t="n">
-        <v>7226832</v>
+        <v>7227490</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,12 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091019</v>
+        <v>126091028</v>
       </c>
       <c r="B103" t="n">
-        <v>91238</v>
+        <v>57656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557005</v>
+        <v>557117</v>
       </c>
       <c r="R103" t="n">
-        <v>7227490</v>
+        <v>7227635</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11027,6 +11027,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11060,7 +11065,7 @@
         <v>126091358</v>
       </c>
       <c r="B104" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11158,10 +11163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091028</v>
+        <v>126091392</v>
       </c>
       <c r="B105" t="n">
-        <v>57652</v>
+        <v>56232</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11169,21 +11174,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11193,10 +11198,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557117</v>
+        <v>556271</v>
       </c>
       <c r="R105" t="n">
-        <v>7227635</v>
+        <v>7226832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11223,17 +11228,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091115</v>
+        <v>126091072</v>
       </c>
       <c r="B106" t="n">
-        <v>57756</v>
+        <v>80081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556797</v>
+        <v>556913</v>
       </c>
       <c r="R106" t="n">
-        <v>7227252</v>
+        <v>7227621</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11365,10 +11365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091072</v>
+        <v>126091380</v>
       </c>
       <c r="B107" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556913</v>
+        <v>556261</v>
       </c>
       <c r="R107" t="n">
-        <v>7227621</v>
+        <v>7227068</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091380</v>
+        <v>126091070</v>
       </c>
       <c r="B108" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556261</v>
+        <v>556723</v>
       </c>
       <c r="R108" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11567,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091070</v>
+        <v>126091416</v>
       </c>
       <c r="B109" t="n">
-        <v>80077</v>
+        <v>91260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556723</v>
+        <v>556600</v>
       </c>
       <c r="R109" t="n">
-        <v>7227276</v>
+        <v>7227123</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11668,10 +11668,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091341</v>
+        <v>126091010</v>
       </c>
       <c r="B110" t="n">
-        <v>91238</v>
+        <v>79009</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11679,21 +11679,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556187</v>
+        <v>556904</v>
       </c>
       <c r="R110" t="n">
-        <v>7226946</v>
+        <v>7227703</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11733,12 +11733,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11769,10 +11769,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091010</v>
+        <v>126091341</v>
       </c>
       <c r="B111" t="n">
-        <v>79005</v>
+        <v>91242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11780,21 +11780,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556904</v>
+        <v>556187</v>
       </c>
       <c r="R111" t="n">
-        <v>7227703</v>
+        <v>7226946</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11873,7 +11873,7 @@
         <v>126091407</v>
       </c>
       <c r="B112" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091416</v>
+        <v>126091421</v>
       </c>
       <c r="B113" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556600</v>
+        <v>556111</v>
       </c>
       <c r="R113" t="n">
-        <v>7227123</v>
+        <v>7226873</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12042,6 +12042,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12072,32 +12077,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091421</v>
+        <v>126091115</v>
       </c>
       <c r="B114" t="n">
-        <v>78973</v>
+        <v>57760</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12107,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556111</v>
+        <v>556797</v>
       </c>
       <c r="R114" t="n">
-        <v>7226873</v>
+        <v>7227252</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12137,17 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B115" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R115" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091084</v>
+        <v>126091068</v>
       </c>
       <c r="B116" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556737</v>
+        <v>556707</v>
       </c>
       <c r="R116" t="n">
-        <v>7227192</v>
+        <v>7227243</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12344,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091121</v>
+        <v>126091017</v>
       </c>
       <c r="B117" t="n">
-        <v>91234</v>
+        <v>91242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556907</v>
+        <v>556929</v>
       </c>
       <c r="R117" t="n">
-        <v>7227720</v>
+        <v>7227610</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091068</v>
+        <v>126091121</v>
       </c>
       <c r="B118" t="n">
-        <v>80077</v>
+        <v>91238</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556707</v>
+        <v>556907</v>
       </c>
       <c r="R118" t="n">
-        <v>7227243</v>
+        <v>7227720</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091017</v>
+        <v>126091102</v>
       </c>
       <c r="B119" t="n">
-        <v>91238</v>
+        <v>80080</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556929</v>
+        <v>556740</v>
       </c>
       <c r="R119" t="n">
-        <v>7227610</v>
+        <v>7227186</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091445</v>
+        <v>126091387</v>
       </c>
       <c r="B120" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556584</v>
+        <v>556497</v>
       </c>
       <c r="R120" t="n">
-        <v>7227109</v>
+        <v>7226978</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12784,32 +12784,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091444</v>
+        <v>126091379</v>
       </c>
       <c r="B121" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556584</v>
+        <v>556305</v>
       </c>
       <c r="R121" t="n">
-        <v>7227068</v>
+        <v>7227093</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,32 +12885,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091410</v>
+        <v>126091394</v>
       </c>
       <c r="B122" t="n">
-        <v>80112</v>
+        <v>91538</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R122" t="n">
-        <v>7227068</v>
+        <v>7226757</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,27 +12986,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091424</v>
+        <v>126091445</v>
       </c>
       <c r="B123" t="n">
-        <v>78973</v>
+        <v>80115</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R123" t="n">
-        <v>7226986</v>
+        <v>7227109</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,11 +13057,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13092,32 +13087,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091387</v>
+        <v>126091444</v>
       </c>
       <c r="B124" t="n">
-        <v>80077</v>
+        <v>80115</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13127,10 +13122,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R124" t="n">
-        <v>7226978</v>
+        <v>7227068</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13193,32 +13188,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091379</v>
+        <v>126091410</v>
       </c>
       <c r="B125" t="n">
-        <v>80077</v>
+        <v>80116</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13228,10 +13223,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R125" t="n">
-        <v>7227093</v>
+        <v>7227068</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13294,10 +13289,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091394</v>
+        <v>126091424</v>
       </c>
       <c r="B126" t="n">
-        <v>91534</v>
+        <v>78977</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13305,21 +13300,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13329,10 +13324,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556098</v>
+        <v>556549</v>
       </c>
       <c r="R126" t="n">
-        <v>7226757</v>
+        <v>7226986</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13365,6 +13360,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13398,7 +13398,7 @@
         <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>126091433</v>
       </c>
       <c r="B128" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>126091366</v>
       </c>
       <c r="B129" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>126091363</v>
       </c>
       <c r="B130" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>126091085</v>
       </c>
       <c r="B131" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13905,10 +13905,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091338</v>
+        <v>126091071</v>
       </c>
       <c r="B132" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13916,21 +13916,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556326</v>
+        <v>556807</v>
       </c>
       <c r="R132" t="n">
-        <v>7227114</v>
+        <v>7227608</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14006,10 +14006,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091071</v>
+        <v>126091367</v>
       </c>
       <c r="B133" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556807</v>
+        <v>556347</v>
       </c>
       <c r="R133" t="n">
-        <v>7227608</v>
+        <v>7226967</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14071,12 +14071,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14107,10 +14107,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091367</v>
+        <v>126091385</v>
       </c>
       <c r="B134" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556347</v>
+        <v>556410</v>
       </c>
       <c r="R134" t="n">
-        <v>7226967</v>
+        <v>7226996</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14208,10 +14208,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091385</v>
+        <v>126091338</v>
       </c>
       <c r="B135" t="n">
-        <v>80077</v>
+        <v>91242</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14219,21 +14219,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14243,10 +14243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556410</v>
+        <v>556326</v>
       </c>
       <c r="R135" t="n">
-        <v>7226996</v>
+        <v>7227114</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14309,10 +14309,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091029</v>
+        <v>126091063</v>
       </c>
       <c r="B136" t="n">
-        <v>57652</v>
+        <v>80081</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14320,21 +14320,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556819</v>
+        <v>556836</v>
       </c>
       <c r="R136" t="n">
-        <v>7227694</v>
+        <v>7227732</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14380,11 +14380,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14415,32 +14410,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091413</v>
+        <v>126091443</v>
       </c>
       <c r="B137" t="n">
-        <v>56835</v>
+        <v>80115</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556662</v>
+        <v>556529</v>
       </c>
       <c r="R137" t="n">
-        <v>7227178</v>
+        <v>7226958</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14486,11 +14481,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14521,10 +14511,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091431</v>
+        <v>126091437</v>
       </c>
       <c r="B138" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14556,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556179</v>
+        <v>556361</v>
       </c>
       <c r="R138" t="n">
-        <v>7226822</v>
+        <v>7227004</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14622,32 +14612,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091415</v>
+        <v>126091105</v>
       </c>
       <c r="B139" t="n">
-        <v>91256</v>
+        <v>80116</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14657,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556315</v>
+        <v>556807</v>
       </c>
       <c r="R139" t="n">
-        <v>7226927</v>
+        <v>7227608</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14687,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14723,32 +14713,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091429</v>
+        <v>126091413</v>
       </c>
       <c r="B140" t="n">
-        <v>80111</v>
+        <v>56839</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14758,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556272</v>
+        <v>556662</v>
       </c>
       <c r="R140" t="n">
-        <v>7227058</v>
+        <v>7227178</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14794,6 +14784,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14824,10 +14819,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091127</v>
+        <v>126091415</v>
       </c>
       <c r="B141" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14859,10 +14854,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556728</v>
+        <v>556315</v>
       </c>
       <c r="R141" t="n">
-        <v>7227249</v>
+        <v>7226927</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14889,12 +14884,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14925,32 +14920,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091443</v>
+        <v>126091127</v>
       </c>
       <c r="B142" t="n">
-        <v>80111</v>
+        <v>91260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14960,10 +14955,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556529</v>
+        <v>556728</v>
       </c>
       <c r="R142" t="n">
-        <v>7226958</v>
+        <v>7227249</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14990,12 +14985,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15026,27 +15021,27 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091437</v>
+        <v>126091140</v>
       </c>
       <c r="B143" t="n">
-        <v>80111</v>
+        <v>78977</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15061,10 +15056,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556361</v>
+        <v>557026</v>
       </c>
       <c r="R143" t="n">
-        <v>7227004</v>
+        <v>7227519</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15091,12 +15086,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,32 +15127,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091432</v>
+        <v>126091371</v>
       </c>
       <c r="B144" t="n">
-        <v>80111</v>
+        <v>80081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15162,10 +15162,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556230</v>
+        <v>556365</v>
       </c>
       <c r="R144" t="n">
-        <v>7226809</v>
+        <v>7227004</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15228,10 +15228,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091105</v>
+        <v>126091431</v>
       </c>
       <c r="B145" t="n">
-        <v>80112</v>
+        <v>80115</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15239,21 +15239,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15263,10 +15263,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556807</v>
+        <v>556179</v>
       </c>
       <c r="R145" t="n">
-        <v>7227608</v>
+        <v>7226822</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15329,27 +15329,27 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091140</v>
+        <v>126091429</v>
       </c>
       <c r="B146" t="n">
-        <v>78973</v>
+        <v>80115</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>557026</v>
+        <v>556272</v>
       </c>
       <c r="R146" t="n">
-        <v>7227519</v>
+        <v>7227058</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15394,17 +15394,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15435,32 +15430,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091371</v>
+        <v>126091432</v>
       </c>
       <c r="B147" t="n">
-        <v>80077</v>
+        <v>80115</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15470,10 +15465,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556365</v>
+        <v>556230</v>
       </c>
       <c r="R147" t="n">
-        <v>7227004</v>
+        <v>7226809</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15536,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091063</v>
+        <v>126091029</v>
       </c>
       <c r="B148" t="n">
-        <v>80077</v>
+        <v>57656</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15547,21 +15542,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15571,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556836</v>
+        <v>556819</v>
       </c>
       <c r="R148" t="n">
-        <v>7227732</v>
+        <v>7227694</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15607,6 +15602,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15640,7 +15640,7 @@
         <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15743,32 +15743,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091397</v>
+        <v>126091388</v>
       </c>
       <c r="B150" t="n">
-        <v>80104</v>
+        <v>80081</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556378</v>
+        <v>556529</v>
       </c>
       <c r="R150" t="n">
-        <v>7226996</v>
+        <v>7226958</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15844,32 +15844,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091404</v>
+        <v>126091378</v>
       </c>
       <c r="B151" t="n">
-        <v>80112</v>
+        <v>80081</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15879,10 +15879,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556272</v>
+        <v>556353</v>
       </c>
       <c r="R151" t="n">
-        <v>7227058</v>
+        <v>7227115</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15945,27 +15945,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091169</v>
+        <v>126091149</v>
       </c>
       <c r="B152" t="n">
-        <v>80111</v>
+        <v>78977</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556756</v>
+        <v>556807</v>
       </c>
       <c r="R152" t="n">
-        <v>7227253</v>
+        <v>7227608</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16016,6 +16016,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16046,10 +16051,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091149</v>
+        <v>126091350</v>
       </c>
       <c r="B153" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16057,21 +16062,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16081,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556807</v>
+        <v>556589</v>
       </c>
       <c r="R153" t="n">
-        <v>7227608</v>
+        <v>7227059</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16111,17 +16116,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Lång bål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,10 +16157,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091388</v>
+        <v>126091040</v>
       </c>
       <c r="B154" t="n">
-        <v>80077</v>
+        <v>57656</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16163,21 +16168,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16187,10 +16192,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556529</v>
+        <v>556781</v>
       </c>
       <c r="R154" t="n">
-        <v>7226958</v>
+        <v>7227272</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16217,12 +16222,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16253,32 +16263,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091378</v>
+        <v>126091397</v>
       </c>
       <c r="B155" t="n">
-        <v>80077</v>
+        <v>80108</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16288,10 +16298,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556353</v>
+        <v>556378</v>
       </c>
       <c r="R155" t="n">
-        <v>7227115</v>
+        <v>7226996</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16354,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091350</v>
+        <v>126091404</v>
       </c>
       <c r="B156" t="n">
-        <v>57652</v>
+        <v>80116</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16389,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556589</v>
+        <v>556272</v>
       </c>
       <c r="R156" t="n">
-        <v>7227059</v>
+        <v>7227058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16425,11 +16435,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16460,32 +16465,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091040</v>
+        <v>126091169</v>
       </c>
       <c r="B157" t="n">
-        <v>57652</v>
+        <v>80115</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16495,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556781</v>
+        <v>556756</v>
       </c>
       <c r="R157" t="n">
-        <v>7227272</v>
+        <v>7227253</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16531,11 +16536,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16569,7 +16569,7 @@
         <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126091347</v>
+        <v>126091382</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556316</v>
+        <v>556140</v>
       </c>
       <c r="R30" t="n">
-        <v>7226927</v>
+        <v>7226895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3589,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3624,7 +3619,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126091034</v>
+        <v>126091347</v>
       </c>
       <c r="B31" t="n">
         <v>57656</v>
@@ -3659,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556720</v>
+        <v>556316</v>
       </c>
       <c r="R31" t="n">
-        <v>7227243</v>
+        <v>7226927</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3689,12 +3684,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3730,10 +3725,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126091382</v>
+        <v>126091034</v>
       </c>
       <c r="B32" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3741,21 +3736,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3760,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556140</v>
+        <v>556720</v>
       </c>
       <c r="R32" t="n">
-        <v>7226895</v>
+        <v>7227243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,12 +3790,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091090</v>
+        <v>126091345</v>
       </c>
       <c r="B69" t="n">
-        <v>79984</v>
+        <v>57656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556690</v>
+        <v>556499</v>
       </c>
       <c r="R69" t="n">
-        <v>7227262</v>
+        <v>7227184</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7567,12 +7567,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7603,32 +7608,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091345</v>
+        <v>126091337</v>
       </c>
       <c r="B70" t="n">
-        <v>57656</v>
+        <v>91207</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7638,10 +7643,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556499</v>
+        <v>556374</v>
       </c>
       <c r="R70" t="n">
-        <v>7227184</v>
+        <v>7226996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7674,11 +7679,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7709,32 +7709,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091337</v>
+        <v>126091384</v>
       </c>
       <c r="B71" t="n">
-        <v>91207</v>
+        <v>80081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556374</v>
+        <v>556376</v>
       </c>
       <c r="R71" t="n">
-        <v>7226996</v>
+        <v>7227009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,32 +7810,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091384</v>
+        <v>126091090</v>
       </c>
       <c r="B72" t="n">
-        <v>80081</v>
+        <v>79984</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556376</v>
+        <v>556690</v>
       </c>
       <c r="R72" t="n">
-        <v>7227009</v>
+        <v>7227262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091072</v>
+        <v>126091115</v>
       </c>
       <c r="B106" t="n">
-        <v>80081</v>
+        <v>57760</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556913</v>
+        <v>556797</v>
       </c>
       <c r="R106" t="n">
-        <v>7227621</v>
+        <v>7227252</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091380</v>
+        <v>126091072</v>
       </c>
       <c r="B107" t="n">
         <v>80081</v>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556261</v>
+        <v>556913</v>
       </c>
       <c r="R107" t="n">
-        <v>7227068</v>
+        <v>7227621</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,7 +11466,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091070</v>
+        <v>126091380</v>
       </c>
       <c r="B108" t="n">
         <v>80081</v>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556723</v>
+        <v>556261</v>
       </c>
       <c r="R108" t="n">
-        <v>7227276</v>
+        <v>7227068</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11567,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091416</v>
+        <v>126091070</v>
       </c>
       <c r="B109" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556600</v>
+        <v>556723</v>
       </c>
       <c r="R109" t="n">
-        <v>7227123</v>
+        <v>7227276</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11668,10 +11668,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091010</v>
+        <v>126091416</v>
       </c>
       <c r="B110" t="n">
-        <v>79009</v>
+        <v>91260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11679,21 +11679,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556904</v>
+        <v>556600</v>
       </c>
       <c r="R110" t="n">
-        <v>7227703</v>
+        <v>7227123</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11733,12 +11733,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11769,10 +11769,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091341</v>
+        <v>126091010</v>
       </c>
       <c r="B111" t="n">
-        <v>91242</v>
+        <v>79009</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11780,21 +11780,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556187</v>
+        <v>556904</v>
       </c>
       <c r="R111" t="n">
-        <v>7226946</v>
+        <v>7227703</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11870,32 +11870,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091407</v>
+        <v>126091341</v>
       </c>
       <c r="B112" t="n">
-        <v>80116</v>
+        <v>91242</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556365</v>
+        <v>556187</v>
       </c>
       <c r="R112" t="n">
-        <v>7227004</v>
+        <v>7226946</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11971,32 +11971,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091421</v>
+        <v>126091407</v>
       </c>
       <c r="B113" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556111</v>
+        <v>556365</v>
       </c>
       <c r="R113" t="n">
-        <v>7226873</v>
+        <v>7227004</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12042,11 +12042,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,32 +12072,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091115</v>
+        <v>126091421</v>
       </c>
       <c r="B114" t="n">
-        <v>57760</v>
+        <v>78977</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556797</v>
+        <v>556111</v>
       </c>
       <c r="R114" t="n">
-        <v>7227252</v>
+        <v>7226873</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12142,12 +12137,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091084</v>
+        <v>126091017</v>
       </c>
       <c r="B115" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556737</v>
+        <v>556929</v>
       </c>
       <c r="R115" t="n">
-        <v>7227192</v>
+        <v>7227610</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12243,12 +12243,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091068</v>
+        <v>126091121</v>
       </c>
       <c r="B116" t="n">
-        <v>80081</v>
+        <v>91238</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556707</v>
+        <v>556907</v>
       </c>
       <c r="R116" t="n">
-        <v>7227243</v>
+        <v>7227720</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091017</v>
+        <v>126091102</v>
       </c>
       <c r="B117" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556929</v>
+        <v>556740</v>
       </c>
       <c r="R117" t="n">
-        <v>7227610</v>
+        <v>7227186</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,12 +12445,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091121</v>
+        <v>126091084</v>
       </c>
       <c r="B118" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556907</v>
+        <v>556737</v>
       </c>
       <c r="R118" t="n">
-        <v>7227720</v>
+        <v>7227192</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12546,12 +12546,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091102</v>
+        <v>126091068</v>
       </c>
       <c r="B119" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556740</v>
+        <v>556707</v>
       </c>
       <c r="R119" t="n">
-        <v>7227186</v>
+        <v>7227243</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091387</v>
+        <v>126091052</v>
       </c>
       <c r="B120" t="n">
-        <v>80081</v>
+        <v>98370</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556497</v>
+        <v>557007</v>
       </c>
       <c r="R120" t="n">
-        <v>7226978</v>
+        <v>7227805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12748,12 +12748,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12784,7 +12784,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091379</v>
+        <v>126091387</v>
       </c>
       <c r="B121" t="n">
         <v>80081</v>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556305</v>
+        <v>556497</v>
       </c>
       <c r="R121" t="n">
-        <v>7227093</v>
+        <v>7226978</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,10 +12885,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091394</v>
+        <v>126091379</v>
       </c>
       <c r="B122" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12896,21 +12896,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556098</v>
+        <v>556305</v>
       </c>
       <c r="R122" t="n">
-        <v>7226757</v>
+        <v>7227093</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,32 +12986,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091445</v>
+        <v>126091394</v>
       </c>
       <c r="B123" t="n">
-        <v>80115</v>
+        <v>91538</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R123" t="n">
-        <v>7227109</v>
+        <v>7226757</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13087,7 +13087,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091444</v>
+        <v>126091445</v>
       </c>
       <c r="B124" t="n">
         <v>80115</v>
@@ -13125,7 +13125,7 @@
         <v>556584</v>
       </c>
       <c r="R124" t="n">
-        <v>7227068</v>
+        <v>7227109</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13188,10 +13188,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091410</v>
+        <v>126091444</v>
       </c>
       <c r="B125" t="n">
-        <v>80116</v>
+        <v>80115</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13199,21 +13199,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13289,32 +13289,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091424</v>
+        <v>126091410</v>
       </c>
       <c r="B126" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13324,10 +13324,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556549</v>
+        <v>556584</v>
       </c>
       <c r="R126" t="n">
-        <v>7226986</v>
+        <v>7227068</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13360,11 +13360,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13395,32 +13390,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091052</v>
+        <v>126091424</v>
       </c>
       <c r="B127" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13430,10 +13425,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>557007</v>
+        <v>556549</v>
       </c>
       <c r="R127" t="n">
-        <v>7227805</v>
+        <v>7226986</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,12 +13455,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13496,32 +13496,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091433</v>
+        <v>126091366</v>
       </c>
       <c r="B128" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556280</v>
+        <v>556348</v>
       </c>
       <c r="R128" t="n">
-        <v>7226845</v>
+        <v>7226965</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13597,7 +13597,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091366</v>
+        <v>126091363</v>
       </c>
       <c r="B129" t="n">
         <v>80081</v>
@@ -13632,10 +13632,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556348</v>
+        <v>556361</v>
       </c>
       <c r="R129" t="n">
-        <v>7226965</v>
+        <v>7226943</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13668,6 +13668,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13698,7 +13703,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126091363</v>
+        <v>126091085</v>
       </c>
       <c r="B130" t="n">
         <v>80081</v>
@@ -13733,10 +13738,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>556361</v>
+        <v>556709</v>
       </c>
       <c r="R130" t="n">
-        <v>7226943</v>
+        <v>7227134</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13763,17 +13768,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13804,7 +13804,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126091085</v>
+        <v>126091071</v>
       </c>
       <c r="B131" t="n">
         <v>80081</v>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>556709</v>
+        <v>556807</v>
       </c>
       <c r="R131" t="n">
-        <v>7227134</v>
+        <v>7227608</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13905,7 +13905,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091071</v>
+        <v>126091367</v>
       </c>
       <c r="B132" t="n">
         <v>80081</v>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556807</v>
+        <v>556347</v>
       </c>
       <c r="R132" t="n">
-        <v>7227608</v>
+        <v>7226967</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14006,7 +14006,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091367</v>
+        <v>126091385</v>
       </c>
       <c r="B133" t="n">
         <v>80081</v>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556347</v>
+        <v>556410</v>
       </c>
       <c r="R133" t="n">
-        <v>7226967</v>
+        <v>7226996</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14107,10 +14107,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091385</v>
+        <v>126091338</v>
       </c>
       <c r="B134" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14118,21 +14118,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556410</v>
+        <v>556326</v>
       </c>
       <c r="R134" t="n">
-        <v>7226996</v>
+        <v>7227114</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14208,32 +14208,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091338</v>
+        <v>126091433</v>
       </c>
       <c r="B135" t="n">
-        <v>91242</v>
+        <v>80115</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14243,10 +14243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556326</v>
+        <v>556280</v>
       </c>
       <c r="R135" t="n">
-        <v>7227114</v>
+        <v>7226845</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091063</v>
+        <v>126091431</v>
       </c>
       <c r="B136" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556836</v>
+        <v>556179</v>
       </c>
       <c r="R136" t="n">
-        <v>7227732</v>
+        <v>7226822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14410,7 +14410,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091443</v>
+        <v>126091429</v>
       </c>
       <c r="B137" t="n">
         <v>80115</v>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556529</v>
+        <v>556272</v>
       </c>
       <c r="R137" t="n">
-        <v>7226958</v>
+        <v>7227058</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14511,7 +14511,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091437</v>
+        <v>126091443</v>
       </c>
       <c r="B138" t="n">
         <v>80115</v>
@@ -14546,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556361</v>
+        <v>556529</v>
       </c>
       <c r="R138" t="n">
-        <v>7227004</v>
+        <v>7226958</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,10 +14612,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091105</v>
+        <v>126091437</v>
       </c>
       <c r="B139" t="n">
-        <v>80116</v>
+        <v>80115</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14623,21 +14623,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556807</v>
+        <v>556361</v>
       </c>
       <c r="R139" t="n">
-        <v>7227608</v>
+        <v>7227004</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14677,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14713,32 +14713,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091413</v>
+        <v>126091432</v>
       </c>
       <c r="B140" t="n">
-        <v>56839</v>
+        <v>80115</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556662</v>
+        <v>556230</v>
       </c>
       <c r="R140" t="n">
-        <v>7227178</v>
+        <v>7226809</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14784,11 +14784,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14819,32 +14814,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091415</v>
+        <v>126091105</v>
       </c>
       <c r="B141" t="n">
-        <v>91260</v>
+        <v>80116</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14854,10 +14849,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556315</v>
+        <v>556807</v>
       </c>
       <c r="R141" t="n">
-        <v>7226927</v>
+        <v>7227608</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14884,12 +14879,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14920,7 +14915,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091127</v>
+        <v>126091415</v>
       </c>
       <c r="B142" t="n">
         <v>91260</v>
@@ -14955,10 +14950,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556728</v>
+        <v>556315</v>
       </c>
       <c r="R142" t="n">
-        <v>7227249</v>
+        <v>7226927</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14985,12 +14980,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15021,10 +15016,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091140</v>
+        <v>126091127</v>
       </c>
       <c r="B143" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15032,21 +15027,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15056,10 +15051,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>557026</v>
+        <v>556728</v>
       </c>
       <c r="R143" t="n">
-        <v>7227519</v>
+        <v>7227249</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15092,11 +15087,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,10 +15117,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091371</v>
+        <v>126091140</v>
       </c>
       <c r="B144" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15138,21 +15128,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15162,10 +15152,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556365</v>
+        <v>557026</v>
       </c>
       <c r="R144" t="n">
-        <v>7227004</v>
+        <v>7227519</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15192,12 +15182,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15228,32 +15223,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091431</v>
+        <v>126091371</v>
       </c>
       <c r="B145" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15263,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556179</v>
+        <v>556365</v>
       </c>
       <c r="R145" t="n">
-        <v>7226822</v>
+        <v>7227004</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15329,32 +15324,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091429</v>
+        <v>126091063</v>
       </c>
       <c r="B146" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15359,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556272</v>
+        <v>556836</v>
       </c>
       <c r="R146" t="n">
-        <v>7227058</v>
+        <v>7227732</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15394,12 +15389,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15430,32 +15425,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091432</v>
+        <v>126091029</v>
       </c>
       <c r="B147" t="n">
-        <v>80115</v>
+        <v>57656</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556230</v>
+        <v>556819</v>
       </c>
       <c r="R147" t="n">
-        <v>7226809</v>
+        <v>7227694</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15495,12 +15490,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091029</v>
+        <v>126091413</v>
       </c>
       <c r="B148" t="n">
-        <v>57656</v>
+        <v>56839</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556819</v>
+        <v>556662</v>
       </c>
       <c r="R148" t="n">
-        <v>7227694</v>
+        <v>7227178</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15596,17 +15596,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091395</v>
+        <v>126091362</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556308</v>
+        <v>556369</v>
       </c>
       <c r="R2" t="n">
-        <v>7226876</v>
+        <v>7226946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091342</v>
+        <v>126091065</v>
       </c>
       <c r="B3" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556306</v>
+        <v>556817</v>
       </c>
       <c r="R3" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091440</v>
+        <v>126091370</v>
       </c>
       <c r="B4" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556465</v>
+        <v>556364</v>
       </c>
       <c r="R4" t="n">
-        <v>7226995</v>
+        <v>7226989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091408</v>
+        <v>126091128</v>
       </c>
       <c r="B5" t="n">
-        <v>80116</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556467</v>
+        <v>556830</v>
       </c>
       <c r="R5" t="n">
-        <v>7226993</v>
+        <v>7227331</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091362</v>
+        <v>126091123</v>
       </c>
       <c r="B6" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556369</v>
+        <v>557106</v>
       </c>
       <c r="R6" t="n">
-        <v>7226946</v>
+        <v>7227606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091065</v>
+        <v>126091408</v>
       </c>
       <c r="B7" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556817</v>
+        <v>556467</v>
       </c>
       <c r="R7" t="n">
-        <v>7227591</v>
+        <v>7226993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091370</v>
+        <v>126091440</v>
       </c>
       <c r="B8" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556364</v>
+        <v>556465</v>
       </c>
       <c r="R8" t="n">
-        <v>7226989</v>
+        <v>7226995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091128</v>
+        <v>126091395</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556830</v>
+        <v>556308</v>
       </c>
       <c r="R9" t="n">
-        <v>7227331</v>
+        <v>7226876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091123</v>
+        <v>126091342</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557106</v>
+        <v>556306</v>
       </c>
       <c r="R10" t="n">
-        <v>7227606</v>
+        <v>7226876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091147</v>
+        <v>126091389</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556819</v>
+        <v>556589</v>
       </c>
       <c r="R11" t="n">
-        <v>7227694</v>
+        <v>7227109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,17 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,7 +1685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091389</v>
+        <v>126091064</v>
       </c>
       <c r="B12" t="n">
         <v>80081</v>
@@ -1725,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556589</v>
+        <v>556833</v>
       </c>
       <c r="R12" t="n">
-        <v>7227109</v>
+        <v>7227720</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,7 +1786,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091064</v>
+        <v>126091374</v>
       </c>
       <c r="B13" t="n">
         <v>80081</v>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556833</v>
+        <v>556371</v>
       </c>
       <c r="R13" t="n">
-        <v>7227720</v>
+        <v>7226988</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1856,12 +1851,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091335</v>
+        <v>126091428</v>
       </c>
       <c r="B14" t="n">
-        <v>91207</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556339</v>
+        <v>556314</v>
       </c>
       <c r="R14" t="n">
-        <v>7226946</v>
+        <v>7226891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091374</v>
+        <v>126091420</v>
       </c>
       <c r="B15" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2004,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2028,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556371</v>
+        <v>556284</v>
       </c>
       <c r="R15" t="n">
-        <v>7226988</v>
+        <v>7227078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,6 +2059,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,32 +2094,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091365</v>
+        <v>126091043</v>
       </c>
       <c r="B16" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556359</v>
+        <v>556756</v>
       </c>
       <c r="R16" t="n">
-        <v>7226943</v>
+        <v>7227253</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091043</v>
+        <v>126091335</v>
       </c>
       <c r="B17" t="n">
-        <v>80109</v>
+        <v>91207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556756</v>
+        <v>556339</v>
       </c>
       <c r="R17" t="n">
-        <v>7227253</v>
+        <v>7226946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2296,27 +2296,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091439</v>
+        <v>126091425</v>
       </c>
       <c r="B18" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556374</v>
+        <v>556591</v>
       </c>
       <c r="R18" t="n">
-        <v>7227007</v>
+        <v>7227022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2367,6 +2367,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,27 +2402,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091420</v>
+        <v>126091439</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2432,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556284</v>
+        <v>556374</v>
       </c>
       <c r="R19" t="n">
-        <v>7227078</v>
+        <v>7227007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2468,11 +2473,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,27 +2503,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091428</v>
+        <v>126091147</v>
       </c>
       <c r="B20" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556314</v>
+        <v>556819</v>
       </c>
       <c r="R20" t="n">
-        <v>7226891</v>
+        <v>7227694</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,12 +2568,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091425</v>
+        <v>126091365</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556591</v>
+        <v>556359</v>
       </c>
       <c r="R21" t="n">
-        <v>7227022</v>
+        <v>7226943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,11 +2680,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091164</v>
+        <v>126091435</v>
       </c>
       <c r="B24" t="n">
-        <v>88651</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556775</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091340</v>
+        <v>126091106</v>
       </c>
       <c r="B25" t="n">
-        <v>91242</v>
+        <v>80116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556312</v>
+        <v>556709</v>
       </c>
       <c r="R25" t="n">
-        <v>7227107</v>
+        <v>7227248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091435</v>
+        <v>126091164</v>
       </c>
       <c r="B26" t="n">
-        <v>80115</v>
+        <v>88651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556359</v>
+        <v>556775</v>
       </c>
       <c r="R26" t="n">
-        <v>7226941</v>
+        <v>7227253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091106</v>
+        <v>126091340</v>
       </c>
       <c r="B27" t="n">
-        <v>80116</v>
+        <v>91242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556709</v>
+        <v>556312</v>
       </c>
       <c r="R27" t="n">
-        <v>7227248</v>
+        <v>7227107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091042</v>
+        <v>126091356</v>
       </c>
       <c r="B33" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556817</v>
+        <v>556271</v>
       </c>
       <c r="R33" t="n">
-        <v>7227591</v>
+        <v>7227059</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,32 +3932,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091406</v>
+        <v>126091414</v>
       </c>
       <c r="B34" t="n">
-        <v>80116</v>
+        <v>91260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556314</v>
+        <v>556303</v>
       </c>
       <c r="R34" t="n">
-        <v>7226891</v>
+        <v>7226905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091349</v>
+        <v>126091369</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4044,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556613</v>
+        <v>556333</v>
       </c>
       <c r="R35" t="n">
-        <v>7227051</v>
+        <v>7227009</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4104,11 +4104,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4139,10 +4134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091356</v>
+        <v>126091124</v>
       </c>
       <c r="B36" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,21 +4145,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556271</v>
+        <v>556698</v>
       </c>
       <c r="R36" t="n">
-        <v>7227059</v>
+        <v>7227248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4240,10 +4235,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091414</v>
+        <v>126091013</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>91242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4251,21 +4246,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556303</v>
+        <v>556830</v>
       </c>
       <c r="R37" t="n">
-        <v>7226905</v>
+        <v>7227704</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4305,12 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,32 +4336,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091369</v>
+        <v>126091042</v>
       </c>
       <c r="B38" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4376,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556333</v>
+        <v>556817</v>
       </c>
       <c r="R38" t="n">
-        <v>7227009</v>
+        <v>7227591</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,12 +4401,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4442,32 +4437,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091124</v>
+        <v>126091406</v>
       </c>
       <c r="B39" t="n">
-        <v>91260</v>
+        <v>80116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556698</v>
+        <v>556314</v>
       </c>
       <c r="R39" t="n">
-        <v>7227248</v>
+        <v>7226891</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4543,32 +4538,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091013</v>
+        <v>126091448</v>
       </c>
       <c r="B40" t="n">
-        <v>91242</v>
+        <v>91912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556830</v>
+        <v>556484</v>
       </c>
       <c r="R40" t="n">
-        <v>7227704</v>
+        <v>7226980</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,12 +4603,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4644,32 +4639,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091448</v>
+        <v>126091349</v>
       </c>
       <c r="B41" t="n">
-        <v>91912</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556484</v>
+        <v>556613</v>
       </c>
       <c r="R41" t="n">
-        <v>7226980</v>
+        <v>7227051</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,6 +4710,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091145</v>
+        <v>126091129</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556897</v>
+        <v>556685</v>
       </c>
       <c r="R43" t="n">
-        <v>7227735</v>
+        <v>7227107</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,17 +4911,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4952,10 +4947,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091129</v>
+        <v>126091403</v>
       </c>
       <c r="B44" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4963,21 +4958,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4987,10 +4982,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556685</v>
+        <v>556357</v>
       </c>
       <c r="R44" t="n">
-        <v>7227107</v>
+        <v>7227004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5017,12 +5012,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5053,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091403</v>
+        <v>126091145</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556357</v>
+        <v>556897</v>
       </c>
       <c r="R45" t="n">
-        <v>7227004</v>
+        <v>7227735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,12 +5113,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091044</v>
+        <v>126091107</v>
       </c>
       <c r="B46" t="n">
-        <v>80109</v>
+        <v>80116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556826</v>
+        <v>556723</v>
       </c>
       <c r="R46" t="n">
-        <v>7227309</v>
+        <v>7227276</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5255,10 +5255,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091107</v>
+        <v>126091044</v>
       </c>
       <c r="B47" t="n">
-        <v>80116</v>
+        <v>80109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5266,21 +5266,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5290,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556723</v>
+        <v>556826</v>
       </c>
       <c r="R47" t="n">
-        <v>7227276</v>
+        <v>7227309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,7 +5356,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B48" t="n">
         <v>78977</v>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R48" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5421,12 +5421,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5457,7 +5462,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091422</v>
+        <v>126091144</v>
       </c>
       <c r="B49" t="n">
         <v>78977</v>
@@ -5492,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556407</v>
+        <v>557048</v>
       </c>
       <c r="R49" t="n">
-        <v>7226992</v>
+        <v>7227797</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5522,17 +5527,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5672,7 +5672,7 @@
         <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091148</v>
+        <v>126091381</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5781,21 +5781,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556787</v>
+        <v>556280</v>
       </c>
       <c r="R52" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5835,17 +5835,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5876,10 +5871,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091381</v>
+        <v>126091148</v>
       </c>
       <c r="B53" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5887,21 +5882,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5911,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556280</v>
+        <v>556787</v>
       </c>
       <c r="R53" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5941,12 +5936,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5977,7 +5977,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091430</v>
+        <v>126091438</v>
       </c>
       <c r="B54" t="n">
         <v>80115</v>
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556140</v>
+        <v>556350</v>
       </c>
       <c r="R54" t="n">
-        <v>7226895</v>
+        <v>7226997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,7 +6078,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091438</v>
+        <v>126091430</v>
       </c>
       <c r="B55" t="n">
         <v>80115</v>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556350</v>
+        <v>556140</v>
       </c>
       <c r="R55" t="n">
-        <v>7226997</v>
+        <v>7226895</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,32 +6280,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091343</v>
+        <v>126091442</v>
       </c>
       <c r="B57" t="n">
-        <v>91242</v>
+        <v>80115</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556373</v>
+        <v>556494</v>
       </c>
       <c r="R57" t="n">
-        <v>7227010</v>
+        <v>7226972</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091400</v>
+        <v>126091151</v>
       </c>
       <c r="B58" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556261</v>
+        <v>556935</v>
       </c>
       <c r="R58" t="n">
-        <v>7227068</v>
+        <v>7227614</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6446,12 +6446,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091409</v>
+        <v>126091400</v>
       </c>
       <c r="B59" t="n">
-        <v>80116</v>
+        <v>80080</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556480</v>
+        <v>556261</v>
       </c>
       <c r="R59" t="n">
-        <v>7226980</v>
+        <v>7227068</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,10 +6588,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091442</v>
+        <v>126091409</v>
       </c>
       <c r="B60" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6594,21 +6599,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556494</v>
+        <v>556480</v>
       </c>
       <c r="R60" t="n">
-        <v>7226972</v>
+        <v>7226980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6684,10 +6689,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091151</v>
+        <v>126091095</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>91538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6695,21 +6700,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6719,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556935</v>
+        <v>557005</v>
       </c>
       <c r="R61" t="n">
-        <v>7227614</v>
+        <v>7227490</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6755,11 +6760,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091373</v>
+        <v>126091343</v>
       </c>
       <c r="B62" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556350</v>
+        <v>556373</v>
       </c>
       <c r="R62" t="n">
-        <v>7226997</v>
+        <v>7227010</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091359</v>
+        <v>126091373</v>
       </c>
       <c r="B63" t="n">
         <v>80081</v>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556280</v>
+        <v>556350</v>
       </c>
       <c r="R63" t="n">
-        <v>7226845</v>
+        <v>7226997</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091361</v>
+        <v>126091359</v>
       </c>
       <c r="B64" t="n">
         <v>80081</v>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556321</v>
+        <v>556280</v>
       </c>
       <c r="R64" t="n">
-        <v>7226929</v>
+        <v>7226845</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091417</v>
+        <v>126091361</v>
       </c>
       <c r="B65" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556559</v>
+        <v>556321</v>
       </c>
       <c r="R65" t="n">
-        <v>7226989</v>
+        <v>7226929</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091386</v>
+        <v>126091417</v>
       </c>
       <c r="B66" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556480</v>
+        <v>556559</v>
       </c>
       <c r="R66" t="n">
-        <v>7226980</v>
+        <v>7226989</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091066</v>
+        <v>126091386</v>
       </c>
       <c r="B67" t="n">
         <v>80081</v>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>556480</v>
       </c>
       <c r="R67" t="n">
-        <v>7227602</v>
+        <v>7226980</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,17 +7360,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7401,10 +7396,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091095</v>
+        <v>126091066</v>
       </c>
       <c r="B68" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7412,21 +7407,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>557005</v>
+        <v>556946</v>
       </c>
       <c r="R68" t="n">
-        <v>7227490</v>
+        <v>7227602</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7472,6 +7467,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,10 +7502,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091345</v>
+        <v>126091384</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7513,21 +7513,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556499</v>
+        <v>556376</v>
       </c>
       <c r="R69" t="n">
-        <v>7227184</v>
+        <v>7227009</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,11 +7573,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7608,10 +7603,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091337</v>
+        <v>126091090</v>
       </c>
       <c r="B70" t="n">
-        <v>91207</v>
+        <v>79984</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7619,21 +7614,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7643,10 +7638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556374</v>
+        <v>556690</v>
       </c>
       <c r="R70" t="n">
-        <v>7226996</v>
+        <v>7227262</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7673,12 +7668,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7709,32 +7704,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B71" t="n">
-        <v>80081</v>
+        <v>91207</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7744,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R71" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,32 +7805,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091090</v>
+        <v>126091345</v>
       </c>
       <c r="B72" t="n">
-        <v>79984</v>
+        <v>57656</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7845,10 +7840,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556690</v>
+        <v>556499</v>
       </c>
       <c r="R72" t="n">
-        <v>7227262</v>
+        <v>7227184</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7875,12 +7870,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7911,32 +7911,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091393</v>
+        <v>126091015</v>
       </c>
       <c r="B73" t="n">
-        <v>79984</v>
+        <v>91242</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556291</v>
+        <v>556931</v>
       </c>
       <c r="R73" t="n">
-        <v>7226913</v>
+        <v>7227622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,12 +7976,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091402</v>
+        <v>126091174</v>
       </c>
       <c r="B74" t="n">
-        <v>80080</v>
+        <v>91652</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>4217</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556280</v>
+        <v>556888</v>
       </c>
       <c r="R74" t="n">
-        <v>7227059</v>
+        <v>7227746</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091346</v>
+        <v>126091360</v>
       </c>
       <c r="B75" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556194</v>
+        <v>556326</v>
       </c>
       <c r="R75" t="n">
-        <v>7226815</v>
+        <v>7226893</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8184,11 +8184,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8219,10 +8214,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091015</v>
+        <v>126091375</v>
       </c>
       <c r="B76" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8230,21 +8225,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556931</v>
+        <v>556423</v>
       </c>
       <c r="R76" t="n">
-        <v>7227622</v>
+        <v>7226984</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8284,12 +8279,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8320,10 +8315,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091051</v>
+        <v>126091067</v>
       </c>
       <c r="B77" t="n">
-        <v>79946</v>
+        <v>80081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8331,21 +8326,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>388</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8355,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556679</v>
+        <v>556690</v>
       </c>
       <c r="R77" t="n">
-        <v>7227232</v>
+        <v>7227262</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8421,10 +8416,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091143</v>
+        <v>126091355</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8432,21 +8427,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557106</v>
+        <v>556346</v>
       </c>
       <c r="R78" t="n">
-        <v>7227606</v>
+        <v>7227118</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8486,12 +8481,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,10 +8517,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091012</v>
+        <v>126091393</v>
       </c>
       <c r="B79" t="n">
-        <v>91207</v>
+        <v>79984</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8533,21 +8528,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8557,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556977</v>
+        <v>556291</v>
       </c>
       <c r="R79" t="n">
-        <v>7227576</v>
+        <v>7226913</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8587,12 +8582,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8623,10 +8618,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091174</v>
+        <v>126091012</v>
       </c>
       <c r="B80" t="n">
-        <v>91652</v>
+        <v>91207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8634,21 +8629,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,10 +8653,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556888</v>
+        <v>556977</v>
       </c>
       <c r="R80" t="n">
-        <v>7227746</v>
+        <v>7227576</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8724,10 +8719,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091360</v>
+        <v>126091402</v>
       </c>
       <c r="B81" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8735,21 +8730,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556326</v>
+        <v>556280</v>
       </c>
       <c r="R81" t="n">
-        <v>7226893</v>
+        <v>7227059</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091375</v>
+        <v>126091143</v>
       </c>
       <c r="B82" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8831,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556423</v>
+        <v>557106</v>
       </c>
       <c r="R82" t="n">
-        <v>7226984</v>
+        <v>7227606</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8890,12 +8885,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,10 +8921,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091067</v>
+        <v>126091051</v>
       </c>
       <c r="B83" t="n">
-        <v>80081</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8937,21 +8932,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8961,10 +8956,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556690</v>
+        <v>556679</v>
       </c>
       <c r="R83" t="n">
-        <v>7227262</v>
+        <v>7227232</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9027,10 +9022,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091355</v>
+        <v>126091346</v>
       </c>
       <c r="B84" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,21 +9033,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556346</v>
+        <v>556194</v>
       </c>
       <c r="R84" t="n">
-        <v>7227118</v>
+        <v>7226815</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9098,6 +9093,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091351</v>
+        <v>126091383</v>
       </c>
       <c r="B85" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556346</v>
+        <v>556230</v>
       </c>
       <c r="R85" t="n">
-        <v>7227118</v>
+        <v>7226809</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9229,7 +9229,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091383</v>
+        <v>126091377</v>
       </c>
       <c r="B86" t="n">
         <v>80081</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556230</v>
+        <v>556584</v>
       </c>
       <c r="R86" t="n">
-        <v>7226809</v>
+        <v>7227068</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091377</v>
+        <v>126091344</v>
       </c>
       <c r="B87" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9341,21 +9341,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556584</v>
+        <v>556452</v>
       </c>
       <c r="R87" t="n">
-        <v>7227068</v>
+        <v>7226989</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091153</v>
+        <v>126091372</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556996</v>
+        <v>556359</v>
       </c>
       <c r="R88" t="n">
-        <v>7227559</v>
+        <v>7226988</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9496,12 +9496,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9532,27 +9532,27 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091141</v>
+        <v>126091165</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556931</v>
+        <v>556874</v>
       </c>
       <c r="R89" t="n">
-        <v>7227622</v>
+        <v>7227697</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9603,11 +9603,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9638,10 +9633,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091372</v>
+        <v>126091141</v>
       </c>
       <c r="B90" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9649,21 +9644,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9673,10 +9668,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556359</v>
+        <v>556931</v>
       </c>
       <c r="R90" t="n">
-        <v>7226988</v>
+        <v>7227622</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9703,12 +9698,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9739,32 +9739,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091344</v>
+        <v>126091351</v>
       </c>
       <c r="B91" t="n">
-        <v>91242</v>
+        <v>80109</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556452</v>
+        <v>556346</v>
       </c>
       <c r="R91" t="n">
-        <v>7226989</v>
+        <v>7227118</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9941,27 +9941,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091165</v>
+        <v>126091153</v>
       </c>
       <c r="B93" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556874</v>
+        <v>556996</v>
       </c>
       <c r="R93" t="n">
-        <v>7227697</v>
+        <v>7227559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10148,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091441</v>
+        <v>126091418</v>
       </c>
       <c r="B95" t="n">
-        <v>80115</v>
+        <v>91260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556480</v>
+        <v>556550</v>
       </c>
       <c r="R95" t="n">
-        <v>7226980</v>
+        <v>7227005</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,32 +10249,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091167</v>
+        <v>126091357</v>
       </c>
       <c r="B96" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556728</v>
+        <v>556061</v>
       </c>
       <c r="R96" t="n">
-        <v>7227275</v>
+        <v>7226781</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091405</v>
+        <v>126091339</v>
       </c>
       <c r="B97" t="n">
-        <v>80116</v>
+        <v>91242</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556230</v>
+        <v>556393</v>
       </c>
       <c r="R97" t="n">
-        <v>7226809</v>
+        <v>7226994</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10451,7 +10451,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091418</v>
+        <v>126091125</v>
       </c>
       <c r="B98" t="n">
         <v>91260</v>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556550</v>
+        <v>556893</v>
       </c>
       <c r="R98" t="n">
-        <v>7227005</v>
+        <v>7227703</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10552,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091357</v>
+        <v>126091167</v>
       </c>
       <c r="B99" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556061</v>
+        <v>556728</v>
       </c>
       <c r="R99" t="n">
-        <v>7226781</v>
+        <v>7227275</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10653,32 +10653,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091125</v>
+        <v>126091405</v>
       </c>
       <c r="B100" t="n">
-        <v>91260</v>
+        <v>80116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556893</v>
+        <v>556230</v>
       </c>
       <c r="R100" t="n">
-        <v>7227703</v>
+        <v>7226809</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10754,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091339</v>
+        <v>126091441</v>
       </c>
       <c r="B101" t="n">
-        <v>91242</v>
+        <v>80115</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556393</v>
+        <v>556480</v>
       </c>
       <c r="R101" t="n">
-        <v>7226994</v>
+        <v>7226980</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091019</v>
+        <v>126091358</v>
       </c>
       <c r="B102" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557005</v>
+        <v>556070</v>
       </c>
       <c r="R102" t="n">
-        <v>7227490</v>
+        <v>7226750</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,12 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091028</v>
+        <v>126091019</v>
       </c>
       <c r="B103" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557117</v>
+        <v>557005</v>
       </c>
       <c r="R103" t="n">
-        <v>7227635</v>
+        <v>7227490</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11027,11 +11027,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11062,10 +11057,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091358</v>
+        <v>126091028</v>
       </c>
       <c r="B104" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11073,21 +11068,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11097,10 +11092,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>556070</v>
+        <v>557117</v>
       </c>
       <c r="R104" t="n">
-        <v>7226750</v>
+        <v>7227635</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11127,12 +11122,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091115</v>
+        <v>126091072</v>
       </c>
       <c r="B106" t="n">
-        <v>57760</v>
+        <v>80081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556797</v>
+        <v>556913</v>
       </c>
       <c r="R106" t="n">
-        <v>7227252</v>
+        <v>7227621</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091072</v>
+        <v>126091380</v>
       </c>
       <c r="B107" t="n">
         <v>80081</v>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556913</v>
+        <v>556261</v>
       </c>
       <c r="R107" t="n">
-        <v>7227621</v>
+        <v>7227068</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,7 +11466,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091380</v>
+        <v>126091070</v>
       </c>
       <c r="B108" t="n">
         <v>80081</v>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556261</v>
+        <v>556723</v>
       </c>
       <c r="R108" t="n">
-        <v>7227068</v>
+        <v>7227276</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11567,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091070</v>
+        <v>126091341</v>
       </c>
       <c r="B109" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556723</v>
+        <v>556187</v>
       </c>
       <c r="R109" t="n">
-        <v>7227276</v>
+        <v>7226946</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11769,32 +11769,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091010</v>
+        <v>126091407</v>
       </c>
       <c r="B111" t="n">
-        <v>79009</v>
+        <v>80116</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556904</v>
+        <v>556365</v>
       </c>
       <c r="R111" t="n">
-        <v>7227703</v>
+        <v>7227004</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11870,10 +11870,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091341</v>
+        <v>126091421</v>
       </c>
       <c r="B112" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11881,21 +11881,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556187</v>
+        <v>556111</v>
       </c>
       <c r="R112" t="n">
-        <v>7226946</v>
+        <v>7226873</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11941,6 +11941,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11971,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091407</v>
+        <v>126091010</v>
       </c>
       <c r="B113" t="n">
-        <v>80116</v>
+        <v>79009</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556365</v>
+        <v>556904</v>
       </c>
       <c r="R113" t="n">
-        <v>7227004</v>
+        <v>7227703</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12036,12 +12041,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12072,32 +12077,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091421</v>
+        <v>126091115</v>
       </c>
       <c r="B114" t="n">
-        <v>78977</v>
+        <v>57760</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12107,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556111</v>
+        <v>556797</v>
       </c>
       <c r="R114" t="n">
-        <v>7226873</v>
+        <v>7227252</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12137,17 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091017</v>
+        <v>126091084</v>
       </c>
       <c r="B115" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556929</v>
+        <v>556737</v>
       </c>
       <c r="R115" t="n">
-        <v>7227610</v>
+        <v>7227192</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12243,12 +12243,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091121</v>
+        <v>126091068</v>
       </c>
       <c r="B116" t="n">
-        <v>91238</v>
+        <v>80081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556907</v>
+        <v>556707</v>
       </c>
       <c r="R116" t="n">
-        <v>7227720</v>
+        <v>7227243</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091102</v>
+        <v>126091017</v>
       </c>
       <c r="B117" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556740</v>
+        <v>556929</v>
       </c>
       <c r="R117" t="n">
-        <v>7227186</v>
+        <v>7227610</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,12 +12445,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B118" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R118" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091068</v>
+        <v>126091121</v>
       </c>
       <c r="B119" t="n">
-        <v>80081</v>
+        <v>91238</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556707</v>
+        <v>556907</v>
       </c>
       <c r="R119" t="n">
-        <v>7227243</v>
+        <v>7227720</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091052</v>
+        <v>126091394</v>
       </c>
       <c r="B120" t="n">
-        <v>98370</v>
+        <v>91538</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>557007</v>
+        <v>556098</v>
       </c>
       <c r="R120" t="n">
-        <v>7227805</v>
+        <v>7226757</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12748,12 +12748,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12986,10 +12986,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091394</v>
+        <v>126091424</v>
       </c>
       <c r="B123" t="n">
-        <v>91538</v>
+        <v>78977</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556098</v>
+        <v>556549</v>
       </c>
       <c r="R123" t="n">
-        <v>7226757</v>
+        <v>7226986</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,6 +13057,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13087,10 +13092,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091445</v>
+        <v>126091410</v>
       </c>
       <c r="B124" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13098,21 +13103,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13125,7 +13130,7 @@
         <v>556584</v>
       </c>
       <c r="R124" t="n">
-        <v>7227109</v>
+        <v>7227068</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13289,10 +13294,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091410</v>
+        <v>126091445</v>
       </c>
       <c r="B126" t="n">
-        <v>80116</v>
+        <v>80115</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13300,21 +13305,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13327,7 +13332,7 @@
         <v>556584</v>
       </c>
       <c r="R126" t="n">
-        <v>7227068</v>
+        <v>7227109</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13390,32 +13395,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091424</v>
+        <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13425,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556549</v>
+        <v>557007</v>
       </c>
       <c r="R127" t="n">
-        <v>7226986</v>
+        <v>7227805</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13455,17 +13460,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13804,10 +13804,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126091071</v>
+        <v>126091338</v>
       </c>
       <c r="B131" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13815,21 +13815,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>556807</v>
+        <v>556326</v>
       </c>
       <c r="R131" t="n">
-        <v>7227608</v>
+        <v>7227114</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13905,7 +13905,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091367</v>
+        <v>126091071</v>
       </c>
       <c r="B132" t="n">
         <v>80081</v>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556347</v>
+        <v>556807</v>
       </c>
       <c r="R132" t="n">
-        <v>7226967</v>
+        <v>7227608</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14006,7 +14006,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091385</v>
+        <v>126091367</v>
       </c>
       <c r="B133" t="n">
         <v>80081</v>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556410</v>
+        <v>556347</v>
       </c>
       <c r="R133" t="n">
-        <v>7226996</v>
+        <v>7226967</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14107,10 +14107,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091338</v>
+        <v>126091385</v>
       </c>
       <c r="B134" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14118,21 +14118,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556326</v>
+        <v>556410</v>
       </c>
       <c r="R134" t="n">
-        <v>7227114</v>
+        <v>7226996</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091431</v>
+        <v>126091415</v>
       </c>
       <c r="B136" t="n">
-        <v>80115</v>
+        <v>91260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556179</v>
+        <v>556315</v>
       </c>
       <c r="R136" t="n">
-        <v>7226822</v>
+        <v>7226927</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14410,32 +14410,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091429</v>
+        <v>126091127</v>
       </c>
       <c r="B137" t="n">
-        <v>80115</v>
+        <v>91260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556272</v>
+        <v>556728</v>
       </c>
       <c r="R137" t="n">
-        <v>7227058</v>
+        <v>7227249</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14475,12 +14475,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14511,32 +14511,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091443</v>
+        <v>126091371</v>
       </c>
       <c r="B138" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14546,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556529</v>
+        <v>556365</v>
       </c>
       <c r="R138" t="n">
-        <v>7226958</v>
+        <v>7227004</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,32 +14612,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091437</v>
+        <v>126091063</v>
       </c>
       <c r="B139" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556361</v>
+        <v>556836</v>
       </c>
       <c r="R139" t="n">
-        <v>7227004</v>
+        <v>7227732</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14677,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14713,10 +14713,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091432</v>
+        <v>126091105</v>
       </c>
       <c r="B140" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14724,21 +14724,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556230</v>
+        <v>556807</v>
       </c>
       <c r="R140" t="n">
-        <v>7226809</v>
+        <v>7227608</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14814,10 +14814,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091105</v>
+        <v>126091429</v>
       </c>
       <c r="B141" t="n">
-        <v>80116</v>
+        <v>80115</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14825,21 +14825,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14849,10 +14849,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556807</v>
+        <v>556272</v>
       </c>
       <c r="R141" t="n">
-        <v>7227608</v>
+        <v>7227058</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14879,12 +14879,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14915,32 +14915,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091415</v>
+        <v>126091443</v>
       </c>
       <c r="B142" t="n">
-        <v>91260</v>
+        <v>80115</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14950,10 +14950,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556315</v>
+        <v>556529</v>
       </c>
       <c r="R142" t="n">
-        <v>7226927</v>
+        <v>7226958</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15016,32 +15016,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091127</v>
+        <v>126091431</v>
       </c>
       <c r="B143" t="n">
-        <v>91260</v>
+        <v>80115</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15051,10 +15051,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556728</v>
+        <v>556179</v>
       </c>
       <c r="R143" t="n">
-        <v>7227249</v>
+        <v>7226822</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15081,12 +15081,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15223,32 +15223,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091371</v>
+        <v>126091432</v>
       </c>
       <c r="B145" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15258,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556365</v>
+        <v>556230</v>
       </c>
       <c r="R145" t="n">
-        <v>7227004</v>
+        <v>7226809</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15324,32 +15324,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091063</v>
+        <v>126091437</v>
       </c>
       <c r="B146" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556836</v>
+        <v>556361</v>
       </c>
       <c r="R146" t="n">
-        <v>7227732</v>
+        <v>7227004</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091152</v>
+        <v>126091388</v>
       </c>
       <c r="B149" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556975</v>
+        <v>556529</v>
       </c>
       <c r="R149" t="n">
-        <v>7227579</v>
+        <v>7226958</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,17 +15702,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15743,7 +15738,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091388</v>
+        <v>126091378</v>
       </c>
       <c r="B150" t="n">
         <v>80081</v>
@@ -15778,10 +15773,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556529</v>
+        <v>556353</v>
       </c>
       <c r="R150" t="n">
-        <v>7226958</v>
+        <v>7227115</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15844,10 +15839,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091378</v>
+        <v>126091350</v>
       </c>
       <c r="B151" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15855,21 +15850,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15879,10 +15874,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556353</v>
+        <v>556589</v>
       </c>
       <c r="R151" t="n">
-        <v>7227115</v>
+        <v>7227059</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15915,6 +15910,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15945,10 +15945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091149</v>
+        <v>126091040</v>
       </c>
       <c r="B152" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556807</v>
+        <v>556781</v>
       </c>
       <c r="R152" t="n">
-        <v>7227608</v>
+        <v>7227272</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Lång bål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,32 +16051,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091350</v>
+        <v>126091169</v>
       </c>
       <c r="B153" t="n">
-        <v>57656</v>
+        <v>80115</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556589</v>
+        <v>556756</v>
       </c>
       <c r="R153" t="n">
-        <v>7227059</v>
+        <v>7227253</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16116,17 +16116,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16157,10 +16152,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091040</v>
+        <v>126091152</v>
       </c>
       <c r="B154" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16168,21 +16163,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16192,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556781</v>
+        <v>556975</v>
       </c>
       <c r="R154" t="n">
-        <v>7227272</v>
+        <v>7227579</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16232,7 +16227,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16263,10 +16258,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091397</v>
+        <v>126091404</v>
       </c>
       <c r="B155" t="n">
-        <v>80108</v>
+        <v>80116</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16274,21 +16269,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16298,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556378</v>
+        <v>556272</v>
       </c>
       <c r="R155" t="n">
-        <v>7226996</v>
+        <v>7227058</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16364,32 +16359,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091149</v>
       </c>
       <c r="B156" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16394,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556807</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7227608</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16429,12 +16424,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16465,10 +16465,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091169</v>
+        <v>126091397</v>
       </c>
       <c r="B157" t="n">
-        <v>80115</v>
+        <v>80108</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16476,21 +16476,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556756</v>
+        <v>556378</v>
       </c>
       <c r="R157" t="n">
-        <v>7227253</v>
+        <v>7226996</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16530,12 +16530,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16569,7 +16569,7 @@
         <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091389</v>
+        <v>126091428</v>
       </c>
       <c r="B11" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556589</v>
+        <v>556314</v>
       </c>
       <c r="R11" t="n">
-        <v>7227109</v>
+        <v>7226891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091064</v>
+        <v>126091420</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556833</v>
+        <v>556284</v>
       </c>
       <c r="R12" t="n">
-        <v>7227720</v>
+        <v>7227078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1750,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091374</v>
+        <v>126091043</v>
       </c>
       <c r="B13" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556371</v>
+        <v>556756</v>
       </c>
       <c r="R13" t="n">
-        <v>7226988</v>
+        <v>7227253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,12 +1856,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091428</v>
+        <v>126091335</v>
       </c>
       <c r="B14" t="n">
-        <v>80115</v>
+        <v>91207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1922,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556314</v>
+        <v>556339</v>
       </c>
       <c r="R14" t="n">
-        <v>7226891</v>
+        <v>7226946</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1988,7 +1993,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091420</v>
+        <v>126091425</v>
       </c>
       <c r="B15" t="n">
         <v>78977</v>
@@ -2023,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556284</v>
+        <v>556591</v>
       </c>
       <c r="R15" t="n">
-        <v>7227078</v>
+        <v>7227022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091043</v>
+        <v>126091439</v>
       </c>
       <c r="B16" t="n">
-        <v>80109</v>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,21 +2110,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2129,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556756</v>
+        <v>556374</v>
       </c>
       <c r="R16" t="n">
-        <v>7227253</v>
+        <v>7227007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,12 +2164,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,32 +2200,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091335</v>
+        <v>126091147</v>
       </c>
       <c r="B17" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556339</v>
+        <v>556819</v>
       </c>
       <c r="R17" t="n">
-        <v>7226946</v>
+        <v>7227694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,12 +2265,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2296,10 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091425</v>
+        <v>126091389</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,21 +2317,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556591</v>
+        <v>556589</v>
       </c>
       <c r="R18" t="n">
-        <v>7227022</v>
+        <v>7227109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2367,11 +2377,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091439</v>
+        <v>126091064</v>
       </c>
       <c r="B19" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556374</v>
+        <v>556833</v>
       </c>
       <c r="R19" t="n">
-        <v>7227007</v>
+        <v>7227720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2467,12 +2472,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,10 +2508,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091147</v>
+        <v>126091374</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2519,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556819</v>
+        <v>556371</v>
       </c>
       <c r="R20" t="n">
-        <v>7227694</v>
+        <v>7226988</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,17 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B22" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R22" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R23" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091435</v>
+        <v>126091368</v>
       </c>
       <c r="B24" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556346</v>
       </c>
       <c r="R24" t="n">
-        <v>7226941</v>
+        <v>7226961</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B25" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R25" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091164</v>
+        <v>126091435</v>
       </c>
       <c r="B26" t="n">
-        <v>88651</v>
+        <v>80115</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556775</v>
+        <v>556359</v>
       </c>
       <c r="R26" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091340</v>
+        <v>126091106</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>80116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556312</v>
+        <v>556709</v>
       </c>
       <c r="R27" t="n">
-        <v>7227107</v>
+        <v>7227248</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091368</v>
+        <v>126091164</v>
       </c>
       <c r="B28" t="n">
-        <v>80081</v>
+        <v>88651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556346</v>
+        <v>556775</v>
       </c>
       <c r="R28" t="n">
-        <v>7226961</v>
+        <v>7227253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091073</v>
+        <v>126091340</v>
       </c>
       <c r="B29" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556756</v>
+        <v>556312</v>
       </c>
       <c r="R29" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3831,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091356</v>
+        <v>126091349</v>
       </c>
       <c r="B33" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,21 +3842,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556271</v>
+        <v>556613</v>
       </c>
       <c r="R33" t="n">
-        <v>7227059</v>
+        <v>7227051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,6 +3902,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,10 +3937,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091414</v>
+        <v>126091356</v>
       </c>
       <c r="B34" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,21 +3948,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3972,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556303</v>
+        <v>556271</v>
       </c>
       <c r="R34" t="n">
-        <v>7226905</v>
+        <v>7227059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4033,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091369</v>
+        <v>126091414</v>
       </c>
       <c r="B35" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4049,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556333</v>
+        <v>556303</v>
       </c>
       <c r="R35" t="n">
-        <v>7227009</v>
+        <v>7226905</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4134,10 +4139,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091124</v>
+        <v>126091369</v>
       </c>
       <c r="B36" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4145,21 +4150,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4174,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556698</v>
+        <v>556333</v>
       </c>
       <c r="R36" t="n">
-        <v>7227248</v>
+        <v>7227009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,12 +4204,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,10 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091013</v>
+        <v>126091124</v>
       </c>
       <c r="B37" t="n">
-        <v>91242</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,21 +4251,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556830</v>
+        <v>556698</v>
       </c>
       <c r="R37" t="n">
-        <v>7227704</v>
+        <v>7227248</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,32 +4341,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091042</v>
+        <v>126091013</v>
       </c>
       <c r="B38" t="n">
-        <v>80109</v>
+        <v>91242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4371,10 +4376,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556817</v>
+        <v>556830</v>
       </c>
       <c r="R38" t="n">
-        <v>7227591</v>
+        <v>7227704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,10 +4442,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091406</v>
+        <v>126091042</v>
       </c>
       <c r="B39" t="n">
-        <v>80116</v>
+        <v>80109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4448,21 +4453,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4472,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556314</v>
+        <v>556817</v>
       </c>
       <c r="R39" t="n">
-        <v>7226891</v>
+        <v>7227591</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4507,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4538,32 +4543,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091448</v>
+        <v>126091406</v>
       </c>
       <c r="B40" t="n">
-        <v>91912</v>
+        <v>80116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>898</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4573,10 +4578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556484</v>
+        <v>556314</v>
       </c>
       <c r="R40" t="n">
-        <v>7226980</v>
+        <v>7226891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4639,32 +4644,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091349</v>
+        <v>126091448</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>91912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4674,10 +4679,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556613</v>
+        <v>556484</v>
       </c>
       <c r="R41" t="n">
-        <v>7227051</v>
+        <v>7226980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4710,11 +4715,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091075</v>
+        <v>126091348</v>
       </c>
       <c r="B42" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556792</v>
+        <v>556351</v>
       </c>
       <c r="R42" t="n">
-        <v>7227253</v>
+        <v>7226920</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4947,10 +4952,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091403</v>
+        <v>126091075</v>
       </c>
       <c r="B44" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,21 +4963,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556357</v>
+        <v>556792</v>
       </c>
       <c r="R44" t="n">
-        <v>7227004</v>
+        <v>7227253</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,12 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091145</v>
+        <v>126091403</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556897</v>
+        <v>556357</v>
       </c>
       <c r="R45" t="n">
-        <v>7227735</v>
+        <v>7227004</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,17 +5118,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,32 +5154,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091107</v>
+        <v>126091145</v>
       </c>
       <c r="B46" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556723</v>
+        <v>556897</v>
       </c>
       <c r="R46" t="n">
-        <v>7227276</v>
+        <v>7227735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5225,6 +5225,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,10 +5260,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091044</v>
+        <v>126091107</v>
       </c>
       <c r="B47" t="n">
-        <v>80109</v>
+        <v>80116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5266,21 +5271,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5290,10 +5295,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556826</v>
+        <v>556723</v>
       </c>
       <c r="R47" t="n">
-        <v>7227309</v>
+        <v>7227276</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5356,32 +5361,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091422</v>
+        <v>126091044</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5391,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556407</v>
+        <v>556826</v>
       </c>
       <c r="R48" t="n">
-        <v>7226992</v>
+        <v>7227309</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5421,17 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,7 +5462,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091144</v>
+        <v>126091422</v>
       </c>
       <c r="B49" t="n">
         <v>78977</v>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557048</v>
+        <v>556407</v>
       </c>
       <c r="R49" t="n">
-        <v>7227797</v>
+        <v>7226992</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,12 +5527,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5563,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091348</v>
+        <v>126091144</v>
       </c>
       <c r="B50" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,21 +5579,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556351</v>
+        <v>557048</v>
       </c>
       <c r="R50" t="n">
-        <v>7226920</v>
+        <v>7227797</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5628,17 +5633,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5871,27 +5871,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091148</v>
+        <v>126091438</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556787</v>
+        <v>556350</v>
       </c>
       <c r="R53" t="n">
-        <v>7227605</v>
+        <v>7226997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5936,17 +5936,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5977,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091438</v>
+        <v>126091430</v>
       </c>
       <c r="B54" t="n">
         <v>80115</v>
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556350</v>
+        <v>556140</v>
       </c>
       <c r="R54" t="n">
-        <v>7226997</v>
+        <v>7226895</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6078,32 +6073,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091430</v>
+        <v>126091401</v>
       </c>
       <c r="B55" t="n">
-        <v>80115</v>
+        <v>80080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6113,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556140</v>
+        <v>556271</v>
       </c>
       <c r="R55" t="n">
-        <v>7226895</v>
+        <v>7227059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6179,10 +6174,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091401</v>
+        <v>126091148</v>
       </c>
       <c r="B56" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6190,21 +6185,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6214,10 +6209,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556271</v>
+        <v>556787</v>
       </c>
       <c r="R56" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6244,12 +6239,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7911,10 +7911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091015</v>
+        <v>126091346</v>
       </c>
       <c r="B73" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,21 +7922,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556931</v>
+        <v>556194</v>
       </c>
       <c r="R73" t="n">
-        <v>7227622</v>
+        <v>7226815</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,12 +7976,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8012,32 +8017,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091174</v>
+        <v>126091015</v>
       </c>
       <c r="B74" t="n">
-        <v>91652</v>
+        <v>91242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8052,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556888</v>
+        <v>556931</v>
       </c>
       <c r="R74" t="n">
-        <v>7227746</v>
+        <v>7227622</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8113,32 +8118,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091360</v>
+        <v>126091174</v>
       </c>
       <c r="B75" t="n">
-        <v>80081</v>
+        <v>91652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8153,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556326</v>
+        <v>556888</v>
       </c>
       <c r="R75" t="n">
-        <v>7226893</v>
+        <v>7227746</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,12 +8183,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8214,7 +8219,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091375</v>
+        <v>126091360</v>
       </c>
       <c r="B76" t="n">
         <v>80081</v>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556423</v>
+        <v>556326</v>
       </c>
       <c r="R76" t="n">
-        <v>7226984</v>
+        <v>7226893</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8315,7 +8320,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091067</v>
+        <v>126091375</v>
       </c>
       <c r="B77" t="n">
         <v>80081</v>
@@ -8350,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556690</v>
+        <v>556423</v>
       </c>
       <c r="R77" t="n">
-        <v>7227262</v>
+        <v>7226984</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,12 +8385,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,7 +8421,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091355</v>
+        <v>126091067</v>
       </c>
       <c r="B78" t="n">
         <v>80081</v>
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556346</v>
+        <v>556690</v>
       </c>
       <c r="R78" t="n">
-        <v>7227118</v>
+        <v>7227262</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8481,12 +8486,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8517,32 +8522,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091393</v>
+        <v>126091355</v>
       </c>
       <c r="B79" t="n">
-        <v>79984</v>
+        <v>80081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8552,10 +8557,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556291</v>
+        <v>556346</v>
       </c>
       <c r="R79" t="n">
-        <v>7226913</v>
+        <v>7227118</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8618,10 +8623,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091012</v>
+        <v>126091393</v>
       </c>
       <c r="B80" t="n">
-        <v>91207</v>
+        <v>79984</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8629,21 +8634,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8653,10 +8658,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556977</v>
+        <v>556291</v>
       </c>
       <c r="R80" t="n">
-        <v>7227576</v>
+        <v>7226913</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8683,12 +8688,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8719,32 +8724,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091402</v>
+        <v>126091012</v>
       </c>
       <c r="B81" t="n">
-        <v>80080</v>
+        <v>91207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8754,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556280</v>
+        <v>556977</v>
       </c>
       <c r="R81" t="n">
-        <v>7227059</v>
+        <v>7227576</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8784,12 +8789,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8820,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091143</v>
+        <v>126091402</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8831,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>557106</v>
+        <v>556280</v>
       </c>
       <c r="R82" t="n">
-        <v>7227606</v>
+        <v>7227059</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8885,12 +8890,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8921,10 +8926,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091051</v>
+        <v>126091143</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8932,21 +8937,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8956,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556679</v>
+        <v>557106</v>
       </c>
       <c r="R83" t="n">
-        <v>7227232</v>
+        <v>7227606</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9022,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091346</v>
+        <v>126091051</v>
       </c>
       <c r="B84" t="n">
-        <v>57656</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9033,21 +9038,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9057,10 +9062,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556194</v>
+        <v>556679</v>
       </c>
       <c r="R84" t="n">
-        <v>7226815</v>
+        <v>7227232</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9087,17 +9092,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091358</v>
+        <v>126091019</v>
       </c>
       <c r="B102" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>556070</v>
+        <v>557005</v>
       </c>
       <c r="R102" t="n">
-        <v>7226750</v>
+        <v>7227490</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,12 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091019</v>
+        <v>126091028</v>
       </c>
       <c r="B103" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557005</v>
+        <v>557117</v>
       </c>
       <c r="R103" t="n">
-        <v>7227490</v>
+        <v>7227635</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11027,6 +11027,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11057,10 +11062,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091028</v>
+        <v>126091358</v>
       </c>
       <c r="B104" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11068,21 +11073,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11092,10 +11097,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>557117</v>
+        <v>556070</v>
       </c>
       <c r="R104" t="n">
-        <v>7227635</v>
+        <v>7226750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11122,17 +11127,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11769,10 +11769,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091407</v>
+        <v>126091115</v>
       </c>
       <c r="B111" t="n">
-        <v>80116</v>
+        <v>57760</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11780,21 +11780,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>103031</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556365</v>
+        <v>556797</v>
       </c>
       <c r="R111" t="n">
-        <v>7227004</v>
+        <v>7227252</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11870,32 +11870,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091421</v>
+        <v>126091407</v>
       </c>
       <c r="B112" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556111</v>
+        <v>556365</v>
       </c>
       <c r="R112" t="n">
-        <v>7226873</v>
+        <v>7227004</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11941,11 +11941,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,10 +11971,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091010</v>
+        <v>126091421</v>
       </c>
       <c r="B113" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11987,21 +11982,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556904</v>
+        <v>556111</v>
       </c>
       <c r="R113" t="n">
-        <v>7227703</v>
+        <v>7226873</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12041,12 +12036,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,32 +12077,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091115</v>
+        <v>126091010</v>
       </c>
       <c r="B114" t="n">
-        <v>57760</v>
+        <v>79009</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103031</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556797</v>
+        <v>556904</v>
       </c>
       <c r="R114" t="n">
-        <v>7227252</v>
+        <v>7227703</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091415</v>
+        <v>126091105</v>
       </c>
       <c r="B136" t="n">
-        <v>91260</v>
+        <v>80116</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556315</v>
+        <v>556807</v>
       </c>
       <c r="R136" t="n">
-        <v>7226927</v>
+        <v>7227608</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14410,32 +14410,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091127</v>
+        <v>126091429</v>
       </c>
       <c r="B137" t="n">
-        <v>91260</v>
+        <v>80115</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14445,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556728</v>
+        <v>556272</v>
       </c>
       <c r="R137" t="n">
-        <v>7227249</v>
+        <v>7227058</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14475,12 +14475,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14511,32 +14511,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091371</v>
+        <v>126091443</v>
       </c>
       <c r="B138" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14546,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556365</v>
+        <v>556529</v>
       </c>
       <c r="R138" t="n">
-        <v>7227004</v>
+        <v>7226958</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,32 +14612,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091063</v>
+        <v>126091431</v>
       </c>
       <c r="B139" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14647,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556836</v>
+        <v>556179</v>
       </c>
       <c r="R139" t="n">
-        <v>7227732</v>
+        <v>7226822</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14677,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14713,32 +14713,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091105</v>
+        <v>126091140</v>
       </c>
       <c r="B140" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14748,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556807</v>
+        <v>557026</v>
       </c>
       <c r="R140" t="n">
-        <v>7227608</v>
+        <v>7227519</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14784,6 +14784,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14814,7 +14819,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091429</v>
+        <v>126091432</v>
       </c>
       <c r="B141" t="n">
         <v>80115</v>
@@ -14849,10 +14854,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556272</v>
+        <v>556230</v>
       </c>
       <c r="R141" t="n">
-        <v>7227058</v>
+        <v>7226809</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14915,7 +14920,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091443</v>
+        <v>126091437</v>
       </c>
       <c r="B142" t="n">
         <v>80115</v>
@@ -14950,10 +14955,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556529</v>
+        <v>556361</v>
       </c>
       <c r="R142" t="n">
-        <v>7226958</v>
+        <v>7227004</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15016,32 +15021,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091431</v>
+        <v>126091029</v>
       </c>
       <c r="B143" t="n">
-        <v>80115</v>
+        <v>57656</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15051,10 +15056,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556179</v>
+        <v>556819</v>
       </c>
       <c r="R143" t="n">
-        <v>7226822</v>
+        <v>7227694</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15081,12 +15086,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15117,10 +15127,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091140</v>
+        <v>126091415</v>
       </c>
       <c r="B144" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15128,21 +15138,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15152,10 +15162,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>557026</v>
+        <v>556315</v>
       </c>
       <c r="R144" t="n">
-        <v>7227519</v>
+        <v>7226927</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15182,17 +15192,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15223,32 +15228,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091432</v>
+        <v>126091127</v>
       </c>
       <c r="B145" t="n">
-        <v>80115</v>
+        <v>91260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15258,10 +15263,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556230</v>
+        <v>556728</v>
       </c>
       <c r="R145" t="n">
-        <v>7226809</v>
+        <v>7227249</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15288,12 +15293,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15324,32 +15329,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091437</v>
+        <v>126091371</v>
       </c>
       <c r="B146" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15359,7 +15364,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556361</v>
+        <v>556365</v>
       </c>
       <c r="R146" t="n">
         <v>7227004</v>
@@ -15425,10 +15430,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091029</v>
+        <v>126091063</v>
       </c>
       <c r="B147" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15436,21 +15441,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15460,10 +15465,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556819</v>
+        <v>556836</v>
       </c>
       <c r="R147" t="n">
-        <v>7227694</v>
+        <v>7227732</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15496,11 +15501,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15637,32 +15637,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091388</v>
+        <v>126091169</v>
       </c>
       <c r="B149" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556529</v>
+        <v>556756</v>
       </c>
       <c r="R149" t="n">
-        <v>7226958</v>
+        <v>7227253</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,12 +15702,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15738,10 +15738,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091378</v>
+        <v>126091152</v>
       </c>
       <c r="B150" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15749,21 +15749,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15773,10 +15773,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556353</v>
+        <v>556975</v>
       </c>
       <c r="R150" t="n">
-        <v>7227115</v>
+        <v>7227579</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15803,12 +15803,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15839,32 +15844,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091350</v>
+        <v>126091404</v>
       </c>
       <c r="B151" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15874,10 +15879,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556589</v>
+        <v>556272</v>
       </c>
       <c r="R151" t="n">
-        <v>7227059</v>
+        <v>7227058</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15910,11 +15915,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15945,10 +15945,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091040</v>
+        <v>126091149</v>
       </c>
       <c r="B152" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556781</v>
+        <v>556807</v>
       </c>
       <c r="R152" t="n">
-        <v>7227272</v>
+        <v>7227608</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,10 +16051,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091169</v>
+        <v>126091397</v>
       </c>
       <c r="B153" t="n">
-        <v>80115</v>
+        <v>80108</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16062,21 +16062,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16086,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556756</v>
+        <v>556378</v>
       </c>
       <c r="R153" t="n">
-        <v>7227253</v>
+        <v>7226996</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16116,12 +16116,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,32 +16152,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091152</v>
+        <v>126091053</v>
       </c>
       <c r="B154" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16187,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556975</v>
+        <v>556996</v>
       </c>
       <c r="R154" t="n">
-        <v>7227579</v>
+        <v>7227559</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16223,11 +16223,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16258,32 +16253,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091404</v>
+        <v>126091388</v>
       </c>
       <c r="B155" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16293,10 +16288,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556272</v>
+        <v>556529</v>
       </c>
       <c r="R155" t="n">
-        <v>7227058</v>
+        <v>7226958</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16359,10 +16354,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091149</v>
+        <v>126091378</v>
       </c>
       <c r="B156" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16370,21 +16365,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16394,10 +16389,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556807</v>
+        <v>556353</v>
       </c>
       <c r="R156" t="n">
-        <v>7227608</v>
+        <v>7227115</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16424,17 +16419,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16465,32 +16455,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091397</v>
+        <v>126091350</v>
       </c>
       <c r="B157" t="n">
-        <v>80108</v>
+        <v>57656</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16490,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556378</v>
+        <v>556589</v>
       </c>
       <c r="R157" t="n">
-        <v>7226996</v>
+        <v>7227059</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16536,6 +16526,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16566,32 +16561,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091053</v>
+        <v>126091040</v>
       </c>
       <c r="B158" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16601,10 +16596,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556996</v>
+        <v>556781</v>
       </c>
       <c r="R158" t="n">
-        <v>7227559</v>
+        <v>7227272</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16637,6 +16632,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091362</v>
+        <v>126091395</v>
       </c>
       <c r="B2" t="n">
-        <v>80081</v>
+        <v>91538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556369</v>
+        <v>556308</v>
       </c>
       <c r="R2" t="n">
-        <v>7226946</v>
+        <v>7226876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091065</v>
+        <v>126091440</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556817</v>
+        <v>556465</v>
       </c>
       <c r="R3" t="n">
-        <v>7227591</v>
+        <v>7226995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091370</v>
+        <v>126091408</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556364</v>
+        <v>556467</v>
       </c>
       <c r="R4" t="n">
-        <v>7226989</v>
+        <v>7226993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091408</v>
+        <v>126091362</v>
       </c>
       <c r="B7" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556467</v>
+        <v>556369</v>
       </c>
       <c r="R7" t="n">
-        <v>7226993</v>
+        <v>7226946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091440</v>
+        <v>126091342</v>
       </c>
       <c r="B8" t="n">
-        <v>80115</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556465</v>
+        <v>556306</v>
       </c>
       <c r="R8" t="n">
-        <v>7226995</v>
+        <v>7226876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091395</v>
+        <v>126091065</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>80081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556308</v>
+        <v>556817</v>
       </c>
       <c r="R9" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091342</v>
+        <v>126091370</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556306</v>
+        <v>556364</v>
       </c>
       <c r="R10" t="n">
-        <v>7226876</v>
+        <v>7226989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091428</v>
+        <v>126091043</v>
       </c>
       <c r="B11" t="n">
-        <v>80115</v>
+        <v>80109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556314</v>
+        <v>556756</v>
       </c>
       <c r="R11" t="n">
-        <v>7226891</v>
+        <v>7227253</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,27 +1685,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091420</v>
+        <v>126091439</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556284</v>
+        <v>556374</v>
       </c>
       <c r="R12" t="n">
-        <v>7227078</v>
+        <v>7227007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091043</v>
+        <v>126091420</v>
       </c>
       <c r="B13" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556756</v>
+        <v>556284</v>
       </c>
       <c r="R13" t="n">
-        <v>7227253</v>
+        <v>7227078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1856,12 +1851,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091335</v>
+        <v>126091428</v>
       </c>
       <c r="B14" t="n">
-        <v>91207</v>
+        <v>80115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556339</v>
+        <v>556314</v>
       </c>
       <c r="R14" t="n">
-        <v>7226946</v>
+        <v>7226891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126091425</v>
+        <v>126091147</v>
       </c>
       <c r="B15" t="n">
         <v>78977</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556591</v>
+        <v>556819</v>
       </c>
       <c r="R15" t="n">
-        <v>7227022</v>
+        <v>7227694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091439</v>
+        <v>126091389</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556374</v>
+        <v>556589</v>
       </c>
       <c r="R16" t="n">
-        <v>7227007</v>
+        <v>7227109</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091147</v>
+        <v>126091365</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556819</v>
+        <v>556359</v>
       </c>
       <c r="R17" t="n">
-        <v>7227694</v>
+        <v>7226943</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,17 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091389</v>
+        <v>126091064</v>
       </c>
       <c r="B18" t="n">
         <v>80081</v>
@@ -2341,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556589</v>
+        <v>556833</v>
       </c>
       <c r="R18" t="n">
-        <v>7227109</v>
+        <v>7227720</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2371,12 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,32 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091064</v>
+        <v>126091335</v>
       </c>
       <c r="B19" t="n">
-        <v>80081</v>
+        <v>91207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556833</v>
+        <v>556339</v>
       </c>
       <c r="R19" t="n">
-        <v>7227720</v>
+        <v>7226946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,12 +2467,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2508,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091374</v>
+        <v>126091425</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2519,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556371</v>
+        <v>556591</v>
       </c>
       <c r="R20" t="n">
-        <v>7226988</v>
+        <v>7227022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2579,6 +2574,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,7 +2609,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091365</v>
+        <v>126091374</v>
       </c>
       <c r="B21" t="n">
         <v>80081</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556359</v>
+        <v>556371</v>
       </c>
       <c r="R21" t="n">
-        <v>7226943</v>
+        <v>7226988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R22" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B23" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R23" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091368</v>
+        <v>126091164</v>
       </c>
       <c r="B24" t="n">
-        <v>80081</v>
+        <v>88651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556346</v>
+        <v>556775</v>
       </c>
       <c r="R24" t="n">
-        <v>7226961</v>
+        <v>7227253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091073</v>
+        <v>126091435</v>
       </c>
       <c r="B25" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556756</v>
+        <v>556359</v>
       </c>
       <c r="R25" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,10 +3114,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091435</v>
+        <v>126091106</v>
       </c>
       <c r="B26" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556359</v>
+        <v>556709</v>
       </c>
       <c r="R26" t="n">
-        <v>7226941</v>
+        <v>7227248</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B27" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R27" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091164</v>
+        <v>126091368</v>
       </c>
       <c r="B28" t="n">
-        <v>88651</v>
+        <v>80081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556775</v>
+        <v>556346</v>
       </c>
       <c r="R28" t="n">
-        <v>7227253</v>
+        <v>7226961</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091349</v>
+        <v>126091042</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556613</v>
+        <v>556817</v>
       </c>
       <c r="R33" t="n">
-        <v>7227051</v>
+        <v>7227591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,17 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3937,10 +3932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091356</v>
+        <v>126091414</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>91260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,21 +3943,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3972,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556271</v>
+        <v>556303</v>
       </c>
       <c r="R34" t="n">
-        <v>7227059</v>
+        <v>7226905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,7 +4033,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091414</v>
+        <v>126091124</v>
       </c>
       <c r="B35" t="n">
         <v>91260</v>
@@ -4073,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556303</v>
+        <v>556698</v>
       </c>
       <c r="R35" t="n">
-        <v>7226905</v>
+        <v>7227248</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4103,12 +4098,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4139,32 +4134,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091369</v>
+        <v>126091406</v>
       </c>
       <c r="B36" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4174,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556333</v>
+        <v>556314</v>
       </c>
       <c r="R36" t="n">
-        <v>7227009</v>
+        <v>7226891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,32 +4235,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091124</v>
+        <v>126091448</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>91912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>898</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4275,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556698</v>
+        <v>556484</v>
       </c>
       <c r="R37" t="n">
-        <v>7227248</v>
+        <v>7226980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4305,12 +4300,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,32 +4437,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091042</v>
+        <v>126091369</v>
       </c>
       <c r="B39" t="n">
-        <v>80109</v>
+        <v>80081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4477,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556817</v>
+        <v>556333</v>
       </c>
       <c r="R39" t="n">
-        <v>7227591</v>
+        <v>7227009</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4543,32 +4538,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091406</v>
+        <v>126091356</v>
       </c>
       <c r="B40" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4578,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556314</v>
+        <v>556271</v>
       </c>
       <c r="R40" t="n">
-        <v>7226891</v>
+        <v>7227059</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4644,32 +4639,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126091448</v>
+        <v>126091349</v>
       </c>
       <c r="B41" t="n">
-        <v>91912</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556484</v>
+        <v>556613</v>
       </c>
       <c r="R41" t="n">
-        <v>7226980</v>
+        <v>7227051</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,6 +4710,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091348</v>
+        <v>126091403</v>
       </c>
       <c r="B42" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556351</v>
+        <v>556357</v>
       </c>
       <c r="R42" t="n">
-        <v>7226920</v>
+        <v>7227004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4816,11 +4816,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4851,32 +4846,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091129</v>
+        <v>126091044</v>
       </c>
       <c r="B43" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556685</v>
+        <v>556826</v>
       </c>
       <c r="R43" t="n">
-        <v>7227107</v>
+        <v>7227309</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4916,12 +4911,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4952,32 +4947,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091075</v>
+        <v>126091107</v>
       </c>
       <c r="B44" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4987,10 +4982,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556792</v>
+        <v>556723</v>
       </c>
       <c r="R44" t="n">
-        <v>7227253</v>
+        <v>7227276</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,10 +5048,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091403</v>
+        <v>126091144</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,21 +5059,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5088,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556357</v>
+        <v>557048</v>
       </c>
       <c r="R45" t="n">
-        <v>7227004</v>
+        <v>7227797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5118,12 +5113,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5154,7 +5149,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091145</v>
+        <v>126091422</v>
       </c>
       <c r="B46" t="n">
         <v>78977</v>
@@ -5189,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556897</v>
+        <v>556407</v>
       </c>
       <c r="R46" t="n">
-        <v>7227735</v>
+        <v>7226992</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5219,12 +5214,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5260,32 +5255,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091107</v>
+        <v>126091145</v>
       </c>
       <c r="B47" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5295,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556723</v>
+        <v>556897</v>
       </c>
       <c r="R47" t="n">
-        <v>7227276</v>
+        <v>7227735</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,6 +5326,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5361,32 +5361,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091044</v>
+        <v>126091129</v>
       </c>
       <c r="B48" t="n">
-        <v>80109</v>
+        <v>91260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556826</v>
+        <v>556685</v>
       </c>
       <c r="R48" t="n">
-        <v>7227309</v>
+        <v>7227107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091422</v>
+        <v>126091075</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556407</v>
+        <v>556792</v>
       </c>
       <c r="R49" t="n">
-        <v>7226992</v>
+        <v>7227253</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,17 +5527,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5568,32 +5563,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091144</v>
+        <v>126091352</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5603,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557048</v>
+        <v>556293</v>
       </c>
       <c r="R50" t="n">
-        <v>7227797</v>
+        <v>7227068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5633,12 +5628,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5669,32 +5664,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091352</v>
+        <v>126091348</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556293</v>
+        <v>556351</v>
       </c>
       <c r="R51" t="n">
-        <v>7227068</v>
+        <v>7226920</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5740,6 +5735,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,32 +5770,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091381</v>
+        <v>126091430</v>
       </c>
       <c r="B52" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556280</v>
+        <v>556140</v>
       </c>
       <c r="R52" t="n">
-        <v>7227059</v>
+        <v>7226895</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5972,27 +5972,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091430</v>
+        <v>126091148</v>
       </c>
       <c r="B54" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556140</v>
+        <v>556787</v>
       </c>
       <c r="R54" t="n">
-        <v>7226895</v>
+        <v>7227605</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,12 +6037,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6174,10 +6179,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091148</v>
+        <v>126091381</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6185,21 +6190,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6209,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556787</v>
+        <v>556280</v>
       </c>
       <c r="R56" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6239,17 +6244,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6280,32 +6280,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091442</v>
+        <v>126091095</v>
       </c>
       <c r="B57" t="n">
-        <v>80115</v>
+        <v>91538</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>556494</v>
+        <v>557005</v>
       </c>
       <c r="R57" t="n">
-        <v>7226972</v>
+        <v>7227490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091151</v>
+        <v>126091400</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556935</v>
+        <v>556261</v>
       </c>
       <c r="R58" t="n">
-        <v>7227614</v>
+        <v>7227068</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6446,17 +6446,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6487,32 +6482,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091400</v>
+        <v>126091409</v>
       </c>
       <c r="B59" t="n">
-        <v>80080</v>
+        <v>80116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556261</v>
+        <v>556480</v>
       </c>
       <c r="R59" t="n">
-        <v>7227068</v>
+        <v>7226980</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,32 +6583,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091409</v>
+        <v>126091151</v>
       </c>
       <c r="B60" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556480</v>
+        <v>556935</v>
       </c>
       <c r="R60" t="n">
-        <v>7226980</v>
+        <v>7227614</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6653,12 +6648,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6689,32 +6689,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091095</v>
+        <v>126091442</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>80115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557005</v>
+        <v>556494</v>
       </c>
       <c r="R61" t="n">
-        <v>7227490</v>
+        <v>7226972</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091343</v>
+        <v>126091417</v>
       </c>
       <c r="B62" t="n">
-        <v>91242</v>
+        <v>91260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556373</v>
+        <v>556559</v>
       </c>
       <c r="R62" t="n">
-        <v>7227010</v>
+        <v>7226989</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091373</v>
+        <v>126091359</v>
       </c>
       <c r="B63" t="n">
         <v>80081</v>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556350</v>
+        <v>556280</v>
       </c>
       <c r="R63" t="n">
-        <v>7226997</v>
+        <v>7226845</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091359</v>
+        <v>126091373</v>
       </c>
       <c r="B64" t="n">
         <v>80081</v>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556280</v>
+        <v>556350</v>
       </c>
       <c r="R64" t="n">
-        <v>7226845</v>
+        <v>7226997</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091361</v>
+        <v>126091343</v>
       </c>
       <c r="B65" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556321</v>
+        <v>556373</v>
       </c>
       <c r="R65" t="n">
-        <v>7226929</v>
+        <v>7227010</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091417</v>
+        <v>126091361</v>
       </c>
       <c r="B66" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556559</v>
+        <v>556321</v>
       </c>
       <c r="R66" t="n">
-        <v>7226989</v>
+        <v>7226929</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091386</v>
+        <v>126091066</v>
       </c>
       <c r="B67" t="n">
         <v>80081</v>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556480</v>
+        <v>556946</v>
       </c>
       <c r="R67" t="n">
-        <v>7226980</v>
+        <v>7227602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,12 +7360,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7396,7 +7401,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091066</v>
+        <v>126091386</v>
       </c>
       <c r="B68" t="n">
         <v>80081</v>
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556946</v>
+        <v>556480</v>
       </c>
       <c r="R68" t="n">
-        <v>7227602</v>
+        <v>7226980</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7461,17 +7466,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091384</v>
+        <v>126091337</v>
       </c>
       <c r="B69" t="n">
-        <v>80081</v>
+        <v>91207</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556376</v>
+        <v>556374</v>
       </c>
       <c r="R69" t="n">
-        <v>7227009</v>
+        <v>7226996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7704,32 +7704,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126091337</v>
+        <v>126091384</v>
       </c>
       <c r="B71" t="n">
-        <v>91207</v>
+        <v>80081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>556374</v>
+        <v>556376</v>
       </c>
       <c r="R71" t="n">
-        <v>7226996</v>
+        <v>7227009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7911,10 +7911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091346</v>
+        <v>126091051</v>
       </c>
       <c r="B73" t="n">
-        <v>57656</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,21 +7922,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556194</v>
+        <v>556679</v>
       </c>
       <c r="R73" t="n">
-        <v>7226815</v>
+        <v>7227232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,17 +7976,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8017,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091015</v>
+        <v>126091393</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>79984</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8052,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556931</v>
+        <v>556291</v>
       </c>
       <c r="R74" t="n">
-        <v>7227622</v>
+        <v>7226913</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8082,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8118,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091174</v>
+        <v>126091012</v>
       </c>
       <c r="B75" t="n">
-        <v>91652</v>
+        <v>91207</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8129,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8153,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556888</v>
+        <v>556977</v>
       </c>
       <c r="R75" t="n">
-        <v>7227746</v>
+        <v>7227576</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8219,10 +8214,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091360</v>
+        <v>126091143</v>
       </c>
       <c r="B76" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8230,21 +8225,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556326</v>
+        <v>557106</v>
       </c>
       <c r="R76" t="n">
-        <v>7226893</v>
+        <v>7227606</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8284,12 +8279,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8320,10 +8315,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091375</v>
+        <v>126091402</v>
       </c>
       <c r="B77" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8331,21 +8326,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8355,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556423</v>
+        <v>556280</v>
       </c>
       <c r="R77" t="n">
-        <v>7226984</v>
+        <v>7227059</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8421,7 +8416,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091067</v>
+        <v>126091375</v>
       </c>
       <c r="B78" t="n">
         <v>80081</v>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556690</v>
+        <v>556423</v>
       </c>
       <c r="R78" t="n">
-        <v>7227262</v>
+        <v>7226984</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8486,12 +8481,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,32 +8517,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091355</v>
+        <v>126091174</v>
       </c>
       <c r="B79" t="n">
-        <v>80081</v>
+        <v>91652</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>4217</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8557,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556346</v>
+        <v>556888</v>
       </c>
       <c r="R79" t="n">
-        <v>7227118</v>
+        <v>7227746</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8587,12 +8582,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8623,32 +8618,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091393</v>
+        <v>126091360</v>
       </c>
       <c r="B80" t="n">
-        <v>79984</v>
+        <v>80081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8658,10 +8653,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556291</v>
+        <v>556326</v>
       </c>
       <c r="R80" t="n">
-        <v>7226913</v>
+        <v>7226893</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8724,32 +8719,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091012</v>
+        <v>126091015</v>
       </c>
       <c r="B81" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556977</v>
+        <v>556931</v>
       </c>
       <c r="R81" t="n">
-        <v>7227576</v>
+        <v>7227622</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091402</v>
+        <v>126091355</v>
       </c>
       <c r="B82" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8831,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556280</v>
+        <v>556346</v>
       </c>
       <c r="R82" t="n">
-        <v>7227059</v>
+        <v>7227118</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8926,10 +8921,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091143</v>
+        <v>126091067</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8937,21 +8932,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8961,10 +8956,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>557106</v>
+        <v>556690</v>
       </c>
       <c r="R83" t="n">
-        <v>7227606</v>
+        <v>7227262</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9027,10 +9022,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091051</v>
+        <v>126091346</v>
       </c>
       <c r="B84" t="n">
-        <v>79946</v>
+        <v>57656</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,21 +9033,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556679</v>
+        <v>556194</v>
       </c>
       <c r="R84" t="n">
-        <v>7227232</v>
+        <v>7226815</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9092,12 +9087,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,7 +9128,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091383</v>
+        <v>126091377</v>
       </c>
       <c r="B85" t="n">
         <v>80081</v>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556230</v>
+        <v>556584</v>
       </c>
       <c r="R85" t="n">
-        <v>7226809</v>
+        <v>7227068</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9229,7 +9229,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091377</v>
+        <v>126091372</v>
       </c>
       <c r="B86" t="n">
         <v>80081</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556584</v>
+        <v>556359</v>
       </c>
       <c r="R86" t="n">
-        <v>7227068</v>
+        <v>7226988</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091344</v>
+        <v>126091383</v>
       </c>
       <c r="B87" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9341,21 +9341,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556452</v>
+        <v>556230</v>
       </c>
       <c r="R87" t="n">
-        <v>7226989</v>
+        <v>7226809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091372</v>
+        <v>126091344</v>
       </c>
       <c r="B88" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556359</v>
+        <v>556452</v>
       </c>
       <c r="R88" t="n">
-        <v>7226988</v>
+        <v>7226989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9532,32 +9532,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091165</v>
+        <v>126091027</v>
       </c>
       <c r="B89" t="n">
-        <v>80115</v>
+        <v>57656</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556874</v>
+        <v>557059</v>
       </c>
       <c r="R89" t="n">
-        <v>7227697</v>
+        <v>7227538</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9603,6 +9603,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9633,27 +9638,27 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091141</v>
+        <v>126091166</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9668,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556931</v>
+        <v>556690</v>
       </c>
       <c r="R90" t="n">
-        <v>7227622</v>
+        <v>7227262</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9704,11 +9709,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9739,32 +9739,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091351</v>
+        <v>126091153</v>
       </c>
       <c r="B91" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556346</v>
+        <v>556996</v>
       </c>
       <c r="R91" t="n">
-        <v>7227118</v>
+        <v>7227559</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9804,12 +9804,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9840,7 +9840,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091166</v>
+        <v>126091165</v>
       </c>
       <c r="B92" t="n">
         <v>80115</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556690</v>
+        <v>556874</v>
       </c>
       <c r="R92" t="n">
-        <v>7227262</v>
+        <v>7227697</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9941,7 +9941,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091153</v>
+        <v>126091141</v>
       </c>
       <c r="B93" t="n">
         <v>78977</v>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556996</v>
+        <v>556931</v>
       </c>
       <c r="R93" t="n">
-        <v>7227559</v>
+        <v>7227622</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10012,6 +10012,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10042,32 +10047,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126091027</v>
+        <v>126091351</v>
       </c>
       <c r="B94" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10077,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>557059</v>
+        <v>556346</v>
       </c>
       <c r="R94" t="n">
-        <v>7227538</v>
+        <v>7227118</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10107,17 +10112,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10148,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091418</v>
+        <v>126091441</v>
       </c>
       <c r="B95" t="n">
-        <v>91260</v>
+        <v>80115</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556550</v>
+        <v>556480</v>
       </c>
       <c r="R95" t="n">
-        <v>7227005</v>
+        <v>7226980</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,32 +10249,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091357</v>
+        <v>126091167</v>
       </c>
       <c r="B96" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556061</v>
+        <v>556728</v>
       </c>
       <c r="R96" t="n">
-        <v>7226781</v>
+        <v>7227275</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,10 +10350,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091339</v>
+        <v>126091418</v>
       </c>
       <c r="B97" t="n">
-        <v>91242</v>
+        <v>91260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10361,21 +10361,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556393</v>
+        <v>556550</v>
       </c>
       <c r="R97" t="n">
-        <v>7226994</v>
+        <v>7227005</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091167</v>
+        <v>126091405</v>
       </c>
       <c r="B99" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10563,21 +10563,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556728</v>
+        <v>556230</v>
       </c>
       <c r="R99" t="n">
-        <v>7227275</v>
+        <v>7226809</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10653,32 +10653,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091405</v>
+        <v>126091357</v>
       </c>
       <c r="B100" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556230</v>
+        <v>556061</v>
       </c>
       <c r="R100" t="n">
-        <v>7226809</v>
+        <v>7226781</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10754,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091441</v>
+        <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>80115</v>
+        <v>91242</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556480</v>
+        <v>556393</v>
       </c>
       <c r="R101" t="n">
-        <v>7226980</v>
+        <v>7226994</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091019</v>
+        <v>126091358</v>
       </c>
       <c r="B102" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>557005</v>
+        <v>556070</v>
       </c>
       <c r="R102" t="n">
-        <v>7227490</v>
+        <v>7226750</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,12 +10920,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126091028</v>
+        <v>126091019</v>
       </c>
       <c r="B103" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10991,10 +10991,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>557117</v>
+        <v>557005</v>
       </c>
       <c r="R103" t="n">
-        <v>7227635</v>
+        <v>7227490</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11027,11 +11027,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11062,10 +11057,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091358</v>
+        <v>126091392</v>
       </c>
       <c r="B104" t="n">
-        <v>80081</v>
+        <v>56232</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11073,21 +11068,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>206004</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11097,10 +11092,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>556070</v>
+        <v>556271</v>
       </c>
       <c r="R104" t="n">
-        <v>7226750</v>
+        <v>7226832</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11163,10 +11158,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091392</v>
+        <v>126091028</v>
       </c>
       <c r="B105" t="n">
-        <v>56232</v>
+        <v>57656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11174,21 +11169,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11198,10 +11193,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>556271</v>
+        <v>557117</v>
       </c>
       <c r="R105" t="n">
-        <v>7226832</v>
+        <v>7227635</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11228,12 +11223,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091072</v>
+        <v>126091407</v>
       </c>
       <c r="B106" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556913</v>
+        <v>556365</v>
       </c>
       <c r="R106" t="n">
-        <v>7227621</v>
+        <v>7227004</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11365,32 +11365,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091380</v>
+        <v>126091115</v>
       </c>
       <c r="B107" t="n">
-        <v>80081</v>
+        <v>57760</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556261</v>
+        <v>556797</v>
       </c>
       <c r="R107" t="n">
-        <v>7227068</v>
+        <v>7227252</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091070</v>
+        <v>126091010</v>
       </c>
       <c r="B108" t="n">
-        <v>80081</v>
+        <v>79009</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11477,21 +11477,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556723</v>
+        <v>556904</v>
       </c>
       <c r="R108" t="n">
-        <v>7227276</v>
+        <v>7227703</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091341</v>
+        <v>126091416</v>
       </c>
       <c r="B109" t="n">
-        <v>91242</v>
+        <v>91260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556187</v>
+        <v>556600</v>
       </c>
       <c r="R109" t="n">
-        <v>7226946</v>
+        <v>7227123</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11668,10 +11668,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091416</v>
+        <v>126091421</v>
       </c>
       <c r="B110" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11679,21 +11679,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556600</v>
+        <v>556111</v>
       </c>
       <c r="R110" t="n">
-        <v>7227123</v>
+        <v>7226873</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11739,6 +11739,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11769,32 +11774,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091115</v>
+        <v>126091070</v>
       </c>
       <c r="B111" t="n">
-        <v>57760</v>
+        <v>80081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556797</v>
+        <v>556723</v>
       </c>
       <c r="R111" t="n">
-        <v>7227252</v>
+        <v>7227276</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11870,32 +11875,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091407</v>
+        <v>126091380</v>
       </c>
       <c r="B112" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11905,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556365</v>
+        <v>556261</v>
       </c>
       <c r="R112" t="n">
-        <v>7227004</v>
+        <v>7227068</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11971,10 +11976,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091421</v>
+        <v>126091341</v>
       </c>
       <c r="B113" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11982,21 +11987,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556111</v>
+        <v>556187</v>
       </c>
       <c r="R113" t="n">
-        <v>7226873</v>
+        <v>7226946</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12042,11 +12047,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,10 +12077,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091010</v>
+        <v>126091072</v>
       </c>
       <c r="B114" t="n">
-        <v>79009</v>
+        <v>80081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556904</v>
+        <v>556913</v>
       </c>
       <c r="R114" t="n">
-        <v>7227703</v>
+        <v>7227621</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091068</v>
+        <v>126091017</v>
       </c>
       <c r="B116" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556707</v>
+        <v>556929</v>
       </c>
       <c r="R116" t="n">
-        <v>7227243</v>
+        <v>7227610</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091017</v>
+        <v>126091068</v>
       </c>
       <c r="B117" t="n">
-        <v>91242</v>
+        <v>80081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12391,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556929</v>
+        <v>556707</v>
       </c>
       <c r="R117" t="n">
-        <v>7227610</v>
+        <v>7227243</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091102</v>
+        <v>126091121</v>
       </c>
       <c r="B118" t="n">
-        <v>80080</v>
+        <v>91238</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556740</v>
+        <v>556907</v>
       </c>
       <c r="R118" t="n">
-        <v>7227186</v>
+        <v>7227720</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12546,12 +12546,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091121</v>
+        <v>126091102</v>
       </c>
       <c r="B119" t="n">
-        <v>91238</v>
+        <v>80080</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556907</v>
+        <v>556740</v>
       </c>
       <c r="R119" t="n">
-        <v>7227720</v>
+        <v>7227186</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091394</v>
+        <v>126091052</v>
       </c>
       <c r="B120" t="n">
-        <v>91538</v>
+        <v>98373</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556098</v>
+        <v>557007</v>
       </c>
       <c r="R120" t="n">
-        <v>7226757</v>
+        <v>7227805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12748,12 +12748,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12784,32 +12784,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091387</v>
+        <v>126091445</v>
       </c>
       <c r="B121" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R121" t="n">
-        <v>7226978</v>
+        <v>7227109</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091379</v>
+        <v>126091387</v>
       </c>
       <c r="B122" t="n">
         <v>80081</v>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556305</v>
+        <v>556497</v>
       </c>
       <c r="R122" t="n">
-        <v>7227093</v>
+        <v>7226978</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,10 +12986,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091424</v>
+        <v>126091379</v>
       </c>
       <c r="B123" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556549</v>
+        <v>556305</v>
       </c>
       <c r="R123" t="n">
-        <v>7226986</v>
+        <v>7227093</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,11 +13057,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13092,32 +13087,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091410</v>
+        <v>126091394</v>
       </c>
       <c r="B124" t="n">
-        <v>80116</v>
+        <v>91538</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13127,10 +13122,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556584</v>
+        <v>556098</v>
       </c>
       <c r="R124" t="n">
-        <v>7227068</v>
+        <v>7226757</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13294,10 +13289,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091445</v>
+        <v>126091410</v>
       </c>
       <c r="B126" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13305,21 +13300,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13332,7 +13327,7 @@
         <v>556584</v>
       </c>
       <c r="R126" t="n">
-        <v>7227109</v>
+        <v>7227068</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13395,32 +13390,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091052</v>
+        <v>126091424</v>
       </c>
       <c r="B127" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13430,10 +13425,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>557007</v>
+        <v>556549</v>
       </c>
       <c r="R127" t="n">
-        <v>7227805</v>
+        <v>7226986</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,12 +13455,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13496,32 +13496,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091366</v>
+        <v>126091433</v>
       </c>
       <c r="B128" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556348</v>
+        <v>556280</v>
       </c>
       <c r="R128" t="n">
-        <v>7226965</v>
+        <v>7226845</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13597,7 +13597,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091363</v>
+        <v>126091366</v>
       </c>
       <c r="B129" t="n">
         <v>80081</v>
@@ -13632,10 +13632,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556361</v>
+        <v>556348</v>
       </c>
       <c r="R129" t="n">
-        <v>7226943</v>
+        <v>7226965</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13668,11 +13668,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14107,7 +14102,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091385</v>
+        <v>126091363</v>
       </c>
       <c r="B134" t="n">
         <v>80081</v>
@@ -14142,10 +14137,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556410</v>
+        <v>556361</v>
       </c>
       <c r="R134" t="n">
-        <v>7226996</v>
+        <v>7226943</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14178,6 +14173,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14208,32 +14208,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091433</v>
+        <v>126091385</v>
       </c>
       <c r="B135" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14243,10 +14243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556280</v>
+        <v>556410</v>
       </c>
       <c r="R135" t="n">
-        <v>7226845</v>
+        <v>7226996</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091105</v>
+        <v>126091413</v>
       </c>
       <c r="B136" t="n">
-        <v>80116</v>
+        <v>56839</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556807</v>
+        <v>556662</v>
       </c>
       <c r="R136" t="n">
-        <v>7227608</v>
+        <v>7227178</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,12 +14374,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14410,7 +14415,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091429</v>
+        <v>126091431</v>
       </c>
       <c r="B137" t="n">
         <v>80115</v>
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556272</v>
+        <v>556179</v>
       </c>
       <c r="R137" t="n">
-        <v>7227058</v>
+        <v>7226822</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14511,32 +14516,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091443</v>
+        <v>126091415</v>
       </c>
       <c r="B138" t="n">
-        <v>80115</v>
+        <v>91260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14546,10 +14551,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556529</v>
+        <v>556315</v>
       </c>
       <c r="R138" t="n">
-        <v>7226958</v>
+        <v>7226927</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,7 +14617,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091431</v>
+        <v>126091429</v>
       </c>
       <c r="B139" t="n">
         <v>80115</v>
@@ -14647,10 +14652,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556179</v>
+        <v>556272</v>
       </c>
       <c r="R139" t="n">
-        <v>7226822</v>
+        <v>7227058</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14713,10 +14718,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091140</v>
+        <v>126091127</v>
       </c>
       <c r="B140" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14724,21 +14729,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14748,10 +14753,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>557026</v>
+        <v>556728</v>
       </c>
       <c r="R140" t="n">
-        <v>7227519</v>
+        <v>7227249</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14784,11 +14789,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14819,7 +14819,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091432</v>
+        <v>126091443</v>
       </c>
       <c r="B141" t="n">
         <v>80115</v>
@@ -14854,10 +14854,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556230</v>
+        <v>556529</v>
       </c>
       <c r="R141" t="n">
-        <v>7226809</v>
+        <v>7226958</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15021,32 +15021,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091029</v>
+        <v>126091432</v>
       </c>
       <c r="B143" t="n">
-        <v>57656</v>
+        <v>80115</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15056,10 +15056,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556819</v>
+        <v>556230</v>
       </c>
       <c r="R143" t="n">
-        <v>7227694</v>
+        <v>7226809</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15086,17 +15086,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,32 +15122,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091415</v>
+        <v>126091105</v>
       </c>
       <c r="B144" t="n">
-        <v>91260</v>
+        <v>80116</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15162,10 +15157,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556315</v>
+        <v>556807</v>
       </c>
       <c r="R144" t="n">
-        <v>7226927</v>
+        <v>7227608</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15192,12 +15187,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15228,10 +15223,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091127</v>
+        <v>126091140</v>
       </c>
       <c r="B145" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15239,21 +15234,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15263,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556728</v>
+        <v>557026</v>
       </c>
       <c r="R145" t="n">
-        <v>7227249</v>
+        <v>7227519</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15299,6 +15294,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15531,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091413</v>
+        <v>126091029</v>
       </c>
       <c r="B148" t="n">
-        <v>56839</v>
+        <v>57656</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -15566,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556662</v>
+        <v>556819</v>
       </c>
       <c r="R148" t="n">
-        <v>7227178</v>
+        <v>7227694</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15596,17 +15596,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Tupp</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15637,27 +15637,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091169</v>
+        <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556756</v>
+        <v>556975</v>
       </c>
       <c r="R149" t="n">
-        <v>7227253</v>
+        <v>7227579</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15708,6 +15708,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15738,32 +15743,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091152</v>
+        <v>126091397</v>
       </c>
       <c r="B150" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15773,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556975</v>
+        <v>556378</v>
       </c>
       <c r="R150" t="n">
-        <v>7227579</v>
+        <v>7226996</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15803,17 +15808,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15945,27 +15945,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091149</v>
+        <v>126091169</v>
       </c>
       <c r="B152" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556807</v>
+        <v>556756</v>
       </c>
       <c r="R152" t="n">
-        <v>7227608</v>
+        <v>7227253</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16016,11 +16016,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16051,32 +16046,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091397</v>
+        <v>126091149</v>
       </c>
       <c r="B153" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16086,10 +16081,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556378</v>
+        <v>556807</v>
       </c>
       <c r="R153" t="n">
-        <v>7226996</v>
+        <v>7227608</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16116,12 +16111,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,32 +16152,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091053</v>
+        <v>126091350</v>
       </c>
       <c r="B154" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16187,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556996</v>
+        <v>556589</v>
       </c>
       <c r="R154" t="n">
-        <v>7227559</v>
+        <v>7227059</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16217,12 +16217,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16253,10 +16258,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091388</v>
+        <v>126091040</v>
       </c>
       <c r="B155" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16264,21 +16269,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16288,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556529</v>
+        <v>556781</v>
       </c>
       <c r="R155" t="n">
-        <v>7226958</v>
+        <v>7227272</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16318,12 +16323,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16354,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091378</v>
+        <v>126091053</v>
       </c>
       <c r="B156" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16389,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556353</v>
+        <v>556996</v>
       </c>
       <c r="R156" t="n">
-        <v>7227115</v>
+        <v>7227559</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16419,12 +16429,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16455,10 +16465,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091350</v>
+        <v>126091388</v>
       </c>
       <c r="B157" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16466,21 +16476,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16490,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556589</v>
+        <v>556529</v>
       </c>
       <c r="R157" t="n">
-        <v>7227059</v>
+        <v>7226958</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16526,11 +16536,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16561,10 +16566,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091040</v>
+        <v>126091378</v>
       </c>
       <c r="B158" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16572,21 +16577,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16596,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556781</v>
+        <v>556353</v>
       </c>
       <c r="R158" t="n">
-        <v>7227272</v>
+        <v>7227115</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16626,17 +16631,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091389</v>
+        <v>126091335</v>
       </c>
       <c r="B16" t="n">
-        <v>80081</v>
+        <v>91207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556589</v>
+        <v>556339</v>
       </c>
       <c r="R16" t="n">
-        <v>7227109</v>
+        <v>7226946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091365</v>
+        <v>126091425</v>
       </c>
       <c r="B17" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556359</v>
+        <v>556591</v>
       </c>
       <c r="R17" t="n">
-        <v>7226943</v>
+        <v>7227022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,6 +2271,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2301,7 +2306,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091064</v>
+        <v>126091389</v>
       </c>
       <c r="B18" t="n">
         <v>80081</v>
@@ -2336,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556833</v>
+        <v>556589</v>
       </c>
       <c r="R18" t="n">
-        <v>7227720</v>
+        <v>7227109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,12 +2371,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091335</v>
+        <v>126091365</v>
       </c>
       <c r="B19" t="n">
-        <v>91207</v>
+        <v>80081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556339</v>
+        <v>556359</v>
       </c>
       <c r="R19" t="n">
-        <v>7226946</v>
+        <v>7226943</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,10 +2508,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091425</v>
+        <v>126091064</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,21 +2519,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2538,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556591</v>
+        <v>556833</v>
       </c>
       <c r="R20" t="n">
-        <v>7227022</v>
+        <v>7227720</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2568,17 +2573,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091164</v>
+        <v>126091435</v>
       </c>
       <c r="B24" t="n">
-        <v>88651</v>
+        <v>80115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556775</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091435</v>
+        <v>126091106</v>
       </c>
       <c r="B25" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556359</v>
+        <v>556709</v>
       </c>
       <c r="R25" t="n">
-        <v>7226941</v>
+        <v>7227248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B26" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R26" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091073</v>
+        <v>126091368</v>
       </c>
       <c r="B27" t="n">
         <v>80081</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556756</v>
+        <v>556346</v>
       </c>
       <c r="R27" t="n">
-        <v>7227253</v>
+        <v>7226961</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091368</v>
+        <v>126091340</v>
       </c>
       <c r="B28" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556346</v>
+        <v>556312</v>
       </c>
       <c r="R28" t="n">
-        <v>7226961</v>
+        <v>7227107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091340</v>
+        <v>126091164</v>
       </c>
       <c r="B29" t="n">
-        <v>91242</v>
+        <v>88651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556312</v>
+        <v>556775</v>
       </c>
       <c r="R29" t="n">
-        <v>7227107</v>
+        <v>7227253</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5770,32 +5770,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091430</v>
+        <v>126091381</v>
       </c>
       <c r="B52" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556140</v>
+        <v>556280</v>
       </c>
       <c r="R52" t="n">
-        <v>7226895</v>
+        <v>7227059</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091438</v>
+        <v>126091430</v>
       </c>
       <c r="B53" t="n">
         <v>80115</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556350</v>
+        <v>556140</v>
       </c>
       <c r="R53" t="n">
-        <v>7226997</v>
+        <v>7226895</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5972,27 +5972,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091148</v>
+        <v>126091438</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556787</v>
+        <v>556350</v>
       </c>
       <c r="R54" t="n">
-        <v>7227605</v>
+        <v>7226997</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,17 +6037,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6078,10 +6073,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091401</v>
+        <v>126091148</v>
       </c>
       <c r="B55" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6089,21 +6084,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6113,10 +6108,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556271</v>
+        <v>556787</v>
       </c>
       <c r="R55" t="n">
-        <v>7227059</v>
+        <v>7227605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6143,12 +6138,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126091381</v>
+        <v>126091401</v>
       </c>
       <c r="B56" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6190,21 +6190,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>556280</v>
+        <v>556271</v>
       </c>
       <c r="R56" t="n">
         <v>7227059</v>
@@ -9128,32 +9128,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091377</v>
+        <v>126091166</v>
       </c>
       <c r="B85" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556584</v>
+        <v>556690</v>
       </c>
       <c r="R85" t="n">
-        <v>7227068</v>
+        <v>7227262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9229,10 +9229,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091372</v>
+        <v>126091153</v>
       </c>
       <c r="B86" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9240,21 +9240,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556359</v>
+        <v>556996</v>
       </c>
       <c r="R86" t="n">
-        <v>7226988</v>
+        <v>7227559</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9330,32 +9330,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091383</v>
+        <v>126091165</v>
       </c>
       <c r="B87" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556230</v>
+        <v>556874</v>
       </c>
       <c r="R87" t="n">
-        <v>7226809</v>
+        <v>7227697</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9431,10 +9431,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091344</v>
+        <v>126091141</v>
       </c>
       <c r="B88" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556452</v>
+        <v>556931</v>
       </c>
       <c r="R88" t="n">
-        <v>7226989</v>
+        <v>7227622</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9496,12 +9496,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9532,32 +9537,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091027</v>
+        <v>126091351</v>
       </c>
       <c r="B89" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9567,10 +9572,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>557059</v>
+        <v>556346</v>
       </c>
       <c r="R89" t="n">
-        <v>7227538</v>
+        <v>7227118</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9597,17 +9602,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9638,32 +9638,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091166</v>
+        <v>126091377</v>
       </c>
       <c r="B90" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556690</v>
+        <v>556584</v>
       </c>
       <c r="R90" t="n">
-        <v>7227262</v>
+        <v>7227068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9739,10 +9739,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091153</v>
+        <v>126091372</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556996</v>
+        <v>556359</v>
       </c>
       <c r="R91" t="n">
-        <v>7227559</v>
+        <v>7226988</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9804,12 +9804,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9840,32 +9840,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091165</v>
+        <v>126091383</v>
       </c>
       <c r="B92" t="n">
-        <v>80115</v>
+        <v>80081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556874</v>
+        <v>556230</v>
       </c>
       <c r="R92" t="n">
-        <v>7227697</v>
+        <v>7226809</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9941,10 +9941,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091141</v>
+        <v>126091344</v>
       </c>
       <c r="B93" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9952,21 +9952,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556931</v>
+        <v>556452</v>
       </c>
       <c r="R93" t="n">
-        <v>7227622</v>
+        <v>7226989</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10006,17 +10006,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10047,32 +10042,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126091351</v>
+        <v>126091027</v>
       </c>
       <c r="B94" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>556346</v>
+        <v>557059</v>
       </c>
       <c r="R94" t="n">
-        <v>7227118</v>
+        <v>7227538</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10112,12 +10107,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11057,10 +11057,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091392</v>
+        <v>126091028</v>
       </c>
       <c r="B104" t="n">
-        <v>56232</v>
+        <v>57656</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11068,21 +11068,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>556271</v>
+        <v>557117</v>
       </c>
       <c r="R104" t="n">
-        <v>7226832</v>
+        <v>7227635</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11122,12 +11122,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11158,10 +11163,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126091028</v>
+        <v>126091392</v>
       </c>
       <c r="B105" t="n">
-        <v>57656</v>
+        <v>56232</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11169,21 +11174,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11193,10 +11198,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>557117</v>
+        <v>556271</v>
       </c>
       <c r="R105" t="n">
-        <v>7227635</v>
+        <v>7226832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11223,17 +11228,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11365,32 +11365,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091115</v>
+        <v>126091416</v>
       </c>
       <c r="B107" t="n">
-        <v>57760</v>
+        <v>91260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556797</v>
+        <v>556600</v>
       </c>
       <c r="R107" t="n">
-        <v>7227252</v>
+        <v>7227123</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,10 +11466,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091010</v>
+        <v>126091421</v>
       </c>
       <c r="B108" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11477,21 +11477,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556904</v>
+        <v>556111</v>
       </c>
       <c r="R108" t="n">
-        <v>7227703</v>
+        <v>7226873</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,12 +11531,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11567,10 +11572,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091416</v>
+        <v>126091070</v>
       </c>
       <c r="B109" t="n">
-        <v>91260</v>
+        <v>80081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11578,21 +11583,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11602,10 +11607,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556600</v>
+        <v>556723</v>
       </c>
       <c r="R109" t="n">
-        <v>7227123</v>
+        <v>7227276</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,12 +11637,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11668,10 +11673,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091421</v>
+        <v>126091380</v>
       </c>
       <c r="B110" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11679,21 +11684,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,10 +11708,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556111</v>
+        <v>556261</v>
       </c>
       <c r="R110" t="n">
-        <v>7226873</v>
+        <v>7227068</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11739,11 +11744,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091070</v>
+        <v>126091341</v>
       </c>
       <c r="B111" t="n">
-        <v>80081</v>
+        <v>91242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11785,21 +11785,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556723</v>
+        <v>556187</v>
       </c>
       <c r="R111" t="n">
-        <v>7227276</v>
+        <v>7226946</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11839,12 +11839,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11875,7 +11875,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091380</v>
+        <v>126091072</v>
       </c>
       <c r="B112" t="n">
         <v>80081</v>
@@ -11910,10 +11910,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556261</v>
+        <v>556913</v>
       </c>
       <c r="R112" t="n">
-        <v>7227068</v>
+        <v>7227621</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11976,32 +11976,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091341</v>
+        <v>126091115</v>
       </c>
       <c r="B113" t="n">
-        <v>91242</v>
+        <v>57760</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556187</v>
+        <v>556797</v>
       </c>
       <c r="R113" t="n">
-        <v>7226946</v>
+        <v>7227252</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12041,12 +12041,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,10 +12077,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091072</v>
+        <v>126091010</v>
       </c>
       <c r="B114" t="n">
-        <v>80081</v>
+        <v>79009</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12088,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556913</v>
+        <v>556904</v>
       </c>
       <c r="R114" t="n">
-        <v>7227621</v>
+        <v>7227703</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12178,10 +12178,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B115" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12189,21 +12189,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R115" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091017</v>
+        <v>126091121</v>
       </c>
       <c r="B116" t="n">
-        <v>91242</v>
+        <v>91238</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556929</v>
+        <v>556907</v>
       </c>
       <c r="R116" t="n">
-        <v>7227610</v>
+        <v>7227720</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12380,7 +12380,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091068</v>
+        <v>126091084</v>
       </c>
       <c r="B117" t="n">
         <v>80081</v>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556707</v>
+        <v>556737</v>
       </c>
       <c r="R117" t="n">
-        <v>7227243</v>
+        <v>7227192</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,12 +12445,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12481,10 +12481,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126091121</v>
+        <v>126091017</v>
       </c>
       <c r="B118" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12492,21 +12492,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>556907</v>
+        <v>556929</v>
       </c>
       <c r="R118" t="n">
-        <v>7227720</v>
+        <v>7227610</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091102</v>
+        <v>126091068</v>
       </c>
       <c r="B119" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556740</v>
+        <v>556707</v>
       </c>
       <c r="R119" t="n">
-        <v>7227186</v>
+        <v>7227243</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12647,12 +12647,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091052</v>
+        <v>126091394</v>
       </c>
       <c r="B120" t="n">
-        <v>98373</v>
+        <v>91538</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>557007</v>
+        <v>556098</v>
       </c>
       <c r="R120" t="n">
-        <v>7227805</v>
+        <v>7226757</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12748,12 +12748,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12885,32 +12885,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091387</v>
+        <v>126091444</v>
       </c>
       <c r="B122" t="n">
-        <v>80081</v>
+        <v>80115</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>556497</v>
+        <v>556584</v>
       </c>
       <c r="R122" t="n">
-        <v>7226978</v>
+        <v>7227068</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,32 +12986,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091379</v>
+        <v>126091410</v>
       </c>
       <c r="B123" t="n">
-        <v>80081</v>
+        <v>80116</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556305</v>
+        <v>556584</v>
       </c>
       <c r="R123" t="n">
-        <v>7227093</v>
+        <v>7227068</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091394</v>
+        <v>126091424</v>
       </c>
       <c r="B124" t="n">
-        <v>91538</v>
+        <v>78977</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13098,21 +13098,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13122,10 +13122,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556098</v>
+        <v>556549</v>
       </c>
       <c r="R124" t="n">
-        <v>7226757</v>
+        <v>7226986</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13158,6 +13158,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13188,10 +13193,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091444</v>
+        <v>126091052</v>
       </c>
       <c r="B125" t="n">
-        <v>80115</v>
+        <v>98373</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13199,21 +13204,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13223,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>556584</v>
+        <v>557007</v>
       </c>
       <c r="R125" t="n">
-        <v>7227068</v>
+        <v>7227805</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13253,12 +13258,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13289,32 +13294,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091410</v>
+        <v>126091387</v>
       </c>
       <c r="B126" t="n">
-        <v>80116</v>
+        <v>80081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13324,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556584</v>
+        <v>556497</v>
       </c>
       <c r="R126" t="n">
-        <v>7227068</v>
+        <v>7226978</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13390,10 +13395,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091424</v>
+        <v>126091379</v>
       </c>
       <c r="B127" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13401,21 +13406,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13425,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556549</v>
+        <v>556305</v>
       </c>
       <c r="R127" t="n">
-        <v>7226986</v>
+        <v>7227093</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13461,11 +13466,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD127" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091395</v>
+        <v>126091342</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556308</v>
+        <v>556306</v>
       </c>
       <c r="R2" t="n">
         <v>7226876</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091440</v>
+        <v>126091395</v>
       </c>
       <c r="B3" t="n">
-        <v>80115</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556465</v>
+        <v>556308</v>
       </c>
       <c r="R3" t="n">
-        <v>7226995</v>
+        <v>7226876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091408</v>
+        <v>126091362</v>
       </c>
       <c r="B4" t="n">
-        <v>80116</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556467</v>
+        <v>556369</v>
       </c>
       <c r="R4" t="n">
-        <v>7226993</v>
+        <v>7226946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091128</v>
+        <v>126091440</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>80118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556830</v>
+        <v>556465</v>
       </c>
       <c r="R5" t="n">
-        <v>7227331</v>
+        <v>7226995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091123</v>
+        <v>126091065</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>80084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557106</v>
+        <v>556817</v>
       </c>
       <c r="R6" t="n">
-        <v>7227606</v>
+        <v>7227591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091362</v>
+        <v>126091370</v>
       </c>
       <c r="B7" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556369</v>
+        <v>556364</v>
       </c>
       <c r="R7" t="n">
-        <v>7226946</v>
+        <v>7226989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126091342</v>
+        <v>126091408</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>80119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556306</v>
+        <v>556467</v>
       </c>
       <c r="R8" t="n">
-        <v>7226876</v>
+        <v>7226993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126091065</v>
+        <v>126091128</v>
       </c>
       <c r="B9" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556817</v>
+        <v>556830</v>
       </c>
       <c r="R9" t="n">
-        <v>7227591</v>
+        <v>7227331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091370</v>
+        <v>126091123</v>
       </c>
       <c r="B10" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556364</v>
+        <v>557106</v>
       </c>
       <c r="R10" t="n">
-        <v>7226989</v>
+        <v>7227606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1587,7 +1587,7 @@
         <v>126091043</v>
       </c>
       <c r="B11" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126091439</v>
       </c>
       <c r="B12" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126091420</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>126091428</v>
       </c>
       <c r="B14" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>126091147</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,32 +2099,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126091335</v>
+        <v>126091389</v>
       </c>
       <c r="B16" t="n">
-        <v>91207</v>
+        <v>80084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556339</v>
+        <v>556589</v>
       </c>
       <c r="R16" t="n">
-        <v>7226946</v>
+        <v>7227109</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091425</v>
+        <v>126091064</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556591</v>
+        <v>556833</v>
       </c>
       <c r="R17" t="n">
-        <v>7227022</v>
+        <v>7227720</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,17 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,32 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091389</v>
+        <v>126091335</v>
       </c>
       <c r="B18" t="n">
-        <v>80081</v>
+        <v>91210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2341,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556589</v>
+        <v>556339</v>
       </c>
       <c r="R18" t="n">
-        <v>7227109</v>
+        <v>7226946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091365</v>
+        <v>126091374</v>
       </c>
       <c r="B19" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556359</v>
+        <v>556371</v>
       </c>
       <c r="R19" t="n">
-        <v>7226943</v>
+        <v>7226988</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126091064</v>
+        <v>126091425</v>
       </c>
       <c r="B20" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2519,21 +2514,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2543,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556833</v>
+        <v>556591</v>
       </c>
       <c r="R20" t="n">
-        <v>7227720</v>
+        <v>7227022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,12 +2568,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,10 +2609,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091374</v>
+        <v>126091365</v>
       </c>
       <c r="B21" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556371</v>
+        <v>556359</v>
       </c>
       <c r="R21" t="n">
-        <v>7226988</v>
+        <v>7226943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091041</v>
+        <v>126091146</v>
       </c>
       <c r="B22" t="n">
-        <v>57816</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557020</v>
+        <v>556904</v>
       </c>
       <c r="R22" t="n">
-        <v>7227532</v>
+        <v>7227703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091146</v>
+        <v>126091041</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>57817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,21 +2822,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556904</v>
+        <v>557020</v>
       </c>
       <c r="R23" t="n">
-        <v>7227703</v>
+        <v>7227532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091435</v>
+        <v>126091164</v>
       </c>
       <c r="B24" t="n">
-        <v>80115</v>
+        <v>88654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556775</v>
       </c>
       <c r="R24" t="n">
-        <v>7226941</v>
+        <v>7227253</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091106</v>
+        <v>126091340</v>
       </c>
       <c r="B25" t="n">
-        <v>80116</v>
+        <v>91245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556709</v>
+        <v>556312</v>
       </c>
       <c r="R25" t="n">
-        <v>7227248</v>
+        <v>7227107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091073</v>
+        <v>126091435</v>
       </c>
       <c r="B26" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556756</v>
+        <v>556359</v>
       </c>
       <c r="R26" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091368</v>
+        <v>126091106</v>
       </c>
       <c r="B27" t="n">
-        <v>80081</v>
+        <v>80119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556346</v>
+        <v>556709</v>
       </c>
       <c r="R27" t="n">
-        <v>7226961</v>
+        <v>7227248</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091340</v>
+        <v>126091368</v>
       </c>
       <c r="B28" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556312</v>
+        <v>556346</v>
       </c>
       <c r="R28" t="n">
-        <v>7227107</v>
+        <v>7226961</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091164</v>
+        <v>126091073</v>
       </c>
       <c r="B29" t="n">
-        <v>88651</v>
+        <v>80084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556775</v>
+        <v>556756</v>
       </c>
       <c r="R29" t="n">
         <v>7227253</v>
@@ -3521,7 +3521,7 @@
         <v>126091382</v>
       </c>
       <c r="B30" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>126091347</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>126091034</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126091042</v>
+        <v>126091448</v>
       </c>
       <c r="B33" t="n">
-        <v>80109</v>
+        <v>91915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556817</v>
+        <v>556484</v>
       </c>
       <c r="R33" t="n">
-        <v>7227591</v>
+        <v>7226980</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126091414</v>
+        <v>126091013</v>
       </c>
       <c r="B34" t="n">
-        <v>91260</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,21 +3943,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556303</v>
+        <v>556830</v>
       </c>
       <c r="R34" t="n">
-        <v>7226905</v>
+        <v>7227704</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4033,10 +4033,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126091124</v>
+        <v>126091356</v>
       </c>
       <c r="B35" t="n">
-        <v>91260</v>
+        <v>80084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4044,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556698</v>
+        <v>556271</v>
       </c>
       <c r="R35" t="n">
-        <v>7227248</v>
+        <v>7227059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4134,10 +4134,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126091406</v>
+        <v>126091042</v>
       </c>
       <c r="B36" t="n">
-        <v>80116</v>
+        <v>80112</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4145,21 +4145,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556314</v>
+        <v>556817</v>
       </c>
       <c r="R36" t="n">
-        <v>7226891</v>
+        <v>7227591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4235,32 +4235,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126091448</v>
+        <v>126091414</v>
       </c>
       <c r="B37" t="n">
-        <v>91912</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4270,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556484</v>
+        <v>556303</v>
       </c>
       <c r="R37" t="n">
-        <v>7226980</v>
+        <v>7226905</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126091013</v>
+        <v>126091369</v>
       </c>
       <c r="B38" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,21 +4347,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556830</v>
+        <v>556333</v>
       </c>
       <c r="R38" t="n">
-        <v>7227704</v>
+        <v>7227009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4437,10 +4437,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126091369</v>
+        <v>126091124</v>
       </c>
       <c r="B39" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>556333</v>
+        <v>556698</v>
       </c>
       <c r="R39" t="n">
-        <v>7227009</v>
+        <v>7227248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4502,12 +4502,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4538,32 +4538,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126091356</v>
+        <v>126091406</v>
       </c>
       <c r="B40" t="n">
-        <v>80081</v>
+        <v>80119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>556271</v>
+        <v>556314</v>
       </c>
       <c r="R40" t="n">
-        <v>7227059</v>
+        <v>7226891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
         <v>126091349</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091403</v>
+        <v>126091075</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>80084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556357</v>
+        <v>556792</v>
       </c>
       <c r="R42" t="n">
-        <v>7227004</v>
+        <v>7227253</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,32 +4846,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091044</v>
+        <v>126091403</v>
       </c>
       <c r="B43" t="n">
-        <v>80109</v>
+        <v>80083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556826</v>
+        <v>556357</v>
       </c>
       <c r="R43" t="n">
-        <v>7227309</v>
+        <v>7227004</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091107</v>
+        <v>126091044</v>
       </c>
       <c r="B44" t="n">
-        <v>80116</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,21 +4958,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556723</v>
+        <v>556826</v>
       </c>
       <c r="R44" t="n">
-        <v>7227276</v>
+        <v>7227309</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,32 +5048,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091144</v>
+        <v>126091107</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>80119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557048</v>
+        <v>556723</v>
       </c>
       <c r="R45" t="n">
-        <v>7227797</v>
+        <v>7227276</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091422</v>
+        <v>126091144</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556407</v>
+        <v>557048</v>
       </c>
       <c r="R46" t="n">
-        <v>7226992</v>
+        <v>7227797</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,17 +5214,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091145</v>
+        <v>126091422</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5290,10 +5285,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556897</v>
+        <v>556407</v>
       </c>
       <c r="R47" t="n">
-        <v>7227735</v>
+        <v>7226992</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5320,12 +5315,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5361,10 +5356,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091129</v>
+        <v>126091145</v>
       </c>
       <c r="B48" t="n">
-        <v>91260</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5372,21 +5367,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556685</v>
+        <v>556897</v>
       </c>
       <c r="R48" t="n">
-        <v>7227107</v>
+        <v>7227735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5426,12 +5421,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091075</v>
+        <v>126091129</v>
       </c>
       <c r="B49" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556792</v>
+        <v>556685</v>
       </c>
       <c r="R49" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5563,32 +5563,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091352</v>
+        <v>126091348</v>
       </c>
       <c r="B50" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556293</v>
+        <v>556351</v>
       </c>
       <c r="R50" t="n">
-        <v>7227068</v>
+        <v>7226920</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5634,6 +5634,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5664,32 +5669,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126091348</v>
+        <v>126091352</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556351</v>
+        <v>556293</v>
       </c>
       <c r="R51" t="n">
-        <v>7226920</v>
+        <v>7227068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5735,11 +5740,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5770,32 +5770,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126091381</v>
+        <v>126091430</v>
       </c>
       <c r="B52" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>556280</v>
+        <v>556140</v>
       </c>
       <c r="R52" t="n">
-        <v>7227059</v>
+        <v>7226895</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126091430</v>
+        <v>126091438</v>
       </c>
       <c r="B53" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>556140</v>
+        <v>556350</v>
       </c>
       <c r="R53" t="n">
-        <v>7226895</v>
+        <v>7226997</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5972,27 +5972,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126091438</v>
+        <v>126091148</v>
       </c>
       <c r="B54" t="n">
-        <v>80115</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>556350</v>
+        <v>556787</v>
       </c>
       <c r="R54" t="n">
-        <v>7226997</v>
+        <v>7227605</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,12 +6037,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6073,10 +6078,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126091148</v>
+        <v>126091381</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,21 +6089,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6108,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>556787</v>
+        <v>556280</v>
       </c>
       <c r="R55" t="n">
-        <v>7227605</v>
+        <v>7227059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,17 +6143,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6182,7 +6182,7 @@
         <v>126091401</v>
       </c>
       <c r="B56" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,10 +6280,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126091095</v>
+        <v>126091400</v>
       </c>
       <c r="B57" t="n">
-        <v>91538</v>
+        <v>80083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557005</v>
+        <v>556261</v>
       </c>
       <c r="R57" t="n">
-        <v>7227490</v>
+        <v>7227068</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126091400</v>
+        <v>126091409</v>
       </c>
       <c r="B58" t="n">
-        <v>80080</v>
+        <v>80119</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>556261</v>
+        <v>556480</v>
       </c>
       <c r="R58" t="n">
-        <v>7227068</v>
+        <v>7226980</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6482,32 +6482,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126091409</v>
+        <v>126091151</v>
       </c>
       <c r="B59" t="n">
-        <v>80116</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>556480</v>
+        <v>556935</v>
       </c>
       <c r="R59" t="n">
-        <v>7226980</v>
+        <v>7227614</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,12 +6547,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6583,10 +6588,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126091151</v>
+        <v>126091373</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6594,21 +6599,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556935</v>
+        <v>556350</v>
       </c>
       <c r="R60" t="n">
-        <v>7227614</v>
+        <v>7226997</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6648,17 +6653,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6689,32 +6689,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126091442</v>
+        <v>126091359</v>
       </c>
       <c r="B61" t="n">
-        <v>80115</v>
+        <v>80084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>556494</v>
+        <v>556280</v>
       </c>
       <c r="R61" t="n">
-        <v>7226972</v>
+        <v>7226845</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6790,10 +6790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126091417</v>
+        <v>126091361</v>
       </c>
       <c r="B62" t="n">
-        <v>91260</v>
+        <v>80084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6801,21 +6801,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6825,10 +6825,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>556559</v>
+        <v>556321</v>
       </c>
       <c r="R62" t="n">
-        <v>7226989</v>
+        <v>7226929</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,32 +6891,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126091359</v>
+        <v>126091442</v>
       </c>
       <c r="B63" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>556280</v>
+        <v>556494</v>
       </c>
       <c r="R63" t="n">
-        <v>7226845</v>
+        <v>7226972</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126091373</v>
+        <v>126091417</v>
       </c>
       <c r="B64" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>556350</v>
+        <v>556559</v>
       </c>
       <c r="R64" t="n">
-        <v>7226997</v>
+        <v>7226989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126091343</v>
+        <v>126091386</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>556373</v>
+        <v>556480</v>
       </c>
       <c r="R65" t="n">
-        <v>7227010</v>
+        <v>7226980</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,10 +7194,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126091361</v>
+        <v>126091066</v>
       </c>
       <c r="B66" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>556321</v>
+        <v>556946</v>
       </c>
       <c r="R66" t="n">
-        <v>7226929</v>
+        <v>7227602</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7259,12 +7259,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7295,10 +7300,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126091066</v>
+        <v>126091095</v>
       </c>
       <c r="B67" t="n">
-        <v>80081</v>
+        <v>91541</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7306,21 +7311,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7330,10 +7335,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>556946</v>
+        <v>557005</v>
       </c>
       <c r="R67" t="n">
-        <v>7227602</v>
+        <v>7227490</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7366,11 +7371,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7401,10 +7401,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126091386</v>
+        <v>126091343</v>
       </c>
       <c r="B68" t="n">
-        <v>80081</v>
+        <v>91245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7412,21 +7412,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>556480</v>
+        <v>556373</v>
       </c>
       <c r="R68" t="n">
-        <v>7226980</v>
+        <v>7227010</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,32 +7502,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126091337</v>
+        <v>126091345</v>
       </c>
       <c r="B69" t="n">
-        <v>91207</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>556374</v>
+        <v>556499</v>
       </c>
       <c r="R69" t="n">
-        <v>7226996</v>
+        <v>7227184</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,6 +7573,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7603,10 +7608,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126091090</v>
+        <v>126091337</v>
       </c>
       <c r="B70" t="n">
-        <v>79984</v>
+        <v>91210</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7614,21 +7619,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7638,10 +7643,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>556690</v>
+        <v>556374</v>
       </c>
       <c r="R70" t="n">
-        <v>7227262</v>
+        <v>7226996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,12 +7673,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7707,7 +7712,7 @@
         <v>126091384</v>
       </c>
       <c r="B71" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7805,32 +7810,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126091345</v>
+        <v>126091090</v>
       </c>
       <c r="B72" t="n">
-        <v>57656</v>
+        <v>79987</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7840,10 +7845,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556499</v>
+        <v>556690</v>
       </c>
       <c r="R72" t="n">
-        <v>7227184</v>
+        <v>7227262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7870,17 +7875,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7911,10 +7911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091051</v>
+        <v>126091015</v>
       </c>
       <c r="B73" t="n">
-        <v>79946</v>
+        <v>91245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7922,21 +7922,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>388</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556679</v>
+        <v>556931</v>
       </c>
       <c r="R73" t="n">
-        <v>7227232</v>
+        <v>7227622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091393</v>
+        <v>126091051</v>
       </c>
       <c r="B74" t="n">
-        <v>79984</v>
+        <v>79949</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556291</v>
+        <v>556679</v>
       </c>
       <c r="R74" t="n">
-        <v>7226913</v>
+        <v>7227232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8113,32 +8113,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091012</v>
+        <v>126091346</v>
       </c>
       <c r="B75" t="n">
-        <v>91207</v>
+        <v>57657</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556977</v>
+        <v>556194</v>
       </c>
       <c r="R75" t="n">
-        <v>7227576</v>
+        <v>7226815</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,12 +8178,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8214,32 +8219,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091143</v>
+        <v>126091393</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>79987</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8249,10 +8254,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>557106</v>
+        <v>556291</v>
       </c>
       <c r="R76" t="n">
-        <v>7227606</v>
+        <v>7226913</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8279,12 +8284,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8315,32 +8320,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091402</v>
+        <v>126091012</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>91210</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556280</v>
+        <v>556977</v>
       </c>
       <c r="R77" t="n">
-        <v>7227059</v>
+        <v>7227576</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,12 +8385,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,10 +8421,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091375</v>
+        <v>126091143</v>
       </c>
       <c r="B78" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,21 +8432,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8451,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>556423</v>
+        <v>557106</v>
       </c>
       <c r="R78" t="n">
-        <v>7226984</v>
+        <v>7227606</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8481,12 +8486,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8520,7 +8525,7 @@
         <v>126091174</v>
       </c>
       <c r="B79" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8621,7 +8626,7 @@
         <v>126091360</v>
       </c>
       <c r="B80" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8719,10 +8724,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091015</v>
+        <v>126091375</v>
       </c>
       <c r="B81" t="n">
-        <v>91242</v>
+        <v>80084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8730,21 +8735,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8754,10 +8759,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556931</v>
+        <v>556423</v>
       </c>
       <c r="R81" t="n">
-        <v>7227622</v>
+        <v>7226984</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8784,12 +8789,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8820,10 +8825,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091355</v>
+        <v>126091402</v>
       </c>
       <c r="B82" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8831,21 +8836,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556346</v>
+        <v>556280</v>
       </c>
       <c r="R82" t="n">
-        <v>7227118</v>
+        <v>7227059</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8924,7 +8929,7 @@
         <v>126091067</v>
       </c>
       <c r="B83" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9022,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091346</v>
+        <v>126091355</v>
       </c>
       <c r="B84" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9033,21 +9038,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9057,10 +9062,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556194</v>
+        <v>556346</v>
       </c>
       <c r="R84" t="n">
-        <v>7226815</v>
+        <v>7227118</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9093,11 +9098,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9128,32 +9128,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126091166</v>
+        <v>126091344</v>
       </c>
       <c r="B85" t="n">
-        <v>80115</v>
+        <v>91245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>556690</v>
+        <v>556452</v>
       </c>
       <c r="R85" t="n">
-        <v>7227262</v>
+        <v>7226989</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9229,27 +9229,27 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126091153</v>
+        <v>126091166</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>80118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>556996</v>
+        <v>556690</v>
       </c>
       <c r="R86" t="n">
-        <v>7227559</v>
+        <v>7227262</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9330,32 +9330,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126091165</v>
+        <v>126091383</v>
       </c>
       <c r="B87" t="n">
-        <v>80115</v>
+        <v>80084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>556874</v>
+        <v>556230</v>
       </c>
       <c r="R87" t="n">
-        <v>7227697</v>
+        <v>7226809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9431,10 +9431,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126091141</v>
+        <v>126091377</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>556931</v>
+        <v>556584</v>
       </c>
       <c r="R88" t="n">
-        <v>7227622</v>
+        <v>7227068</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9496,17 +9496,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9537,32 +9532,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126091351</v>
+        <v>126091153</v>
       </c>
       <c r="B89" t="n">
-        <v>80109</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9572,10 +9567,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>556346</v>
+        <v>556996</v>
       </c>
       <c r="R89" t="n">
-        <v>7227118</v>
+        <v>7227559</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9602,12 +9597,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9638,32 +9633,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126091377</v>
+        <v>126091165</v>
       </c>
       <c r="B90" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9673,10 +9668,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>556584</v>
+        <v>556874</v>
       </c>
       <c r="R90" t="n">
-        <v>7227068</v>
+        <v>7227697</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9703,12 +9698,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9739,10 +9734,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126091372</v>
+        <v>126091141</v>
       </c>
       <c r="B91" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9750,21 +9745,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9774,10 +9769,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556359</v>
+        <v>556931</v>
       </c>
       <c r="R91" t="n">
-        <v>7226988</v>
+        <v>7227622</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9804,12 +9799,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9840,10 +9840,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126091383</v>
+        <v>126091372</v>
       </c>
       <c r="B92" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>556230</v>
+        <v>556359</v>
       </c>
       <c r="R92" t="n">
-        <v>7226809</v>
+        <v>7226988</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9941,32 +9941,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126091344</v>
+        <v>126091351</v>
       </c>
       <c r="B93" t="n">
-        <v>91242</v>
+        <v>80112</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9976,10 +9976,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>556452</v>
+        <v>556346</v>
       </c>
       <c r="R93" t="n">
-        <v>7226989</v>
+        <v>7227118</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10045,7 +10045,7 @@
         <v>126091027</v>
       </c>
       <c r="B94" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10148,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091441</v>
+        <v>126091339</v>
       </c>
       <c r="B95" t="n">
-        <v>80115</v>
+        <v>91245</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556480</v>
+        <v>556393</v>
       </c>
       <c r="R95" t="n">
-        <v>7226980</v>
+        <v>7226994</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,10 +10249,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091167</v>
+        <v>126091441</v>
       </c>
       <c r="B96" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556728</v>
+        <v>556480</v>
       </c>
       <c r="R96" t="n">
-        <v>7227275</v>
+        <v>7226980</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091418</v>
+        <v>126091167</v>
       </c>
       <c r="B97" t="n">
-        <v>91260</v>
+        <v>80118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556550</v>
+        <v>556728</v>
       </c>
       <c r="R97" t="n">
-        <v>7227005</v>
+        <v>7227275</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10415,12 +10415,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10451,10 +10451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091125</v>
+        <v>126091418</v>
       </c>
       <c r="B98" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556893</v>
+        <v>556550</v>
       </c>
       <c r="R98" t="n">
-        <v>7227703</v>
+        <v>7227005</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10552,32 +10552,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091405</v>
+        <v>126091357</v>
       </c>
       <c r="B99" t="n">
-        <v>80116</v>
+        <v>80084</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556230</v>
+        <v>556061</v>
       </c>
       <c r="R99" t="n">
-        <v>7226809</v>
+        <v>7226781</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10653,10 +10653,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091357</v>
+        <v>126091125</v>
       </c>
       <c r="B100" t="n">
-        <v>80081</v>
+        <v>91263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10664,21 +10664,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556061</v>
+        <v>556893</v>
       </c>
       <c r="R100" t="n">
-        <v>7226781</v>
+        <v>7227703</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10754,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091339</v>
+        <v>126091405</v>
       </c>
       <c r="B101" t="n">
-        <v>91242</v>
+        <v>80119</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556393</v>
+        <v>556230</v>
       </c>
       <c r="R101" t="n">
-        <v>7226994</v>
+        <v>7226809</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10855,10 +10855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126091358</v>
+        <v>126091028</v>
       </c>
       <c r="B102" t="n">
-        <v>80081</v>
+        <v>57657</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10866,21 +10866,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>556070</v>
+        <v>557117</v>
       </c>
       <c r="R102" t="n">
-        <v>7226750</v>
+        <v>7227635</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10920,12 +10920,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10959,7 +10964,7 @@
         <v>126091019</v>
       </c>
       <c r="B103" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11057,10 +11062,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126091028</v>
+        <v>126091358</v>
       </c>
       <c r="B104" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11068,21 +11073,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11092,10 +11097,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>557117</v>
+        <v>556070</v>
       </c>
       <c r="R104" t="n">
-        <v>7227635</v>
+        <v>7226750</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11122,17 +11127,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11166,7 +11166,7 @@
         <v>126091392</v>
       </c>
       <c r="B105" t="n">
-        <v>56232</v>
+        <v>56233</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11264,32 +11264,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126091407</v>
+        <v>126091341</v>
       </c>
       <c r="B106" t="n">
-        <v>80116</v>
+        <v>91245</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>556365</v>
+        <v>556187</v>
       </c>
       <c r="R106" t="n">
-        <v>7227004</v>
+        <v>7226946</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11365,10 +11365,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126091416</v>
+        <v>126091010</v>
       </c>
       <c r="B107" t="n">
-        <v>91260</v>
+        <v>79012</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11376,21 +11376,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>556600</v>
+        <v>556904</v>
       </c>
       <c r="R107" t="n">
-        <v>7227123</v>
+        <v>7227703</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11466,32 +11466,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091421</v>
+        <v>126091115</v>
       </c>
       <c r="B108" t="n">
-        <v>78977</v>
+        <v>57761</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556111</v>
+        <v>556797</v>
       </c>
       <c r="R108" t="n">
-        <v>7226873</v>
+        <v>7227252</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11531,17 +11531,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11572,10 +11567,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091070</v>
+        <v>126091072</v>
       </c>
       <c r="B109" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11607,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556723</v>
+        <v>556913</v>
       </c>
       <c r="R109" t="n">
-        <v>7227276</v>
+        <v>7227621</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11676,7 +11671,7 @@
         <v>126091380</v>
       </c>
       <c r="B110" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11774,32 +11769,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091341</v>
+        <v>126091407</v>
       </c>
       <c r="B111" t="n">
-        <v>91242</v>
+        <v>80119</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11809,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556187</v>
+        <v>556365</v>
       </c>
       <c r="R111" t="n">
-        <v>7226946</v>
+        <v>7227004</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11875,10 +11870,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091072</v>
+        <v>126091070</v>
       </c>
       <c r="B112" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11910,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556913</v>
+        <v>556723</v>
       </c>
       <c r="R112" t="n">
-        <v>7227621</v>
+        <v>7227276</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11976,32 +11971,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091115</v>
+        <v>126091416</v>
       </c>
       <c r="B113" t="n">
-        <v>57760</v>
+        <v>91263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12011,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556797</v>
+        <v>556600</v>
       </c>
       <c r="R113" t="n">
-        <v>7227252</v>
+        <v>7227123</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12041,12 +12036,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12077,10 +12072,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091010</v>
+        <v>126091421</v>
       </c>
       <c r="B114" t="n">
-        <v>79009</v>
+        <v>78980</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12088,21 +12083,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556904</v>
+        <v>556111</v>
       </c>
       <c r="R114" t="n">
-        <v>7227703</v>
+        <v>7226873</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12142,12 +12137,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12181,7 +12181,7 @@
         <v>126091102</v>
       </c>
       <c r="B115" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12279,10 +12279,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126091121</v>
+        <v>126091084</v>
       </c>
       <c r="B116" t="n">
-        <v>91238</v>
+        <v>80084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12290,21 +12290,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12314,10 +12314,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>556907</v>
+        <v>556737</v>
       </c>
       <c r="R116" t="n">
-        <v>7227720</v>
+        <v>7227192</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12344,12 +12344,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126091084</v>
+        <v>126091068</v>
       </c>
       <c r="B117" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12415,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>556737</v>
+        <v>556707</v>
       </c>
       <c r="R117" t="n">
-        <v>7227192</v>
+        <v>7227243</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12445,12 +12445,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12484,7 +12484,7 @@
         <v>126091017</v>
       </c>
       <c r="B118" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12582,10 +12582,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126091068</v>
+        <v>126091121</v>
       </c>
       <c r="B119" t="n">
-        <v>80081</v>
+        <v>91241</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>556707</v>
+        <v>556907</v>
       </c>
       <c r="R119" t="n">
-        <v>7227243</v>
+        <v>7227720</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12683,32 +12683,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126091394</v>
+        <v>126091445</v>
       </c>
       <c r="B120" t="n">
-        <v>91538</v>
+        <v>80118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>556098</v>
+        <v>556584</v>
       </c>
       <c r="R120" t="n">
-        <v>7226757</v>
+        <v>7227109</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12784,10 +12784,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126091445</v>
+        <v>126091444</v>
       </c>
       <c r="B121" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>556584</v>
       </c>
       <c r="R121" t="n">
-        <v>7227109</v>
+        <v>7227068</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,10 +12885,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126091444</v>
+        <v>126091410</v>
       </c>
       <c r="B122" t="n">
-        <v>80115</v>
+        <v>80119</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12896,21 +12896,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12986,32 +12986,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126091410</v>
+        <v>126091424</v>
       </c>
       <c r="B123" t="n">
-        <v>80116</v>
+        <v>78980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>556584</v>
+        <v>556549</v>
       </c>
       <c r="R123" t="n">
-        <v>7227068</v>
+        <v>7226986</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,6 +13057,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13087,10 +13092,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126091424</v>
+        <v>126091387</v>
       </c>
       <c r="B124" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13098,21 +13103,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13122,10 +13127,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>556549</v>
+        <v>556497</v>
       </c>
       <c r="R124" t="n">
-        <v>7226986</v>
+        <v>7226978</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13158,11 +13163,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126091052</v>
+        <v>126091379</v>
       </c>
       <c r="B125" t="n">
-        <v>98373</v>
+        <v>80084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>557007</v>
+        <v>556305</v>
       </c>
       <c r="R125" t="n">
-        <v>7227805</v>
+        <v>7227093</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13258,12 +13258,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13294,10 +13294,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126091387</v>
+        <v>126091394</v>
       </c>
       <c r="B126" t="n">
-        <v>80081</v>
+        <v>91541</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13305,21 +13305,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>556497</v>
+        <v>556098</v>
       </c>
       <c r="R126" t="n">
-        <v>7226978</v>
+        <v>7226757</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13395,32 +13395,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126091379</v>
+        <v>126091052</v>
       </c>
       <c r="B127" t="n">
-        <v>80081</v>
+        <v>98382</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13430,10 +13430,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>556305</v>
+        <v>557007</v>
       </c>
       <c r="R127" t="n">
-        <v>7227093</v>
+        <v>7227805</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,12 +13460,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13496,32 +13496,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126091433</v>
+        <v>126091085</v>
       </c>
       <c r="B128" t="n">
-        <v>80115</v>
+        <v>80084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13531,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>556280</v>
+        <v>556709</v>
       </c>
       <c r="R128" t="n">
-        <v>7226845</v>
+        <v>7227134</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13561,12 +13561,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13597,10 +13597,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126091366</v>
+        <v>126091071</v>
       </c>
       <c r="B129" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13632,10 +13632,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>556348</v>
+        <v>556807</v>
       </c>
       <c r="R129" t="n">
-        <v>7226965</v>
+        <v>7227608</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13662,12 +13662,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13698,10 +13698,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126091085</v>
+        <v>126091367</v>
       </c>
       <c r="B130" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13733,10 +13733,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>556709</v>
+        <v>556347</v>
       </c>
       <c r="R130" t="n">
-        <v>7227134</v>
+        <v>7226967</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13763,12 +13763,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13799,32 +13799,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126091338</v>
+        <v>126091433</v>
       </c>
       <c r="B131" t="n">
-        <v>91242</v>
+        <v>80118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>556326</v>
+        <v>556280</v>
       </c>
       <c r="R131" t="n">
-        <v>7227114</v>
+        <v>7226845</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13900,10 +13900,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126091071</v>
+        <v>126091385</v>
       </c>
       <c r="B132" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13935,10 +13935,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>556807</v>
+        <v>556410</v>
       </c>
       <c r="R132" t="n">
-        <v>7227608</v>
+        <v>7226996</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14001,10 +14001,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126091367</v>
+        <v>126091338</v>
       </c>
       <c r="B133" t="n">
-        <v>80081</v>
+        <v>91245</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14012,21 +14012,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14036,10 +14036,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>556347</v>
+        <v>556326</v>
       </c>
       <c r="R133" t="n">
-        <v>7226967</v>
+        <v>7227114</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14102,10 +14102,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126091363</v>
+        <v>126091366</v>
       </c>
       <c r="B134" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>556361</v>
+        <v>556348</v>
       </c>
       <c r="R134" t="n">
-        <v>7226943</v>
+        <v>7226965</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14173,11 +14173,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14208,10 +14203,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126091385</v>
+        <v>126091363</v>
       </c>
       <c r="B135" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14243,10 +14238,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>556410</v>
+        <v>556361</v>
       </c>
       <c r="R135" t="n">
-        <v>7226996</v>
+        <v>7226943</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14279,6 +14274,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14309,10 +14309,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091413</v>
+        <v>126091029</v>
       </c>
       <c r="B136" t="n">
-        <v>56839</v>
+        <v>57657</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14320,16 +14320,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556662</v>
+        <v>556819</v>
       </c>
       <c r="R136" t="n">
-        <v>7227178</v>
+        <v>7227694</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,17 +14374,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Tupp</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14415,32 +14415,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091431</v>
+        <v>126091413</v>
       </c>
       <c r="B137" t="n">
-        <v>80115</v>
+        <v>56840</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14450,10 +14450,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556179</v>
+        <v>556662</v>
       </c>
       <c r="R137" t="n">
-        <v>7226822</v>
+        <v>7227178</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14486,6 +14486,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14516,32 +14521,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091415</v>
+        <v>126091431</v>
       </c>
       <c r="B138" t="n">
-        <v>91260</v>
+        <v>80118</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14551,10 +14556,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556315</v>
+        <v>556179</v>
       </c>
       <c r="R138" t="n">
-        <v>7226927</v>
+        <v>7226822</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14617,32 +14622,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091429</v>
+        <v>126091415</v>
       </c>
       <c r="B139" t="n">
-        <v>80115</v>
+        <v>91263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14652,10 +14657,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556272</v>
+        <v>556315</v>
       </c>
       <c r="R139" t="n">
-        <v>7227058</v>
+        <v>7226927</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14718,32 +14723,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091127</v>
+        <v>126091429</v>
       </c>
       <c r="B140" t="n">
-        <v>91260</v>
+        <v>80118</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14753,10 +14758,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556728</v>
+        <v>556272</v>
       </c>
       <c r="R140" t="n">
-        <v>7227249</v>
+        <v>7227058</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14783,12 +14788,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14819,32 +14824,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091443</v>
+        <v>126091127</v>
       </c>
       <c r="B141" t="n">
-        <v>80115</v>
+        <v>91263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14854,10 +14859,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556529</v>
+        <v>556728</v>
       </c>
       <c r="R141" t="n">
-        <v>7226958</v>
+        <v>7227249</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14884,12 +14889,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14920,10 +14925,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091437</v>
+        <v>126091443</v>
       </c>
       <c r="B142" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14955,10 +14960,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556361</v>
+        <v>556529</v>
       </c>
       <c r="R142" t="n">
-        <v>7227004</v>
+        <v>7226958</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15021,10 +15026,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091432</v>
+        <v>126091437</v>
       </c>
       <c r="B143" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15056,10 +15061,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556230</v>
+        <v>556361</v>
       </c>
       <c r="R143" t="n">
-        <v>7226809</v>
+        <v>7227004</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15122,10 +15127,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091105</v>
+        <v>126091432</v>
       </c>
       <c r="B144" t="n">
-        <v>80116</v>
+        <v>80118</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15133,21 +15138,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15157,10 +15162,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556807</v>
+        <v>556230</v>
       </c>
       <c r="R144" t="n">
-        <v>7227608</v>
+        <v>7226809</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15187,12 +15192,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15223,32 +15228,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091140</v>
+        <v>126091105</v>
       </c>
       <c r="B145" t="n">
-        <v>78977</v>
+        <v>80119</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15258,10 +15263,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>557026</v>
+        <v>556807</v>
       </c>
       <c r="R145" t="n">
-        <v>7227519</v>
+        <v>7227608</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15294,11 +15299,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15329,10 +15329,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091371</v>
+        <v>126091140</v>
       </c>
       <c r="B146" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,21 +15340,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>556365</v>
+        <v>557026</v>
       </c>
       <c r="R146" t="n">
-        <v>7227004</v>
+        <v>7227519</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15394,12 +15394,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15430,10 +15435,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091063</v>
+        <v>126091371</v>
       </c>
       <c r="B147" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15465,10 +15470,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556836</v>
+        <v>556365</v>
       </c>
       <c r="R147" t="n">
-        <v>7227732</v>
+        <v>7227004</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15495,12 +15500,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15531,10 +15536,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091029</v>
+        <v>126091063</v>
       </c>
       <c r="B148" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15542,21 +15547,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15566,10 +15571,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556819</v>
+        <v>556836</v>
       </c>
       <c r="R148" t="n">
-        <v>7227694</v>
+        <v>7227732</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15602,11 +15607,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091152</v>
+        <v>126091350</v>
       </c>
       <c r="B149" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556975</v>
+        <v>556589</v>
       </c>
       <c r="R149" t="n">
-        <v>7227579</v>
+        <v>7227059</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,17 +15702,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15743,32 +15743,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091397</v>
+        <v>126091040</v>
       </c>
       <c r="B150" t="n">
-        <v>80108</v>
+        <v>57657</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556378</v>
+        <v>556781</v>
       </c>
       <c r="R150" t="n">
-        <v>7226996</v>
+        <v>7227272</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15808,12 +15808,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15844,10 +15849,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091404</v>
+        <v>126091053</v>
       </c>
       <c r="B151" t="n">
-        <v>80116</v>
+        <v>98382</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15855,21 +15860,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15879,10 +15884,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556272</v>
+        <v>556996</v>
       </c>
       <c r="R151" t="n">
-        <v>7227058</v>
+        <v>7227559</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15909,12 +15914,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15945,27 +15950,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091169</v>
+        <v>126091152</v>
       </c>
       <c r="B152" t="n">
-        <v>80115</v>
+        <v>78980</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -15980,10 +15985,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556756</v>
+        <v>556975</v>
       </c>
       <c r="R152" t="n">
-        <v>7227253</v>
+        <v>7227579</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16016,6 +16021,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16046,32 +16056,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091149</v>
+        <v>126091397</v>
       </c>
       <c r="B153" t="n">
-        <v>78977</v>
+        <v>80111</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16081,10 +16091,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556807</v>
+        <v>556378</v>
       </c>
       <c r="R153" t="n">
-        <v>7227608</v>
+        <v>7226996</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16111,17 +16121,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16152,10 +16157,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091350</v>
+        <v>126091388</v>
       </c>
       <c r="B154" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16163,21 +16168,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16187,10 +16192,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556589</v>
+        <v>556529</v>
       </c>
       <c r="R154" t="n">
-        <v>7227059</v>
+        <v>7226958</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16223,11 +16228,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16258,10 +16258,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091040</v>
+        <v>126091378</v>
       </c>
       <c r="B155" t="n">
-        <v>57656</v>
+        <v>80084</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16269,21 +16269,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556781</v>
+        <v>556353</v>
       </c>
       <c r="R155" t="n">
-        <v>7227272</v>
+        <v>7227115</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16323,17 +16323,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16364,10 +16359,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091053</v>
+        <v>126091404</v>
       </c>
       <c r="B156" t="n">
-        <v>98373</v>
+        <v>80119</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16375,21 +16370,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16399,10 +16394,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556996</v>
+        <v>556272</v>
       </c>
       <c r="R156" t="n">
-        <v>7227559</v>
+        <v>7227058</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16429,12 +16424,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16465,32 +16460,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091388</v>
+        <v>126091169</v>
       </c>
       <c r="B157" t="n">
-        <v>80081</v>
+        <v>80118</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16500,10 +16495,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556529</v>
+        <v>556756</v>
       </c>
       <c r="R157" t="n">
-        <v>7226958</v>
+        <v>7227253</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16530,12 +16525,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16566,10 +16561,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091378</v>
+        <v>126091149</v>
       </c>
       <c r="B158" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16577,21 +16572,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16601,10 +16596,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556353</v>
+        <v>556807</v>
       </c>
       <c r="R158" t="n">
-        <v>7227115</v>
+        <v>7227608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16631,12 +16626,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -2912,32 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091164</v>
+        <v>126091435</v>
       </c>
       <c r="B24" t="n">
-        <v>88654</v>
+        <v>80118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556775</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>7227253</v>
+        <v>7226941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2977,12 +2977,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3013,32 +3013,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126091340</v>
+        <v>126091106</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>80119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556312</v>
+        <v>556709</v>
       </c>
       <c r="R25" t="n">
-        <v>7227107</v>
+        <v>7227248</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3114,32 +3114,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091435</v>
+        <v>126091368</v>
       </c>
       <c r="B26" t="n">
-        <v>80118</v>
+        <v>80084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556359</v>
+        <v>556346</v>
       </c>
       <c r="R26" t="n">
-        <v>7226941</v>
+        <v>7226961</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091106</v>
+        <v>126091073</v>
       </c>
       <c r="B27" t="n">
-        <v>80119</v>
+        <v>80084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556709</v>
+        <v>556756</v>
       </c>
       <c r="R27" t="n">
-        <v>7227248</v>
+        <v>7227253</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3316,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091368</v>
+        <v>126091164</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>88654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556346</v>
+        <v>556775</v>
       </c>
       <c r="R28" t="n">
-        <v>7226961</v>
+        <v>7227253</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091073</v>
+        <v>126091340</v>
       </c>
       <c r="B29" t="n">
-        <v>80084</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556756</v>
+        <v>556312</v>
       </c>
       <c r="R29" t="n">
-        <v>7227253</v>
+        <v>7227107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4745,10 +4745,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126091075</v>
+        <v>126091348</v>
       </c>
       <c r="B42" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4756,21 +4756,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>556792</v>
+        <v>556351</v>
       </c>
       <c r="R42" t="n">
-        <v>7227253</v>
+        <v>7226920</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,12 +4810,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4846,10 +4851,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126091403</v>
+        <v>126091075</v>
       </c>
       <c r="B43" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4857,21 +4862,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>556357</v>
+        <v>556792</v>
       </c>
       <c r="R43" t="n">
-        <v>7227004</v>
+        <v>7227253</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4911,12 +4916,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,32 +4952,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126091044</v>
+        <v>126091403</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>80083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4982,10 +4987,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>556826</v>
+        <v>556357</v>
       </c>
       <c r="R44" t="n">
-        <v>7227309</v>
+        <v>7227004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,12 +5017,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126091107</v>
+        <v>126091044</v>
       </c>
       <c r="B45" t="n">
-        <v>80119</v>
+        <v>80112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5059,21 +5064,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>556723</v>
+        <v>556826</v>
       </c>
       <c r="R45" t="n">
-        <v>7227276</v>
+        <v>7227309</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,32 +5154,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126091144</v>
+        <v>126091107</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>80119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5189,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557048</v>
+        <v>556723</v>
       </c>
       <c r="R46" t="n">
-        <v>7227797</v>
+        <v>7227276</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,7 +5255,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126091422</v>
+        <v>126091144</v>
       </c>
       <c r="B47" t="n">
         <v>78980</v>
@@ -5285,10 +5290,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>556407</v>
+        <v>557048</v>
       </c>
       <c r="R47" t="n">
-        <v>7226992</v>
+        <v>7227797</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5315,17 +5320,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5356,7 +5356,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126091145</v>
+        <v>126091422</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>556897</v>
+        <v>556407</v>
       </c>
       <c r="R48" t="n">
-        <v>7227735</v>
+        <v>7226992</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5421,12 +5421,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126091129</v>
+        <v>126091145</v>
       </c>
       <c r="B49" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,21 +5473,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556685</v>
+        <v>556897</v>
       </c>
       <c r="R49" t="n">
-        <v>7227107</v>
+        <v>7227735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,12 +5527,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5563,10 +5568,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126091348</v>
+        <v>126091129</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5574,21 +5579,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5598,10 +5603,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>556351</v>
+        <v>556685</v>
       </c>
       <c r="R50" t="n">
-        <v>7226920</v>
+        <v>7227107</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5628,17 +5633,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7911,32 +7911,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126091015</v>
+        <v>126091393</v>
       </c>
       <c r="B73" t="n">
-        <v>91245</v>
+        <v>79987</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>556931</v>
+        <v>556291</v>
       </c>
       <c r="R73" t="n">
-        <v>7227622</v>
+        <v>7226913</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7976,12 +7976,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8012,32 +8012,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126091051</v>
+        <v>126091012</v>
       </c>
       <c r="B74" t="n">
-        <v>79949</v>
+        <v>91210</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>388</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>556679</v>
+        <v>556977</v>
       </c>
       <c r="R74" t="n">
-        <v>7227232</v>
+        <v>7227576</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126091346</v>
+        <v>126091143</v>
       </c>
       <c r="B75" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8124,21 +8124,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>556194</v>
+        <v>557106</v>
       </c>
       <c r="R75" t="n">
-        <v>7226815</v>
+        <v>7227606</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8178,17 +8178,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8219,10 +8214,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126091393</v>
+        <v>126091174</v>
       </c>
       <c r="B76" t="n">
-        <v>79987</v>
+        <v>91655</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8230,21 +8225,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>4217</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8254,10 +8249,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>556291</v>
+        <v>556888</v>
       </c>
       <c r="R76" t="n">
-        <v>7226913</v>
+        <v>7227746</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8284,12 +8279,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8320,32 +8315,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126091012</v>
+        <v>126091360</v>
       </c>
       <c r="B77" t="n">
-        <v>91210</v>
+        <v>80084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8355,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>556977</v>
+        <v>556326</v>
       </c>
       <c r="R77" t="n">
-        <v>7227576</v>
+        <v>7226893</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,12 +8380,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8421,10 +8416,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126091143</v>
+        <v>126091375</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8432,21 +8427,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8456,10 +8451,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>557106</v>
+        <v>556423</v>
       </c>
       <c r="R78" t="n">
-        <v>7227606</v>
+        <v>7226984</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8486,12 +8481,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8522,32 +8517,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126091174</v>
+        <v>126091402</v>
       </c>
       <c r="B79" t="n">
-        <v>91655</v>
+        <v>80083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4217</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8557,10 +8552,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>556888</v>
+        <v>556280</v>
       </c>
       <c r="R79" t="n">
-        <v>7227746</v>
+        <v>7227059</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8587,12 +8582,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8623,7 +8618,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126091360</v>
+        <v>126091067</v>
       </c>
       <c r="B80" t="n">
         <v>80084</v>
@@ -8658,10 +8653,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>556326</v>
+        <v>556690</v>
       </c>
       <c r="R80" t="n">
-        <v>7226893</v>
+        <v>7227262</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8688,12 +8683,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8724,7 +8719,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126091375</v>
+        <v>126091355</v>
       </c>
       <c r="B81" t="n">
         <v>80084</v>
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>556423</v>
+        <v>556346</v>
       </c>
       <c r="R81" t="n">
-        <v>7226984</v>
+        <v>7227118</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126091402</v>
+        <v>126091015</v>
       </c>
       <c r="B82" t="n">
-        <v>80083</v>
+        <v>91245</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8836,21 +8831,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>556280</v>
+        <v>556931</v>
       </c>
       <c r="R82" t="n">
-        <v>7227059</v>
+        <v>7227622</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8890,12 +8885,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,10 +8921,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126091067</v>
+        <v>126091051</v>
       </c>
       <c r="B83" t="n">
-        <v>80084</v>
+        <v>79949</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8937,21 +8932,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>388</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8961,10 +8956,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>556690</v>
+        <v>556679</v>
       </c>
       <c r="R83" t="n">
-        <v>7227262</v>
+        <v>7227232</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9027,10 +9022,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126091355</v>
+        <v>126091346</v>
       </c>
       <c r="B84" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,21 +9033,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9062,10 +9057,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>556346</v>
+        <v>556194</v>
       </c>
       <c r="R84" t="n">
-        <v>7227118</v>
+        <v>7226815</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9098,6 +9093,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10148,32 +10148,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126091339</v>
+        <v>126091441</v>
       </c>
       <c r="B95" t="n">
-        <v>91245</v>
+        <v>80118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>556393</v>
+        <v>556480</v>
       </c>
       <c r="R95" t="n">
-        <v>7226994</v>
+        <v>7226980</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,7 +10249,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126091441</v>
+        <v>126091167</v>
       </c>
       <c r="B96" t="n">
         <v>80118</v>
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>556480</v>
+        <v>556728</v>
       </c>
       <c r="R96" t="n">
-        <v>7226980</v>
+        <v>7227275</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10350,32 +10350,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126091167</v>
+        <v>126091418</v>
       </c>
       <c r="B97" t="n">
-        <v>80118</v>
+        <v>91263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>556728</v>
+        <v>556550</v>
       </c>
       <c r="R97" t="n">
-        <v>7227275</v>
+        <v>7227005</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10415,12 +10415,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10451,10 +10451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126091418</v>
+        <v>126091357</v>
       </c>
       <c r="B98" t="n">
-        <v>91263</v>
+        <v>80084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10462,21 +10462,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>556550</v>
+        <v>556061</v>
       </c>
       <c r="R98" t="n">
-        <v>7227005</v>
+        <v>7226781</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10552,10 +10552,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126091357</v>
+        <v>126091125</v>
       </c>
       <c r="B99" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10563,21 +10563,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>556061</v>
+        <v>556893</v>
       </c>
       <c r="R99" t="n">
-        <v>7226781</v>
+        <v>7227703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10617,12 +10617,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10653,32 +10653,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126091125</v>
+        <v>126091405</v>
       </c>
       <c r="B100" t="n">
-        <v>91263</v>
+        <v>80119</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>556893</v>
+        <v>556230</v>
       </c>
       <c r="R100" t="n">
-        <v>7227703</v>
+        <v>7226809</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10718,12 +10718,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10754,32 +10754,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126091405</v>
+        <v>126091339</v>
       </c>
       <c r="B101" t="n">
-        <v>80119</v>
+        <v>91245</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>556230</v>
+        <v>556393</v>
       </c>
       <c r="R101" t="n">
-        <v>7226809</v>
+        <v>7226994</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11466,32 +11466,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126091115</v>
+        <v>126091072</v>
       </c>
       <c r="B108" t="n">
-        <v>57761</v>
+        <v>80084</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11501,10 +11501,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>556797</v>
+        <v>556913</v>
       </c>
       <c r="R108" t="n">
-        <v>7227252</v>
+        <v>7227621</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11567,7 +11567,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126091072</v>
+        <v>126091380</v>
       </c>
       <c r="B109" t="n">
         <v>80084</v>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>556913</v>
+        <v>556261</v>
       </c>
       <c r="R109" t="n">
-        <v>7227621</v>
+        <v>7227068</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11668,32 +11668,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126091380</v>
+        <v>126091407</v>
       </c>
       <c r="B110" t="n">
-        <v>80084</v>
+        <v>80119</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>556261</v>
+        <v>556365</v>
       </c>
       <c r="R110" t="n">
-        <v>7227068</v>
+        <v>7227004</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11769,32 +11769,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126091407</v>
+        <v>126091070</v>
       </c>
       <c r="B111" t="n">
-        <v>80119</v>
+        <v>80084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11804,10 +11804,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>556365</v>
+        <v>556723</v>
       </c>
       <c r="R111" t="n">
-        <v>7227004</v>
+        <v>7227276</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11870,10 +11870,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126091070</v>
+        <v>126091416</v>
       </c>
       <c r="B112" t="n">
-        <v>80084</v>
+        <v>91263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11881,21 +11881,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>556723</v>
+        <v>556600</v>
       </c>
       <c r="R112" t="n">
-        <v>7227276</v>
+        <v>7227123</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11935,12 +11935,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11971,10 +11971,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126091416</v>
+        <v>126091421</v>
       </c>
       <c r="B113" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>556600</v>
+        <v>556111</v>
       </c>
       <c r="R113" t="n">
-        <v>7227123</v>
+        <v>7226873</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12042,6 +12042,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12072,32 +12077,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126091421</v>
+        <v>126091115</v>
       </c>
       <c r="B114" t="n">
-        <v>78980</v>
+        <v>57761</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12107,10 +12112,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>556111</v>
+        <v>556797</v>
       </c>
       <c r="R114" t="n">
-        <v>7226873</v>
+        <v>7227252</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12137,17 +12142,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14309,32 +14309,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126091029</v>
+        <v>126091431</v>
       </c>
       <c r="B136" t="n">
-        <v>57657</v>
+        <v>80118</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>556819</v>
+        <v>556179</v>
       </c>
       <c r="R136" t="n">
-        <v>7227694</v>
+        <v>7226822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14374,17 +14374,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14415,10 +14410,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126091413</v>
+        <v>126091415</v>
       </c>
       <c r="B137" t="n">
-        <v>56840</v>
+        <v>91263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14426,21 +14421,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14450,10 +14445,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>556662</v>
+        <v>556315</v>
       </c>
       <c r="R137" t="n">
-        <v>7227178</v>
+        <v>7226927</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14486,11 +14481,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14521,7 +14511,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126091431</v>
+        <v>126091429</v>
       </c>
       <c r="B138" t="n">
         <v>80118</v>
@@ -14556,10 +14546,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>556179</v>
+        <v>556272</v>
       </c>
       <c r="R138" t="n">
-        <v>7226822</v>
+        <v>7227058</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14622,7 +14612,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126091415</v>
+        <v>126091127</v>
       </c>
       <c r="B139" t="n">
         <v>91263</v>
@@ -14657,10 +14647,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>556315</v>
+        <v>556728</v>
       </c>
       <c r="R139" t="n">
-        <v>7226927</v>
+        <v>7227249</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14687,12 +14677,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14723,7 +14713,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126091429</v>
+        <v>126091443</v>
       </c>
       <c r="B140" t="n">
         <v>80118</v>
@@ -14758,10 +14748,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>556272</v>
+        <v>556529</v>
       </c>
       <c r="R140" t="n">
-        <v>7227058</v>
+        <v>7226958</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14824,32 +14814,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126091127</v>
+        <v>126091437</v>
       </c>
       <c r="B141" t="n">
-        <v>91263</v>
+        <v>80118</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14859,10 +14849,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>556728</v>
+        <v>556361</v>
       </c>
       <c r="R141" t="n">
-        <v>7227249</v>
+        <v>7227004</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14889,12 +14879,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14925,7 +14915,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126091443</v>
+        <v>126091432</v>
       </c>
       <c r="B142" t="n">
         <v>80118</v>
@@ -14960,10 +14950,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>556529</v>
+        <v>556230</v>
       </c>
       <c r="R142" t="n">
-        <v>7226958</v>
+        <v>7226809</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15026,10 +15016,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126091437</v>
+        <v>126091105</v>
       </c>
       <c r="B143" t="n">
-        <v>80118</v>
+        <v>80119</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15037,21 +15027,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15061,10 +15051,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>556361</v>
+        <v>556807</v>
       </c>
       <c r="R143" t="n">
-        <v>7227004</v>
+        <v>7227608</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15091,12 +15081,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15127,27 +15117,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126091432</v>
+        <v>126091140</v>
       </c>
       <c r="B144" t="n">
-        <v>80118</v>
+        <v>78980</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15162,10 +15152,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>556230</v>
+        <v>557026</v>
       </c>
       <c r="R144" t="n">
-        <v>7226809</v>
+        <v>7227519</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15192,12 +15182,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15228,32 +15223,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126091105</v>
+        <v>126091371</v>
       </c>
       <c r="B145" t="n">
-        <v>80119</v>
+        <v>80084</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15263,10 +15258,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>556807</v>
+        <v>556365</v>
       </c>
       <c r="R145" t="n">
-        <v>7227608</v>
+        <v>7227004</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15293,12 +15288,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15329,10 +15324,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126091140</v>
+        <v>126091063</v>
       </c>
       <c r="B146" t="n">
-        <v>78980</v>
+        <v>80084</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,21 +15335,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15364,10 +15359,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>557026</v>
+        <v>556836</v>
       </c>
       <c r="R146" t="n">
-        <v>7227519</v>
+        <v>7227732</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15400,11 +15395,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15435,10 +15425,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126091371</v>
+        <v>126091029</v>
       </c>
       <c r="B147" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15446,21 +15436,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15470,10 +15460,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>556365</v>
+        <v>556819</v>
       </c>
       <c r="R147" t="n">
-        <v>7227004</v>
+        <v>7227694</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15500,12 +15490,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15536,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126091063</v>
+        <v>126091413</v>
       </c>
       <c r="B148" t="n">
-        <v>80084</v>
+        <v>56840</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15547,21 +15542,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15571,10 +15566,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>556836</v>
+        <v>556662</v>
       </c>
       <c r="R148" t="n">
-        <v>7227732</v>
+        <v>7227178</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15601,12 +15596,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15637,10 +15637,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126091350</v>
+        <v>126091152</v>
       </c>
       <c r="B149" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,21 +15648,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>556589</v>
+        <v>556975</v>
       </c>
       <c r="R149" t="n">
-        <v>7227059</v>
+        <v>7227579</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15702,17 +15702,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15743,32 +15743,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126091040</v>
+        <v>126091397</v>
       </c>
       <c r="B150" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15778,10 +15778,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>556781</v>
+        <v>556378</v>
       </c>
       <c r="R150" t="n">
-        <v>7227272</v>
+        <v>7226996</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15808,17 +15808,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15849,32 +15844,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126091053</v>
+        <v>126091388</v>
       </c>
       <c r="B151" t="n">
-        <v>98382</v>
+        <v>80084</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15884,10 +15879,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>556996</v>
+        <v>556529</v>
       </c>
       <c r="R151" t="n">
-        <v>7227559</v>
+        <v>7226958</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15914,12 +15909,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15950,27 +15945,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126091152</v>
+        <v>126091169</v>
       </c>
       <c r="B152" t="n">
-        <v>78980</v>
+        <v>80118</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -15985,10 +15980,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>556975</v>
+        <v>556756</v>
       </c>
       <c r="R152" t="n">
-        <v>7227579</v>
+        <v>7227253</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16021,11 +16016,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16056,32 +16046,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126091397</v>
+        <v>126091149</v>
       </c>
       <c r="B153" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16091,10 +16081,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>556378</v>
+        <v>556807</v>
       </c>
       <c r="R153" t="n">
-        <v>7226996</v>
+        <v>7227608</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16121,12 +16111,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16157,10 +16152,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126091388</v>
+        <v>126091350</v>
       </c>
       <c r="B154" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16168,21 +16163,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16192,10 +16187,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>556529</v>
+        <v>556589</v>
       </c>
       <c r="R154" t="n">
-        <v>7226958</v>
+        <v>7227059</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16228,6 +16223,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16258,10 +16258,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126091378</v>
+        <v>126091040</v>
       </c>
       <c r="B155" t="n">
-        <v>80084</v>
+        <v>57657</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16269,21 +16269,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>556353</v>
+        <v>556781</v>
       </c>
       <c r="R155" t="n">
-        <v>7227115</v>
+        <v>7227272</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16323,12 +16323,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16359,32 +16364,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126091404</v>
+        <v>126091378</v>
       </c>
       <c r="B156" t="n">
-        <v>80119</v>
+        <v>80084</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16394,10 +16399,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>556272</v>
+        <v>556353</v>
       </c>
       <c r="R156" t="n">
-        <v>7227058</v>
+        <v>7227115</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16460,10 +16465,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126091169</v>
+        <v>126091404</v>
       </c>
       <c r="B157" t="n">
-        <v>80118</v>
+        <v>80119</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16471,21 +16476,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16495,10 +16500,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>556756</v>
+        <v>556272</v>
       </c>
       <c r="R157" t="n">
-        <v>7227253</v>
+        <v>7227058</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16525,12 +16530,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16561,32 +16566,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126091149</v>
+        <v>126091053</v>
       </c>
       <c r="B158" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16596,10 +16601,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>556807</v>
+        <v>556996</v>
       </c>
       <c r="R158" t="n">
-        <v>7227608</v>
+        <v>7227559</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16632,11 +16637,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Lång bål</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 23789-2025 artfynd.xlsx
+++ b/artfynd/A 23789-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091342</v>
+        <v>126091065</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>80084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556306</v>
+        <v>556817</v>
       </c>
       <c r="R2" t="n">
-        <v>7226876</v>
+        <v>7227591</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091395</v>
+        <v>126091440</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>80118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556308</v>
+        <v>556465</v>
       </c>
       <c r="R3" t="n">
-        <v>7226876</v>
+        <v>7226995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091362</v>
+        <v>126091408</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556369</v>
+        <v>556467</v>
       </c>
       <c r="R4" t="n">
-        <v>7226946</v>
+        <v>7226993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126091440</v>
+        <v>126091362</v>
       </c>
       <c r="B5" t="n">
-        <v>80118</v>
+        <v>80084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556465</v>
+        <v>556369</v>
       </c>
       <c r="R5" t="n">
-        <v>7226995</v>
+        <v>7226946</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091065</v>
+        <v>126091342</